--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489274</v>
+        <v>122489220</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461895</v>
+        <v>461881</v>
       </c>
       <c r="R2" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Garnlav, återkommande i området.</t>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122489220</v>
+        <v>122489274</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>78652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +798,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461881</v>
+        <v>461895</v>
       </c>
       <c r="R3" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
+          <t>Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122488593</v>
+        <v>122489147</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>90833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +900,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -996,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122489147</v>
+        <v>122488593</v>
       </c>
       <c r="B5" t="n">
-        <v>90828</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489220</v>
+        <v>122489147</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>90846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R2" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122489274</v>
+        <v>122488593</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,6 +795,11 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461895</v>
+        <v>461988</v>
       </c>
       <c r="R3" t="n">
         <v>6788288</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489147</v>
+        <v>122489220</v>
       </c>
       <c r="B4" t="n">
-        <v>90833</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,29 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R4" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122488593</v>
+        <v>122489274</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,6 +1009,11 @@
       <c r="E5" t="n">
         <v>6425</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1016,7 +1031,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461988</v>
+        <v>461895</v>
       </c>
       <c r="R5" t="n">
         <v>6788288</v>
@@ -1054,6 +1069,11 @@
           <t>2025-02-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Garnlav, återkommande i området.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1075,6 +1095,7681 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122566822</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>461763</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6788475</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122566802</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79274</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>461811</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6788280</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122566878</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>461712</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6788236</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122566820</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>461732</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6788430</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122566814</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78392</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>461814</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6788266</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122566884</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>461793</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6788303</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122566827</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>461879</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6788396</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122566847</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>461789</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6788194</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122566809</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>461822</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6788353</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122566888</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>461791</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6788187</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122566824</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>461810</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6788470</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122566830</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>461991</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6788324</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122566854</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>461714</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6788188</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122566813</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57383</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>461803</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6788243</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122566887</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>461810</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6788470</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122566818</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>461816</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6788330</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122566881</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>461742</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6788295</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122566804</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79274</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>461614</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6788152</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122566883</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>461777</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6788298</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122566821</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>461699</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6788443</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122566880</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>461737</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6788251</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122566848</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>461791</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6788187</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122566872</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>461659</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6788194</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122566819</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>461667</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6788182</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122566885</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>461804</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6788319</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122566825</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>461843</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6788468</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122566845</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>461794</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6788217</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122566835</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>461929</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6788278</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122566801</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79274</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>461945</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6788255</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122566864</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>461619</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6788144</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122566846</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>461791</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6788209</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122566841</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>461809</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6788250</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122566840</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>461810</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6788278</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122566869</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>461678</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6788157</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122566861</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>461537</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6788149</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122566851</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>461758</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6788174</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122566873</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>461655</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6788205</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122566882</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>461757</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6788299</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122566839</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>461829</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6788287</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122566871</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>461676</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6788174</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122566832</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>461991</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6788292</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122566876</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>461695</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6788224</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122566875</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>461669</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6788203</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122566850</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>461771</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6788185</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122566863</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>461589</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6788148</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122566877</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>461706</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6788223</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122566833</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>461972</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6788277</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122566859</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>461506</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6788139</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122566842</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>461803</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6788243</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122566808</v>
+      </c>
+      <c r="B55" t="n">
+        <v>90826</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>461872</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6788413</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122566862</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>461562</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6788141</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>122566834</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>461929</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6788262</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122566823</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>461778</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6788485</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122566886</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>461810</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6788325</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122566837</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>461917</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6788292</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122566853</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>461732</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6788166</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>122566807</v>
+      </c>
+      <c r="B62" t="n">
+        <v>74757</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>461739</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6788280</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>122566852</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>461741</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6788170</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>122566816</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>461930</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6788270</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>122566865</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>461628</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6788142</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>122566826</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>461846</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6788492</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>122566817</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>461788</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6788303</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>122566849</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>461787</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6788182</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>122566805</v>
+      </c>
+      <c r="B69" t="n">
+        <v>74757</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>461848</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6788429</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122566855</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>461704</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6788171</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>122566874</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>461665</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6788207</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>122566831</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>462004</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6788320</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>122566879</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>461721</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6788242</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>122566844</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>461816</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6788215</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>122566803</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79274</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>461598</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6788148</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>122566828</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>461923</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6788324</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>122566843</v>
+      </c>
+      <c r="B77" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>461811</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6788237</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>122566838</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>461878</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6788313</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>122566811</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>461936</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6788279</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>122566829</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>461952</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6788327</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122489147</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122488593</v>
+        <v>122489274</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461988</v>
+        <v>461895</v>
       </c>
       <c r="R3" t="n">
         <v>6788288</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489220</v>
+        <v>122488593</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R4" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122489274</v>
+        <v>122489220</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461895</v>
+        <v>461881</v>
       </c>
       <c r="R5" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Garnlav, återkommande i området.</t>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566822</v>
+        <v>122566816</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461763</v>
+        <v>461930</v>
       </c>
       <c r="R6" t="n">
-        <v>6788475</v>
+        <v>6788270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566802</v>
+        <v>122566834</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461811</v>
+        <v>461929</v>
       </c>
       <c r="R7" t="n">
-        <v>6788280</v>
+        <v>6788262</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566878</v>
+        <v>122566864</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461712</v>
+        <v>461619</v>
       </c>
       <c r="R8" t="n">
-        <v>6788236</v>
+        <v>6788144</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566820</v>
+        <v>122566873</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461732</v>
+        <v>461655</v>
       </c>
       <c r="R9" t="n">
-        <v>6788430</v>
+        <v>6788205</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566814</v>
+        <v>122566827</v>
       </c>
       <c r="B10" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461814</v>
+        <v>461879</v>
       </c>
       <c r="R10" t="n">
-        <v>6788266</v>
+        <v>6788396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566884</v>
+        <v>122566877</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461793</v>
+        <v>461706</v>
       </c>
       <c r="R11" t="n">
-        <v>6788303</v>
+        <v>6788223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566827</v>
+        <v>122566829</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461879</v>
+        <v>461952</v>
       </c>
       <c r="R12" t="n">
-        <v>6788396</v>
+        <v>6788327</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566847</v>
+        <v>122566872</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1852,7 +1857,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461789</v>
+        <v>461659</v>
       </c>
       <c r="R13" t="n">
         <v>6788194</v>
@@ -1914,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566809</v>
+        <v>122566842</v>
       </c>
       <c r="B14" t="n">
-        <v>90846</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461822</v>
+        <v>461803</v>
       </c>
       <c r="R14" t="n">
-        <v>6788353</v>
+        <v>6788243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566888</v>
+        <v>122566853</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461791</v>
+        <v>461732</v>
       </c>
       <c r="R15" t="n">
-        <v>6788187</v>
+        <v>6788166</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566824</v>
+        <v>122566859</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461810</v>
+        <v>461506</v>
       </c>
       <c r="R16" t="n">
-        <v>6788470</v>
+        <v>6788139</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566830</v>
+        <v>122566875</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461991</v>
+        <v>461669</v>
       </c>
       <c r="R17" t="n">
-        <v>6788324</v>
+        <v>6788203</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566854</v>
+        <v>122566813</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,34 +2343,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461714</v>
+        <v>461803</v>
       </c>
       <c r="R18" t="n">
-        <v>6788188</v>
+        <v>6788243</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2398,6 +2408,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566813</v>
+        <v>122566833</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,39 +2455,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461803</v>
+        <v>461972</v>
       </c>
       <c r="R19" t="n">
-        <v>6788243</v>
+        <v>6788277</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2505,11 +2515,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566887</v>
+        <v>122566819</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,38 +2553,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461810</v>
+        <v>461667</v>
       </c>
       <c r="R20" t="n">
-        <v>6788470</v>
+        <v>6788182</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,7 +2648,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566818</v>
+        <v>122566865</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2678,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461816</v>
+        <v>461628</v>
       </c>
       <c r="R21" t="n">
-        <v>6788330</v>
+        <v>6788142</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,7 +2750,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566881</v>
+        <v>122566846</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2780,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461742</v>
+        <v>461791</v>
       </c>
       <c r="R22" t="n">
-        <v>6788295</v>
+        <v>6788209</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566804</v>
+        <v>122566845</v>
       </c>
       <c r="B23" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,21 +2868,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2892,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461614</v>
+        <v>461794</v>
       </c>
       <c r="R23" t="n">
-        <v>6788152</v>
+        <v>6788217</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,7 +2954,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566883</v>
+        <v>122566843</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2984,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461777</v>
+        <v>461811</v>
       </c>
       <c r="R24" t="n">
-        <v>6788298</v>
+        <v>6788237</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566821</v>
+        <v>122566805</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461699</v>
+        <v>461848</v>
       </c>
       <c r="R25" t="n">
-        <v>6788443</v>
+        <v>6788429</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,7 +3158,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566880</v>
+        <v>122566863</v>
       </c>
       <c r="B26" t="n">
         <v>78656</v>
@@ -3188,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461737</v>
+        <v>461589</v>
       </c>
       <c r="R26" t="n">
-        <v>6788251</v>
+        <v>6788148</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,7 +3260,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566848</v>
+        <v>122566869</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3290,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461791</v>
+        <v>461678</v>
       </c>
       <c r="R27" t="n">
-        <v>6788187</v>
+        <v>6788157</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,7 +3362,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566872</v>
+        <v>122566876</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -3392,10 +3402,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461659</v>
+        <v>461695</v>
       </c>
       <c r="R28" t="n">
-        <v>6788194</v>
+        <v>6788224</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,7 +3464,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566819</v>
+        <v>122566820</v>
       </c>
       <c r="B29" t="n">
         <v>78656</v>
@@ -3488,21 +3498,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461667</v>
+        <v>461732</v>
       </c>
       <c r="R29" t="n">
-        <v>6788182</v>
+        <v>6788430</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3561,7 +3566,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566885</v>
+        <v>122566824</v>
       </c>
       <c r="B30" t="n">
         <v>78656</v>
@@ -3601,10 +3606,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461804</v>
+        <v>461810</v>
       </c>
       <c r="R30" t="n">
-        <v>6788319</v>
+        <v>6788470</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3663,7 +3668,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566825</v>
+        <v>122566854</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -3703,10 +3708,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461843</v>
+        <v>461714</v>
       </c>
       <c r="R31" t="n">
-        <v>6788468</v>
+        <v>6788188</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3765,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566845</v>
+        <v>122566803</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3781,21 +3786,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3805,10 +3810,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461794</v>
+        <v>461598</v>
       </c>
       <c r="R32" t="n">
-        <v>6788217</v>
+        <v>6788148</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,7 +3872,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566835</v>
+        <v>122566861</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -3907,10 +3912,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461929</v>
+        <v>461537</v>
       </c>
       <c r="R33" t="n">
-        <v>6788278</v>
+        <v>6788149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3969,10 +3974,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566801</v>
+        <v>122566881</v>
       </c>
       <c r="B34" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3985,21 +3990,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4009,10 +4014,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461945</v>
+        <v>461742</v>
       </c>
       <c r="R34" t="n">
-        <v>6788255</v>
+        <v>6788295</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4071,7 +4076,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566864</v>
+        <v>122566885</v>
       </c>
       <c r="B35" t="n">
         <v>78656</v>
@@ -4111,10 +4116,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461619</v>
+        <v>461804</v>
       </c>
       <c r="R35" t="n">
-        <v>6788144</v>
+        <v>6788319</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,7 +4178,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566846</v>
+        <v>122566822</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4213,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461791</v>
+        <v>461763</v>
       </c>
       <c r="R36" t="n">
-        <v>6788209</v>
+        <v>6788475</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4275,7 +4280,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566841</v>
+        <v>122566849</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4315,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461809</v>
+        <v>461787</v>
       </c>
       <c r="R37" t="n">
-        <v>6788250</v>
+        <v>6788182</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4377,7 +4382,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566840</v>
+        <v>122566878</v>
       </c>
       <c r="B38" t="n">
         <v>78656</v>
@@ -4417,10 +4422,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461810</v>
+        <v>461712</v>
       </c>
       <c r="R38" t="n">
-        <v>6788278</v>
+        <v>6788236</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,7 +4484,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566869</v>
+        <v>122566884</v>
       </c>
       <c r="B39" t="n">
         <v>78656</v>
@@ -4519,10 +4524,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461678</v>
+        <v>461793</v>
       </c>
       <c r="R39" t="n">
-        <v>6788157</v>
+        <v>6788303</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4581,7 +4586,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566861</v>
+        <v>122566840</v>
       </c>
       <c r="B40" t="n">
         <v>78656</v>
@@ -4621,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461537</v>
+        <v>461810</v>
       </c>
       <c r="R40" t="n">
-        <v>6788149</v>
+        <v>6788278</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4683,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566851</v>
+        <v>122566887</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4695,25 +4700,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4723,10 +4728,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461758</v>
+        <v>461810</v>
       </c>
       <c r="R41" t="n">
-        <v>6788174</v>
+        <v>6788470</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4785,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566873</v>
+        <v>122566814</v>
       </c>
       <c r="B42" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4801,21 +4806,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,10 +4830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461655</v>
+        <v>461814</v>
       </c>
       <c r="R42" t="n">
-        <v>6788205</v>
+        <v>6788266</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,7 +4892,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566882</v>
+        <v>122566871</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4927,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461757</v>
+        <v>461676</v>
       </c>
       <c r="R43" t="n">
-        <v>6788299</v>
+        <v>6788174</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,7 +4994,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566839</v>
+        <v>122566837</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -5029,10 +5034,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461829</v>
+        <v>461917</v>
       </c>
       <c r="R44" t="n">
-        <v>6788287</v>
+        <v>6788292</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,7 +5096,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566871</v>
+        <v>122566879</v>
       </c>
       <c r="B45" t="n">
         <v>78656</v>
@@ -5131,10 +5136,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461676</v>
+        <v>461721</v>
       </c>
       <c r="R45" t="n">
-        <v>6788174</v>
+        <v>6788242</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5193,7 +5198,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566832</v>
+        <v>122566850</v>
       </c>
       <c r="B46" t="n">
         <v>78656</v>
@@ -5233,10 +5238,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461991</v>
+        <v>461771</v>
       </c>
       <c r="R46" t="n">
-        <v>6788292</v>
+        <v>6788185</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5295,7 +5300,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566876</v>
+        <v>122566847</v>
       </c>
       <c r="B47" t="n">
         <v>78656</v>
@@ -5335,10 +5340,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461695</v>
+        <v>461789</v>
       </c>
       <c r="R47" t="n">
-        <v>6788224</v>
+        <v>6788194</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5397,10 +5402,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566875</v>
+        <v>122566811</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5413,34 +5418,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461669</v>
+        <v>461936</v>
       </c>
       <c r="R48" t="n">
-        <v>6788203</v>
+        <v>6788279</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5499,7 +5509,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566850</v>
+        <v>122566835</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -5539,10 +5549,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461771</v>
+        <v>461929</v>
       </c>
       <c r="R49" t="n">
-        <v>6788185</v>
+        <v>6788278</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5601,7 +5611,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566863</v>
+        <v>122566874</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -5641,10 +5651,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461589</v>
+        <v>461665</v>
       </c>
       <c r="R50" t="n">
-        <v>6788148</v>
+        <v>6788207</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5703,10 +5713,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566877</v>
+        <v>122566807</v>
       </c>
       <c r="B51" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5719,21 +5729,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5743,10 +5753,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461706</v>
+        <v>461739</v>
       </c>
       <c r="R51" t="n">
-        <v>6788223</v>
+        <v>6788280</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5805,7 +5815,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566833</v>
+        <v>122566851</v>
       </c>
       <c r="B52" t="n">
         <v>78656</v>
@@ -5845,10 +5855,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461972</v>
+        <v>461758</v>
       </c>
       <c r="R52" t="n">
-        <v>6788277</v>
+        <v>6788174</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5907,7 +5917,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566859</v>
+        <v>122566832</v>
       </c>
       <c r="B53" t="n">
         <v>78656</v>
@@ -5947,10 +5957,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461506</v>
+        <v>461991</v>
       </c>
       <c r="R53" t="n">
-        <v>6788139</v>
+        <v>6788292</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6009,10 +6019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566842</v>
+        <v>122566802</v>
       </c>
       <c r="B54" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6025,21 +6035,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6049,10 +6059,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461803</v>
+        <v>461811</v>
       </c>
       <c r="R54" t="n">
-        <v>6788243</v>
+        <v>6788280</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6111,10 +6121,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566808</v>
+        <v>122566852</v>
       </c>
       <c r="B55" t="n">
-        <v>90826</v>
+        <v>78656</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6127,21 +6137,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6151,10 +6161,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461872</v>
+        <v>461741</v>
       </c>
       <c r="R55" t="n">
-        <v>6788413</v>
+        <v>6788170</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6213,7 +6223,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566862</v>
+        <v>122566880</v>
       </c>
       <c r="B56" t="n">
         <v>78656</v>
@@ -6253,10 +6263,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461562</v>
+        <v>461737</v>
       </c>
       <c r="R56" t="n">
-        <v>6788141</v>
+        <v>6788251</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6315,7 +6325,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566834</v>
+        <v>122566821</v>
       </c>
       <c r="B57" t="n">
         <v>78656</v>
@@ -6355,10 +6365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461929</v>
+        <v>461699</v>
       </c>
       <c r="R57" t="n">
-        <v>6788262</v>
+        <v>6788443</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6417,7 +6427,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566823</v>
+        <v>122566848</v>
       </c>
       <c r="B58" t="n">
         <v>78656</v>
@@ -6457,10 +6467,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461778</v>
+        <v>461791</v>
       </c>
       <c r="R58" t="n">
-        <v>6788485</v>
+        <v>6788187</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,7 +6529,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566886</v>
+        <v>122566825</v>
       </c>
       <c r="B59" t="n">
         <v>78656</v>
@@ -6559,10 +6569,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461810</v>
+        <v>461843</v>
       </c>
       <c r="R59" t="n">
-        <v>6788325</v>
+        <v>6788468</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6621,7 +6631,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566837</v>
+        <v>122566841</v>
       </c>
       <c r="B60" t="n">
         <v>78656</v>
@@ -6661,10 +6671,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461917</v>
+        <v>461809</v>
       </c>
       <c r="R60" t="n">
-        <v>6788292</v>
+        <v>6788250</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,7 +6733,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566853</v>
+        <v>122566838</v>
       </c>
       <c r="B61" t="n">
         <v>78656</v>
@@ -6763,10 +6773,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461732</v>
+        <v>461878</v>
       </c>
       <c r="R61" t="n">
-        <v>6788166</v>
+        <v>6788313</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6825,10 +6835,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566807</v>
+        <v>122566808</v>
       </c>
       <c r="B62" t="n">
-        <v>74757</v>
+        <v>90839</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6841,21 +6851,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6865,10 +6875,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461739</v>
+        <v>461872</v>
       </c>
       <c r="R62" t="n">
-        <v>6788280</v>
+        <v>6788413</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6927,7 +6937,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566852</v>
+        <v>122566883</v>
       </c>
       <c r="B63" t="n">
         <v>78656</v>
@@ -6967,10 +6977,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461741</v>
+        <v>461777</v>
       </c>
       <c r="R63" t="n">
-        <v>6788170</v>
+        <v>6788298</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7029,10 +7039,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566816</v>
+        <v>122566809</v>
       </c>
       <c r="B64" t="n">
-        <v>57399</v>
+        <v>90859</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7045,39 +7055,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461930</v>
+        <v>461822</v>
       </c>
       <c r="R64" t="n">
-        <v>6788270</v>
+        <v>6788353</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,10 +7141,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566865</v>
+        <v>122566888</v>
       </c>
       <c r="B65" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7148,25 +7153,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7176,10 +7181,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461628</v>
+        <v>461791</v>
       </c>
       <c r="R65" t="n">
-        <v>6788142</v>
+        <v>6788187</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,7 +7243,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566826</v>
+        <v>122566855</v>
       </c>
       <c r="B66" t="n">
         <v>78656</v>
@@ -7278,10 +7283,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461846</v>
+        <v>461704</v>
       </c>
       <c r="R66" t="n">
-        <v>6788492</v>
+        <v>6788171</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,10 +7345,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566817</v>
+        <v>122566804</v>
       </c>
       <c r="B67" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7356,21 +7361,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7380,10 +7385,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461788</v>
+        <v>461614</v>
       </c>
       <c r="R67" t="n">
-        <v>6788303</v>
+        <v>6788152</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,7 +7447,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566849</v>
+        <v>122566817</v>
       </c>
       <c r="B68" t="n">
         <v>78656</v>
@@ -7482,10 +7487,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461787</v>
+        <v>461788</v>
       </c>
       <c r="R68" t="n">
-        <v>6788182</v>
+        <v>6788303</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7544,10 +7549,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566805</v>
+        <v>122566862</v>
       </c>
       <c r="B69" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7560,21 +7565,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7584,10 +7589,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461848</v>
+        <v>461562</v>
       </c>
       <c r="R69" t="n">
-        <v>6788429</v>
+        <v>6788141</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7646,7 +7651,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566855</v>
+        <v>122566826</v>
       </c>
       <c r="B70" t="n">
         <v>78656</v>
@@ -7686,10 +7691,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461704</v>
+        <v>461846</v>
       </c>
       <c r="R70" t="n">
-        <v>6788171</v>
+        <v>6788492</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7748,7 +7753,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566874</v>
+        <v>122566844</v>
       </c>
       <c r="B71" t="n">
         <v>78656</v>
@@ -7788,10 +7793,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461665</v>
+        <v>461816</v>
       </c>
       <c r="R71" t="n">
-        <v>6788207</v>
+        <v>6788215</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7850,7 +7855,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566831</v>
+        <v>122566882</v>
       </c>
       <c r="B72" t="n">
         <v>78656</v>
@@ -7890,10 +7895,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>462004</v>
+        <v>461757</v>
       </c>
       <c r="R72" t="n">
-        <v>6788320</v>
+        <v>6788299</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7952,7 +7957,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566879</v>
+        <v>122566886</v>
       </c>
       <c r="B73" t="n">
         <v>78656</v>
@@ -7992,10 +7997,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461721</v>
+        <v>461810</v>
       </c>
       <c r="R73" t="n">
-        <v>6788242</v>
+        <v>6788325</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8054,7 +8059,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566844</v>
+        <v>122566818</v>
       </c>
       <c r="B74" t="n">
         <v>78656</v>
@@ -8097,7 +8102,7 @@
         <v>461816</v>
       </c>
       <c r="R74" t="n">
-        <v>6788215</v>
+        <v>6788330</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8156,10 +8161,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566803</v>
+        <v>122566823</v>
       </c>
       <c r="B75" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8172,21 +8177,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8196,10 +8201,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461598</v>
+        <v>461778</v>
       </c>
       <c r="R75" t="n">
-        <v>6788148</v>
+        <v>6788485</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8360,10 +8365,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566843</v>
+        <v>122566801</v>
       </c>
       <c r="B77" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8376,21 +8381,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8400,10 +8405,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461811</v>
+        <v>461945</v>
       </c>
       <c r="R77" t="n">
-        <v>6788237</v>
+        <v>6788255</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8462,7 +8467,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566838</v>
+        <v>122566830</v>
       </c>
       <c r="B78" t="n">
         <v>78656</v>
@@ -8502,10 +8507,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461878</v>
+        <v>461991</v>
       </c>
       <c r="R78" t="n">
-        <v>6788313</v>
+        <v>6788324</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8564,10 +8569,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566811</v>
+        <v>122566839</v>
       </c>
       <c r="B79" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8580,39 +8585,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461936</v>
+        <v>461829</v>
       </c>
       <c r="R79" t="n">
-        <v>6788279</v>
+        <v>6788287</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8671,7 +8671,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122566829</v>
+        <v>122566831</v>
       </c>
       <c r="B80" t="n">
         <v>78656</v>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461952</v>
+        <v>462004</v>
       </c>
       <c r="R80" t="n">
-        <v>6788327</v>
+        <v>6788320</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7141,10 +7141,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566888</v>
+        <v>122566855</v>
       </c>
       <c r="B65" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7153,25 +7153,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7181,10 +7181,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461791</v>
+        <v>461704</v>
       </c>
       <c r="R65" t="n">
-        <v>6788187</v>
+        <v>6788171</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7243,10 +7243,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566855</v>
+        <v>122566804</v>
       </c>
       <c r="B66" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7259,21 +7259,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7283,10 +7283,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461704</v>
+        <v>461614</v>
       </c>
       <c r="R66" t="n">
-        <v>6788171</v>
+        <v>6788152</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7345,10 +7345,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566804</v>
+        <v>122566817</v>
       </c>
       <c r="B67" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7361,21 +7361,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461614</v>
+        <v>461788</v>
       </c>
       <c r="R67" t="n">
-        <v>6788152</v>
+        <v>6788303</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7447,7 +7447,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566817</v>
+        <v>122566862</v>
       </c>
       <c r="B68" t="n">
         <v>78656</v>
@@ -7487,10 +7487,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461788</v>
+        <v>461562</v>
       </c>
       <c r="R68" t="n">
-        <v>6788303</v>
+        <v>6788141</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7549,7 +7549,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566862</v>
+        <v>122566826</v>
       </c>
       <c r="B69" t="n">
         <v>78656</v>
@@ -7589,10 +7589,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461562</v>
+        <v>461846</v>
       </c>
       <c r="R69" t="n">
-        <v>6788141</v>
+        <v>6788492</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7651,10 +7651,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566826</v>
+        <v>122566888</v>
       </c>
       <c r="B70" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7663,25 +7663,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461846</v>
+        <v>461791</v>
       </c>
       <c r="R70" t="n">
-        <v>6788492</v>
+        <v>6788187</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8771,6 +8771,116 @@
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>122566812</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>461803</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6788243</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489147</v>
+        <v>122488593</v>
       </c>
       <c r="B2" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122489274</v>
+        <v>122489220</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461895</v>
+        <v>461881</v>
       </c>
       <c r="R3" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Garnlav, återkommande i området.</t>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122488593</v>
+        <v>122489147</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>90859</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122489220</v>
+        <v>122489274</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461881</v>
+        <v>461895</v>
       </c>
       <c r="R5" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
+          <t>Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566816</v>
+        <v>122566830</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,39 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461930</v>
+        <v>461991</v>
       </c>
       <c r="R6" t="n">
-        <v>6788270</v>
+        <v>6788324</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566834</v>
+        <v>122566872</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461929</v>
+        <v>461659</v>
       </c>
       <c r="R7" t="n">
-        <v>6788262</v>
+        <v>6788194</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566864</v>
+        <v>122566885</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461619</v>
+        <v>461804</v>
       </c>
       <c r="R8" t="n">
-        <v>6788144</v>
+        <v>6788319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566873</v>
+        <v>122566838</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1449,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461655</v>
+        <v>461878</v>
       </c>
       <c r="R9" t="n">
-        <v>6788205</v>
+        <v>6788313</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566827</v>
+        <v>122566852</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1551,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461879</v>
+        <v>461741</v>
       </c>
       <c r="R10" t="n">
-        <v>6788396</v>
+        <v>6788170</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566877</v>
+        <v>122566865</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461706</v>
+        <v>461628</v>
       </c>
       <c r="R11" t="n">
-        <v>6788223</v>
+        <v>6788142</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566829</v>
+        <v>122566848</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461952</v>
+        <v>461791</v>
       </c>
       <c r="R12" t="n">
-        <v>6788327</v>
+        <v>6788187</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566872</v>
+        <v>122566825</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461659</v>
+        <v>461843</v>
       </c>
       <c r="R13" t="n">
-        <v>6788194</v>
+        <v>6788468</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566842</v>
+        <v>122566847</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -1959,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461803</v>
+        <v>461789</v>
       </c>
       <c r="R14" t="n">
-        <v>6788243</v>
+        <v>6788194</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566853</v>
+        <v>122566818</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2061,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461732</v>
+        <v>461816</v>
       </c>
       <c r="R15" t="n">
-        <v>6788166</v>
+        <v>6788330</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566859</v>
+        <v>122566820</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461506</v>
+        <v>461732</v>
       </c>
       <c r="R16" t="n">
-        <v>6788139</v>
+        <v>6788430</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566875</v>
+        <v>122566850</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2265,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461669</v>
+        <v>461771</v>
       </c>
       <c r="R17" t="n">
-        <v>6788203</v>
+        <v>6788185</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566813</v>
+        <v>122566883</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,39 +2338,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461803</v>
+        <v>461777</v>
       </c>
       <c r="R18" t="n">
-        <v>6788243</v>
+        <v>6788298</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,11 +2398,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566833</v>
+        <v>122566807</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461972</v>
+        <v>461739</v>
       </c>
       <c r="R19" t="n">
-        <v>6788277</v>
+        <v>6788280</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566819</v>
+        <v>122566832</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -2575,21 +2560,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461667</v>
+        <v>461991</v>
       </c>
       <c r="R20" t="n">
-        <v>6788182</v>
+        <v>6788292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2648,7 +2628,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566865</v>
+        <v>122566881</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2688,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461628</v>
+        <v>461742</v>
       </c>
       <c r="R21" t="n">
-        <v>6788142</v>
+        <v>6788295</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566846</v>
+        <v>122566875</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2790,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461791</v>
+        <v>461669</v>
       </c>
       <c r="R22" t="n">
-        <v>6788209</v>
+        <v>6788203</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2852,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566845</v>
+        <v>122566816</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2868,34 +2848,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461794</v>
+        <v>461930</v>
       </c>
       <c r="R23" t="n">
-        <v>6788217</v>
+        <v>6788270</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2954,7 +2939,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566843</v>
+        <v>122566837</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2994,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461811</v>
+        <v>461917</v>
       </c>
       <c r="R24" t="n">
-        <v>6788237</v>
+        <v>6788292</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566805</v>
+        <v>122566835</v>
       </c>
       <c r="B25" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3072,21 +3057,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461848</v>
+        <v>461929</v>
       </c>
       <c r="R25" t="n">
-        <v>6788429</v>
+        <v>6788278</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3158,7 +3143,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566863</v>
+        <v>122566831</v>
       </c>
       <c r="B26" t="n">
         <v>78656</v>
@@ -3198,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461589</v>
+        <v>462004</v>
       </c>
       <c r="R26" t="n">
-        <v>6788148</v>
+        <v>6788320</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,7 +3245,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566869</v>
+        <v>122566879</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3300,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461678</v>
+        <v>461721</v>
       </c>
       <c r="R27" t="n">
-        <v>6788157</v>
+        <v>6788242</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3362,7 +3347,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566876</v>
+        <v>122566821</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -3402,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461695</v>
+        <v>461699</v>
       </c>
       <c r="R28" t="n">
-        <v>6788224</v>
+        <v>6788443</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3464,7 +3449,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566820</v>
+        <v>122566840</v>
       </c>
       <c r="B29" t="n">
         <v>78656</v>
@@ -3504,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461732</v>
+        <v>461810</v>
       </c>
       <c r="R29" t="n">
-        <v>6788430</v>
+        <v>6788278</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3566,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566824</v>
+        <v>122566813</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3582,34 +3567,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461810</v>
+        <v>461803</v>
       </c>
       <c r="R30" t="n">
-        <v>6788470</v>
+        <v>6788243</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,6 +3632,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3668,7 +3663,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566854</v>
+        <v>122566853</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -3708,10 +3703,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461714</v>
+        <v>461732</v>
       </c>
       <c r="R31" t="n">
-        <v>6788188</v>
+        <v>6788166</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3770,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566803</v>
+        <v>122566855</v>
       </c>
       <c r="B32" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3786,21 +3781,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3810,10 +3805,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461598</v>
+        <v>461704</v>
       </c>
       <c r="R32" t="n">
-        <v>6788148</v>
+        <v>6788171</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3872,7 +3867,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566861</v>
+        <v>122566863</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -3912,10 +3907,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461537</v>
+        <v>461589</v>
       </c>
       <c r="R33" t="n">
-        <v>6788149</v>
+        <v>6788148</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3974,7 +3969,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566881</v>
+        <v>122566843</v>
       </c>
       <c r="B34" t="n">
         <v>78656</v>
@@ -4014,10 +4009,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461742</v>
+        <v>461811</v>
       </c>
       <c r="R34" t="n">
-        <v>6788295</v>
+        <v>6788237</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,7 +4071,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566885</v>
+        <v>122566877</v>
       </c>
       <c r="B35" t="n">
         <v>78656</v>
@@ -4116,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461804</v>
+        <v>461706</v>
       </c>
       <c r="R35" t="n">
-        <v>6788319</v>
+        <v>6788223</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4178,7 +4173,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566822</v>
+        <v>122566876</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4218,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461763</v>
+        <v>461695</v>
       </c>
       <c r="R36" t="n">
-        <v>6788475</v>
+        <v>6788224</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4280,7 +4275,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566849</v>
+        <v>122566880</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4320,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461787</v>
+        <v>461737</v>
       </c>
       <c r="R37" t="n">
-        <v>6788182</v>
+        <v>6788251</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4377,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566878</v>
+        <v>122566804</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4398,21 +4393,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4422,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461712</v>
+        <v>461614</v>
       </c>
       <c r="R38" t="n">
-        <v>6788236</v>
+        <v>6788152</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4484,7 +4479,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566884</v>
+        <v>122566828</v>
       </c>
       <c r="B39" t="n">
         <v>78656</v>
@@ -4524,10 +4519,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461793</v>
+        <v>461923</v>
       </c>
       <c r="R39" t="n">
-        <v>6788303</v>
+        <v>6788324</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4586,7 +4581,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566840</v>
+        <v>122566822</v>
       </c>
       <c r="B40" t="n">
         <v>78656</v>
@@ -4626,10 +4621,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461810</v>
+        <v>461763</v>
       </c>
       <c r="R40" t="n">
-        <v>6788278</v>
+        <v>6788475</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4688,10 +4683,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566887</v>
+        <v>122566833</v>
       </c>
       <c r="B41" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4700,25 +4695,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4728,10 +4723,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461810</v>
+        <v>461972</v>
       </c>
       <c r="R41" t="n">
-        <v>6788470</v>
+        <v>6788277</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4790,10 +4785,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566814</v>
+        <v>122566826</v>
       </c>
       <c r="B42" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4806,21 +4801,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4830,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461814</v>
+        <v>461846</v>
       </c>
       <c r="R42" t="n">
-        <v>6788266</v>
+        <v>6788492</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4892,7 +4887,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566871</v>
+        <v>122566851</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4932,7 +4927,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461676</v>
+        <v>461758</v>
       </c>
       <c r="R43" t="n">
         <v>6788174</v>
@@ -4994,7 +4989,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566837</v>
+        <v>122566834</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -5034,10 +5029,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461917</v>
+        <v>461929</v>
       </c>
       <c r="R44" t="n">
-        <v>6788292</v>
+        <v>6788262</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5096,7 +5091,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566879</v>
+        <v>122566884</v>
       </c>
       <c r="B45" t="n">
         <v>78656</v>
@@ -5136,10 +5131,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461721</v>
+        <v>461793</v>
       </c>
       <c r="R45" t="n">
-        <v>6788242</v>
+        <v>6788303</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5198,7 +5193,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566850</v>
+        <v>122566845</v>
       </c>
       <c r="B46" t="n">
         <v>78656</v>
@@ -5238,10 +5233,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461771</v>
+        <v>461794</v>
       </c>
       <c r="R46" t="n">
-        <v>6788185</v>
+        <v>6788217</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5300,10 +5295,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566847</v>
+        <v>122566814</v>
       </c>
       <c r="B47" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5316,21 +5311,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5340,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461789</v>
+        <v>461814</v>
       </c>
       <c r="R47" t="n">
-        <v>6788194</v>
+        <v>6788266</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5402,10 +5397,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566811</v>
+        <v>122566886</v>
       </c>
       <c r="B48" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5418,39 +5413,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461936</v>
+        <v>461810</v>
       </c>
       <c r="R48" t="n">
-        <v>6788279</v>
+        <v>6788325</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5509,7 +5499,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566835</v>
+        <v>122566819</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -5543,16 +5533,21 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461929</v>
+        <v>461667</v>
       </c>
       <c r="R49" t="n">
-        <v>6788278</v>
+        <v>6788182</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5611,7 +5606,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566874</v>
+        <v>122566842</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -5651,10 +5646,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461665</v>
+        <v>461803</v>
       </c>
       <c r="R50" t="n">
-        <v>6788207</v>
+        <v>6788243</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5713,10 +5708,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566807</v>
+        <v>122566861</v>
       </c>
       <c r="B51" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5729,21 +5724,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5753,10 +5748,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461739</v>
+        <v>461537</v>
       </c>
       <c r="R51" t="n">
-        <v>6788280</v>
+        <v>6788149</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5815,7 +5810,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566851</v>
+        <v>122566841</v>
       </c>
       <c r="B52" t="n">
         <v>78656</v>
@@ -5855,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461758</v>
+        <v>461809</v>
       </c>
       <c r="R52" t="n">
-        <v>6788174</v>
+        <v>6788250</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5917,7 +5912,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566832</v>
+        <v>122566824</v>
       </c>
       <c r="B53" t="n">
         <v>78656</v>
@@ -5957,10 +5952,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461991</v>
+        <v>461810</v>
       </c>
       <c r="R53" t="n">
-        <v>6788292</v>
+        <v>6788470</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6019,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566802</v>
+        <v>122566878</v>
       </c>
       <c r="B54" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6035,21 +6030,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6059,10 +6054,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461811</v>
+        <v>461712</v>
       </c>
       <c r="R54" t="n">
-        <v>6788280</v>
+        <v>6788236</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6121,10 +6116,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566852</v>
+        <v>122566808</v>
       </c>
       <c r="B55" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6137,21 +6132,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6161,10 +6156,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461741</v>
+        <v>461872</v>
       </c>
       <c r="R55" t="n">
-        <v>6788170</v>
+        <v>6788413</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6223,7 +6218,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566880</v>
+        <v>122566849</v>
       </c>
       <c r="B56" t="n">
         <v>78656</v>
@@ -6263,10 +6258,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461737</v>
+        <v>461787</v>
       </c>
       <c r="R56" t="n">
-        <v>6788251</v>
+        <v>6788182</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6325,10 +6320,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566821</v>
+        <v>122566801</v>
       </c>
       <c r="B57" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6341,21 +6336,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6365,10 +6360,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461699</v>
+        <v>461945</v>
       </c>
       <c r="R57" t="n">
-        <v>6788443</v>
+        <v>6788255</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,10 +6422,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566848</v>
+        <v>122566887</v>
       </c>
       <c r="B58" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6439,25 +6434,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6467,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461791</v>
+        <v>461810</v>
       </c>
       <c r="R58" t="n">
-        <v>6788187</v>
+        <v>6788470</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6529,10 +6524,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566825</v>
+        <v>122566809</v>
       </c>
       <c r="B59" t="n">
-        <v>78656</v>
+        <v>90859</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6545,21 +6540,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6569,10 +6564,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461843</v>
+        <v>461822</v>
       </c>
       <c r="R59" t="n">
-        <v>6788468</v>
+        <v>6788353</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6631,7 +6626,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566841</v>
+        <v>122566827</v>
       </c>
       <c r="B60" t="n">
         <v>78656</v>
@@ -6671,10 +6666,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461809</v>
+        <v>461879</v>
       </c>
       <c r="R60" t="n">
-        <v>6788250</v>
+        <v>6788396</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6733,7 +6728,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566838</v>
+        <v>122566839</v>
       </c>
       <c r="B61" t="n">
         <v>78656</v>
@@ -6773,10 +6768,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461878</v>
+        <v>461829</v>
       </c>
       <c r="R61" t="n">
-        <v>6788313</v>
+        <v>6788287</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6835,10 +6830,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566808</v>
+        <v>122566862</v>
       </c>
       <c r="B62" t="n">
-        <v>90839</v>
+        <v>78656</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6851,21 +6846,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6875,10 +6870,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461872</v>
+        <v>461562</v>
       </c>
       <c r="R62" t="n">
-        <v>6788413</v>
+        <v>6788141</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6937,7 +6932,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566883</v>
+        <v>122566829</v>
       </c>
       <c r="B63" t="n">
         <v>78656</v>
@@ -6977,10 +6972,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461777</v>
+        <v>461952</v>
       </c>
       <c r="R63" t="n">
-        <v>6788298</v>
+        <v>6788327</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7039,10 +7034,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566809</v>
+        <v>122566869</v>
       </c>
       <c r="B64" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7055,21 +7050,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7079,10 +7074,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461822</v>
+        <v>461678</v>
       </c>
       <c r="R64" t="n">
-        <v>6788353</v>
+        <v>6788157</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7141,7 +7136,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566855</v>
+        <v>122566882</v>
       </c>
       <c r="B65" t="n">
         <v>78656</v>
@@ -7181,10 +7176,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461704</v>
+        <v>461757</v>
       </c>
       <c r="R65" t="n">
-        <v>6788171</v>
+        <v>6788299</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7243,7 +7238,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566804</v>
+        <v>122566803</v>
       </c>
       <c r="B66" t="n">
         <v>79274</v>
@@ -7283,10 +7278,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461614</v>
+        <v>461598</v>
       </c>
       <c r="R66" t="n">
-        <v>6788152</v>
+        <v>6788148</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7345,7 +7340,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566817</v>
+        <v>122566846</v>
       </c>
       <c r="B67" t="n">
         <v>78656</v>
@@ -7385,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461788</v>
+        <v>461791</v>
       </c>
       <c r="R67" t="n">
-        <v>6788303</v>
+        <v>6788209</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7447,7 +7442,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566862</v>
+        <v>122566854</v>
       </c>
       <c r="B68" t="n">
         <v>78656</v>
@@ -7487,10 +7482,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461562</v>
+        <v>461714</v>
       </c>
       <c r="R68" t="n">
-        <v>6788141</v>
+        <v>6788188</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7549,7 +7544,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566826</v>
+        <v>122566844</v>
       </c>
       <c r="B69" t="n">
         <v>78656</v>
@@ -7589,10 +7584,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461846</v>
+        <v>461816</v>
       </c>
       <c r="R69" t="n">
-        <v>6788492</v>
+        <v>6788215</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7651,10 +7646,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566888</v>
+        <v>122566823</v>
       </c>
       <c r="B70" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7663,25 +7658,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7691,10 +7686,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461791</v>
+        <v>461778</v>
       </c>
       <c r="R70" t="n">
-        <v>6788187</v>
+        <v>6788485</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7753,10 +7748,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566844</v>
+        <v>122566811</v>
       </c>
       <c r="B71" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7769,34 +7764,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461816</v>
+        <v>461936</v>
       </c>
       <c r="R71" t="n">
-        <v>6788215</v>
+        <v>6788279</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7855,10 +7855,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566882</v>
+        <v>122566888</v>
       </c>
       <c r="B72" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7867,25 +7867,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461757</v>
+        <v>461791</v>
       </c>
       <c r="R72" t="n">
-        <v>6788299</v>
+        <v>6788187</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7957,7 +7957,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566886</v>
+        <v>122566864</v>
       </c>
       <c r="B73" t="n">
         <v>78656</v>
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461810</v>
+        <v>461619</v>
       </c>
       <c r="R73" t="n">
-        <v>6788325</v>
+        <v>6788144</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566818</v>
+        <v>122566802</v>
       </c>
       <c r="B74" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8075,21 +8075,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8099,10 +8099,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461816</v>
+        <v>461811</v>
       </c>
       <c r="R74" t="n">
-        <v>6788330</v>
+        <v>6788280</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8161,7 +8161,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566823</v>
+        <v>122566871</v>
       </c>
       <c r="B75" t="n">
         <v>78656</v>
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461778</v>
+        <v>461676</v>
       </c>
       <c r="R75" t="n">
-        <v>6788485</v>
+        <v>6788174</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8263,10 +8263,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566828</v>
+        <v>122566805</v>
       </c>
       <c r="B76" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461923</v>
+        <v>461848</v>
       </c>
       <c r="R76" t="n">
-        <v>6788324</v>
+        <v>6788429</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566801</v>
+        <v>122566817</v>
       </c>
       <c r="B77" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8381,21 +8381,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461945</v>
+        <v>461788</v>
       </c>
       <c r="R77" t="n">
-        <v>6788255</v>
+        <v>6788303</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8467,7 +8467,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566830</v>
+        <v>122566859</v>
       </c>
       <c r="B78" t="n">
         <v>78656</v>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461991</v>
+        <v>461506</v>
       </c>
       <c r="R78" t="n">
-        <v>6788324</v>
+        <v>6788139</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8569,7 +8569,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566839</v>
+        <v>122566874</v>
       </c>
       <c r="B79" t="n">
         <v>78656</v>
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461829</v>
+        <v>461665</v>
       </c>
       <c r="R79" t="n">
-        <v>6788287</v>
+        <v>6788207</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8671,7 +8671,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122566831</v>
+        <v>122566873</v>
       </c>
       <c r="B80" t="n">
         <v>78656</v>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>462004</v>
+        <v>461655</v>
       </c>
       <c r="R80" t="n">
-        <v>6788320</v>
+        <v>6788205</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -1914,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566847</v>
+        <v>122566818</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461789</v>
+        <v>461816</v>
       </c>
       <c r="R14" t="n">
-        <v>6788194</v>
+        <v>6788330</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566818</v>
+        <v>122566847</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461816</v>
+        <v>461789</v>
       </c>
       <c r="R15" t="n">
-        <v>6788330</v>
+        <v>6788194</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566816</v>
+        <v>122566837</v>
       </c>
       <c r="B23" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,39 +2848,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461930</v>
+        <v>461917</v>
       </c>
       <c r="R23" t="n">
-        <v>6788270</v>
+        <v>6788292</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566837</v>
+        <v>122566816</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,34 +2950,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461917</v>
+        <v>461930</v>
       </c>
       <c r="R24" t="n">
-        <v>6788292</v>
+        <v>6788270</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3663,7 +3663,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566853</v>
+        <v>122566855</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461732</v>
+        <v>461704</v>
       </c>
       <c r="R31" t="n">
-        <v>6788166</v>
+        <v>6788171</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3765,7 +3765,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566855</v>
+        <v>122566863</v>
       </c>
       <c r="B32" t="n">
         <v>78656</v>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461704</v>
+        <v>461589</v>
       </c>
       <c r="R32" t="n">
-        <v>6788171</v>
+        <v>6788148</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,7 +3867,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566863</v>
+        <v>122566853</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461589</v>
+        <v>461732</v>
       </c>
       <c r="R33" t="n">
-        <v>6788148</v>
+        <v>6788166</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566822</v>
+        <v>122566851</v>
       </c>
       <c r="B40" t="n">
         <v>78656</v>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461763</v>
+        <v>461758</v>
       </c>
       <c r="R40" t="n">
-        <v>6788475</v>
+        <v>6788174</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4683,7 +4683,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566833</v>
+        <v>122566834</v>
       </c>
       <c r="B41" t="n">
         <v>78656</v>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461972</v>
+        <v>461929</v>
       </c>
       <c r="R41" t="n">
-        <v>6788277</v>
+        <v>6788262</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566826</v>
+        <v>122566822</v>
       </c>
       <c r="B42" t="n">
         <v>78656</v>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461846</v>
+        <v>461763</v>
       </c>
       <c r="R42" t="n">
-        <v>6788492</v>
+        <v>6788475</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566851</v>
+        <v>122566833</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461758</v>
+        <v>461972</v>
       </c>
       <c r="R43" t="n">
-        <v>6788174</v>
+        <v>6788277</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,7 +4989,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566834</v>
+        <v>122566826</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461929</v>
+        <v>461846</v>
       </c>
       <c r="R44" t="n">
-        <v>6788262</v>
+        <v>6788492</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6116,10 +6116,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566808</v>
+        <v>122566801</v>
       </c>
       <c r="B55" t="n">
-        <v>90839</v>
+        <v>79274</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6132,21 +6132,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6156,10 +6156,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461872</v>
+        <v>461945</v>
       </c>
       <c r="R55" t="n">
-        <v>6788413</v>
+        <v>6788255</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6218,10 +6218,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566849</v>
+        <v>122566808</v>
       </c>
       <c r="B56" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6234,21 +6234,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461787</v>
+        <v>461872</v>
       </c>
       <c r="R56" t="n">
-        <v>6788182</v>
+        <v>6788413</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6320,10 +6320,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566801</v>
+        <v>122566809</v>
       </c>
       <c r="B57" t="n">
-        <v>79274</v>
+        <v>90859</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6336,21 +6336,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461945</v>
+        <v>461822</v>
       </c>
       <c r="R57" t="n">
-        <v>6788255</v>
+        <v>6788353</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566809</v>
+        <v>122566849</v>
       </c>
       <c r="B59" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6540,21 +6540,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461822</v>
+        <v>461787</v>
       </c>
       <c r="R59" t="n">
-        <v>6788353</v>
+        <v>6788182</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122488593</v>
+        <v>122489147</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>90853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489147</v>
+        <v>122488593</v>
       </c>
       <c r="B4" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566830</v>
+        <v>122566886</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461991</v>
+        <v>461810</v>
       </c>
       <c r="R6" t="n">
-        <v>6788324</v>
+        <v>6788325</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566872</v>
+        <v>122566833</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461659</v>
+        <v>461972</v>
       </c>
       <c r="R7" t="n">
-        <v>6788194</v>
+        <v>6788277</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566885</v>
+        <v>122566831</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461804</v>
+        <v>462004</v>
       </c>
       <c r="R8" t="n">
-        <v>6788319</v>
+        <v>6788320</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566838</v>
+        <v>122566819</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1438,16 +1438,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461878</v>
+        <v>461667</v>
       </c>
       <c r="R9" t="n">
-        <v>6788313</v>
+        <v>6788182</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566852</v>
+        <v>122566827</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461741</v>
+        <v>461879</v>
       </c>
       <c r="R10" t="n">
-        <v>6788170</v>
+        <v>6788396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566865</v>
+        <v>122566852</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461628</v>
+        <v>461741</v>
       </c>
       <c r="R11" t="n">
-        <v>6788142</v>
+        <v>6788170</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566848</v>
+        <v>122566862</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461791</v>
+        <v>461562</v>
       </c>
       <c r="R12" t="n">
-        <v>6788187</v>
+        <v>6788141</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566825</v>
+        <v>122566884</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461843</v>
+        <v>461793</v>
       </c>
       <c r="R13" t="n">
-        <v>6788468</v>
+        <v>6788303</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566818</v>
+        <v>122566887</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461816</v>
+        <v>461810</v>
       </c>
       <c r="R14" t="n">
-        <v>6788330</v>
+        <v>6788470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566847</v>
+        <v>122566817</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461789</v>
+        <v>461788</v>
       </c>
       <c r="R15" t="n">
-        <v>6788194</v>
+        <v>6788303</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566820</v>
+        <v>122566847</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461732</v>
+        <v>461789</v>
       </c>
       <c r="R16" t="n">
-        <v>6788430</v>
+        <v>6788194</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566850</v>
+        <v>122566879</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461771</v>
+        <v>461721</v>
       </c>
       <c r="R17" t="n">
-        <v>6788185</v>
+        <v>6788242</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,7 +2327,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566883</v>
+        <v>122566855</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461777</v>
+        <v>461704</v>
       </c>
       <c r="R18" t="n">
-        <v>6788298</v>
+        <v>6788171</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566807</v>
+        <v>122566882</v>
       </c>
       <c r="B19" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461739</v>
+        <v>461757</v>
       </c>
       <c r="R19" t="n">
-        <v>6788280</v>
+        <v>6788299</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,7 +2531,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566832</v>
+        <v>122566873</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -2566,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461991</v>
+        <v>461655</v>
       </c>
       <c r="R20" t="n">
-        <v>6788292</v>
+        <v>6788205</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,7 +2633,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566881</v>
+        <v>122566839</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2668,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461742</v>
+        <v>461829</v>
       </c>
       <c r="R21" t="n">
-        <v>6788295</v>
+        <v>6788287</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,7 +2735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566875</v>
+        <v>122566826</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2770,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461669</v>
+        <v>461846</v>
       </c>
       <c r="R22" t="n">
-        <v>6788203</v>
+        <v>6788492</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566837</v>
+        <v>122566848</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2872,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461917</v>
+        <v>461791</v>
       </c>
       <c r="R23" t="n">
-        <v>6788292</v>
+        <v>6788187</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566816</v>
+        <v>122566837</v>
       </c>
       <c r="B24" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2950,39 +2955,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461930</v>
+        <v>461917</v>
       </c>
       <c r="R24" t="n">
-        <v>6788270</v>
+        <v>6788292</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566835</v>
+        <v>122566843</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461929</v>
+        <v>461811</v>
       </c>
       <c r="R25" t="n">
-        <v>6788278</v>
+        <v>6788237</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566831</v>
+        <v>122566869</v>
       </c>
       <c r="B26" t="n">
         <v>78656</v>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462004</v>
+        <v>461678</v>
       </c>
       <c r="R26" t="n">
-        <v>6788320</v>
+        <v>6788157</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,7 +3245,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566879</v>
+        <v>122566828</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461721</v>
+        <v>461923</v>
       </c>
       <c r="R27" t="n">
-        <v>6788242</v>
+        <v>6788324</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566821</v>
+        <v>122566883</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461699</v>
+        <v>461777</v>
       </c>
       <c r="R28" t="n">
-        <v>6788443</v>
+        <v>6788298</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566840</v>
+        <v>122566814</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,21 +3465,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461810</v>
+        <v>461814</v>
       </c>
       <c r="R29" t="n">
-        <v>6788278</v>
+        <v>6788266</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566813</v>
+        <v>122566844</v>
       </c>
       <c r="B30" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,39 +3567,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461803</v>
+        <v>461816</v>
       </c>
       <c r="R30" t="n">
-        <v>6788243</v>
+        <v>6788215</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,11 +3627,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3663,7 +3653,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566855</v>
+        <v>122566853</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -3703,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461704</v>
+        <v>461732</v>
       </c>
       <c r="R31" t="n">
-        <v>6788171</v>
+        <v>6788166</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3765,7 +3755,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566863</v>
+        <v>122566865</v>
       </c>
       <c r="B32" t="n">
         <v>78656</v>
@@ -3805,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461589</v>
+        <v>461628</v>
       </c>
       <c r="R32" t="n">
-        <v>6788148</v>
+        <v>6788142</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,7 +3857,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566853</v>
+        <v>122566876</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -3907,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461732</v>
+        <v>461695</v>
       </c>
       <c r="R33" t="n">
-        <v>6788166</v>
+        <v>6788224</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3969,7 +3959,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566843</v>
+        <v>122566841</v>
       </c>
       <c r="B34" t="n">
         <v>78656</v>
@@ -4009,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461811</v>
+        <v>461809</v>
       </c>
       <c r="R34" t="n">
-        <v>6788237</v>
+        <v>6788250</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4071,7 +4061,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566877</v>
+        <v>122566875</v>
       </c>
       <c r="B35" t="n">
         <v>78656</v>
@@ -4111,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461706</v>
+        <v>461669</v>
       </c>
       <c r="R35" t="n">
-        <v>6788223</v>
+        <v>6788203</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,7 +4163,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566876</v>
+        <v>122566840</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4213,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461695</v>
+        <v>461810</v>
       </c>
       <c r="R36" t="n">
-        <v>6788224</v>
+        <v>6788278</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4275,7 +4265,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566880</v>
+        <v>122566874</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4315,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461737</v>
+        <v>461665</v>
       </c>
       <c r="R37" t="n">
-        <v>6788251</v>
+        <v>6788207</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4377,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566804</v>
+        <v>122566813</v>
       </c>
       <c r="B38" t="n">
-        <v>79274</v>
+        <v>57383</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4393,34 +4383,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461614</v>
+        <v>461803</v>
       </c>
       <c r="R38" t="n">
-        <v>6788152</v>
+        <v>6788243</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4453,6 +4448,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4479,7 +4479,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566828</v>
+        <v>122566823</v>
       </c>
       <c r="B39" t="n">
         <v>78656</v>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461923</v>
+        <v>461778</v>
       </c>
       <c r="R39" t="n">
-        <v>6788324</v>
+        <v>6788485</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566851</v>
+        <v>122566818</v>
       </c>
       <c r="B40" t="n">
         <v>78656</v>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461758</v>
+        <v>461816</v>
       </c>
       <c r="R40" t="n">
-        <v>6788174</v>
+        <v>6788330</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566834</v>
+        <v>122566804</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4699,21 +4699,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461929</v>
+        <v>461614</v>
       </c>
       <c r="R41" t="n">
-        <v>6788262</v>
+        <v>6788152</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566822</v>
+        <v>122566880</v>
       </c>
       <c r="B42" t="n">
         <v>78656</v>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461763</v>
+        <v>461737</v>
       </c>
       <c r="R42" t="n">
-        <v>6788475</v>
+        <v>6788251</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566833</v>
+        <v>122566825</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461972</v>
+        <v>461843</v>
       </c>
       <c r="R43" t="n">
-        <v>6788277</v>
+        <v>6788468</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,7 +4989,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566826</v>
+        <v>122566820</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461846</v>
+        <v>461732</v>
       </c>
       <c r="R44" t="n">
-        <v>6788492</v>
+        <v>6788430</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,7 +5091,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566884</v>
+        <v>122566838</v>
       </c>
       <c r="B45" t="n">
         <v>78656</v>
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461793</v>
+        <v>461878</v>
       </c>
       <c r="R45" t="n">
-        <v>6788303</v>
+        <v>6788313</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5193,10 +5193,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566845</v>
+        <v>122566811</v>
       </c>
       <c r="B46" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5209,34 +5209,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461794</v>
+        <v>461936</v>
       </c>
       <c r="R46" t="n">
-        <v>6788217</v>
+        <v>6788279</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5295,10 +5300,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566814</v>
+        <v>122566824</v>
       </c>
       <c r="B47" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5311,21 +5316,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5335,10 +5340,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461814</v>
+        <v>461810</v>
       </c>
       <c r="R47" t="n">
-        <v>6788266</v>
+        <v>6788470</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5397,7 +5402,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566886</v>
+        <v>122566877</v>
       </c>
       <c r="B48" t="n">
         <v>78656</v>
@@ -5437,10 +5442,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461810</v>
+        <v>461706</v>
       </c>
       <c r="R48" t="n">
-        <v>6788325</v>
+        <v>6788223</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5499,7 +5504,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566819</v>
+        <v>122566846</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -5533,21 +5538,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461667</v>
+        <v>461791</v>
       </c>
       <c r="R49" t="n">
-        <v>6788182</v>
+        <v>6788209</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5606,10 +5606,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566842</v>
+        <v>122566805</v>
       </c>
       <c r="B50" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5622,21 +5622,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461803</v>
+        <v>461848</v>
       </c>
       <c r="R50" t="n">
-        <v>6788243</v>
+        <v>6788429</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566861</v>
+        <v>122566822</v>
       </c>
       <c r="B51" t="n">
         <v>78656</v>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461537</v>
+        <v>461763</v>
       </c>
       <c r="R51" t="n">
-        <v>6788149</v>
+        <v>6788475</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5810,7 +5810,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566841</v>
+        <v>122566871</v>
       </c>
       <c r="B52" t="n">
         <v>78656</v>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461809</v>
+        <v>461676</v>
       </c>
       <c r="R52" t="n">
-        <v>6788250</v>
+        <v>6788174</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5912,7 +5912,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566824</v>
+        <v>122566830</v>
       </c>
       <c r="B53" t="n">
         <v>78656</v>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461810</v>
+        <v>461991</v>
       </c>
       <c r="R53" t="n">
-        <v>6788470</v>
+        <v>6788324</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6014,7 +6014,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566878</v>
+        <v>122566834</v>
       </c>
       <c r="B54" t="n">
         <v>78656</v>
@@ -6054,10 +6054,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461712</v>
+        <v>461929</v>
       </c>
       <c r="R54" t="n">
-        <v>6788236</v>
+        <v>6788262</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6116,10 +6116,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566801</v>
+        <v>122566832</v>
       </c>
       <c r="B55" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6132,21 +6132,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6156,10 +6156,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461945</v>
+        <v>461991</v>
       </c>
       <c r="R55" t="n">
-        <v>6788255</v>
+        <v>6788292</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6218,10 +6218,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566808</v>
+        <v>122566809</v>
       </c>
       <c r="B56" t="n">
-        <v>90839</v>
+        <v>90853</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6234,21 +6234,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461872</v>
+        <v>461822</v>
       </c>
       <c r="R56" t="n">
-        <v>6788413</v>
+        <v>6788353</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6320,10 +6320,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566809</v>
+        <v>122566835</v>
       </c>
       <c r="B57" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6336,21 +6336,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461822</v>
+        <v>461929</v>
       </c>
       <c r="R57" t="n">
-        <v>6788353</v>
+        <v>6788278</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6422,10 +6422,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566887</v>
+        <v>122566851</v>
       </c>
       <c r="B58" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6434,25 +6434,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461810</v>
+        <v>461758</v>
       </c>
       <c r="R58" t="n">
-        <v>6788470</v>
+        <v>6788174</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566849</v>
+        <v>122566829</v>
       </c>
       <c r="B59" t="n">
         <v>78656</v>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461787</v>
+        <v>461952</v>
       </c>
       <c r="R59" t="n">
-        <v>6788182</v>
+        <v>6788327</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6626,10 +6626,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566827</v>
+        <v>122566816</v>
       </c>
       <c r="B60" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6642,34 +6642,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461879</v>
+        <v>461930</v>
       </c>
       <c r="R60" t="n">
-        <v>6788396</v>
+        <v>6788270</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6728,10 +6733,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566839</v>
+        <v>122566801</v>
       </c>
       <c r="B61" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6744,21 +6749,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6768,10 +6773,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461829</v>
+        <v>461945</v>
       </c>
       <c r="R61" t="n">
-        <v>6788287</v>
+        <v>6788255</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6830,10 +6835,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566862</v>
+        <v>122566888</v>
       </c>
       <c r="B62" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6842,25 +6847,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6870,10 +6875,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461562</v>
+        <v>461791</v>
       </c>
       <c r="R62" t="n">
-        <v>6788141</v>
+        <v>6788187</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,10 +6937,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566829</v>
+        <v>122566803</v>
       </c>
       <c r="B63" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6948,21 +6953,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6972,10 +6977,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461952</v>
+        <v>461598</v>
       </c>
       <c r="R63" t="n">
-        <v>6788327</v>
+        <v>6788148</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,7 +7039,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566869</v>
+        <v>122566861</v>
       </c>
       <c r="B64" t="n">
         <v>78656</v>
@@ -7074,10 +7079,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461678</v>
+        <v>461537</v>
       </c>
       <c r="R64" t="n">
-        <v>6788157</v>
+        <v>6788149</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,7 +7141,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566882</v>
+        <v>122566849</v>
       </c>
       <c r="B65" t="n">
         <v>78656</v>
@@ -7176,10 +7181,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461757</v>
+        <v>461787</v>
       </c>
       <c r="R65" t="n">
-        <v>6788299</v>
+        <v>6788182</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7243,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566803</v>
+        <v>122566854</v>
       </c>
       <c r="B66" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7254,21 +7259,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7278,10 +7283,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461598</v>
+        <v>461714</v>
       </c>
       <c r="R66" t="n">
-        <v>6788148</v>
+        <v>6788188</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,7 +7345,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566846</v>
+        <v>122566845</v>
       </c>
       <c r="B67" t="n">
         <v>78656</v>
@@ -7380,10 +7385,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461791</v>
+        <v>461794</v>
       </c>
       <c r="R67" t="n">
-        <v>6788209</v>
+        <v>6788217</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,7 +7447,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566854</v>
+        <v>122566842</v>
       </c>
       <c r="B68" t="n">
         <v>78656</v>
@@ -7482,10 +7487,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461714</v>
+        <v>461803</v>
       </c>
       <c r="R68" t="n">
-        <v>6788188</v>
+        <v>6788243</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7544,10 +7549,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566844</v>
+        <v>122566802</v>
       </c>
       <c r="B69" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7560,21 +7565,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7584,10 +7589,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461816</v>
+        <v>461811</v>
       </c>
       <c r="R69" t="n">
-        <v>6788215</v>
+        <v>6788280</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7646,7 +7651,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566823</v>
+        <v>122566859</v>
       </c>
       <c r="B70" t="n">
         <v>78656</v>
@@ -7686,10 +7691,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461778</v>
+        <v>461506</v>
       </c>
       <c r="R70" t="n">
-        <v>6788485</v>
+        <v>6788139</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7748,10 +7753,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566811</v>
+        <v>122566881</v>
       </c>
       <c r="B71" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7764,39 +7769,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461936</v>
+        <v>461742</v>
       </c>
       <c r="R71" t="n">
-        <v>6788279</v>
+        <v>6788295</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7855,10 +7855,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566888</v>
+        <v>122566878</v>
       </c>
       <c r="B72" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7867,25 +7867,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461791</v>
+        <v>461712</v>
       </c>
       <c r="R72" t="n">
-        <v>6788187</v>
+        <v>6788236</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566802</v>
+        <v>122566863</v>
       </c>
       <c r="B74" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8075,21 +8075,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8099,10 +8099,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461811</v>
+        <v>461589</v>
       </c>
       <c r="R74" t="n">
-        <v>6788280</v>
+        <v>6788148</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8161,7 +8161,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566871</v>
+        <v>122566885</v>
       </c>
       <c r="B75" t="n">
         <v>78656</v>
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461676</v>
+        <v>461804</v>
       </c>
       <c r="R75" t="n">
-        <v>6788174</v>
+        <v>6788319</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8263,10 +8263,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566805</v>
+        <v>122566808</v>
       </c>
       <c r="B76" t="n">
-        <v>74757</v>
+        <v>90833</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461848</v>
+        <v>461872</v>
       </c>
       <c r="R76" t="n">
-        <v>6788429</v>
+        <v>6788413</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8365,7 +8365,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566817</v>
+        <v>122566850</v>
       </c>
       <c r="B77" t="n">
         <v>78656</v>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461788</v>
+        <v>461771</v>
       </c>
       <c r="R77" t="n">
-        <v>6788303</v>
+        <v>6788185</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8467,7 +8467,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566859</v>
+        <v>122566872</v>
       </c>
       <c r="B78" t="n">
         <v>78656</v>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461506</v>
+        <v>461659</v>
       </c>
       <c r="R78" t="n">
-        <v>6788139</v>
+        <v>6788194</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566874</v>
+        <v>122566807</v>
       </c>
       <c r="B79" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8585,21 +8585,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461665</v>
+        <v>461739</v>
       </c>
       <c r="R79" t="n">
-        <v>6788207</v>
+        <v>6788280</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8671,7 +8671,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122566873</v>
+        <v>122566821</v>
       </c>
       <c r="B80" t="n">
         <v>78656</v>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461655</v>
+        <v>461699</v>
       </c>
       <c r="R80" t="n">
-        <v>6788205</v>
+        <v>6788443</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122489220</v>
+        <v>122488593</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R3" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122488593</v>
+        <v>122489220</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R4" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566886</v>
+        <v>122566835</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461810</v>
+        <v>461929</v>
       </c>
       <c r="R6" t="n">
-        <v>6788325</v>
+        <v>6788278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566831</v>
+        <v>122566828</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462004</v>
+        <v>461923</v>
       </c>
       <c r="R8" t="n">
-        <v>6788320</v>
+        <v>6788324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566819</v>
+        <v>122566846</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1438,21 +1438,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461667</v>
+        <v>461791</v>
       </c>
       <c r="R9" t="n">
-        <v>6788182</v>
+        <v>6788209</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566827</v>
+        <v>122566838</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1551,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461879</v>
+        <v>461878</v>
       </c>
       <c r="R10" t="n">
-        <v>6788396</v>
+        <v>6788313</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566852</v>
+        <v>122566824</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461741</v>
+        <v>461810</v>
       </c>
       <c r="R11" t="n">
-        <v>6788170</v>
+        <v>6788470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566862</v>
+        <v>122566831</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461562</v>
+        <v>462004</v>
       </c>
       <c r="R12" t="n">
-        <v>6788141</v>
+        <v>6788320</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566884</v>
+        <v>122566801</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461793</v>
+        <v>461945</v>
       </c>
       <c r="R13" t="n">
-        <v>6788303</v>
+        <v>6788255</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566887</v>
+        <v>122566883</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461810</v>
+        <v>461777</v>
       </c>
       <c r="R14" t="n">
-        <v>6788470</v>
+        <v>6788298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566817</v>
+        <v>122566847</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2061,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461788</v>
+        <v>461789</v>
       </c>
       <c r="R15" t="n">
-        <v>6788303</v>
+        <v>6788194</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566847</v>
+        <v>122566879</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461789</v>
+        <v>461721</v>
       </c>
       <c r="R16" t="n">
-        <v>6788194</v>
+        <v>6788242</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566879</v>
+        <v>122566825</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2265,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461721</v>
+        <v>461843</v>
       </c>
       <c r="R17" t="n">
-        <v>6788242</v>
+        <v>6788468</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566855</v>
+        <v>122566803</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461704</v>
+        <v>461598</v>
       </c>
       <c r="R18" t="n">
-        <v>6788171</v>
+        <v>6788148</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,7 +2424,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566882</v>
+        <v>122566859</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2469,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461757</v>
+        <v>461506</v>
       </c>
       <c r="R19" t="n">
-        <v>6788299</v>
+        <v>6788139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566873</v>
+        <v>122566805</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2542,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461655</v>
+        <v>461848</v>
       </c>
       <c r="R20" t="n">
-        <v>6788205</v>
+        <v>6788429</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,7 +2628,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566839</v>
+        <v>122566844</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461829</v>
+        <v>461816</v>
       </c>
       <c r="R21" t="n">
-        <v>6788287</v>
+        <v>6788215</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566826</v>
+        <v>122566849</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2775,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461846</v>
+        <v>461787</v>
       </c>
       <c r="R22" t="n">
-        <v>6788492</v>
+        <v>6788182</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566848</v>
+        <v>122566808</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>90833</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,21 +2848,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461791</v>
+        <v>461872</v>
       </c>
       <c r="R23" t="n">
-        <v>6788187</v>
+        <v>6788413</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,7 +2934,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566837</v>
+        <v>122566865</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2979,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461917</v>
+        <v>461628</v>
       </c>
       <c r="R24" t="n">
-        <v>6788292</v>
+        <v>6788142</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,7 +3036,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566843</v>
+        <v>122566820</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3081,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461811</v>
+        <v>461732</v>
       </c>
       <c r="R25" t="n">
-        <v>6788237</v>
+        <v>6788430</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,7 +3138,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566869</v>
+        <v>122566854</v>
       </c>
       <c r="B26" t="n">
         <v>78656</v>
@@ -3183,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461678</v>
+        <v>461714</v>
       </c>
       <c r="R26" t="n">
-        <v>6788157</v>
+        <v>6788188</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,7 +3240,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566828</v>
+        <v>122566823</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3285,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461923</v>
+        <v>461778</v>
       </c>
       <c r="R27" t="n">
-        <v>6788324</v>
+        <v>6788485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,7 +3342,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566883</v>
+        <v>122566822</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -3387,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461777</v>
+        <v>461763</v>
       </c>
       <c r="R28" t="n">
-        <v>6788298</v>
+        <v>6788475</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566814</v>
+        <v>122566839</v>
       </c>
       <c r="B29" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,21 +3460,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3484,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461814</v>
+        <v>461829</v>
       </c>
       <c r="R29" t="n">
-        <v>6788266</v>
+        <v>6788287</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,7 +3546,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566844</v>
+        <v>122566869</v>
       </c>
       <c r="B30" t="n">
         <v>78656</v>
@@ -3591,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461816</v>
+        <v>461678</v>
       </c>
       <c r="R30" t="n">
-        <v>6788215</v>
+        <v>6788157</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,7 +3648,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566853</v>
+        <v>122566855</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -3693,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461732</v>
+        <v>461704</v>
       </c>
       <c r="R31" t="n">
-        <v>6788166</v>
+        <v>6788171</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,7 +3750,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566865</v>
+        <v>122566864</v>
       </c>
       <c r="B32" t="n">
         <v>78656</v>
@@ -3795,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461628</v>
+        <v>461619</v>
       </c>
       <c r="R32" t="n">
-        <v>6788142</v>
+        <v>6788144</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,7 +3852,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566876</v>
+        <v>122566863</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -3897,10 +3892,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461695</v>
+        <v>461589</v>
       </c>
       <c r="R33" t="n">
-        <v>6788224</v>
+        <v>6788148</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,7 +3954,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566841</v>
+        <v>122566837</v>
       </c>
       <c r="B34" t="n">
         <v>78656</v>
@@ -3999,10 +3994,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461809</v>
+        <v>461917</v>
       </c>
       <c r="R34" t="n">
-        <v>6788250</v>
+        <v>6788292</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,7 +4056,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566875</v>
+        <v>122566842</v>
       </c>
       <c r="B35" t="n">
         <v>78656</v>
@@ -4101,10 +4096,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461669</v>
+        <v>461803</v>
       </c>
       <c r="R35" t="n">
-        <v>6788203</v>
+        <v>6788243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,7 +4158,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566840</v>
+        <v>122566829</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4203,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461810</v>
+        <v>461952</v>
       </c>
       <c r="R36" t="n">
-        <v>6788278</v>
+        <v>6788327</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,7 +4260,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566874</v>
+        <v>122566848</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4305,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461665</v>
+        <v>461791</v>
       </c>
       <c r="R37" t="n">
-        <v>6788207</v>
+        <v>6788187</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566813</v>
+        <v>122566845</v>
       </c>
       <c r="B38" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4383,39 +4378,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461803</v>
+        <v>461794</v>
       </c>
       <c r="R38" t="n">
-        <v>6788243</v>
+        <v>6788217</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4448,11 +4438,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4479,10 +4464,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566823</v>
+        <v>122566816</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4495,34 +4480,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461778</v>
+        <v>461930</v>
       </c>
       <c r="R39" t="n">
-        <v>6788485</v>
+        <v>6788270</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4581,7 +4571,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566818</v>
+        <v>122566877</v>
       </c>
       <c r="B40" t="n">
         <v>78656</v>
@@ -4621,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461816</v>
+        <v>461706</v>
       </c>
       <c r="R40" t="n">
-        <v>6788330</v>
+        <v>6788223</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4683,10 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566804</v>
+        <v>122566872</v>
       </c>
       <c r="B41" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4699,21 +4689,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4723,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461614</v>
+        <v>461659</v>
       </c>
       <c r="R41" t="n">
-        <v>6788152</v>
+        <v>6788194</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4785,7 +4775,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566880</v>
+        <v>122566861</v>
       </c>
       <c r="B42" t="n">
         <v>78656</v>
@@ -4825,10 +4815,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461737</v>
+        <v>461537</v>
       </c>
       <c r="R42" t="n">
-        <v>6788251</v>
+        <v>6788149</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,7 +4877,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566825</v>
+        <v>122566843</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4927,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461843</v>
+        <v>461811</v>
       </c>
       <c r="R43" t="n">
-        <v>6788468</v>
+        <v>6788237</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,7 +4979,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566820</v>
+        <v>122566886</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -5029,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461732</v>
+        <v>461810</v>
       </c>
       <c r="R44" t="n">
-        <v>6788430</v>
+        <v>6788325</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,7 +5081,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566838</v>
+        <v>122566821</v>
       </c>
       <c r="B45" t="n">
         <v>78656</v>
@@ -5131,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461878</v>
+        <v>461699</v>
       </c>
       <c r="R45" t="n">
-        <v>6788313</v>
+        <v>6788443</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5193,10 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566811</v>
+        <v>122566880</v>
       </c>
       <c r="B46" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5209,39 +5199,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461936</v>
+        <v>461737</v>
       </c>
       <c r="R46" t="n">
-        <v>6788279</v>
+        <v>6788251</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5300,7 +5285,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566824</v>
+        <v>122566875</v>
       </c>
       <c r="B47" t="n">
         <v>78656</v>
@@ -5340,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461810</v>
+        <v>461669</v>
       </c>
       <c r="R47" t="n">
-        <v>6788470</v>
+        <v>6788203</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5402,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566877</v>
+        <v>122566804</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5418,21 +5403,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5442,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461706</v>
+        <v>461614</v>
       </c>
       <c r="R48" t="n">
-        <v>6788223</v>
+        <v>6788152</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5504,7 +5489,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566846</v>
+        <v>122566834</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -5544,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461791</v>
+        <v>461929</v>
       </c>
       <c r="R49" t="n">
-        <v>6788209</v>
+        <v>6788262</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5606,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566805</v>
+        <v>122566884</v>
       </c>
       <c r="B50" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5622,21 +5607,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5646,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461848</v>
+        <v>461793</v>
       </c>
       <c r="R50" t="n">
-        <v>6788429</v>
+        <v>6788303</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5708,7 +5693,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566822</v>
+        <v>122566882</v>
       </c>
       <c r="B51" t="n">
         <v>78656</v>
@@ -5748,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461763</v>
+        <v>461757</v>
       </c>
       <c r="R51" t="n">
-        <v>6788475</v>
+        <v>6788299</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5810,7 +5795,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566871</v>
+        <v>122566819</v>
       </c>
       <c r="B52" t="n">
         <v>78656</v>
@@ -5844,16 +5829,21 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461676</v>
+        <v>461667</v>
       </c>
       <c r="R52" t="n">
-        <v>6788174</v>
+        <v>6788182</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5912,10 +5902,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566830</v>
+        <v>122566802</v>
       </c>
       <c r="B53" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5928,21 +5918,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5952,10 +5942,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461991</v>
+        <v>461811</v>
       </c>
       <c r="R53" t="n">
-        <v>6788324</v>
+        <v>6788280</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6014,7 +6004,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566834</v>
+        <v>122566832</v>
       </c>
       <c r="B54" t="n">
         <v>78656</v>
@@ -6054,10 +6044,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461929</v>
+        <v>461991</v>
       </c>
       <c r="R54" t="n">
-        <v>6788262</v>
+        <v>6788292</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6116,10 +6106,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566832</v>
+        <v>122566814</v>
       </c>
       <c r="B55" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6132,21 +6122,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6156,10 +6146,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461991</v>
+        <v>461814</v>
       </c>
       <c r="R55" t="n">
-        <v>6788292</v>
+        <v>6788266</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6320,7 +6310,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566835</v>
+        <v>122566830</v>
       </c>
       <c r="B57" t="n">
         <v>78656</v>
@@ -6360,10 +6350,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461929</v>
+        <v>461991</v>
       </c>
       <c r="R57" t="n">
-        <v>6788278</v>
+        <v>6788324</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6422,7 +6412,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566851</v>
+        <v>122566853</v>
       </c>
       <c r="B58" t="n">
         <v>78656</v>
@@ -6462,10 +6452,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461758</v>
+        <v>461732</v>
       </c>
       <c r="R58" t="n">
-        <v>6788174</v>
+        <v>6788166</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,7 +6514,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566829</v>
+        <v>122566841</v>
       </c>
       <c r="B59" t="n">
         <v>78656</v>
@@ -6564,10 +6554,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461952</v>
+        <v>461809</v>
       </c>
       <c r="R59" t="n">
-        <v>6788327</v>
+        <v>6788250</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6626,10 +6616,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566816</v>
+        <v>122566813</v>
       </c>
       <c r="B60" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6642,16 +6632,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6662,7 +6652,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6671,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461930</v>
+        <v>461803</v>
       </c>
       <c r="R60" t="n">
-        <v>6788270</v>
+        <v>6788243</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6707,6 +6697,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6733,10 +6728,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566801</v>
+        <v>122566817</v>
       </c>
       <c r="B61" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6749,21 +6744,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6773,10 +6768,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461945</v>
+        <v>461788</v>
       </c>
       <c r="R61" t="n">
-        <v>6788255</v>
+        <v>6788303</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6835,10 +6830,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566888</v>
+        <v>122566873</v>
       </c>
       <c r="B62" t="n">
-        <v>5173</v>
+        <v>78656</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6847,25 +6842,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6875,10 +6870,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461791</v>
+        <v>461655</v>
       </c>
       <c r="R62" t="n">
-        <v>6788187</v>
+        <v>6788205</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6937,10 +6932,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566803</v>
+        <v>122566852</v>
       </c>
       <c r="B63" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6953,21 +6948,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6977,10 +6972,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461598</v>
+        <v>461741</v>
       </c>
       <c r="R63" t="n">
-        <v>6788148</v>
+        <v>6788170</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7039,10 +7034,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566861</v>
+        <v>122566887</v>
       </c>
       <c r="B64" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7051,25 +7046,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7079,10 +7074,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461537</v>
+        <v>461810</v>
       </c>
       <c r="R64" t="n">
-        <v>6788149</v>
+        <v>6788470</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7141,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566849</v>
+        <v>122566888</v>
       </c>
       <c r="B65" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7153,25 +7148,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7181,10 +7176,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461787</v>
+        <v>461791</v>
       </c>
       <c r="R65" t="n">
-        <v>6788182</v>
+        <v>6788187</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7243,10 +7238,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566854</v>
+        <v>122566811</v>
       </c>
       <c r="B66" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7259,34 +7254,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461714</v>
+        <v>461936</v>
       </c>
       <c r="R66" t="n">
-        <v>6788188</v>
+        <v>6788279</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7345,7 +7345,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566845</v>
+        <v>122566827</v>
       </c>
       <c r="B67" t="n">
         <v>78656</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461794</v>
+        <v>461879</v>
       </c>
       <c r="R67" t="n">
-        <v>6788217</v>
+        <v>6788396</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7447,7 +7447,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566842</v>
+        <v>122566881</v>
       </c>
       <c r="B68" t="n">
         <v>78656</v>
@@ -7487,10 +7487,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461803</v>
+        <v>461742</v>
       </c>
       <c r="R68" t="n">
-        <v>6788243</v>
+        <v>6788295</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7549,10 +7549,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566802</v>
+        <v>122566871</v>
       </c>
       <c r="B69" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7565,21 +7565,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7589,10 +7589,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461811</v>
+        <v>461676</v>
       </c>
       <c r="R69" t="n">
-        <v>6788280</v>
+        <v>6788174</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7651,7 +7651,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566859</v>
+        <v>122566851</v>
       </c>
       <c r="B70" t="n">
         <v>78656</v>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461506</v>
+        <v>461758</v>
       </c>
       <c r="R70" t="n">
-        <v>6788139</v>
+        <v>6788174</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7753,7 +7753,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566881</v>
+        <v>122566874</v>
       </c>
       <c r="B71" t="n">
         <v>78656</v>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461742</v>
+        <v>461665</v>
       </c>
       <c r="R71" t="n">
-        <v>6788295</v>
+        <v>6788207</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7855,7 +7855,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566878</v>
+        <v>122566862</v>
       </c>
       <c r="B72" t="n">
         <v>78656</v>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461712</v>
+        <v>461562</v>
       </c>
       <c r="R72" t="n">
-        <v>6788236</v>
+        <v>6788141</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7957,7 +7957,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566864</v>
+        <v>122566826</v>
       </c>
       <c r="B73" t="n">
         <v>78656</v>
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461619</v>
+        <v>461846</v>
       </c>
       <c r="R73" t="n">
-        <v>6788144</v>
+        <v>6788492</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8059,7 +8059,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566863</v>
+        <v>122566876</v>
       </c>
       <c r="B74" t="n">
         <v>78656</v>
@@ -8099,10 +8099,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461589</v>
+        <v>461695</v>
       </c>
       <c r="R74" t="n">
-        <v>6788148</v>
+        <v>6788224</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8263,10 +8263,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566808</v>
+        <v>122566878</v>
       </c>
       <c r="B76" t="n">
-        <v>90833</v>
+        <v>78656</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461872</v>
+        <v>461712</v>
       </c>
       <c r="R76" t="n">
-        <v>6788413</v>
+        <v>6788236</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8365,7 +8365,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566850</v>
+        <v>122566840</v>
       </c>
       <c r="B77" t="n">
         <v>78656</v>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461771</v>
+        <v>461810</v>
       </c>
       <c r="R77" t="n">
-        <v>6788185</v>
+        <v>6788278</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8467,7 +8467,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566872</v>
+        <v>122566850</v>
       </c>
       <c r="B78" t="n">
         <v>78656</v>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461659</v>
+        <v>461771</v>
       </c>
       <c r="R78" t="n">
-        <v>6788194</v>
+        <v>6788185</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566807</v>
+        <v>122566818</v>
       </c>
       <c r="B79" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8585,21 +8585,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461739</v>
+        <v>461816</v>
       </c>
       <c r="R79" t="n">
-        <v>6788280</v>
+        <v>6788330</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8671,10 +8671,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122566821</v>
+        <v>122566807</v>
       </c>
       <c r="B80" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8687,21 +8687,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461699</v>
+        <v>461739</v>
       </c>
       <c r="R80" t="n">
-        <v>6788443</v>
+        <v>6788280</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489147</v>
+        <v>122489220</v>
       </c>
       <c r="B2" t="n">
-        <v>90853</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R2" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +790,7 @@
         <v>122488593</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489220</v>
+        <v>122489147</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>90854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R4" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122489274</v>
+        <v>122566835</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461895</v>
+        <v>461929</v>
       </c>
       <c r="R5" t="n">
-        <v>6788288</v>
+        <v>6788278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,17 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Garnlav, återkommande i området.</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566835</v>
+        <v>122566827</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461929</v>
+        <v>461879</v>
       </c>
       <c r="R6" t="n">
-        <v>6788278</v>
+        <v>6788396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566833</v>
+        <v>122566829</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461972</v>
+        <v>461952</v>
       </c>
       <c r="R7" t="n">
-        <v>6788277</v>
+        <v>6788327</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566828</v>
+        <v>122566813</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,34 +1313,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461923</v>
+        <v>461803</v>
       </c>
       <c r="R8" t="n">
-        <v>6788324</v>
+        <v>6788243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566846</v>
+        <v>122566826</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461791</v>
+        <v>461846</v>
       </c>
       <c r="R9" t="n">
-        <v>6788209</v>
+        <v>6788492</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566838</v>
+        <v>122566850</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461878</v>
+        <v>461771</v>
       </c>
       <c r="R10" t="n">
-        <v>6788313</v>
+        <v>6788185</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566824</v>
+        <v>122566819</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,16 +1647,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461810</v>
+        <v>461667</v>
       </c>
       <c r="R11" t="n">
-        <v>6788470</v>
+        <v>6788182</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566831</v>
+        <v>122566832</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462004</v>
+        <v>461991</v>
       </c>
       <c r="R12" t="n">
-        <v>6788320</v>
+        <v>6788292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566801</v>
+        <v>122566828</v>
       </c>
       <c r="B13" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461945</v>
+        <v>461923</v>
       </c>
       <c r="R13" t="n">
-        <v>6788255</v>
+        <v>6788324</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566883</v>
+        <v>122566880</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461777</v>
+        <v>461737</v>
       </c>
       <c r="R14" t="n">
-        <v>6788298</v>
+        <v>6788251</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566847</v>
+        <v>122566855</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461789</v>
+        <v>461704</v>
       </c>
       <c r="R15" t="n">
-        <v>6788194</v>
+        <v>6788171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566879</v>
+        <v>122566877</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461721</v>
+        <v>461706</v>
       </c>
       <c r="R16" t="n">
-        <v>6788242</v>
+        <v>6788223</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566825</v>
+        <v>122566852</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2260,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461843</v>
+        <v>461741</v>
       </c>
       <c r="R17" t="n">
-        <v>6788468</v>
+        <v>6788170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566803</v>
+        <v>122566811</v>
       </c>
       <c r="B18" t="n">
-        <v>79274</v>
+        <v>57400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,34 +2348,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461598</v>
+        <v>461936</v>
       </c>
       <c r="R18" t="n">
-        <v>6788148</v>
+        <v>6788279</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566859</v>
+        <v>122566834</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2464,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461506</v>
+        <v>461929</v>
       </c>
       <c r="R19" t="n">
-        <v>6788139</v>
+        <v>6788262</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566805</v>
+        <v>122566804</v>
       </c>
       <c r="B20" t="n">
-        <v>74757</v>
+        <v>79275</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,21 +2557,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461848</v>
+        <v>461614</v>
       </c>
       <c r="R20" t="n">
-        <v>6788429</v>
+        <v>6788152</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566844</v>
+        <v>122566814</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,21 +2659,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461816</v>
+        <v>461814</v>
       </c>
       <c r="R21" t="n">
-        <v>6788215</v>
+        <v>6788266</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566849</v>
+        <v>122566807</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>74758</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2746,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461787</v>
+        <v>461739</v>
       </c>
       <c r="R22" t="n">
-        <v>6788182</v>
+        <v>6788280</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566808</v>
+        <v>122566816</v>
       </c>
       <c r="B23" t="n">
-        <v>90833</v>
+        <v>57400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,34 +2863,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461872</v>
+        <v>461930</v>
       </c>
       <c r="R23" t="n">
-        <v>6788413</v>
+        <v>6788270</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566865</v>
+        <v>122566817</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2974,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461628</v>
+        <v>461788</v>
       </c>
       <c r="R24" t="n">
-        <v>6788142</v>
+        <v>6788303</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566820</v>
+        <v>122566873</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3076,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461732</v>
+        <v>461655</v>
       </c>
       <c r="R25" t="n">
-        <v>6788430</v>
+        <v>6788205</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566854</v>
+        <v>122566843</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3178,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461714</v>
+        <v>461811</v>
       </c>
       <c r="R26" t="n">
-        <v>6788188</v>
+        <v>6788237</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566823</v>
+        <v>122566869</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3280,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461778</v>
+        <v>461678</v>
       </c>
       <c r="R27" t="n">
-        <v>6788485</v>
+        <v>6788157</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566822</v>
+        <v>122566846</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3382,10 +3402,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461763</v>
+        <v>461791</v>
       </c>
       <c r="R28" t="n">
-        <v>6788475</v>
+        <v>6788209</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,10 +3464,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566839</v>
+        <v>122566802</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3460,21 +3480,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3484,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461829</v>
+        <v>461811</v>
       </c>
       <c r="R29" t="n">
-        <v>6788287</v>
+        <v>6788280</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3546,10 +3566,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566869</v>
+        <v>122566822</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3586,10 +3606,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461678</v>
+        <v>461763</v>
       </c>
       <c r="R30" t="n">
-        <v>6788157</v>
+        <v>6788475</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566855</v>
+        <v>122566839</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3688,10 +3708,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461704</v>
+        <v>461829</v>
       </c>
       <c r="R31" t="n">
-        <v>6788171</v>
+        <v>6788287</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566864</v>
+        <v>122566844</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3790,10 +3810,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461619</v>
+        <v>461816</v>
       </c>
       <c r="R32" t="n">
-        <v>6788144</v>
+        <v>6788215</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,10 +3872,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566863</v>
+        <v>122566875</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3892,10 +3912,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461589</v>
+        <v>461669</v>
       </c>
       <c r="R33" t="n">
-        <v>6788148</v>
+        <v>6788203</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3954,10 +3974,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566837</v>
+        <v>122566824</v>
       </c>
       <c r="B34" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3994,10 +4014,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461917</v>
+        <v>461810</v>
       </c>
       <c r="R34" t="n">
-        <v>6788292</v>
+        <v>6788470</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,10 +4076,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566842</v>
+        <v>122566861</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4096,10 +4116,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461803</v>
+        <v>461537</v>
       </c>
       <c r="R35" t="n">
-        <v>6788243</v>
+        <v>6788149</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4158,10 +4178,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566829</v>
+        <v>122566863</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4198,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461952</v>
+        <v>461589</v>
       </c>
       <c r="R36" t="n">
-        <v>6788327</v>
+        <v>6788148</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4260,10 +4280,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566848</v>
+        <v>122566823</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4300,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461791</v>
+        <v>461778</v>
       </c>
       <c r="R37" t="n">
-        <v>6788187</v>
+        <v>6788485</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4362,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566845</v>
+        <v>122566831</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4402,10 +4422,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461794</v>
+        <v>462004</v>
       </c>
       <c r="R38" t="n">
-        <v>6788217</v>
+        <v>6788320</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,10 +4484,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566816</v>
+        <v>122566830</v>
       </c>
       <c r="B39" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4480,39 +4500,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461930</v>
+        <v>461991</v>
       </c>
       <c r="R39" t="n">
-        <v>6788270</v>
+        <v>6788324</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566877</v>
+        <v>122566808</v>
       </c>
       <c r="B40" t="n">
-        <v>78656</v>
+        <v>90834</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,21 +4602,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461706</v>
+        <v>461872</v>
       </c>
       <c r="R40" t="n">
-        <v>6788223</v>
+        <v>6788413</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566872</v>
+        <v>122566854</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4713,10 +4728,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461659</v>
+        <v>461714</v>
       </c>
       <c r="R41" t="n">
-        <v>6788194</v>
+        <v>6788188</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4775,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566861</v>
+        <v>122566871</v>
       </c>
       <c r="B42" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4815,10 +4830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461537</v>
+        <v>461676</v>
       </c>
       <c r="R42" t="n">
-        <v>6788149</v>
+        <v>6788174</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4877,10 +4892,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566843</v>
+        <v>122566883</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4917,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461811</v>
+        <v>461777</v>
       </c>
       <c r="R43" t="n">
-        <v>6788237</v>
+        <v>6788298</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4979,10 +4994,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566886</v>
+        <v>122566848</v>
       </c>
       <c r="B44" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5019,10 +5034,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461810</v>
+        <v>461791</v>
       </c>
       <c r="R44" t="n">
-        <v>6788325</v>
+        <v>6788187</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5081,10 +5096,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566821</v>
+        <v>122566841</v>
       </c>
       <c r="B45" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5121,10 +5136,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461699</v>
+        <v>461809</v>
       </c>
       <c r="R45" t="n">
-        <v>6788443</v>
+        <v>6788250</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,10 +5198,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566880</v>
+        <v>122566884</v>
       </c>
       <c r="B46" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5223,10 +5238,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461737</v>
+        <v>461793</v>
       </c>
       <c r="R46" t="n">
-        <v>6788251</v>
+        <v>6788303</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5285,10 +5300,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566875</v>
+        <v>122566847</v>
       </c>
       <c r="B47" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5325,10 +5340,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461669</v>
+        <v>461789</v>
       </c>
       <c r="R47" t="n">
-        <v>6788203</v>
+        <v>6788194</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,10 +5402,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566804</v>
+        <v>122566837</v>
       </c>
       <c r="B48" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5403,21 +5418,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,10 +5442,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461614</v>
+        <v>461917</v>
       </c>
       <c r="R48" t="n">
-        <v>6788152</v>
+        <v>6788292</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,10 +5504,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566834</v>
+        <v>122566818</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5529,10 +5544,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461929</v>
+        <v>461816</v>
       </c>
       <c r="R49" t="n">
-        <v>6788262</v>
+        <v>6788330</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5606,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566884</v>
+        <v>122566825</v>
       </c>
       <c r="B50" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5631,10 +5646,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461793</v>
+        <v>461843</v>
       </c>
       <c r="R50" t="n">
-        <v>6788303</v>
+        <v>6788468</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,10 +5708,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566882</v>
+        <v>122566840</v>
       </c>
       <c r="B51" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5733,10 +5748,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461757</v>
+        <v>461810</v>
       </c>
       <c r="R51" t="n">
-        <v>6788299</v>
+        <v>6788278</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,10 +5810,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566819</v>
+        <v>122566803</v>
       </c>
       <c r="B52" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5811,39 +5826,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461667</v>
+        <v>461598</v>
       </c>
       <c r="R52" t="n">
-        <v>6788182</v>
+        <v>6788148</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5902,10 +5912,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566802</v>
+        <v>122566859</v>
       </c>
       <c r="B53" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5918,21 +5928,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5942,10 +5952,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461811</v>
+        <v>461506</v>
       </c>
       <c r="R53" t="n">
-        <v>6788280</v>
+        <v>6788139</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6004,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566832</v>
+        <v>122566876</v>
       </c>
       <c r="B54" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6044,10 +6054,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461991</v>
+        <v>461695</v>
       </c>
       <c r="R54" t="n">
-        <v>6788292</v>
+        <v>6788224</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6106,10 +6116,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566814</v>
+        <v>122566885</v>
       </c>
       <c r="B55" t="n">
-        <v>78392</v>
+        <v>78657</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6122,21 +6132,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6146,10 +6156,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461814</v>
+        <v>461804</v>
       </c>
       <c r="R55" t="n">
-        <v>6788266</v>
+        <v>6788319</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6208,10 +6218,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566809</v>
+        <v>122566872</v>
       </c>
       <c r="B56" t="n">
-        <v>90853</v>
+        <v>78657</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6224,21 +6234,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6248,10 +6258,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461822</v>
+        <v>461659</v>
       </c>
       <c r="R56" t="n">
-        <v>6788353</v>
+        <v>6788194</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6310,10 +6320,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566830</v>
+        <v>122566879</v>
       </c>
       <c r="B57" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6350,10 +6360,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461991</v>
+        <v>461721</v>
       </c>
       <c r="R57" t="n">
-        <v>6788324</v>
+        <v>6788242</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6412,10 +6422,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566853</v>
+        <v>122566864</v>
       </c>
       <c r="B58" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6452,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461732</v>
+        <v>461619</v>
       </c>
       <c r="R58" t="n">
-        <v>6788166</v>
+        <v>6788144</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6514,10 +6524,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566841</v>
+        <v>122566842</v>
       </c>
       <c r="B59" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6554,10 +6564,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461809</v>
+        <v>461803</v>
       </c>
       <c r="R59" t="n">
-        <v>6788250</v>
+        <v>6788243</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6616,10 +6626,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566813</v>
+        <v>122566882</v>
       </c>
       <c r="B60" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6632,39 +6642,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461803</v>
+        <v>461757</v>
       </c>
       <c r="R60" t="n">
-        <v>6788243</v>
+        <v>6788299</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6697,11 +6702,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566817</v>
+        <v>122566887</v>
       </c>
       <c r="B61" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6740,25 +6740,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461788</v>
+        <v>461810</v>
       </c>
       <c r="R61" t="n">
-        <v>6788303</v>
+        <v>6788470</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6830,10 +6830,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566873</v>
+        <v>122566878</v>
       </c>
       <c r="B62" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461655</v>
+        <v>461712</v>
       </c>
       <c r="R62" t="n">
-        <v>6788205</v>
+        <v>6788236</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566852</v>
+        <v>122566851</v>
       </c>
       <c r="B63" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461741</v>
+        <v>461758</v>
       </c>
       <c r="R63" t="n">
-        <v>6788170</v>
+        <v>6788174</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566887</v>
+        <v>122566886</v>
       </c>
       <c r="B64" t="n">
-        <v>5173</v>
+        <v>78657</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7046,25 +7046,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7077,7 +7077,7 @@
         <v>461810</v>
       </c>
       <c r="R64" t="n">
-        <v>6788470</v>
+        <v>6788325</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566888</v>
+        <v>122566853</v>
       </c>
       <c r="B65" t="n">
-        <v>5173</v>
+        <v>78657</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7148,25 +7148,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461791</v>
+        <v>461732</v>
       </c>
       <c r="R65" t="n">
-        <v>6788187</v>
+        <v>6788166</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566811</v>
+        <v>122566849</v>
       </c>
       <c r="B66" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7254,39 +7254,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461936</v>
+        <v>461787</v>
       </c>
       <c r="R66" t="n">
-        <v>6788279</v>
+        <v>6788182</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7345,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566827</v>
+        <v>122566821</v>
       </c>
       <c r="B67" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7385,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461879</v>
+        <v>461699</v>
       </c>
       <c r="R67" t="n">
-        <v>6788396</v>
+        <v>6788443</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7447,10 +7442,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566881</v>
+        <v>122566845</v>
       </c>
       <c r="B68" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7487,10 +7482,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461742</v>
+        <v>461794</v>
       </c>
       <c r="R68" t="n">
-        <v>6788295</v>
+        <v>6788217</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7549,10 +7544,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566871</v>
+        <v>122566809</v>
       </c>
       <c r="B69" t="n">
-        <v>78656</v>
+        <v>90854</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7565,21 +7560,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7589,10 +7584,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461676</v>
+        <v>461822</v>
       </c>
       <c r="R69" t="n">
-        <v>6788174</v>
+        <v>6788353</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7651,10 +7646,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566851</v>
+        <v>122566820</v>
       </c>
       <c r="B70" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7691,10 +7686,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461758</v>
+        <v>461732</v>
       </c>
       <c r="R70" t="n">
-        <v>6788174</v>
+        <v>6788430</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7753,10 +7748,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566874</v>
+        <v>122566801</v>
       </c>
       <c r="B71" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7769,21 +7764,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7793,10 +7788,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461665</v>
+        <v>461945</v>
       </c>
       <c r="R71" t="n">
-        <v>6788207</v>
+        <v>6788255</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7855,10 +7850,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566862</v>
+        <v>122566805</v>
       </c>
       <c r="B72" t="n">
-        <v>78656</v>
+        <v>74758</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7871,21 +7866,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7895,10 +7890,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461562</v>
+        <v>461848</v>
       </c>
       <c r="R72" t="n">
-        <v>6788141</v>
+        <v>6788429</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7957,10 +7952,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566826</v>
+        <v>122566874</v>
       </c>
       <c r="B73" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7997,10 +7992,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461846</v>
+        <v>461665</v>
       </c>
       <c r="R73" t="n">
-        <v>6788492</v>
+        <v>6788207</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8059,10 +8054,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566876</v>
+        <v>122566833</v>
       </c>
       <c r="B74" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8099,10 +8094,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461695</v>
+        <v>461972</v>
       </c>
       <c r="R74" t="n">
-        <v>6788224</v>
+        <v>6788277</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8161,10 +8156,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566885</v>
+        <v>122566862</v>
       </c>
       <c r="B75" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8201,10 +8196,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461804</v>
+        <v>461562</v>
       </c>
       <c r="R75" t="n">
-        <v>6788319</v>
+        <v>6788141</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8263,10 +8258,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566878</v>
+        <v>122566865</v>
       </c>
       <c r="B76" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8303,10 +8298,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461712</v>
+        <v>461628</v>
       </c>
       <c r="R76" t="n">
-        <v>6788236</v>
+        <v>6788142</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8365,10 +8360,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566840</v>
+        <v>122566881</v>
       </c>
       <c r="B77" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8405,10 +8400,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461810</v>
+        <v>461742</v>
       </c>
       <c r="R77" t="n">
-        <v>6788278</v>
+        <v>6788295</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8467,10 +8462,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566850</v>
+        <v>122566888</v>
       </c>
       <c r="B78" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8479,25 +8474,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8507,10 +8502,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461771</v>
+        <v>461791</v>
       </c>
       <c r="R78" t="n">
-        <v>6788185</v>
+        <v>6788187</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8569,10 +8564,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566818</v>
+        <v>122566838</v>
       </c>
       <c r="B79" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8609,10 +8604,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461816</v>
+        <v>461878</v>
       </c>
       <c r="R79" t="n">
-        <v>6788330</v>
+        <v>6788313</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8671,10 +8666,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122566807</v>
+        <v>122566812</v>
       </c>
       <c r="B80" t="n">
-        <v>74757</v>
+        <v>57400</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8687,34 +8682,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461739</v>
+        <v>461803</v>
       </c>
       <c r="R80" t="n">
-        <v>6788280</v>
+        <v>6788243</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8773,10 +8776,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122566812</v>
+        <v>122488168</v>
       </c>
       <c r="B81" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8811,7 +8814,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8821,10 +8824,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461803</v>
+        <v>461923</v>
       </c>
       <c r="R81" t="n">
-        <v>6788243</v>
+        <v>6788245</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8851,12 +8854,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre gran med hackhål. Hörde spillkråkan i området.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8871,15 +8879,130 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>122489274</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>461895</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6788288</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -1511,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566850</v>
+        <v>122566819</v>
       </c>
       <c r="B10" t="n">
         <v>78657</v>
@@ -1545,16 +1545,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461771</v>
+        <v>461667</v>
       </c>
       <c r="R10" t="n">
-        <v>6788185</v>
+        <v>6788182</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566819</v>
+        <v>122566850</v>
       </c>
       <c r="B11" t="n">
         <v>78657</v>
@@ -1647,21 +1652,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461667</v>
+        <v>461771</v>
       </c>
       <c r="R11" t="n">
-        <v>6788182</v>
+        <v>6788185</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566855</v>
+        <v>122566811</v>
       </c>
       <c r="B15" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,34 +2042,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461704</v>
+        <v>461936</v>
       </c>
       <c r="R15" t="n">
-        <v>6788171</v>
+        <v>6788279</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,7 +2133,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566877</v>
+        <v>122566855</v>
       </c>
       <c r="B16" t="n">
         <v>78657</v>
@@ -2168,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461706</v>
+        <v>461704</v>
       </c>
       <c r="R16" t="n">
-        <v>6788223</v>
+        <v>6788171</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,7 +2235,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566852</v>
+        <v>122566877</v>
       </c>
       <c r="B17" t="n">
         <v>78657</v>
@@ -2270,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461741</v>
+        <v>461706</v>
       </c>
       <c r="R17" t="n">
-        <v>6788170</v>
+        <v>6788223</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566811</v>
+        <v>122566852</v>
       </c>
       <c r="B18" t="n">
-        <v>57400</v>
+        <v>78657</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,39 +2353,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461936</v>
+        <v>461741</v>
       </c>
       <c r="R18" t="n">
-        <v>6788279</v>
+        <v>6788170</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2954,7 +2954,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566817</v>
+        <v>122566846</v>
       </c>
       <c r="B24" t="n">
         <v>78657</v>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461788</v>
+        <v>461791</v>
       </c>
       <c r="R24" t="n">
-        <v>6788303</v>
+        <v>6788209</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,7 +3056,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566873</v>
+        <v>122566817</v>
       </c>
       <c r="B25" t="n">
         <v>78657</v>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461655</v>
+        <v>461788</v>
       </c>
       <c r="R25" t="n">
-        <v>6788205</v>
+        <v>6788303</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3158,7 +3158,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566843</v>
+        <v>122566873</v>
       </c>
       <c r="B26" t="n">
         <v>78657</v>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461811</v>
+        <v>461655</v>
       </c>
       <c r="R26" t="n">
-        <v>6788237</v>
+        <v>6788205</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,7 +3260,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566869</v>
+        <v>122566843</v>
       </c>
       <c r="B27" t="n">
         <v>78657</v>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461678</v>
+        <v>461811</v>
       </c>
       <c r="R27" t="n">
-        <v>6788157</v>
+        <v>6788237</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566846</v>
+        <v>122566869</v>
       </c>
       <c r="B28" t="n">
         <v>78657</v>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461791</v>
+        <v>461678</v>
       </c>
       <c r="R28" t="n">
-        <v>6788209</v>
+        <v>6788157</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566851</v>
+        <v>122566809</v>
       </c>
       <c r="B63" t="n">
-        <v>78657</v>
+        <v>90854</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6948,21 +6948,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461758</v>
+        <v>461822</v>
       </c>
       <c r="R63" t="n">
-        <v>6788174</v>
+        <v>6788353</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,7 +7034,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566886</v>
+        <v>122566851</v>
       </c>
       <c r="B64" t="n">
         <v>78657</v>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461810</v>
+        <v>461758</v>
       </c>
       <c r="R64" t="n">
-        <v>6788325</v>
+        <v>6788174</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566853</v>
+        <v>122566886</v>
       </c>
       <c r="B65" t="n">
         <v>78657</v>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461732</v>
+        <v>461810</v>
       </c>
       <c r="R65" t="n">
-        <v>6788166</v>
+        <v>6788325</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566849</v>
+        <v>122566853</v>
       </c>
       <c r="B66" t="n">
         <v>78657</v>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461787</v>
+        <v>461732</v>
       </c>
       <c r="R66" t="n">
-        <v>6788182</v>
+        <v>6788166</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,7 +7340,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566821</v>
+        <v>122566849</v>
       </c>
       <c r="B67" t="n">
         <v>78657</v>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461699</v>
+        <v>461787</v>
       </c>
       <c r="R67" t="n">
-        <v>6788443</v>
+        <v>6788182</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,7 +7442,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566845</v>
+        <v>122566821</v>
       </c>
       <c r="B68" t="n">
         <v>78657</v>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461794</v>
+        <v>461699</v>
       </c>
       <c r="R68" t="n">
-        <v>6788217</v>
+        <v>6788443</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7544,10 +7544,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566809</v>
+        <v>122566845</v>
       </c>
       <c r="B69" t="n">
-        <v>90854</v>
+        <v>78657</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7560,21 +7560,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461822</v>
+        <v>461794</v>
       </c>
       <c r="R69" t="n">
-        <v>6788353</v>
+        <v>6788217</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566888</v>
+        <v>122566838</v>
       </c>
       <c r="B78" t="n">
-        <v>5173</v>
+        <v>78657</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8474,25 +8474,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461791</v>
+        <v>461878</v>
       </c>
       <c r="R78" t="n">
-        <v>6788187</v>
+        <v>6788313</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8564,10 +8564,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566838</v>
+        <v>122566888</v>
       </c>
       <c r="B79" t="n">
-        <v>78657</v>
+        <v>5173</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8576,25 +8576,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461878</v>
+        <v>461791</v>
       </c>
       <c r="R79" t="n">
-        <v>6788313</v>
+        <v>6788187</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489220</v>
+        <v>122489147</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>90857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R2" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122488593</v>
+        <v>122489220</v>
       </c>
       <c r="B3" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R3" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489147</v>
+        <v>122488593</v>
       </c>
       <c r="B4" t="n">
-        <v>90854</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566835</v>
+        <v>122566874</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461929</v>
+        <v>461665</v>
       </c>
       <c r="R5" t="n">
-        <v>6788278</v>
+        <v>6788207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566827</v>
+        <v>122566807</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>74761</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461879</v>
+        <v>461739</v>
       </c>
       <c r="R6" t="n">
-        <v>6788396</v>
+        <v>6788280</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566829</v>
+        <v>122566861</v>
       </c>
       <c r="B7" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461952</v>
+        <v>461537</v>
       </c>
       <c r="R7" t="n">
-        <v>6788327</v>
+        <v>6788149</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566813</v>
+        <v>122566830</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,39 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461803</v>
+        <v>461991</v>
       </c>
       <c r="R8" t="n">
-        <v>6788243</v>
+        <v>6788324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566826</v>
+        <v>122566854</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461846</v>
+        <v>461714</v>
       </c>
       <c r="R9" t="n">
-        <v>6788492</v>
+        <v>6788188</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566819</v>
+        <v>122566801</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,39 +1517,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461667</v>
+        <v>461945</v>
       </c>
       <c r="R10" t="n">
-        <v>6788182</v>
+        <v>6788255</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566850</v>
+        <v>122566877</v>
       </c>
       <c r="B11" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461771</v>
+        <v>461706</v>
       </c>
       <c r="R11" t="n">
-        <v>6788185</v>
+        <v>6788223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566832</v>
+        <v>122566851</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461991</v>
+        <v>461758</v>
       </c>
       <c r="R12" t="n">
-        <v>6788292</v>
+        <v>6788174</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566828</v>
+        <v>122566885</v>
       </c>
       <c r="B13" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461923</v>
+        <v>461804</v>
       </c>
       <c r="R13" t="n">
-        <v>6788324</v>
+        <v>6788319</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566880</v>
+        <v>122566819</v>
       </c>
       <c r="B14" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1958,16 +1943,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461737</v>
+        <v>461667</v>
       </c>
       <c r="R14" t="n">
-        <v>6788251</v>
+        <v>6788182</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566811</v>
+        <v>122566878</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,39 +2032,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461936</v>
+        <v>461712</v>
       </c>
       <c r="R15" t="n">
-        <v>6788279</v>
+        <v>6788236</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566855</v>
+        <v>122566842</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461704</v>
+        <v>461803</v>
       </c>
       <c r="R16" t="n">
-        <v>6788171</v>
+        <v>6788243</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566877</v>
+        <v>122566802</v>
       </c>
       <c r="B17" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2275,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461706</v>
+        <v>461811</v>
       </c>
       <c r="R17" t="n">
-        <v>6788223</v>
+        <v>6788280</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566852</v>
+        <v>122566808</v>
       </c>
       <c r="B18" t="n">
-        <v>78657</v>
+        <v>90837</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461741</v>
+        <v>461872</v>
       </c>
       <c r="R18" t="n">
-        <v>6788170</v>
+        <v>6788413</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566834</v>
+        <v>122566817</v>
       </c>
       <c r="B19" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2479,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461929</v>
+        <v>461788</v>
       </c>
       <c r="R19" t="n">
-        <v>6788262</v>
+        <v>6788303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566804</v>
+        <v>122566827</v>
       </c>
       <c r="B20" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,21 +2542,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461614</v>
+        <v>461879</v>
       </c>
       <c r="R20" t="n">
-        <v>6788152</v>
+        <v>6788396</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566814</v>
+        <v>122566852</v>
       </c>
       <c r="B21" t="n">
-        <v>78393</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461814</v>
+        <v>461741</v>
       </c>
       <c r="R21" t="n">
-        <v>6788266</v>
+        <v>6788170</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2745,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566807</v>
+        <v>122566869</v>
       </c>
       <c r="B22" t="n">
-        <v>74758</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461739</v>
+        <v>461678</v>
       </c>
       <c r="R22" t="n">
-        <v>6788280</v>
+        <v>6788157</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2847,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566816</v>
+        <v>122566824</v>
       </c>
       <c r="B23" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,39 +2848,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461930</v>
+        <v>461810</v>
       </c>
       <c r="R23" t="n">
-        <v>6788270</v>
+        <v>6788470</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2954,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566846</v>
+        <v>122566823</v>
       </c>
       <c r="B24" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2994,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461791</v>
+        <v>461778</v>
       </c>
       <c r="R24" t="n">
-        <v>6788209</v>
+        <v>6788485</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566817</v>
+        <v>122566822</v>
       </c>
       <c r="B25" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3096,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461788</v>
+        <v>461763</v>
       </c>
       <c r="R25" t="n">
-        <v>6788303</v>
+        <v>6788475</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3158,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566873</v>
+        <v>122566859</v>
       </c>
       <c r="B26" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3198,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461655</v>
+        <v>461506</v>
       </c>
       <c r="R26" t="n">
-        <v>6788205</v>
+        <v>6788139</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566843</v>
+        <v>122566826</v>
       </c>
       <c r="B27" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3300,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461811</v>
+        <v>461846</v>
       </c>
       <c r="R27" t="n">
-        <v>6788237</v>
+        <v>6788492</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3362,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566869</v>
+        <v>122566882</v>
       </c>
       <c r="B28" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3402,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461678</v>
+        <v>461757</v>
       </c>
       <c r="R28" t="n">
-        <v>6788157</v>
+        <v>6788299</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3464,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566802</v>
+        <v>122566832</v>
       </c>
       <c r="B29" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3480,21 +3460,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3484,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461811</v>
+        <v>461991</v>
       </c>
       <c r="R29" t="n">
-        <v>6788280</v>
+        <v>6788292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3566,10 +3546,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566822</v>
+        <v>122566875</v>
       </c>
       <c r="B30" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3606,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461763</v>
+        <v>461669</v>
       </c>
       <c r="R30" t="n">
-        <v>6788475</v>
+        <v>6788203</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3668,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566839</v>
+        <v>122566833</v>
       </c>
       <c r="B31" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3708,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461829</v>
+        <v>461972</v>
       </c>
       <c r="R31" t="n">
-        <v>6788287</v>
+        <v>6788277</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3770,10 +3750,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566844</v>
+        <v>122566879</v>
       </c>
       <c r="B32" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3810,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461816</v>
+        <v>461721</v>
       </c>
       <c r="R32" t="n">
-        <v>6788215</v>
+        <v>6788242</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3872,10 +3852,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566875</v>
+        <v>122566821</v>
       </c>
       <c r="B33" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3912,10 +3892,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461669</v>
+        <v>461699</v>
       </c>
       <c r="R33" t="n">
-        <v>6788203</v>
+        <v>6788443</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3974,10 +3954,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566824</v>
+        <v>122566840</v>
       </c>
       <c r="B34" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4017,7 +3997,7 @@
         <v>461810</v>
       </c>
       <c r="R34" t="n">
-        <v>6788470</v>
+        <v>6788278</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,10 +4056,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566861</v>
+        <v>122566855</v>
       </c>
       <c r="B35" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4116,10 +4096,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461537</v>
+        <v>461704</v>
       </c>
       <c r="R35" t="n">
-        <v>6788149</v>
+        <v>6788171</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4178,10 +4158,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566863</v>
+        <v>122566883</v>
       </c>
       <c r="B36" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4218,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461589</v>
+        <v>461777</v>
       </c>
       <c r="R36" t="n">
-        <v>6788148</v>
+        <v>6788298</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4280,10 +4260,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566823</v>
+        <v>122566813</v>
       </c>
       <c r="B37" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4296,34 +4276,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461778</v>
+        <v>461803</v>
       </c>
       <c r="R37" t="n">
-        <v>6788485</v>
+        <v>6788243</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,6 +4341,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4382,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566831</v>
+        <v>122566847</v>
       </c>
       <c r="B38" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4422,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462004</v>
+        <v>461789</v>
       </c>
       <c r="R38" t="n">
-        <v>6788320</v>
+        <v>6788194</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4484,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566830</v>
+        <v>122566865</v>
       </c>
       <c r="B39" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4524,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461991</v>
+        <v>461628</v>
       </c>
       <c r="R39" t="n">
-        <v>6788324</v>
+        <v>6788142</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4586,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566808</v>
+        <v>122566876</v>
       </c>
       <c r="B40" t="n">
-        <v>90834</v>
+        <v>78660</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4602,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4626,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461872</v>
+        <v>461695</v>
       </c>
       <c r="R40" t="n">
-        <v>6788413</v>
+        <v>6788224</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4688,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566854</v>
+        <v>122566871</v>
       </c>
       <c r="B41" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4728,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461714</v>
+        <v>461676</v>
       </c>
       <c r="R41" t="n">
-        <v>6788188</v>
+        <v>6788174</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4790,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566871</v>
+        <v>122566838</v>
       </c>
       <c r="B42" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4830,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461676</v>
+        <v>461878</v>
       </c>
       <c r="R42" t="n">
-        <v>6788174</v>
+        <v>6788313</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4892,10 +4882,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566883</v>
+        <v>122566816</v>
       </c>
       <c r="B43" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4908,34 +4898,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461777</v>
+        <v>461930</v>
       </c>
       <c r="R43" t="n">
-        <v>6788298</v>
+        <v>6788270</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4994,10 +4989,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566848</v>
+        <v>122566803</v>
       </c>
       <c r="B44" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5010,21 +5005,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5034,10 +5029,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461791</v>
+        <v>461598</v>
       </c>
       <c r="R44" t="n">
-        <v>6788187</v>
+        <v>6788148</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5096,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566841</v>
+        <v>122566864</v>
       </c>
       <c r="B45" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5136,10 +5131,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461809</v>
+        <v>461619</v>
       </c>
       <c r="R45" t="n">
-        <v>6788250</v>
+        <v>6788144</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5198,10 +5193,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566884</v>
+        <v>122566887</v>
       </c>
       <c r="B46" t="n">
-        <v>78657</v>
+        <v>5173</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5210,25 +5205,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5238,10 +5233,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461793</v>
+        <v>461810</v>
       </c>
       <c r="R46" t="n">
-        <v>6788303</v>
+        <v>6788470</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5300,10 +5295,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566847</v>
+        <v>122566873</v>
       </c>
       <c r="B47" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5340,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461789</v>
+        <v>461655</v>
       </c>
       <c r="R47" t="n">
-        <v>6788194</v>
+        <v>6788205</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5402,10 +5397,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566837</v>
+        <v>122566831</v>
       </c>
       <c r="B48" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5442,10 +5437,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461917</v>
+        <v>462004</v>
       </c>
       <c r="R48" t="n">
-        <v>6788292</v>
+        <v>6788320</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5504,10 +5499,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566818</v>
+        <v>122566828</v>
       </c>
       <c r="B49" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5544,10 +5539,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461816</v>
+        <v>461923</v>
       </c>
       <c r="R49" t="n">
-        <v>6788330</v>
+        <v>6788324</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5606,10 +5601,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566825</v>
+        <v>122566835</v>
       </c>
       <c r="B50" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5646,10 +5641,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461843</v>
+        <v>461929</v>
       </c>
       <c r="R50" t="n">
-        <v>6788468</v>
+        <v>6788278</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5708,10 +5703,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566840</v>
+        <v>122566853</v>
       </c>
       <c r="B51" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5748,10 +5743,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461810</v>
+        <v>461732</v>
       </c>
       <c r="R51" t="n">
-        <v>6788278</v>
+        <v>6788166</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5810,10 +5805,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566803</v>
+        <v>122566880</v>
       </c>
       <c r="B52" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5826,21 +5821,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5850,10 +5845,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461598</v>
+        <v>461737</v>
       </c>
       <c r="R52" t="n">
-        <v>6788148</v>
+        <v>6788251</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5912,10 +5907,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566859</v>
+        <v>122566886</v>
       </c>
       <c r="B53" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5952,10 +5947,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461506</v>
+        <v>461810</v>
       </c>
       <c r="R53" t="n">
-        <v>6788139</v>
+        <v>6788325</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6014,10 +6009,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566876</v>
+        <v>122566881</v>
       </c>
       <c r="B54" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6054,10 +6049,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461695</v>
+        <v>461742</v>
       </c>
       <c r="R54" t="n">
-        <v>6788224</v>
+        <v>6788295</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6116,10 +6111,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566885</v>
+        <v>122566829</v>
       </c>
       <c r="B55" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6156,10 +6151,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461804</v>
+        <v>461952</v>
       </c>
       <c r="R55" t="n">
-        <v>6788319</v>
+        <v>6788327</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6218,10 +6213,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566872</v>
+        <v>122566862</v>
       </c>
       <c r="B56" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461659</v>
+        <v>461562</v>
       </c>
       <c r="R56" t="n">
-        <v>6788194</v>
+        <v>6788141</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6320,10 +6315,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566879</v>
+        <v>122566804</v>
       </c>
       <c r="B57" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6336,21 +6331,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6360,10 +6355,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461721</v>
+        <v>461614</v>
       </c>
       <c r="R57" t="n">
-        <v>6788242</v>
+        <v>6788152</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6422,10 +6417,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566864</v>
+        <v>122566863</v>
       </c>
       <c r="B58" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6462,10 +6457,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461619</v>
+        <v>461589</v>
       </c>
       <c r="R58" t="n">
-        <v>6788144</v>
+        <v>6788148</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,10 +6519,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566842</v>
+        <v>122566872</v>
       </c>
       <c r="B59" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6564,10 +6559,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461803</v>
+        <v>461659</v>
       </c>
       <c r="R59" t="n">
-        <v>6788243</v>
+        <v>6788194</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6626,10 +6621,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566882</v>
+        <v>122566818</v>
       </c>
       <c r="B60" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6666,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461757</v>
+        <v>461816</v>
       </c>
       <c r="R60" t="n">
-        <v>6788299</v>
+        <v>6788330</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6728,10 +6723,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566887</v>
+        <v>122566849</v>
       </c>
       <c r="B61" t="n">
-        <v>5173</v>
+        <v>78660</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6740,25 +6735,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6768,10 +6763,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461810</v>
+        <v>461787</v>
       </c>
       <c r="R61" t="n">
-        <v>6788470</v>
+        <v>6788182</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6830,10 +6825,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566878</v>
+        <v>122566846</v>
       </c>
       <c r="B62" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6870,10 +6865,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461712</v>
+        <v>461791</v>
       </c>
       <c r="R62" t="n">
-        <v>6788236</v>
+        <v>6788209</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,10 +6927,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566809</v>
+        <v>122566825</v>
       </c>
       <c r="B63" t="n">
-        <v>90854</v>
+        <v>78660</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6948,21 +6943,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6972,10 +6967,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461822</v>
+        <v>461843</v>
       </c>
       <c r="R63" t="n">
-        <v>6788353</v>
+        <v>6788468</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566851</v>
+        <v>122566841</v>
       </c>
       <c r="B64" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7074,10 +7069,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461758</v>
+        <v>461809</v>
       </c>
       <c r="R64" t="n">
-        <v>6788174</v>
+        <v>6788250</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,10 +7131,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566886</v>
+        <v>122566888</v>
       </c>
       <c r="B65" t="n">
-        <v>78657</v>
+        <v>5173</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7148,25 +7143,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7176,10 +7171,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461810</v>
+        <v>461791</v>
       </c>
       <c r="R65" t="n">
-        <v>6788325</v>
+        <v>6788187</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7233,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566853</v>
+        <v>122566805</v>
       </c>
       <c r="B66" t="n">
-        <v>78657</v>
+        <v>74761</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7254,21 +7249,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7278,10 +7273,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461732</v>
+        <v>461848</v>
       </c>
       <c r="R66" t="n">
-        <v>6788166</v>
+        <v>6788429</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,10 +7335,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566849</v>
+        <v>122566850</v>
       </c>
       <c r="B67" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7380,10 +7375,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461787</v>
+        <v>461771</v>
       </c>
       <c r="R67" t="n">
-        <v>6788182</v>
+        <v>6788185</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,10 +7437,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566821</v>
+        <v>122566844</v>
       </c>
       <c r="B68" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7482,10 +7477,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461699</v>
+        <v>461816</v>
       </c>
       <c r="R68" t="n">
-        <v>6788443</v>
+        <v>6788215</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7547,7 +7542,7 @@
         <v>122566845</v>
       </c>
       <c r="B69" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7646,10 +7641,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566820</v>
+        <v>122566811</v>
       </c>
       <c r="B70" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7662,34 +7657,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461732</v>
+        <v>461936</v>
       </c>
       <c r="R70" t="n">
-        <v>6788430</v>
+        <v>6788279</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7748,10 +7748,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566801</v>
+        <v>122566809</v>
       </c>
       <c r="B71" t="n">
-        <v>79275</v>
+        <v>90857</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7764,21 +7764,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461945</v>
+        <v>461822</v>
       </c>
       <c r="R71" t="n">
-        <v>6788255</v>
+        <v>6788353</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566805</v>
+        <v>122566834</v>
       </c>
       <c r="B72" t="n">
-        <v>74758</v>
+        <v>78660</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461848</v>
+        <v>461929</v>
       </c>
       <c r="R72" t="n">
-        <v>6788429</v>
+        <v>6788262</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7952,10 +7952,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566874</v>
+        <v>122566814</v>
       </c>
       <c r="B73" t="n">
-        <v>78657</v>
+        <v>78396</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7968,21 +7968,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461665</v>
+        <v>461814</v>
       </c>
       <c r="R73" t="n">
-        <v>6788207</v>
+        <v>6788266</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8054,10 +8054,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566833</v>
+        <v>122566843</v>
       </c>
       <c r="B74" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461972</v>
+        <v>461811</v>
       </c>
       <c r="R74" t="n">
-        <v>6788277</v>
+        <v>6788237</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566862</v>
+        <v>122566837</v>
       </c>
       <c r="B75" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461562</v>
+        <v>461917</v>
       </c>
       <c r="R75" t="n">
-        <v>6788141</v>
+        <v>6788292</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8258,10 +8258,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566865</v>
+        <v>122566839</v>
       </c>
       <c r="B76" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461628</v>
+        <v>461829</v>
       </c>
       <c r="R76" t="n">
-        <v>6788142</v>
+        <v>6788287</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8360,10 +8360,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566881</v>
+        <v>122566848</v>
       </c>
       <c r="B77" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461742</v>
+        <v>461791</v>
       </c>
       <c r="R77" t="n">
-        <v>6788295</v>
+        <v>6788187</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566838</v>
+        <v>122566884</v>
       </c>
       <c r="B78" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461878</v>
+        <v>461793</v>
       </c>
       <c r="R78" t="n">
-        <v>6788313</v>
+        <v>6788303</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8564,10 +8564,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566888</v>
+        <v>122566820</v>
       </c>
       <c r="B79" t="n">
-        <v>5173</v>
+        <v>78660</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8576,25 +8576,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461791</v>
+        <v>461732</v>
       </c>
       <c r="R79" t="n">
-        <v>6788187</v>
+        <v>6788430</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489147</v>
+        <v>122489220</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R2" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122489220</v>
+        <v>122488593</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R3" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122488593</v>
+        <v>122489147</v>
       </c>
       <c r="B4" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566874</v>
+        <v>122566837</v>
       </c>
       <c r="B5" t="n">
         <v>78660</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461665</v>
+        <v>461917</v>
       </c>
       <c r="R5" t="n">
-        <v>6788207</v>
+        <v>6788292</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566807</v>
+        <v>122566814</v>
       </c>
       <c r="B6" t="n">
-        <v>74761</v>
+        <v>78396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461739</v>
+        <v>461814</v>
       </c>
       <c r="R6" t="n">
-        <v>6788280</v>
+        <v>6788266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566861</v>
+        <v>122566822</v>
       </c>
       <c r="B7" t="n">
         <v>78660</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461537</v>
+        <v>461763</v>
       </c>
       <c r="R7" t="n">
-        <v>6788149</v>
+        <v>6788475</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566830</v>
+        <v>122566862</v>
       </c>
       <c r="B8" t="n">
         <v>78660</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461991</v>
+        <v>461562</v>
       </c>
       <c r="R8" t="n">
-        <v>6788324</v>
+        <v>6788141</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566854</v>
+        <v>122566880</v>
       </c>
       <c r="B9" t="n">
         <v>78660</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461714</v>
+        <v>461737</v>
       </c>
       <c r="R9" t="n">
-        <v>6788188</v>
+        <v>6788251</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566801</v>
+        <v>122566816</v>
       </c>
       <c r="B10" t="n">
-        <v>79278</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,34 +1517,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461945</v>
+        <v>461930</v>
       </c>
       <c r="R10" t="n">
-        <v>6788255</v>
+        <v>6788270</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566877</v>
+        <v>122566835</v>
       </c>
       <c r="B11" t="n">
         <v>78660</v>
@@ -1643,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461706</v>
+        <v>461929</v>
       </c>
       <c r="R11" t="n">
-        <v>6788223</v>
+        <v>6788278</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566851</v>
+        <v>122566886</v>
       </c>
       <c r="B12" t="n">
         <v>78660</v>
@@ -1745,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461758</v>
+        <v>461810</v>
       </c>
       <c r="R12" t="n">
-        <v>6788174</v>
+        <v>6788325</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566885</v>
+        <v>122566859</v>
       </c>
       <c r="B13" t="n">
         <v>78660</v>
@@ -1847,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461804</v>
+        <v>461506</v>
       </c>
       <c r="R13" t="n">
-        <v>6788319</v>
+        <v>6788139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566819</v>
+        <v>122566865</v>
       </c>
       <c r="B14" t="n">
         <v>78660</v>
@@ -1943,21 +1948,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461667</v>
+        <v>461628</v>
       </c>
       <c r="R14" t="n">
-        <v>6788182</v>
+        <v>6788142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566878</v>
+        <v>122566830</v>
       </c>
       <c r="B15" t="n">
         <v>78660</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461712</v>
+        <v>461991</v>
       </c>
       <c r="R15" t="n">
-        <v>6788236</v>
+        <v>6788324</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566842</v>
+        <v>122566823</v>
       </c>
       <c r="B16" t="n">
         <v>78660</v>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461803</v>
+        <v>461778</v>
       </c>
       <c r="R16" t="n">
-        <v>6788243</v>
+        <v>6788485</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566802</v>
+        <v>122566851</v>
       </c>
       <c r="B17" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461811</v>
+        <v>461758</v>
       </c>
       <c r="R17" t="n">
-        <v>6788280</v>
+        <v>6788174</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566808</v>
+        <v>122566873</v>
       </c>
       <c r="B18" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461872</v>
+        <v>461655</v>
       </c>
       <c r="R18" t="n">
-        <v>6788413</v>
+        <v>6788205</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566817</v>
+        <v>122566831</v>
       </c>
       <c r="B19" t="n">
         <v>78660</v>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461788</v>
+        <v>462004</v>
       </c>
       <c r="R19" t="n">
-        <v>6788303</v>
+        <v>6788320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566827</v>
+        <v>122566884</v>
       </c>
       <c r="B20" t="n">
         <v>78660</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461879</v>
+        <v>461793</v>
       </c>
       <c r="R20" t="n">
-        <v>6788396</v>
+        <v>6788303</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566852</v>
+        <v>122566876</v>
       </c>
       <c r="B21" t="n">
         <v>78660</v>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461741</v>
+        <v>461695</v>
       </c>
       <c r="R21" t="n">
-        <v>6788170</v>
+        <v>6788224</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566869</v>
+        <v>122566864</v>
       </c>
       <c r="B22" t="n">
         <v>78660</v>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461678</v>
+        <v>461619</v>
       </c>
       <c r="R22" t="n">
-        <v>6788157</v>
+        <v>6788144</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566824</v>
+        <v>122566839</v>
       </c>
       <c r="B23" t="n">
         <v>78660</v>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461810</v>
+        <v>461829</v>
       </c>
       <c r="R23" t="n">
-        <v>6788470</v>
+        <v>6788287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566823</v>
+        <v>122566819</v>
       </c>
       <c r="B24" t="n">
         <v>78660</v>
@@ -2968,16 +2968,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461778</v>
+        <v>461667</v>
       </c>
       <c r="R24" t="n">
-        <v>6788485</v>
+        <v>6788182</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,7 +3041,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566822</v>
+        <v>122566849</v>
       </c>
       <c r="B25" t="n">
         <v>78660</v>
@@ -3076,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461763</v>
+        <v>461787</v>
       </c>
       <c r="R25" t="n">
-        <v>6788475</v>
+        <v>6788182</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,7 +3143,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566859</v>
+        <v>122566828</v>
       </c>
       <c r="B26" t="n">
         <v>78660</v>
@@ -3178,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461506</v>
+        <v>461923</v>
       </c>
       <c r="R26" t="n">
-        <v>6788139</v>
+        <v>6788324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,7 +3245,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566826</v>
+        <v>122566817</v>
       </c>
       <c r="B27" t="n">
         <v>78660</v>
@@ -3280,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461846</v>
+        <v>461788</v>
       </c>
       <c r="R27" t="n">
-        <v>6788492</v>
+        <v>6788303</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,7 +3347,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566882</v>
+        <v>122566863</v>
       </c>
       <c r="B28" t="n">
         <v>78660</v>
@@ -3382,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461757</v>
+        <v>461589</v>
       </c>
       <c r="R28" t="n">
-        <v>6788299</v>
+        <v>6788148</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,7 +3449,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566832</v>
+        <v>122566833</v>
       </c>
       <c r="B29" t="n">
         <v>78660</v>
@@ -3484,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461991</v>
+        <v>461972</v>
       </c>
       <c r="R29" t="n">
-        <v>6788292</v>
+        <v>6788277</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3546,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566875</v>
+        <v>122566802</v>
       </c>
       <c r="B30" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3562,21 +3567,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461669</v>
+        <v>461811</v>
       </c>
       <c r="R30" t="n">
-        <v>6788203</v>
+        <v>6788280</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,7 +3653,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566833</v>
+        <v>122566881</v>
       </c>
       <c r="B31" t="n">
         <v>78660</v>
@@ -3688,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461972</v>
+        <v>461742</v>
       </c>
       <c r="R31" t="n">
-        <v>6788277</v>
+        <v>6788295</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,7 +3755,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566879</v>
+        <v>122566820</v>
       </c>
       <c r="B32" t="n">
         <v>78660</v>
@@ -3790,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461721</v>
+        <v>461732</v>
       </c>
       <c r="R32" t="n">
-        <v>6788242</v>
+        <v>6788430</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566821</v>
+        <v>122566809</v>
       </c>
       <c r="B33" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3868,21 +3873,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3892,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461699</v>
+        <v>461822</v>
       </c>
       <c r="R33" t="n">
-        <v>6788443</v>
+        <v>6788353</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3954,7 +3959,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566840</v>
+        <v>122566872</v>
       </c>
       <c r="B34" t="n">
         <v>78660</v>
@@ -3994,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461810</v>
+        <v>461659</v>
       </c>
       <c r="R34" t="n">
-        <v>6788278</v>
+        <v>6788194</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,7 +4061,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566855</v>
+        <v>122566852</v>
       </c>
       <c r="B35" t="n">
         <v>78660</v>
@@ -4096,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461704</v>
+        <v>461741</v>
       </c>
       <c r="R35" t="n">
-        <v>6788171</v>
+        <v>6788170</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4158,7 +4163,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566883</v>
+        <v>122566878</v>
       </c>
       <c r="B36" t="n">
         <v>78660</v>
@@ -4198,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461777</v>
+        <v>461712</v>
       </c>
       <c r="R36" t="n">
-        <v>6788298</v>
+        <v>6788236</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4260,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566813</v>
+        <v>122566888</v>
       </c>
       <c r="B37" t="n">
-        <v>57384</v>
+        <v>5173</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4272,43 +4277,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461803</v>
+        <v>461791</v>
       </c>
       <c r="R37" t="n">
-        <v>6788243</v>
+        <v>6788187</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4341,11 +4341,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4372,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566847</v>
+        <v>122566805</v>
       </c>
       <c r="B38" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4388,21 +4383,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461789</v>
+        <v>461848</v>
       </c>
       <c r="R38" t="n">
-        <v>6788194</v>
+        <v>6788429</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,7 +4469,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566865</v>
+        <v>122566850</v>
       </c>
       <c r="B39" t="n">
         <v>78660</v>
@@ -4514,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461628</v>
+        <v>461771</v>
       </c>
       <c r="R39" t="n">
-        <v>6788142</v>
+        <v>6788185</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566876</v>
+        <v>122566804</v>
       </c>
       <c r="B40" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4592,21 +4587,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461695</v>
+        <v>461614</v>
       </c>
       <c r="R40" t="n">
-        <v>6788224</v>
+        <v>6788152</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,7 +4673,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566871</v>
+        <v>122566883</v>
       </c>
       <c r="B41" t="n">
         <v>78660</v>
@@ -4718,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461676</v>
+        <v>461777</v>
       </c>
       <c r="R41" t="n">
-        <v>6788174</v>
+        <v>6788298</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,7 +4775,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566838</v>
+        <v>122566882</v>
       </c>
       <c r="B42" t="n">
         <v>78660</v>
@@ -4820,10 +4815,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461878</v>
+        <v>461757</v>
       </c>
       <c r="R42" t="n">
-        <v>6788313</v>
+        <v>6788299</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,10 +4877,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566816</v>
+        <v>122566869</v>
       </c>
       <c r="B43" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4898,39 +4893,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461930</v>
+        <v>461678</v>
       </c>
       <c r="R43" t="n">
-        <v>6788270</v>
+        <v>6788157</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566803</v>
+        <v>122566842</v>
       </c>
       <c r="B44" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5005,21 +4995,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5029,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461598</v>
+        <v>461803</v>
       </c>
       <c r="R44" t="n">
-        <v>6788148</v>
+        <v>6788243</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,7 +5081,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566864</v>
+        <v>122566885</v>
       </c>
       <c r="B45" t="n">
         <v>78660</v>
@@ -5131,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461619</v>
+        <v>461804</v>
       </c>
       <c r="R45" t="n">
-        <v>6788144</v>
+        <v>6788319</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5193,10 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566887</v>
+        <v>122566825</v>
       </c>
       <c r="B46" t="n">
-        <v>5173</v>
+        <v>78660</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5205,25 +5195,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5233,10 +5223,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461810</v>
+        <v>461843</v>
       </c>
       <c r="R46" t="n">
-        <v>6788470</v>
+        <v>6788468</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5295,7 +5285,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566873</v>
+        <v>122566840</v>
       </c>
       <c r="B47" t="n">
         <v>78660</v>
@@ -5335,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461655</v>
+        <v>461810</v>
       </c>
       <c r="R47" t="n">
-        <v>6788205</v>
+        <v>6788278</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5397,7 +5387,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566831</v>
+        <v>122566843</v>
       </c>
       <c r="B48" t="n">
         <v>78660</v>
@@ -5437,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462004</v>
+        <v>461811</v>
       </c>
       <c r="R48" t="n">
-        <v>6788320</v>
+        <v>6788237</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5499,7 +5489,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566828</v>
+        <v>122566832</v>
       </c>
       <c r="B49" t="n">
         <v>78660</v>
@@ -5539,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461923</v>
+        <v>461991</v>
       </c>
       <c r="R49" t="n">
-        <v>6788324</v>
+        <v>6788292</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5601,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566835</v>
+        <v>122566811</v>
       </c>
       <c r="B50" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5617,34 +5607,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461929</v>
+        <v>461936</v>
       </c>
       <c r="R50" t="n">
-        <v>6788278</v>
+        <v>6788279</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5703,7 +5698,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566853</v>
+        <v>122566854</v>
       </c>
       <c r="B51" t="n">
         <v>78660</v>
@@ -5743,10 +5738,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461732</v>
+        <v>461714</v>
       </c>
       <c r="R51" t="n">
-        <v>6788166</v>
+        <v>6788188</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5805,7 +5800,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566880</v>
+        <v>122566861</v>
       </c>
       <c r="B52" t="n">
         <v>78660</v>
@@ -5845,10 +5840,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461737</v>
+        <v>461537</v>
       </c>
       <c r="R52" t="n">
-        <v>6788251</v>
+        <v>6788149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5907,7 +5902,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566886</v>
+        <v>122566841</v>
       </c>
       <c r="B53" t="n">
         <v>78660</v>
@@ -5947,10 +5942,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461810</v>
+        <v>461809</v>
       </c>
       <c r="R53" t="n">
-        <v>6788325</v>
+        <v>6788250</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6009,10 +6004,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566881</v>
+        <v>122566801</v>
       </c>
       <c r="B54" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6025,21 +6020,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6049,10 +6044,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461742</v>
+        <v>461945</v>
       </c>
       <c r="R54" t="n">
-        <v>6788295</v>
+        <v>6788255</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6111,10 +6106,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566829</v>
+        <v>122566813</v>
       </c>
       <c r="B55" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6127,34 +6122,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461952</v>
+        <v>461803</v>
       </c>
       <c r="R55" t="n">
-        <v>6788327</v>
+        <v>6788243</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6187,6 +6187,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6213,7 +6218,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566862</v>
+        <v>122566874</v>
       </c>
       <c r="B56" t="n">
         <v>78660</v>
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461562</v>
+        <v>461665</v>
       </c>
       <c r="R56" t="n">
-        <v>6788141</v>
+        <v>6788207</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6315,10 +6320,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566804</v>
+        <v>122566855</v>
       </c>
       <c r="B57" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6331,21 +6336,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6355,10 +6360,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461614</v>
+        <v>461704</v>
       </c>
       <c r="R57" t="n">
-        <v>6788152</v>
+        <v>6788171</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6417,10 +6422,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566863</v>
+        <v>122566803</v>
       </c>
       <c r="B58" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6433,21 +6438,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6457,7 +6462,7 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461589</v>
+        <v>461598</v>
       </c>
       <c r="R58" t="n">
         <v>6788148</v>
@@ -6519,7 +6524,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566872</v>
+        <v>122566879</v>
       </c>
       <c r="B59" t="n">
         <v>78660</v>
@@ -6559,10 +6564,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461659</v>
+        <v>461721</v>
       </c>
       <c r="R59" t="n">
-        <v>6788194</v>
+        <v>6788242</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6621,7 +6626,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566818</v>
+        <v>122566826</v>
       </c>
       <c r="B60" t="n">
         <v>78660</v>
@@ -6661,10 +6666,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461816</v>
+        <v>461846</v>
       </c>
       <c r="R60" t="n">
-        <v>6788330</v>
+        <v>6788492</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,7 +6728,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566849</v>
+        <v>122566871</v>
       </c>
       <c r="B61" t="n">
         <v>78660</v>
@@ -6763,10 +6768,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461787</v>
+        <v>461676</v>
       </c>
       <c r="R61" t="n">
-        <v>6788182</v>
+        <v>6788174</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6825,7 +6830,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566846</v>
+        <v>122566824</v>
       </c>
       <c r="B62" t="n">
         <v>78660</v>
@@ -6865,10 +6870,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461791</v>
+        <v>461810</v>
       </c>
       <c r="R62" t="n">
-        <v>6788209</v>
+        <v>6788470</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6927,10 +6932,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566825</v>
+        <v>122566808</v>
       </c>
       <c r="B63" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6943,21 +6948,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6967,10 +6972,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461843</v>
+        <v>461872</v>
       </c>
       <c r="R63" t="n">
-        <v>6788468</v>
+        <v>6788413</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7029,7 +7034,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566841</v>
+        <v>122566834</v>
       </c>
       <c r="B64" t="n">
         <v>78660</v>
@@ -7069,10 +7074,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461809</v>
+        <v>461929</v>
       </c>
       <c r="R64" t="n">
-        <v>6788250</v>
+        <v>6788262</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7131,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566888</v>
+        <v>122566877</v>
       </c>
       <c r="B65" t="n">
-        <v>5173</v>
+        <v>78660</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7143,25 +7148,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7171,10 +7176,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461791</v>
+        <v>461706</v>
       </c>
       <c r="R65" t="n">
-        <v>6788187</v>
+        <v>6788223</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7233,7 +7238,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566805</v>
+        <v>122566807</v>
       </c>
       <c r="B66" t="n">
         <v>74761</v>
@@ -7273,10 +7278,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461848</v>
+        <v>461739</v>
       </c>
       <c r="R66" t="n">
-        <v>6788429</v>
+        <v>6788280</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7335,7 +7340,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566850</v>
+        <v>122566875</v>
       </c>
       <c r="B67" t="n">
         <v>78660</v>
@@ -7375,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461771</v>
+        <v>461669</v>
       </c>
       <c r="R67" t="n">
-        <v>6788185</v>
+        <v>6788203</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7539,7 +7544,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566845</v>
+        <v>122566847</v>
       </c>
       <c r="B69" t="n">
         <v>78660</v>
@@ -7579,10 +7584,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461794</v>
+        <v>461789</v>
       </c>
       <c r="R69" t="n">
-        <v>6788217</v>
+        <v>6788194</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7641,10 +7646,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566811</v>
+        <v>122566818</v>
       </c>
       <c r="B70" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7657,39 +7662,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461936</v>
+        <v>461816</v>
       </c>
       <c r="R70" t="n">
-        <v>6788279</v>
+        <v>6788330</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7748,10 +7748,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566809</v>
+        <v>122566845</v>
       </c>
       <c r="B71" t="n">
-        <v>90857</v>
+        <v>78660</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7764,21 +7764,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461822</v>
+        <v>461794</v>
       </c>
       <c r="R71" t="n">
-        <v>6788353</v>
+        <v>6788217</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7850,7 +7850,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566834</v>
+        <v>122566821</v>
       </c>
       <c r="B72" t="n">
         <v>78660</v>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461929</v>
+        <v>461699</v>
       </c>
       <c r="R72" t="n">
-        <v>6788262</v>
+        <v>6788443</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7952,10 +7952,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566814</v>
+        <v>122566848</v>
       </c>
       <c r="B73" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7968,21 +7968,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461814</v>
+        <v>461791</v>
       </c>
       <c r="R73" t="n">
-        <v>6788266</v>
+        <v>6788187</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8054,7 +8054,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566843</v>
+        <v>122566827</v>
       </c>
       <c r="B74" t="n">
         <v>78660</v>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461811</v>
+        <v>461879</v>
       </c>
       <c r="R74" t="n">
-        <v>6788237</v>
+        <v>6788396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8156,7 +8156,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566837</v>
+        <v>122566829</v>
       </c>
       <c r="B75" t="n">
         <v>78660</v>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461917</v>
+        <v>461952</v>
       </c>
       <c r="R75" t="n">
-        <v>6788292</v>
+        <v>6788327</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8258,7 +8258,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566839</v>
+        <v>122566853</v>
       </c>
       <c r="B76" t="n">
         <v>78660</v>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461829</v>
+        <v>461732</v>
       </c>
       <c r="R76" t="n">
-        <v>6788287</v>
+        <v>6788166</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8360,7 +8360,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566848</v>
+        <v>122566846</v>
       </c>
       <c r="B77" t="n">
         <v>78660</v>
@@ -8403,7 +8403,7 @@
         <v>461791</v>
       </c>
       <c r="R77" t="n">
-        <v>6788187</v>
+        <v>6788209</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8462,7 +8462,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566884</v>
+        <v>122566838</v>
       </c>
       <c r="B78" t="n">
         <v>78660</v>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461793</v>
+        <v>461878</v>
       </c>
       <c r="R78" t="n">
-        <v>6788303</v>
+        <v>6788313</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8564,10 +8564,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566820</v>
+        <v>122566887</v>
       </c>
       <c r="B79" t="n">
-        <v>78660</v>
+        <v>5173</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8576,25 +8576,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461732</v>
+        <v>461810</v>
       </c>
       <c r="R79" t="n">
-        <v>6788430</v>
+        <v>6788470</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -5387,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566843</v>
+        <v>122566811</v>
       </c>
       <c r="B48" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5403,34 +5403,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461811</v>
+        <v>461936</v>
       </c>
       <c r="R48" t="n">
-        <v>6788237</v>
+        <v>6788279</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,7 +5494,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566832</v>
+        <v>122566843</v>
       </c>
       <c r="B49" t="n">
         <v>78660</v>
@@ -5529,10 +5534,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461991</v>
+        <v>461811</v>
       </c>
       <c r="R49" t="n">
-        <v>6788292</v>
+        <v>6788237</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566811</v>
+        <v>122566832</v>
       </c>
       <c r="B50" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,39 +5612,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461936</v>
+        <v>461991</v>
       </c>
       <c r="R50" t="n">
-        <v>6788279</v>
+        <v>6788292</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566808</v>
+        <v>122566834</v>
       </c>
       <c r="B63" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6948,21 +6948,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461872</v>
+        <v>461929</v>
       </c>
       <c r="R63" t="n">
-        <v>6788413</v>
+        <v>6788262</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,7 +7034,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566834</v>
+        <v>122566877</v>
       </c>
       <c r="B64" t="n">
         <v>78660</v>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461929</v>
+        <v>461706</v>
       </c>
       <c r="R64" t="n">
-        <v>6788262</v>
+        <v>6788223</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566877</v>
+        <v>122566807</v>
       </c>
       <c r="B65" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461706</v>
+        <v>461739</v>
       </c>
       <c r="R65" t="n">
-        <v>6788223</v>
+        <v>6788280</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566807</v>
+        <v>122566875</v>
       </c>
       <c r="B66" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7254,21 +7254,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461739</v>
+        <v>461669</v>
       </c>
       <c r="R66" t="n">
-        <v>6788280</v>
+        <v>6788203</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566875</v>
+        <v>122566808</v>
       </c>
       <c r="B67" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7356,21 +7356,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461669</v>
+        <v>461872</v>
       </c>
       <c r="R67" t="n">
-        <v>6788203</v>
+        <v>6788413</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566814</v>
+        <v>122566816</v>
       </c>
       <c r="B6" t="n">
-        <v>78396</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461814</v>
+        <v>461930</v>
       </c>
       <c r="R6" t="n">
-        <v>6788266</v>
+        <v>6788270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566822</v>
+        <v>122566814</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461763</v>
+        <v>461814</v>
       </c>
       <c r="R7" t="n">
-        <v>6788475</v>
+        <v>6788266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566862</v>
+        <v>122566822</v>
       </c>
       <c r="B8" t="n">
         <v>78660</v>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461562</v>
+        <v>461763</v>
       </c>
       <c r="R8" t="n">
-        <v>6788141</v>
+        <v>6788475</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566880</v>
+        <v>122566862</v>
       </c>
       <c r="B9" t="n">
         <v>78660</v>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461737</v>
+        <v>461562</v>
       </c>
       <c r="R9" t="n">
-        <v>6788251</v>
+        <v>6788141</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566816</v>
+        <v>122566880</v>
       </c>
       <c r="B10" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,39 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461930</v>
+        <v>461737</v>
       </c>
       <c r="R10" t="n">
-        <v>6788270</v>
+        <v>6788251</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -6320,7 +6320,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566855</v>
+        <v>122566879</v>
       </c>
       <c r="B57" t="n">
         <v>78660</v>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461704</v>
+        <v>461721</v>
       </c>
       <c r="R57" t="n">
-        <v>6788171</v>
+        <v>6788242</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6422,10 +6422,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566803</v>
+        <v>122566826</v>
       </c>
       <c r="B58" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461598</v>
+        <v>461846</v>
       </c>
       <c r="R58" t="n">
-        <v>6788148</v>
+        <v>6788492</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566879</v>
+        <v>122566855</v>
       </c>
       <c r="B59" t="n">
         <v>78660</v>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461721</v>
+        <v>461704</v>
       </c>
       <c r="R59" t="n">
-        <v>6788242</v>
+        <v>6788171</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6626,10 +6626,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566826</v>
+        <v>122566803</v>
       </c>
       <c r="B60" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6642,21 +6642,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461846</v>
+        <v>461598</v>
       </c>
       <c r="R60" t="n">
-        <v>6788492</v>
+        <v>6788148</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -3959,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566872</v>
+        <v>122566888</v>
       </c>
       <c r="B34" t="n">
-        <v>78660</v>
+        <v>5173</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3971,25 +3971,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461659</v>
+        <v>461791</v>
       </c>
       <c r="R34" t="n">
-        <v>6788194</v>
+        <v>6788187</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,7 +4061,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566852</v>
+        <v>122566872</v>
       </c>
       <c r="B35" t="n">
         <v>78660</v>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461741</v>
+        <v>461659</v>
       </c>
       <c r="R35" t="n">
-        <v>6788170</v>
+        <v>6788194</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,7 +4163,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566878</v>
+        <v>122566852</v>
       </c>
       <c r="B36" t="n">
         <v>78660</v>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461712</v>
+        <v>461741</v>
       </c>
       <c r="R36" t="n">
-        <v>6788236</v>
+        <v>6788170</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566888</v>
+        <v>122566878</v>
       </c>
       <c r="B37" t="n">
-        <v>5173</v>
+        <v>78660</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4277,25 +4277,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461791</v>
+        <v>461712</v>
       </c>
       <c r="R37" t="n">
-        <v>6788187</v>
+        <v>6788236</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566834</v>
+        <v>122566808</v>
       </c>
       <c r="B63" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6948,21 +6948,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461929</v>
+        <v>461872</v>
       </c>
       <c r="R63" t="n">
-        <v>6788262</v>
+        <v>6788413</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,7 +7034,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566877</v>
+        <v>122566834</v>
       </c>
       <c r="B64" t="n">
         <v>78660</v>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461706</v>
+        <v>461929</v>
       </c>
       <c r="R64" t="n">
-        <v>6788223</v>
+        <v>6788262</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566807</v>
+        <v>122566877</v>
       </c>
       <c r="B65" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461739</v>
+        <v>461706</v>
       </c>
       <c r="R65" t="n">
-        <v>6788280</v>
+        <v>6788223</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566875</v>
+        <v>122566807</v>
       </c>
       <c r="B66" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7254,21 +7254,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461669</v>
+        <v>461739</v>
       </c>
       <c r="R66" t="n">
-        <v>6788203</v>
+        <v>6788280</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566808</v>
+        <v>122566875</v>
       </c>
       <c r="B67" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7356,21 +7356,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461872</v>
+        <v>461669</v>
       </c>
       <c r="R67" t="n">
-        <v>6788413</v>
+        <v>6788203</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -3959,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566888</v>
+        <v>122566872</v>
       </c>
       <c r="B34" t="n">
-        <v>5173</v>
+        <v>78660</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3971,25 +3971,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461791</v>
+        <v>461659</v>
       </c>
       <c r="R34" t="n">
-        <v>6788187</v>
+        <v>6788194</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,7 +4061,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566872</v>
+        <v>122566852</v>
       </c>
       <c r="B35" t="n">
         <v>78660</v>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461659</v>
+        <v>461741</v>
       </c>
       <c r="R35" t="n">
-        <v>6788194</v>
+        <v>6788170</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,7 +4163,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566852</v>
+        <v>122566878</v>
       </c>
       <c r="B36" t="n">
         <v>78660</v>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461741</v>
+        <v>461712</v>
       </c>
       <c r="R36" t="n">
-        <v>6788170</v>
+        <v>6788236</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566878</v>
+        <v>122566888</v>
       </c>
       <c r="B37" t="n">
-        <v>78660</v>
+        <v>5173</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4277,25 +4277,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461712</v>
+        <v>461791</v>
       </c>
       <c r="R37" t="n">
-        <v>6788236</v>
+        <v>6788187</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5387,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566811</v>
+        <v>122566843</v>
       </c>
       <c r="B48" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5403,39 +5403,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461936</v>
+        <v>461811</v>
       </c>
       <c r="R48" t="n">
-        <v>6788279</v>
+        <v>6788237</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,7 +5489,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566843</v>
+        <v>122566832</v>
       </c>
       <c r="B49" t="n">
         <v>78660</v>
@@ -5534,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461811</v>
+        <v>461991</v>
       </c>
       <c r="R49" t="n">
-        <v>6788237</v>
+        <v>6788292</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5596,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566832</v>
+        <v>122566811</v>
       </c>
       <c r="B50" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5612,34 +5607,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461991</v>
+        <v>461936</v>
       </c>
       <c r="R50" t="n">
-        <v>6788292</v>
+        <v>6788279</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6320,7 +6320,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566879</v>
+        <v>122566855</v>
       </c>
       <c r="B57" t="n">
         <v>78660</v>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461721</v>
+        <v>461704</v>
       </c>
       <c r="R57" t="n">
-        <v>6788242</v>
+        <v>6788171</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6422,10 +6422,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566826</v>
+        <v>122566803</v>
       </c>
       <c r="B58" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461846</v>
+        <v>461598</v>
       </c>
       <c r="R58" t="n">
-        <v>6788492</v>
+        <v>6788148</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566855</v>
+        <v>122566879</v>
       </c>
       <c r="B59" t="n">
         <v>78660</v>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461704</v>
+        <v>461721</v>
       </c>
       <c r="R59" t="n">
-        <v>6788171</v>
+        <v>6788242</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6626,10 +6626,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566803</v>
+        <v>122566826</v>
       </c>
       <c r="B60" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6642,21 +6642,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461598</v>
+        <v>461846</v>
       </c>
       <c r="R60" t="n">
-        <v>6788148</v>
+        <v>6788492</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -6106,10 +6106,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566813</v>
+        <v>122566874</v>
       </c>
       <c r="B55" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6122,39 +6122,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461803</v>
+        <v>461665</v>
       </c>
       <c r="R55" t="n">
-        <v>6788243</v>
+        <v>6788207</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6187,11 +6182,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6218,7 +6208,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566874</v>
+        <v>122566855</v>
       </c>
       <c r="B56" t="n">
         <v>78660</v>
@@ -6258,10 +6248,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461665</v>
+        <v>461704</v>
       </c>
       <c r="R56" t="n">
-        <v>6788207</v>
+        <v>6788171</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6320,10 +6310,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566855</v>
+        <v>122566803</v>
       </c>
       <c r="B57" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6336,21 +6326,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6360,10 +6350,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461704</v>
+        <v>461598</v>
       </c>
       <c r="R57" t="n">
-        <v>6788171</v>
+        <v>6788148</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6422,10 +6412,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566803</v>
+        <v>122566879</v>
       </c>
       <c r="B58" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6438,21 +6428,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6462,10 +6452,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461598</v>
+        <v>461721</v>
       </c>
       <c r="R58" t="n">
-        <v>6788148</v>
+        <v>6788242</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,7 +6514,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566879</v>
+        <v>122566826</v>
       </c>
       <c r="B59" t="n">
         <v>78660</v>
@@ -6564,10 +6554,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461721</v>
+        <v>461846</v>
       </c>
       <c r="R59" t="n">
-        <v>6788242</v>
+        <v>6788492</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6626,7 +6616,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566826</v>
+        <v>122566871</v>
       </c>
       <c r="B60" t="n">
         <v>78660</v>
@@ -6666,10 +6656,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461846</v>
+        <v>461676</v>
       </c>
       <c r="R60" t="n">
-        <v>6788492</v>
+        <v>6788174</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6728,7 +6718,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566871</v>
+        <v>122566824</v>
       </c>
       <c r="B61" t="n">
         <v>78660</v>
@@ -6768,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461676</v>
+        <v>461810</v>
       </c>
       <c r="R61" t="n">
-        <v>6788174</v>
+        <v>6788470</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6830,10 +6820,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566824</v>
+        <v>122566808</v>
       </c>
       <c r="B62" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6846,21 +6836,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6870,10 +6860,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461810</v>
+        <v>461872</v>
       </c>
       <c r="R62" t="n">
-        <v>6788470</v>
+        <v>6788413</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,10 +6922,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566808</v>
+        <v>122566834</v>
       </c>
       <c r="B63" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6948,21 +6938,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6972,10 +6962,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461872</v>
+        <v>461929</v>
       </c>
       <c r="R63" t="n">
-        <v>6788413</v>
+        <v>6788262</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,7 +7024,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566834</v>
+        <v>122566877</v>
       </c>
       <c r="B64" t="n">
         <v>78660</v>
@@ -7074,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461929</v>
+        <v>461706</v>
       </c>
       <c r="R64" t="n">
-        <v>6788262</v>
+        <v>6788223</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,10 +7126,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566877</v>
+        <v>122566807</v>
       </c>
       <c r="B65" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7152,21 +7142,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7176,10 +7166,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461706</v>
+        <v>461739</v>
       </c>
       <c r="R65" t="n">
-        <v>6788223</v>
+        <v>6788280</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7228,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566807</v>
+        <v>122566875</v>
       </c>
       <c r="B66" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7254,21 +7244,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7278,10 +7268,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461739</v>
+        <v>461669</v>
       </c>
       <c r="R66" t="n">
-        <v>6788280</v>
+        <v>6788203</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,7 +7330,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566875</v>
+        <v>122566844</v>
       </c>
       <c r="B67" t="n">
         <v>78660</v>
@@ -7380,10 +7370,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461669</v>
+        <v>461816</v>
       </c>
       <c r="R67" t="n">
-        <v>6788203</v>
+        <v>6788215</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,7 +7432,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566844</v>
+        <v>122566847</v>
       </c>
       <c r="B68" t="n">
         <v>78660</v>
@@ -7482,10 +7472,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461816</v>
+        <v>461789</v>
       </c>
       <c r="R68" t="n">
-        <v>6788215</v>
+        <v>6788194</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7544,7 +7534,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566847</v>
+        <v>122566818</v>
       </c>
       <c r="B69" t="n">
         <v>78660</v>
@@ -7584,10 +7574,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461789</v>
+        <v>461816</v>
       </c>
       <c r="R69" t="n">
-        <v>6788194</v>
+        <v>6788330</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7646,7 +7636,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566818</v>
+        <v>122566845</v>
       </c>
       <c r="B70" t="n">
         <v>78660</v>
@@ -7686,10 +7676,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461816</v>
+        <v>461794</v>
       </c>
       <c r="R70" t="n">
-        <v>6788330</v>
+        <v>6788217</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7748,7 +7738,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566845</v>
+        <v>122566821</v>
       </c>
       <c r="B71" t="n">
         <v>78660</v>
@@ -7788,10 +7778,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461794</v>
+        <v>461699</v>
       </c>
       <c r="R71" t="n">
-        <v>6788217</v>
+        <v>6788443</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7850,7 +7840,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566821</v>
+        <v>122566848</v>
       </c>
       <c r="B72" t="n">
         <v>78660</v>
@@ -7890,10 +7880,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461699</v>
+        <v>461791</v>
       </c>
       <c r="R72" t="n">
-        <v>6788443</v>
+        <v>6788187</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7952,7 +7942,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566848</v>
+        <v>122566827</v>
       </c>
       <c r="B73" t="n">
         <v>78660</v>
@@ -7992,10 +7982,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461791</v>
+        <v>461879</v>
       </c>
       <c r="R73" t="n">
-        <v>6788187</v>
+        <v>6788396</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8054,7 +8044,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566827</v>
+        <v>122566829</v>
       </c>
       <c r="B74" t="n">
         <v>78660</v>
@@ -8094,10 +8084,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461879</v>
+        <v>461952</v>
       </c>
       <c r="R74" t="n">
-        <v>6788396</v>
+        <v>6788327</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8156,7 +8146,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566829</v>
+        <v>122566853</v>
       </c>
       <c r="B75" t="n">
         <v>78660</v>
@@ -8196,10 +8186,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461952</v>
+        <v>461732</v>
       </c>
       <c r="R75" t="n">
-        <v>6788327</v>
+        <v>6788166</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8258,7 +8248,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566853</v>
+        <v>122566846</v>
       </c>
       <c r="B76" t="n">
         <v>78660</v>
@@ -8298,10 +8288,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461732</v>
+        <v>461791</v>
       </c>
       <c r="R76" t="n">
-        <v>6788166</v>
+        <v>6788209</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8360,7 +8350,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566846</v>
+        <v>122566838</v>
       </c>
       <c r="B77" t="n">
         <v>78660</v>
@@ -8400,10 +8390,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461791</v>
+        <v>461878</v>
       </c>
       <c r="R77" t="n">
-        <v>6788209</v>
+        <v>6788313</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8462,10 +8452,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566838</v>
+        <v>122566887</v>
       </c>
       <c r="B78" t="n">
-        <v>78660</v>
+        <v>5173</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8474,25 +8464,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8502,10 +8492,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461878</v>
+        <v>461810</v>
       </c>
       <c r="R78" t="n">
-        <v>6788313</v>
+        <v>6788470</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8564,10 +8554,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566887</v>
+        <v>122566812</v>
       </c>
       <c r="B79" t="n">
-        <v>5173</v>
+        <v>57400</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8576,38 +8566,46 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461810</v>
+        <v>461803</v>
       </c>
       <c r="R79" t="n">
-        <v>6788470</v>
+        <v>6788243</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8666,7 +8664,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122566812</v>
+        <v>122488168</v>
       </c>
       <c r="B80" t="n">
         <v>57400</v>
@@ -8704,7 +8702,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8714,10 +8712,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461803</v>
+        <v>461923</v>
       </c>
       <c r="R80" t="n">
-        <v>6788243</v>
+        <v>6788245</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8744,12 +8742,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre gran med hackhål. Hörde spillkråkan i området.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8764,22 +8767,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122488168</v>
+        <v>122566813</v>
       </c>
       <c r="B81" t="n">
-        <v>57400</v>
+        <v>57478</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8792,16 +8795,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8810,24 +8813,21 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461923</v>
+        <v>461803</v>
       </c>
       <c r="R81" t="n">
-        <v>6788245</v>
+        <v>6788243</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8854,17 +8854,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre gran med hackhål. Hörde spillkråkan i området.</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8879,12 +8879,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8894,7 +8894,7 @@
         <v>122489274</v>
       </c>
       <c r="B82" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566885</v>
+        <v>122566808</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>90940</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461804</v>
+        <v>461872</v>
       </c>
       <c r="R15" t="n">
-        <v>6788319</v>
+        <v>6788413</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566873</v>
+        <v>122566885</v>
       </c>
       <c r="B16" t="n">
         <v>78762</v>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461655</v>
+        <v>461804</v>
       </c>
       <c r="R16" t="n">
-        <v>6788205</v>
+        <v>6788319</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566849</v>
+        <v>122566873</v>
       </c>
       <c r="B17" t="n">
         <v>78762</v>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461787</v>
+        <v>461655</v>
       </c>
       <c r="R17" t="n">
-        <v>6788182</v>
+        <v>6788205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566805</v>
+        <v>122566849</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>78762</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461848</v>
+        <v>461787</v>
       </c>
       <c r="R18" t="n">
-        <v>6788429</v>
+        <v>6788182</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566823</v>
+        <v>122566805</v>
       </c>
       <c r="B19" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461778</v>
+        <v>461848</v>
       </c>
       <c r="R19" t="n">
-        <v>6788485</v>
+        <v>6788429</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566803</v>
+        <v>122566823</v>
       </c>
       <c r="B20" t="n">
-        <v>79380</v>
+        <v>78762</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461598</v>
+        <v>461778</v>
       </c>
       <c r="R20" t="n">
-        <v>6788148</v>
+        <v>6788485</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566808</v>
+        <v>122566803</v>
       </c>
       <c r="B21" t="n">
-        <v>90940</v>
+        <v>79380</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461872</v>
+        <v>461598</v>
       </c>
       <c r="R21" t="n">
-        <v>6788413</v>
+        <v>6788148</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3240,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566848</v>
+        <v>122566888</v>
       </c>
       <c r="B27" t="n">
-        <v>78762</v>
+        <v>5173</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3252,25 +3252,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566888</v>
+        <v>122566848</v>
       </c>
       <c r="B28" t="n">
-        <v>5173</v>
+        <v>78762</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3354,25 +3354,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566808</v>
+        <v>122566885</v>
       </c>
       <c r="B15" t="n">
-        <v>90940</v>
+        <v>78762</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461872</v>
+        <v>461804</v>
       </c>
       <c r="R15" t="n">
-        <v>6788413</v>
+        <v>6788319</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566885</v>
+        <v>122566873</v>
       </c>
       <c r="B16" t="n">
         <v>78762</v>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461804</v>
+        <v>461655</v>
       </c>
       <c r="R16" t="n">
-        <v>6788319</v>
+        <v>6788205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566873</v>
+        <v>122566849</v>
       </c>
       <c r="B17" t="n">
         <v>78762</v>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461655</v>
+        <v>461787</v>
       </c>
       <c r="R17" t="n">
-        <v>6788205</v>
+        <v>6788182</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566849</v>
+        <v>122566805</v>
       </c>
       <c r="B18" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461787</v>
+        <v>461848</v>
       </c>
       <c r="R18" t="n">
-        <v>6788182</v>
+        <v>6788429</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566805</v>
+        <v>122566823</v>
       </c>
       <c r="B19" t="n">
-        <v>74863</v>
+        <v>78762</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461848</v>
+        <v>461778</v>
       </c>
       <c r="R19" t="n">
-        <v>6788429</v>
+        <v>6788485</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566823</v>
+        <v>122566803</v>
       </c>
       <c r="B20" t="n">
-        <v>78762</v>
+        <v>79380</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461778</v>
+        <v>461598</v>
       </c>
       <c r="R20" t="n">
-        <v>6788485</v>
+        <v>6788148</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566803</v>
+        <v>122566808</v>
       </c>
       <c r="B21" t="n">
-        <v>79380</v>
+        <v>90940</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461598</v>
+        <v>461872</v>
       </c>
       <c r="R21" t="n">
-        <v>6788148</v>
+        <v>6788413</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3240,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566888</v>
+        <v>122566848</v>
       </c>
       <c r="B27" t="n">
-        <v>5173</v>
+        <v>78762</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3252,25 +3252,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566848</v>
+        <v>122566888</v>
       </c>
       <c r="B28" t="n">
-        <v>78762</v>
+        <v>5173</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3354,25 +3354,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -7427,10 +7427,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566887</v>
+        <v>122566874</v>
       </c>
       <c r="B68" t="n">
-        <v>5173</v>
+        <v>78762</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7439,25 +7439,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461810</v>
+        <v>461665</v>
       </c>
       <c r="R68" t="n">
-        <v>6788470</v>
+        <v>6788207</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7529,7 +7529,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566874</v>
+        <v>122566853</v>
       </c>
       <c r="B69" t="n">
         <v>78762</v>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461665</v>
+        <v>461732</v>
       </c>
       <c r="R69" t="n">
-        <v>6788207</v>
+        <v>6788166</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566853</v>
+        <v>122566801</v>
       </c>
       <c r="B70" t="n">
-        <v>78762</v>
+        <v>79380</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7647,21 +7647,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7671,10 +7671,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461732</v>
+        <v>461945</v>
       </c>
       <c r="R70" t="n">
-        <v>6788166</v>
+        <v>6788255</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7733,10 +7733,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566801</v>
+        <v>122566830</v>
       </c>
       <c r="B71" t="n">
-        <v>79380</v>
+        <v>78762</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7749,21 +7749,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461945</v>
+        <v>461991</v>
       </c>
       <c r="R71" t="n">
-        <v>6788255</v>
+        <v>6788324</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7835,10 +7835,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566830</v>
+        <v>122566887</v>
       </c>
       <c r="B72" t="n">
-        <v>78762</v>
+        <v>5173</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7847,25 +7847,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461991</v>
+        <v>461810</v>
       </c>
       <c r="R72" t="n">
-        <v>6788324</v>
+        <v>6788470</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489147</v>
+        <v>122489220</v>
       </c>
       <c r="B2" t="n">
-        <v>90960</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R2" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +790,7 @@
         <v>122488593</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489220</v>
+        <v>122489147</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>90964</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R4" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566837</v>
+        <v>122566816</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461917</v>
+        <v>461930</v>
       </c>
       <c r="R5" t="n">
-        <v>6788292</v>
+        <v>6788270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566807</v>
+        <v>122566817</v>
       </c>
       <c r="B6" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461739</v>
+        <v>461788</v>
       </c>
       <c r="R6" t="n">
-        <v>6788280</v>
+        <v>6788303</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566828</v>
+        <v>122566819</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,16 +1234,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461923</v>
+        <v>461667</v>
       </c>
       <c r="R7" t="n">
-        <v>6788324</v>
+        <v>6788182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566882</v>
+        <v>122566837</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461757</v>
+        <v>461917</v>
       </c>
       <c r="R8" t="n">
-        <v>6788299</v>
+        <v>6788292</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566816</v>
+        <v>122566822</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,39 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461930</v>
+        <v>461763</v>
       </c>
       <c r="R9" t="n">
-        <v>6788270</v>
+        <v>6788475</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566859</v>
+        <v>122566809</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
+        <v>90964</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461506</v>
+        <v>461822</v>
       </c>
       <c r="R10" t="n">
-        <v>6788139</v>
+        <v>6788353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566802</v>
+        <v>122566865</v>
       </c>
       <c r="B11" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461811</v>
+        <v>461628</v>
       </c>
       <c r="R11" t="n">
-        <v>6788280</v>
+        <v>6788142</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566838</v>
+        <v>122566869</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461878</v>
+        <v>461678</v>
       </c>
       <c r="R12" t="n">
-        <v>6788313</v>
+        <v>6788157</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566861</v>
+        <v>122566826</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461537</v>
+        <v>461846</v>
       </c>
       <c r="R13" t="n">
-        <v>6788149</v>
+        <v>6788492</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566883</v>
+        <v>122566863</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461777</v>
+        <v>461589</v>
       </c>
       <c r="R14" t="n">
-        <v>6788298</v>
+        <v>6788148</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566885</v>
+        <v>122566886</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461804</v>
+        <v>461810</v>
       </c>
       <c r="R15" t="n">
-        <v>6788319</v>
+        <v>6788325</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566873</v>
+        <v>122566872</v>
       </c>
       <c r="B16" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461655</v>
+        <v>461659</v>
       </c>
       <c r="R16" t="n">
-        <v>6788205</v>
+        <v>6788194</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566849</v>
+        <v>122566820</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461787</v>
+        <v>461732</v>
       </c>
       <c r="R17" t="n">
-        <v>6788182</v>
+        <v>6788430</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566805</v>
+        <v>122566885</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461848</v>
+        <v>461804</v>
       </c>
       <c r="R18" t="n">
-        <v>6788429</v>
+        <v>6788319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566823</v>
+        <v>122566849</v>
       </c>
       <c r="B19" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2464,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461778</v>
+        <v>461787</v>
       </c>
       <c r="R19" t="n">
-        <v>6788485</v>
+        <v>6788182</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566803</v>
+        <v>122566842</v>
       </c>
       <c r="B20" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461598</v>
+        <v>461803</v>
       </c>
       <c r="R20" t="n">
-        <v>6788148</v>
+        <v>6788243</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566808</v>
+        <v>122566843</v>
       </c>
       <c r="B21" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461872</v>
+        <v>461811</v>
       </c>
       <c r="R21" t="n">
-        <v>6788413</v>
+        <v>6788237</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566809</v>
+        <v>122566887</v>
       </c>
       <c r="B22" t="n">
-        <v>90960</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,25 +2747,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461822</v>
+        <v>461810</v>
       </c>
       <c r="R22" t="n">
-        <v>6788353</v>
+        <v>6788470</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566824</v>
+        <v>122566888</v>
       </c>
       <c r="B23" t="n">
-        <v>78762</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2844,25 +2849,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461810</v>
+        <v>461791</v>
       </c>
       <c r="R23" t="n">
-        <v>6788470</v>
+        <v>6788187</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566840</v>
+        <v>122566803</v>
       </c>
       <c r="B24" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2950,21 +2955,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2974,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461810</v>
+        <v>461598</v>
       </c>
       <c r="R24" t="n">
-        <v>6788278</v>
+        <v>6788148</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566862</v>
+        <v>122566840</v>
       </c>
       <c r="B25" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3076,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461562</v>
+        <v>461810</v>
       </c>
       <c r="R25" t="n">
-        <v>6788141</v>
+        <v>6788278</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566850</v>
+        <v>122566877</v>
       </c>
       <c r="B26" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3178,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461771</v>
+        <v>461706</v>
       </c>
       <c r="R26" t="n">
-        <v>6788185</v>
+        <v>6788223</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566848</v>
+        <v>122566876</v>
       </c>
       <c r="B27" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3280,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461791</v>
+        <v>461695</v>
       </c>
       <c r="R27" t="n">
-        <v>6788187</v>
+        <v>6788224</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566888</v>
+        <v>122566831</v>
       </c>
       <c r="B28" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3354,25 +3359,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3382,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461791</v>
+        <v>462004</v>
       </c>
       <c r="R28" t="n">
-        <v>6788187</v>
+        <v>6788320</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566854</v>
+        <v>122566834</v>
       </c>
       <c r="B29" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3484,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461714</v>
+        <v>461929</v>
       </c>
       <c r="R29" t="n">
-        <v>6788188</v>
+        <v>6788262</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3546,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566855</v>
+        <v>122566850</v>
       </c>
       <c r="B30" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3586,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461704</v>
+        <v>461771</v>
       </c>
       <c r="R30" t="n">
-        <v>6788171</v>
+        <v>6788185</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,10 +3653,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566884</v>
+        <v>122566862</v>
       </c>
       <c r="B31" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3688,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461793</v>
+        <v>461562</v>
       </c>
       <c r="R31" t="n">
-        <v>6788303</v>
+        <v>6788141</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566863</v>
+        <v>122566818</v>
       </c>
       <c r="B32" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3790,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461589</v>
+        <v>461816</v>
       </c>
       <c r="R32" t="n">
-        <v>6788148</v>
+        <v>6788330</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566875</v>
+        <v>122566852</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3892,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461669</v>
+        <v>461741</v>
       </c>
       <c r="R33" t="n">
-        <v>6788203</v>
+        <v>6788170</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3954,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566877</v>
+        <v>122566874</v>
       </c>
       <c r="B34" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3994,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461706</v>
+        <v>461665</v>
       </c>
       <c r="R34" t="n">
-        <v>6788223</v>
+        <v>6788207</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566845</v>
+        <v>122566875</v>
       </c>
       <c r="B35" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4096,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461794</v>
+        <v>461669</v>
       </c>
       <c r="R35" t="n">
-        <v>6788217</v>
+        <v>6788203</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4158,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566839</v>
+        <v>122566833</v>
       </c>
       <c r="B36" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4198,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461829</v>
+        <v>461972</v>
       </c>
       <c r="R36" t="n">
-        <v>6788287</v>
+        <v>6788277</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4260,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566841</v>
+        <v>122566821</v>
       </c>
       <c r="B37" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4300,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461809</v>
+        <v>461699</v>
       </c>
       <c r="R37" t="n">
-        <v>6788250</v>
+        <v>6788443</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4362,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566847</v>
+        <v>122566804</v>
       </c>
       <c r="B38" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4378,21 +4383,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4402,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461789</v>
+        <v>461614</v>
       </c>
       <c r="R38" t="n">
-        <v>6788194</v>
+        <v>6788152</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566834</v>
+        <v>122566854</v>
       </c>
       <c r="B39" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4504,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461929</v>
+        <v>461714</v>
       </c>
       <c r="R39" t="n">
-        <v>6788262</v>
+        <v>6788188</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566865</v>
+        <v>122566871</v>
       </c>
       <c r="B40" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461628</v>
+        <v>461676</v>
       </c>
       <c r="R40" t="n">
-        <v>6788142</v>
+        <v>6788174</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,10 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566872</v>
+        <v>122566881</v>
       </c>
       <c r="B41" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4708,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461659</v>
+        <v>461742</v>
       </c>
       <c r="R41" t="n">
-        <v>6788194</v>
+        <v>6788295</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4775,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566842</v>
+        <v>122566829</v>
       </c>
       <c r="B42" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4810,10 +4815,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461803</v>
+        <v>461952</v>
       </c>
       <c r="R42" t="n">
-        <v>6788243</v>
+        <v>6788327</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4872,10 +4877,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566878</v>
+        <v>122566882</v>
       </c>
       <c r="B43" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4912,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461712</v>
+        <v>461757</v>
       </c>
       <c r="R43" t="n">
-        <v>6788236</v>
+        <v>6788299</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566880</v>
+        <v>122566883</v>
       </c>
       <c r="B44" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5014,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461737</v>
+        <v>461777</v>
       </c>
       <c r="R44" t="n">
-        <v>6788251</v>
+        <v>6788298</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5076,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566864</v>
+        <v>122566861</v>
       </c>
       <c r="B45" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5116,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461619</v>
+        <v>461537</v>
       </c>
       <c r="R45" t="n">
-        <v>6788144</v>
+        <v>6788149</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5178,10 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566871</v>
+        <v>122566847</v>
       </c>
       <c r="B46" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5218,10 +5223,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461676</v>
+        <v>461789</v>
       </c>
       <c r="R46" t="n">
-        <v>6788174</v>
+        <v>6788194</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5280,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566814</v>
+        <v>122566844</v>
       </c>
       <c r="B47" t="n">
-        <v>78498</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5296,21 +5301,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5320,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461814</v>
+        <v>461816</v>
       </c>
       <c r="R47" t="n">
-        <v>6788266</v>
+        <v>6788215</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5382,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566833</v>
+        <v>122566835</v>
       </c>
       <c r="B48" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5422,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461972</v>
+        <v>461929</v>
       </c>
       <c r="R48" t="n">
-        <v>6788277</v>
+        <v>6788278</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5484,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566827</v>
+        <v>122566855</v>
       </c>
       <c r="B49" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5524,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461879</v>
+        <v>461704</v>
       </c>
       <c r="R49" t="n">
-        <v>6788396</v>
+        <v>6788171</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5586,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566831</v>
+        <v>122566825</v>
       </c>
       <c r="B50" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5626,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>462004</v>
+        <v>461843</v>
       </c>
       <c r="R50" t="n">
-        <v>6788320</v>
+        <v>6788468</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5688,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566832</v>
+        <v>122566801</v>
       </c>
       <c r="B51" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5704,21 +5709,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5728,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461991</v>
+        <v>461945</v>
       </c>
       <c r="R51" t="n">
-        <v>6788292</v>
+        <v>6788255</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5790,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566846</v>
+        <v>122566880</v>
       </c>
       <c r="B52" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5830,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461791</v>
+        <v>461737</v>
       </c>
       <c r="R52" t="n">
-        <v>6788209</v>
+        <v>6788251</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5892,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566852</v>
+        <v>122566878</v>
       </c>
       <c r="B53" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5932,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461741</v>
+        <v>461712</v>
       </c>
       <c r="R53" t="n">
-        <v>6788170</v>
+        <v>6788236</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5994,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566826</v>
+        <v>122566846</v>
       </c>
       <c r="B54" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6034,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461846</v>
+        <v>461791</v>
       </c>
       <c r="R54" t="n">
-        <v>6788492</v>
+        <v>6788209</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6096,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566819</v>
+        <v>122566828</v>
       </c>
       <c r="B55" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6130,21 +6135,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461667</v>
+        <v>461923</v>
       </c>
       <c r="R55" t="n">
-        <v>6788182</v>
+        <v>6788324</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6203,10 +6203,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566886</v>
+        <v>122566830</v>
       </c>
       <c r="B56" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461810</v>
+        <v>461991</v>
       </c>
       <c r="R56" t="n">
-        <v>6788325</v>
+        <v>6788324</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6308,7 +6308,7 @@
         <v>122566879</v>
       </c>
       <c r="B57" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6407,10 +6407,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566820</v>
+        <v>122566824</v>
       </c>
       <c r="B58" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461732</v>
+        <v>461810</v>
       </c>
       <c r="R58" t="n">
-        <v>6788430</v>
+        <v>6788470</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6509,10 +6509,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566881</v>
+        <v>122566839</v>
       </c>
       <c r="B59" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461742</v>
+        <v>461829</v>
       </c>
       <c r="R59" t="n">
-        <v>6788295</v>
+        <v>6788287</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,10 +6611,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566818</v>
+        <v>122566853</v>
       </c>
       <c r="B60" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461816</v>
+        <v>461732</v>
       </c>
       <c r="R60" t="n">
-        <v>6788330</v>
+        <v>6788166</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566817</v>
+        <v>122566864</v>
       </c>
       <c r="B61" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461788</v>
+        <v>461619</v>
       </c>
       <c r="R61" t="n">
-        <v>6788303</v>
+        <v>6788144</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566869</v>
+        <v>122566851</v>
       </c>
       <c r="B62" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461678</v>
+        <v>461758</v>
       </c>
       <c r="R62" t="n">
-        <v>6788157</v>
+        <v>6788174</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6917,10 +6917,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566825</v>
+        <v>122566808</v>
       </c>
       <c r="B63" t="n">
-        <v>78762</v>
+        <v>90944</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6933,21 +6933,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461843</v>
+        <v>461872</v>
       </c>
       <c r="R63" t="n">
-        <v>6788468</v>
+        <v>6788413</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7019,10 +7019,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566822</v>
+        <v>122566814</v>
       </c>
       <c r="B64" t="n">
-        <v>78762</v>
+        <v>78502</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461763</v>
+        <v>461814</v>
       </c>
       <c r="R64" t="n">
-        <v>6788475</v>
+        <v>6788266</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7121,10 +7121,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566876</v>
+        <v>122566884</v>
       </c>
       <c r="B65" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461695</v>
+        <v>461793</v>
       </c>
       <c r="R65" t="n">
-        <v>6788224</v>
+        <v>6788303</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7223,10 +7223,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566835</v>
+        <v>122566848</v>
       </c>
       <c r="B66" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7263,10 +7263,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461929</v>
+        <v>461791</v>
       </c>
       <c r="R66" t="n">
-        <v>6788278</v>
+        <v>6788187</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7325,10 +7325,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566851</v>
+        <v>122566841</v>
       </c>
       <c r="B67" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461758</v>
+        <v>461809</v>
       </c>
       <c r="R67" t="n">
-        <v>6788174</v>
+        <v>6788250</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7427,10 +7427,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566874</v>
+        <v>122566832</v>
       </c>
       <c r="B68" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461665</v>
+        <v>461991</v>
       </c>
       <c r="R68" t="n">
-        <v>6788207</v>
+        <v>6788292</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7529,10 +7529,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566853</v>
+        <v>122566802</v>
       </c>
       <c r="B69" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7545,21 +7545,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461732</v>
+        <v>461811</v>
       </c>
       <c r="R69" t="n">
-        <v>6788166</v>
+        <v>6788280</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566801</v>
+        <v>122566811</v>
       </c>
       <c r="B70" t="n">
-        <v>79380</v>
+        <v>57494</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7647,34 +7647,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461945</v>
+        <v>461936</v>
       </c>
       <c r="R70" t="n">
-        <v>6788255</v>
+        <v>6788279</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7733,10 +7738,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566830</v>
+        <v>122566823</v>
       </c>
       <c r="B71" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7773,10 +7778,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461991</v>
+        <v>461778</v>
       </c>
       <c r="R71" t="n">
-        <v>6788324</v>
+        <v>6788485</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7835,10 +7840,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566887</v>
+        <v>122566807</v>
       </c>
       <c r="B72" t="n">
-        <v>5173</v>
+        <v>74863</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7847,25 +7852,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7880,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461810</v>
+        <v>461739</v>
       </c>
       <c r="R72" t="n">
-        <v>6788470</v>
+        <v>6788280</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7937,10 +7942,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566804</v>
+        <v>122566838</v>
       </c>
       <c r="B73" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7953,21 +7958,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7977,10 +7982,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461614</v>
+        <v>461878</v>
       </c>
       <c r="R73" t="n">
-        <v>6788152</v>
+        <v>6788313</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8039,10 +8044,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566829</v>
+        <v>122566805</v>
       </c>
       <c r="B74" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8055,21 +8060,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8079,10 +8084,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461952</v>
+        <v>461848</v>
       </c>
       <c r="R74" t="n">
-        <v>6788327</v>
+        <v>6788429</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8141,10 +8146,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566843</v>
+        <v>122566873</v>
       </c>
       <c r="B75" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8181,10 +8186,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461811</v>
+        <v>461655</v>
       </c>
       <c r="R75" t="n">
-        <v>6788237</v>
+        <v>6788205</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8243,10 +8248,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566844</v>
+        <v>122566845</v>
       </c>
       <c r="B76" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8283,10 +8288,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461816</v>
+        <v>461794</v>
       </c>
       <c r="R76" t="n">
-        <v>6788215</v>
+        <v>6788217</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8345,10 +8350,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566811</v>
+        <v>122566859</v>
       </c>
       <c r="B77" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8361,39 +8366,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461936</v>
+        <v>461506</v>
       </c>
       <c r="R77" t="n">
-        <v>6788279</v>
+        <v>6788139</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8452,10 +8452,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566821</v>
+        <v>122566827</v>
       </c>
       <c r="B78" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8492,10 +8492,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461699</v>
+        <v>461879</v>
       </c>
       <c r="R78" t="n">
-        <v>6788443</v>
+        <v>6788396</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489220</v>
+        <v>122489147</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>90964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R2" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489147</v>
+        <v>122489220</v>
       </c>
       <c r="B4" t="n">
-        <v>90964</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R4" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566816</v>
+        <v>122566848</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461930</v>
+        <v>461791</v>
       </c>
       <c r="R5" t="n">
-        <v>6788270</v>
+        <v>6788187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566817</v>
+        <v>122566804</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461788</v>
+        <v>461614</v>
       </c>
       <c r="R6" t="n">
-        <v>6788303</v>
+        <v>6788152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566819</v>
+        <v>122566833</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1234,21 +1229,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461667</v>
+        <v>461972</v>
       </c>
       <c r="R7" t="n">
-        <v>6788182</v>
+        <v>6788277</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566837</v>
+        <v>122566886</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1347,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461917</v>
+        <v>461810</v>
       </c>
       <c r="R8" t="n">
-        <v>6788292</v>
+        <v>6788325</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566822</v>
+        <v>122566875</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1449,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461763</v>
+        <v>461669</v>
       </c>
       <c r="R9" t="n">
-        <v>6788475</v>
+        <v>6788203</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566809</v>
+        <v>122566837</v>
       </c>
       <c r="B10" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461822</v>
+        <v>461917</v>
       </c>
       <c r="R10" t="n">
-        <v>6788353</v>
+        <v>6788292</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566865</v>
+        <v>122566859</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1653,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461628</v>
+        <v>461506</v>
       </c>
       <c r="R11" t="n">
-        <v>6788142</v>
+        <v>6788139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566869</v>
+        <v>122566876</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1755,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461678</v>
+        <v>461695</v>
       </c>
       <c r="R12" t="n">
-        <v>6788157</v>
+        <v>6788224</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566826</v>
+        <v>122566884</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1857,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461846</v>
+        <v>461793</v>
       </c>
       <c r="R13" t="n">
-        <v>6788492</v>
+        <v>6788303</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566863</v>
+        <v>122566820</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1959,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461589</v>
+        <v>461732</v>
       </c>
       <c r="R14" t="n">
-        <v>6788148</v>
+        <v>6788430</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566886</v>
+        <v>122566887</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2023,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2064,7 +2054,7 @@
         <v>461810</v>
       </c>
       <c r="R15" t="n">
-        <v>6788325</v>
+        <v>6788470</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566872</v>
+        <v>122566803</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461659</v>
+        <v>461598</v>
       </c>
       <c r="R16" t="n">
-        <v>6788194</v>
+        <v>6788148</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566820</v>
+        <v>122566828</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2265,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461732</v>
+        <v>461923</v>
       </c>
       <c r="R17" t="n">
-        <v>6788430</v>
+        <v>6788324</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566885</v>
+        <v>122566834</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2367,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461804</v>
+        <v>461929</v>
       </c>
       <c r="R18" t="n">
-        <v>6788319</v>
+        <v>6788262</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,7 +2419,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566849</v>
+        <v>122566852</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2469,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461787</v>
+        <v>461741</v>
       </c>
       <c r="R19" t="n">
-        <v>6788182</v>
+        <v>6788170</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566842</v>
+        <v>122566885</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2571,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461803</v>
+        <v>461804</v>
       </c>
       <c r="R20" t="n">
-        <v>6788243</v>
+        <v>6788319</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566843</v>
+        <v>122566830</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2673,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461811</v>
+        <v>461991</v>
       </c>
       <c r="R21" t="n">
-        <v>6788237</v>
+        <v>6788324</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566887</v>
+        <v>122566863</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461810</v>
+        <v>461589</v>
       </c>
       <c r="R22" t="n">
-        <v>6788470</v>
+        <v>6788148</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566888</v>
+        <v>122566877</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,25 +2839,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461791</v>
+        <v>461706</v>
       </c>
       <c r="R23" t="n">
-        <v>6788187</v>
+        <v>6788223</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566803</v>
+        <v>122566881</v>
       </c>
       <c r="B24" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461598</v>
+        <v>461742</v>
       </c>
       <c r="R24" t="n">
-        <v>6788148</v>
+        <v>6788295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566840</v>
+        <v>122566808</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461810</v>
+        <v>461872</v>
       </c>
       <c r="R25" t="n">
-        <v>6788278</v>
+        <v>6788413</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,7 +3133,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566877</v>
+        <v>122566825</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3183,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461706</v>
+        <v>461843</v>
       </c>
       <c r="R26" t="n">
-        <v>6788223</v>
+        <v>6788468</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,7 +3235,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566876</v>
+        <v>122566874</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3285,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461695</v>
+        <v>461665</v>
       </c>
       <c r="R27" t="n">
-        <v>6788224</v>
+        <v>6788207</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,7 +3337,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566831</v>
+        <v>122566851</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3387,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462004</v>
+        <v>461758</v>
       </c>
       <c r="R28" t="n">
-        <v>6788320</v>
+        <v>6788174</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,7 +3439,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566834</v>
+        <v>122566827</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3489,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461929</v>
+        <v>461879</v>
       </c>
       <c r="R29" t="n">
-        <v>6788262</v>
+        <v>6788396</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566850</v>
+        <v>122566818</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3591,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461771</v>
+        <v>461816</v>
       </c>
       <c r="R30" t="n">
-        <v>6788185</v>
+        <v>6788330</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,7 +3643,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566862</v>
+        <v>122566821</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3693,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461562</v>
+        <v>461699</v>
       </c>
       <c r="R31" t="n">
-        <v>6788141</v>
+        <v>6788443</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,7 +3745,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566818</v>
+        <v>122566824</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -3795,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461816</v>
+        <v>461810</v>
       </c>
       <c r="R32" t="n">
-        <v>6788330</v>
+        <v>6788470</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,7 +3847,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566852</v>
+        <v>122566817</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -3897,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461741</v>
+        <v>461788</v>
       </c>
       <c r="R33" t="n">
-        <v>6788170</v>
+        <v>6788303</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,7 +3949,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566874</v>
+        <v>122566822</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -3999,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461665</v>
+        <v>461763</v>
       </c>
       <c r="R34" t="n">
-        <v>6788207</v>
+        <v>6788475</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,7 +4051,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566875</v>
+        <v>122566826</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4101,10 +4091,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461669</v>
+        <v>461846</v>
       </c>
       <c r="R35" t="n">
-        <v>6788203</v>
+        <v>6788492</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,7 +4153,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566833</v>
+        <v>122566882</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4203,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461972</v>
+        <v>461757</v>
       </c>
       <c r="R36" t="n">
-        <v>6788277</v>
+        <v>6788299</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,7 +4255,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566821</v>
+        <v>122566819</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4299,16 +4289,21 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461699</v>
+        <v>461667</v>
       </c>
       <c r="R37" t="n">
-        <v>6788443</v>
+        <v>6788182</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,7 +4362,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566804</v>
+        <v>122566801</v>
       </c>
       <c r="B38" t="n">
         <v>79384</v>
@@ -4407,10 +4402,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461614</v>
+        <v>461945</v>
       </c>
       <c r="R38" t="n">
-        <v>6788152</v>
+        <v>6788255</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,7 +4464,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566854</v>
+        <v>122566823</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4509,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461714</v>
+        <v>461778</v>
       </c>
       <c r="R39" t="n">
-        <v>6788188</v>
+        <v>6788485</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,7 +4566,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566871</v>
+        <v>122566862</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461676</v>
+        <v>461562</v>
       </c>
       <c r="R40" t="n">
-        <v>6788174</v>
+        <v>6788141</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,7 +4668,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566881</v>
+        <v>122566861</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4713,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461742</v>
+        <v>461537</v>
       </c>
       <c r="R41" t="n">
-        <v>6788295</v>
+        <v>6788149</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4775,10 +4770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566829</v>
+        <v>122566811</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,34 +4786,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461952</v>
+        <v>461936</v>
       </c>
       <c r="R42" t="n">
-        <v>6788327</v>
+        <v>6788279</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4877,7 +4877,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566882</v>
+        <v>122566853</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461757</v>
+        <v>461732</v>
       </c>
       <c r="R43" t="n">
-        <v>6788299</v>
+        <v>6788166</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566883</v>
+        <v>122566849</v>
       </c>
       <c r="B44" t="n">
         <v>78766</v>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461777</v>
+        <v>461787</v>
       </c>
       <c r="R44" t="n">
-        <v>6788298</v>
+        <v>6788182</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5081,7 +5081,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566861</v>
+        <v>122566878</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461537</v>
+        <v>461712</v>
       </c>
       <c r="R45" t="n">
-        <v>6788149</v>
+        <v>6788236</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,7 +5183,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566847</v>
+        <v>122566841</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461789</v>
+        <v>461809</v>
       </c>
       <c r="R46" t="n">
-        <v>6788194</v>
+        <v>6788250</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5285,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566844</v>
+        <v>122566802</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5301,21 +5301,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461816</v>
+        <v>461811</v>
       </c>
       <c r="R47" t="n">
-        <v>6788215</v>
+        <v>6788280</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,7 +5387,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566835</v>
+        <v>122566871</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461929</v>
+        <v>461676</v>
       </c>
       <c r="R48" t="n">
-        <v>6788278</v>
+        <v>6788174</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566855</v>
+        <v>122566872</v>
       </c>
       <c r="B49" t="n">
         <v>78766</v>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461704</v>
+        <v>461659</v>
       </c>
       <c r="R49" t="n">
-        <v>6788171</v>
+        <v>6788194</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,7 +5591,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566825</v>
+        <v>122566832</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461843</v>
+        <v>461991</v>
       </c>
       <c r="R50" t="n">
-        <v>6788468</v>
+        <v>6788292</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566801</v>
+        <v>122566835</v>
       </c>
       <c r="B51" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5709,21 +5709,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461945</v>
+        <v>461929</v>
       </c>
       <c r="R51" t="n">
-        <v>6788255</v>
+        <v>6788278</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566880</v>
+        <v>122566814</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5811,21 +5811,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461737</v>
+        <v>461814</v>
       </c>
       <c r="R52" t="n">
-        <v>6788251</v>
+        <v>6788266</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566878</v>
+        <v>122566888</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,25 +5909,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461712</v>
+        <v>461791</v>
       </c>
       <c r="R53" t="n">
-        <v>6788236</v>
+        <v>6788187</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,7 +5999,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566846</v>
+        <v>122566840</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461791</v>
+        <v>461810</v>
       </c>
       <c r="R54" t="n">
-        <v>6788209</v>
+        <v>6788278</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,7 +6101,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566828</v>
+        <v>122566846</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461923</v>
+        <v>461791</v>
       </c>
       <c r="R55" t="n">
-        <v>6788324</v>
+        <v>6788209</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6203,7 +6203,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566830</v>
+        <v>122566845</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461991</v>
+        <v>461794</v>
       </c>
       <c r="R56" t="n">
-        <v>6788324</v>
+        <v>6788217</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6305,10 +6305,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566879</v>
+        <v>122566809</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6321,21 +6321,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461721</v>
+        <v>461822</v>
       </c>
       <c r="R57" t="n">
-        <v>6788242</v>
+        <v>6788353</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566824</v>
+        <v>122566864</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461810</v>
+        <v>461619</v>
       </c>
       <c r="R58" t="n">
-        <v>6788470</v>
+        <v>6788144</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6509,10 +6509,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566839</v>
+        <v>122566807</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6525,21 +6525,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461829</v>
+        <v>461739</v>
       </c>
       <c r="R59" t="n">
-        <v>6788287</v>
+        <v>6788280</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,7 +6611,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566853</v>
+        <v>122566865</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461732</v>
+        <v>461628</v>
       </c>
       <c r="R60" t="n">
-        <v>6788166</v>
+        <v>6788142</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566864</v>
+        <v>122566880</v>
       </c>
       <c r="B61" t="n">
         <v>78766</v>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461619</v>
+        <v>461737</v>
       </c>
       <c r="R61" t="n">
-        <v>6788144</v>
+        <v>6788251</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566851</v>
+        <v>122566805</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6831,21 +6831,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461758</v>
+        <v>461848</v>
       </c>
       <c r="R62" t="n">
-        <v>6788174</v>
+        <v>6788429</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6917,10 +6917,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566808</v>
+        <v>122566855</v>
       </c>
       <c r="B63" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6933,21 +6933,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461872</v>
+        <v>461704</v>
       </c>
       <c r="R63" t="n">
-        <v>6788413</v>
+        <v>6788171</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7019,10 +7019,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566814</v>
+        <v>122566854</v>
       </c>
       <c r="B64" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461814</v>
+        <v>461714</v>
       </c>
       <c r="R64" t="n">
-        <v>6788266</v>
+        <v>6788188</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7121,7 +7121,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566884</v>
+        <v>122566829</v>
       </c>
       <c r="B65" t="n">
         <v>78766</v>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461793</v>
+        <v>461952</v>
       </c>
       <c r="R65" t="n">
-        <v>6788303</v>
+        <v>6788327</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7223,7 +7223,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566848</v>
+        <v>122566842</v>
       </c>
       <c r="B66" t="n">
         <v>78766</v>
@@ -7263,10 +7263,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461791</v>
+        <v>461803</v>
       </c>
       <c r="R66" t="n">
-        <v>6788187</v>
+        <v>6788243</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7325,7 +7325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566841</v>
+        <v>122566883</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461809</v>
+        <v>461777</v>
       </c>
       <c r="R67" t="n">
-        <v>6788250</v>
+        <v>6788298</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7427,7 +7427,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566832</v>
+        <v>122566844</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461991</v>
+        <v>461816</v>
       </c>
       <c r="R68" t="n">
-        <v>6788292</v>
+        <v>6788215</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7529,10 +7529,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566802</v>
+        <v>122566839</v>
       </c>
       <c r="B69" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7545,21 +7545,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461811</v>
+        <v>461829</v>
       </c>
       <c r="R69" t="n">
-        <v>6788280</v>
+        <v>6788287</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566811</v>
+        <v>122566816</v>
       </c>
       <c r="B70" t="n">
         <v>57494</v>
@@ -7676,10 +7676,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461936</v>
+        <v>461930</v>
       </c>
       <c r="R70" t="n">
-        <v>6788279</v>
+        <v>6788270</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566823</v>
+        <v>122566831</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461778</v>
+        <v>462004</v>
       </c>
       <c r="R71" t="n">
-        <v>6788485</v>
+        <v>6788320</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566807</v>
+        <v>122566850</v>
       </c>
       <c r="B72" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7856,21 +7856,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7880,10 +7880,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461739</v>
+        <v>461771</v>
       </c>
       <c r="R72" t="n">
-        <v>6788280</v>
+        <v>6788185</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7942,7 +7942,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566838</v>
+        <v>122566843</v>
       </c>
       <c r="B73" t="n">
         <v>78766</v>
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461878</v>
+        <v>461811</v>
       </c>
       <c r="R73" t="n">
-        <v>6788313</v>
+        <v>6788237</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8044,10 +8044,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566805</v>
+        <v>122566847</v>
       </c>
       <c r="B74" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8060,21 +8060,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461848</v>
+        <v>461789</v>
       </c>
       <c r="R74" t="n">
-        <v>6788429</v>
+        <v>6788194</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566873</v>
+        <v>122566869</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461655</v>
+        <v>461678</v>
       </c>
       <c r="R75" t="n">
-        <v>6788205</v>
+        <v>6788157</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8248,7 +8248,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566845</v>
+        <v>122566838</v>
       </c>
       <c r="B76" t="n">
         <v>78766</v>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461794</v>
+        <v>461878</v>
       </c>
       <c r="R76" t="n">
-        <v>6788217</v>
+        <v>6788313</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566859</v>
+        <v>122566873</v>
       </c>
       <c r="B77" t="n">
         <v>78766</v>
@@ -8390,10 +8390,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461506</v>
+        <v>461655</v>
       </c>
       <c r="R77" t="n">
-        <v>6788139</v>
+        <v>6788205</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8452,7 +8452,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566827</v>
+        <v>122566879</v>
       </c>
       <c r="B78" t="n">
         <v>78766</v>
@@ -8492,10 +8492,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461879</v>
+        <v>461721</v>
       </c>
       <c r="R78" t="n">
-        <v>6788396</v>
+        <v>6788242</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489147</v>
+        <v>122489220</v>
       </c>
       <c r="B2" t="n">
-        <v>90964</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461988</v>
+        <v>461881</v>
       </c>
       <c r="R2" t="n">
-        <v>6788288</v>
+        <v>6788296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122488593</v>
+        <v>122489147</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122489220</v>
+        <v>122488593</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461881</v>
+        <v>461988</v>
       </c>
       <c r="R4" t="n">
-        <v>6788296</v>
+        <v>6788288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566848</v>
+        <v>122566820</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461791</v>
+        <v>461732</v>
       </c>
       <c r="R5" t="n">
-        <v>6788187</v>
+        <v>6788430</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566804</v>
+        <v>122566843</v>
       </c>
       <c r="B6" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461614</v>
+        <v>461811</v>
       </c>
       <c r="R6" t="n">
-        <v>6788152</v>
+        <v>6788237</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566833</v>
+        <v>122566859</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461972</v>
+        <v>461506</v>
       </c>
       <c r="R7" t="n">
-        <v>6788277</v>
+        <v>6788139</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566886</v>
+        <v>122566852</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461810</v>
+        <v>461741</v>
       </c>
       <c r="R8" t="n">
-        <v>6788325</v>
+        <v>6788170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566875</v>
+        <v>122566838</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461669</v>
+        <v>461878</v>
       </c>
       <c r="R9" t="n">
-        <v>6788203</v>
+        <v>6788313</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566837</v>
+        <v>122566840</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461917</v>
+        <v>461810</v>
       </c>
       <c r="R10" t="n">
-        <v>6788292</v>
+        <v>6788278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566859</v>
+        <v>122566809</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461506</v>
+        <v>461822</v>
       </c>
       <c r="R11" t="n">
-        <v>6788139</v>
+        <v>6788353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566876</v>
+        <v>122566811</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,34 +1721,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461695</v>
+        <v>461936</v>
       </c>
       <c r="R12" t="n">
-        <v>6788224</v>
+        <v>6788279</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566884</v>
+        <v>122566869</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1847,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461793</v>
+        <v>461678</v>
       </c>
       <c r="R13" t="n">
-        <v>6788303</v>
+        <v>6788157</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566820</v>
+        <v>122566821</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461732</v>
+        <v>461699</v>
       </c>
       <c r="R14" t="n">
-        <v>6788430</v>
+        <v>6788443</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566887</v>
+        <v>122566888</v>
       </c>
       <c r="B15" t="n">
         <v>5173</v>
@@ -2051,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461810</v>
+        <v>461791</v>
       </c>
       <c r="R15" t="n">
-        <v>6788470</v>
+        <v>6788187</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566803</v>
+        <v>122566835</v>
       </c>
       <c r="B16" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461598</v>
+        <v>461929</v>
       </c>
       <c r="R16" t="n">
-        <v>6788148</v>
+        <v>6788278</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566828</v>
+        <v>122566834</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2255,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461923</v>
+        <v>461929</v>
       </c>
       <c r="R17" t="n">
-        <v>6788324</v>
+        <v>6788262</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566834</v>
+        <v>122566850</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2357,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461929</v>
+        <v>461771</v>
       </c>
       <c r="R18" t="n">
-        <v>6788262</v>
+        <v>6788185</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,7 +2424,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566852</v>
+        <v>122566831</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2459,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461741</v>
+        <v>462004</v>
       </c>
       <c r="R19" t="n">
-        <v>6788170</v>
+        <v>6788320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566885</v>
+        <v>122566848</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2561,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461804</v>
+        <v>461791</v>
       </c>
       <c r="R20" t="n">
-        <v>6788319</v>
+        <v>6788187</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,7 +2628,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566830</v>
+        <v>122566875</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2663,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461991</v>
+        <v>461669</v>
       </c>
       <c r="R21" t="n">
-        <v>6788324</v>
+        <v>6788203</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566863</v>
+        <v>122566883</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2765,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461589</v>
+        <v>461777</v>
       </c>
       <c r="R22" t="n">
-        <v>6788148</v>
+        <v>6788298</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2832,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566877</v>
+        <v>122566844</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2867,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461706</v>
+        <v>461816</v>
       </c>
       <c r="R23" t="n">
-        <v>6788223</v>
+        <v>6788215</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,7 +2934,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566881</v>
+        <v>122566829</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -2969,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461742</v>
+        <v>461952</v>
       </c>
       <c r="R24" t="n">
-        <v>6788295</v>
+        <v>6788327</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566808</v>
+        <v>122566862</v>
       </c>
       <c r="B25" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3052,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461872</v>
+        <v>461562</v>
       </c>
       <c r="R25" t="n">
-        <v>6788413</v>
+        <v>6788141</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,7 +3138,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566825</v>
+        <v>122566861</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3173,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461843</v>
+        <v>461537</v>
       </c>
       <c r="R26" t="n">
-        <v>6788468</v>
+        <v>6788149</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,7 +3240,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566874</v>
+        <v>122566876</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3275,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461665</v>
+        <v>461695</v>
       </c>
       <c r="R27" t="n">
-        <v>6788207</v>
+        <v>6788224</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566851</v>
+        <v>122566805</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3358,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461758</v>
+        <v>461848</v>
       </c>
       <c r="R28" t="n">
-        <v>6788174</v>
+        <v>6788429</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,7 +3444,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566827</v>
+        <v>122566854</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3479,10 +3484,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461879</v>
+        <v>461714</v>
       </c>
       <c r="R29" t="n">
-        <v>6788396</v>
+        <v>6788188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,7 +3546,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566818</v>
+        <v>122566851</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3581,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461816</v>
+        <v>461758</v>
       </c>
       <c r="R30" t="n">
-        <v>6788330</v>
+        <v>6788174</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,7 +3648,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566821</v>
+        <v>122566874</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3683,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461699</v>
+        <v>461665</v>
       </c>
       <c r="R31" t="n">
-        <v>6788443</v>
+        <v>6788207</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,7 +3750,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566824</v>
+        <v>122566884</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -3785,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461810</v>
+        <v>461793</v>
       </c>
       <c r="R32" t="n">
-        <v>6788470</v>
+        <v>6788303</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3852,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566817</v>
+        <v>122566814</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3868,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3892,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461788</v>
+        <v>461814</v>
       </c>
       <c r="R33" t="n">
-        <v>6788303</v>
+        <v>6788266</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3954,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566822</v>
+        <v>122566802</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3965,21 +3970,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,10 +3994,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461763</v>
+        <v>461811</v>
       </c>
       <c r="R34" t="n">
-        <v>6788475</v>
+        <v>6788280</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,7 +4056,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566826</v>
+        <v>122566863</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4091,10 +4096,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461846</v>
+        <v>461589</v>
       </c>
       <c r="R35" t="n">
-        <v>6788492</v>
+        <v>6788148</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,7 +4158,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566882</v>
+        <v>122566872</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4193,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461757</v>
+        <v>461659</v>
       </c>
       <c r="R36" t="n">
-        <v>6788299</v>
+        <v>6788194</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,7 +4260,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566819</v>
+        <v>122566832</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4289,21 +4294,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461667</v>
+        <v>461991</v>
       </c>
       <c r="R37" t="n">
-        <v>6788182</v>
+        <v>6788292</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4362,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566801</v>
+        <v>122566819</v>
       </c>
       <c r="B38" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4378,34 +4378,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461945</v>
+        <v>461667</v>
       </c>
       <c r="R38" t="n">
-        <v>6788255</v>
+        <v>6788182</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566823</v>
+        <v>122566808</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4480,21 +4485,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4504,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461778</v>
+        <v>461872</v>
       </c>
       <c r="R39" t="n">
-        <v>6788485</v>
+        <v>6788413</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,7 +4571,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566862</v>
+        <v>122566817</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461562</v>
+        <v>461788</v>
       </c>
       <c r="R40" t="n">
-        <v>6788141</v>
+        <v>6788303</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,7 +4673,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566861</v>
+        <v>122566882</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4708,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461537</v>
+        <v>461757</v>
       </c>
       <c r="R41" t="n">
-        <v>6788149</v>
+        <v>6788299</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4775,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566811</v>
+        <v>122566822</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4786,39 +4791,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461936</v>
+        <v>461763</v>
       </c>
       <c r="R42" t="n">
-        <v>6788279</v>
+        <v>6788475</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4877,7 +4877,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566853</v>
+        <v>122566881</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461732</v>
+        <v>461742</v>
       </c>
       <c r="R43" t="n">
-        <v>6788166</v>
+        <v>6788295</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566849</v>
+        <v>122566826</v>
       </c>
       <c r="B44" t="n">
         <v>78766</v>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461787</v>
+        <v>461846</v>
       </c>
       <c r="R44" t="n">
-        <v>6788182</v>
+        <v>6788492</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5081,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566878</v>
+        <v>122566807</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,21 +5097,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461712</v>
+        <v>461739</v>
       </c>
       <c r="R45" t="n">
-        <v>6788236</v>
+        <v>6788280</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,7 +5183,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566841</v>
+        <v>122566864</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461809</v>
+        <v>461619</v>
       </c>
       <c r="R46" t="n">
-        <v>6788250</v>
+        <v>6788144</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5285,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566802</v>
+        <v>122566849</v>
       </c>
       <c r="B47" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5301,21 +5301,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461811</v>
+        <v>461787</v>
       </c>
       <c r="R47" t="n">
-        <v>6788280</v>
+        <v>6788182</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,7 +5387,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566871</v>
+        <v>122566880</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461676</v>
+        <v>461737</v>
       </c>
       <c r="R48" t="n">
-        <v>6788174</v>
+        <v>6788251</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566872</v>
+        <v>122566804</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461659</v>
+        <v>461614</v>
       </c>
       <c r="R49" t="n">
-        <v>6788194</v>
+        <v>6788152</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566832</v>
+        <v>122566803</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,21 +5607,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461991</v>
+        <v>461598</v>
       </c>
       <c r="R50" t="n">
-        <v>6788292</v>
+        <v>6788148</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566835</v>
+        <v>122566801</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5709,21 +5709,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461929</v>
+        <v>461945</v>
       </c>
       <c r="R51" t="n">
-        <v>6788278</v>
+        <v>6788255</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566814</v>
+        <v>122566818</v>
       </c>
       <c r="B52" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5811,21 +5811,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461814</v>
+        <v>461816</v>
       </c>
       <c r="R52" t="n">
-        <v>6788266</v>
+        <v>6788330</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566888</v>
+        <v>122566878</v>
       </c>
       <c r="B53" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,25 +5909,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461791</v>
+        <v>461712</v>
       </c>
       <c r="R53" t="n">
-        <v>6788187</v>
+        <v>6788236</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,7 +5999,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566840</v>
+        <v>122566825</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461810</v>
+        <v>461843</v>
       </c>
       <c r="R54" t="n">
-        <v>6788278</v>
+        <v>6788468</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,7 +6101,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566846</v>
+        <v>122566845</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461791</v>
+        <v>461794</v>
       </c>
       <c r="R55" t="n">
-        <v>6788209</v>
+        <v>6788217</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6203,7 +6203,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566845</v>
+        <v>122566877</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461794</v>
+        <v>461706</v>
       </c>
       <c r="R56" t="n">
-        <v>6788217</v>
+        <v>6788223</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6305,10 +6305,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566809</v>
+        <v>122566841</v>
       </c>
       <c r="B57" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6321,21 +6321,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461822</v>
+        <v>461809</v>
       </c>
       <c r="R57" t="n">
-        <v>6788353</v>
+        <v>6788250</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566864</v>
+        <v>122566879</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461619</v>
+        <v>461721</v>
       </c>
       <c r="R58" t="n">
-        <v>6788144</v>
+        <v>6788242</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6509,10 +6509,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566807</v>
+        <v>122566816</v>
       </c>
       <c r="B59" t="n">
-        <v>74863</v>
+        <v>57494</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6525,34 +6525,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461739</v>
+        <v>461930</v>
       </c>
       <c r="R59" t="n">
-        <v>6788280</v>
+        <v>6788270</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,7 +6616,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566865</v>
+        <v>122566837</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -6651,10 +6656,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461628</v>
+        <v>461917</v>
       </c>
       <c r="R60" t="n">
-        <v>6788142</v>
+        <v>6788292</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6713,10 +6718,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566880</v>
+        <v>122566887</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6725,25 +6730,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6753,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461737</v>
+        <v>461810</v>
       </c>
       <c r="R61" t="n">
-        <v>6788251</v>
+        <v>6788470</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6815,10 +6820,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566805</v>
+        <v>122566855</v>
       </c>
       <c r="B62" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6831,21 +6836,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6855,10 +6860,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461848</v>
+        <v>461704</v>
       </c>
       <c r="R62" t="n">
-        <v>6788429</v>
+        <v>6788171</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6917,7 +6922,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566855</v>
+        <v>122566873</v>
       </c>
       <c r="B63" t="n">
         <v>78766</v>
@@ -6957,10 +6962,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461704</v>
+        <v>461655</v>
       </c>
       <c r="R63" t="n">
-        <v>6788171</v>
+        <v>6788205</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7019,7 +7024,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566854</v>
+        <v>122566827</v>
       </c>
       <c r="B64" t="n">
         <v>78766</v>
@@ -7059,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461714</v>
+        <v>461879</v>
       </c>
       <c r="R64" t="n">
-        <v>6788188</v>
+        <v>6788396</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7121,7 +7126,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566829</v>
+        <v>122566886</v>
       </c>
       <c r="B65" t="n">
         <v>78766</v>
@@ -7161,10 +7166,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461952</v>
+        <v>461810</v>
       </c>
       <c r="R65" t="n">
-        <v>6788327</v>
+        <v>6788325</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7325,7 +7330,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566883</v>
+        <v>122566824</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -7365,10 +7370,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461777</v>
+        <v>461810</v>
       </c>
       <c r="R67" t="n">
-        <v>6788298</v>
+        <v>6788470</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7427,7 +7432,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566844</v>
+        <v>122566853</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -7467,10 +7472,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461816</v>
+        <v>461732</v>
       </c>
       <c r="R68" t="n">
-        <v>6788215</v>
+        <v>6788166</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7529,7 +7534,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566839</v>
+        <v>122566830</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -7569,10 +7574,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461829</v>
+        <v>461991</v>
       </c>
       <c r="R69" t="n">
-        <v>6788287</v>
+        <v>6788324</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7631,10 +7636,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566816</v>
+        <v>122566839</v>
       </c>
       <c r="B70" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7647,39 +7652,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461930</v>
+        <v>461829</v>
       </c>
       <c r="R70" t="n">
-        <v>6788270</v>
+        <v>6788287</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566831</v>
+        <v>122566865</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>462004</v>
+        <v>461628</v>
       </c>
       <c r="R71" t="n">
-        <v>6788320</v>
+        <v>6788142</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7840,7 +7840,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566850</v>
+        <v>122566823</v>
       </c>
       <c r="B72" t="n">
         <v>78766</v>
@@ -7880,10 +7880,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461771</v>
+        <v>461778</v>
       </c>
       <c r="R72" t="n">
-        <v>6788185</v>
+        <v>6788485</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7942,7 +7942,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566843</v>
+        <v>122566847</v>
       </c>
       <c r="B73" t="n">
         <v>78766</v>
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461811</v>
+        <v>461789</v>
       </c>
       <c r="R73" t="n">
-        <v>6788237</v>
+        <v>6788194</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8044,7 +8044,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566847</v>
+        <v>122566828</v>
       </c>
       <c r="B74" t="n">
         <v>78766</v>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461789</v>
+        <v>461923</v>
       </c>
       <c r="R74" t="n">
-        <v>6788194</v>
+        <v>6788324</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566869</v>
+        <v>122566833</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461678</v>
+        <v>461972</v>
       </c>
       <c r="R75" t="n">
-        <v>6788157</v>
+        <v>6788277</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8248,7 +8248,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566838</v>
+        <v>122566885</v>
       </c>
       <c r="B76" t="n">
         <v>78766</v>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461878</v>
+        <v>461804</v>
       </c>
       <c r="R76" t="n">
-        <v>6788313</v>
+        <v>6788319</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566873</v>
+        <v>122566846</v>
       </c>
       <c r="B77" t="n">
         <v>78766</v>
@@ -8390,10 +8390,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461655</v>
+        <v>461791</v>
       </c>
       <c r="R77" t="n">
-        <v>6788205</v>
+        <v>6788209</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8452,7 +8452,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566879</v>
+        <v>122566871</v>
       </c>
       <c r="B78" t="n">
         <v>78766</v>
@@ -8492,10 +8492,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461721</v>
+        <v>461676</v>
       </c>
       <c r="R78" t="n">
-        <v>6788242</v>
+        <v>6788174</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122489274</v>
+        <v>122566813</v>
       </c>
       <c r="B81" t="n">
         <v>57478</v>
@@ -8813,24 +8813,21 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461895</v>
+        <v>461803</v>
       </c>
       <c r="R81" t="n">
-        <v>6788288</v>
+        <v>6788243</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8857,17 +8854,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8882,19 +8879,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122566813</v>
+        <v>122489274</v>
       </c>
       <c r="B82" t="n">
         <v>57478</v>
@@ -8928,21 +8925,24 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461803</v>
+        <v>461895</v>
       </c>
       <c r="R82" t="n">
-        <v>6788243</v>
+        <v>6788288</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8994,12 +8994,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566811</v>
+        <v>122566869</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,39 +1721,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461936</v>
+        <v>461678</v>
       </c>
       <c r="R12" t="n">
-        <v>6788279</v>
+        <v>6788157</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566869</v>
+        <v>122566821</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1852,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461678</v>
+        <v>461699</v>
       </c>
       <c r="R13" t="n">
-        <v>6788157</v>
+        <v>6788443</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566821</v>
+        <v>122566811</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,34 +1925,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461699</v>
+        <v>461936</v>
       </c>
       <c r="R14" t="n">
-        <v>6788443</v>
+        <v>6788279</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566854</v>
+        <v>122566851</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461714</v>
+        <v>461758</v>
       </c>
       <c r="R29" t="n">
-        <v>6788188</v>
+        <v>6788174</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566851</v>
+        <v>122566874</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461758</v>
+        <v>461665</v>
       </c>
       <c r="R30" t="n">
-        <v>6788174</v>
+        <v>6788207</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566874</v>
+        <v>122566884</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461665</v>
+        <v>461793</v>
       </c>
       <c r="R31" t="n">
-        <v>6788207</v>
+        <v>6788303</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566884</v>
+        <v>122566854</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461793</v>
+        <v>461714</v>
       </c>
       <c r="R32" t="n">
-        <v>6788303</v>
+        <v>6788188</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -5897,7 +5897,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566878</v>
+        <v>122566825</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461712</v>
+        <v>461843</v>
       </c>
       <c r="R53" t="n">
-        <v>6788236</v>
+        <v>6788468</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,7 +5999,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566825</v>
+        <v>122566845</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461843</v>
+        <v>461794</v>
       </c>
       <c r="R54" t="n">
-        <v>6788468</v>
+        <v>6788217</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,7 +6101,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566845</v>
+        <v>122566878</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461794</v>
+        <v>461712</v>
       </c>
       <c r="R55" t="n">
-        <v>6788217</v>
+        <v>6788236</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7330,7 +7330,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566824</v>
+        <v>122566853</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461810</v>
+        <v>461732</v>
       </c>
       <c r="R67" t="n">
-        <v>6788470</v>
+        <v>6788166</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7432,7 +7432,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566853</v>
+        <v>122566830</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461732</v>
+        <v>461991</v>
       </c>
       <c r="R68" t="n">
-        <v>6788166</v>
+        <v>6788324</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7534,7 +7534,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566830</v>
+        <v>122566839</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -7574,10 +7574,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461991</v>
+        <v>461829</v>
       </c>
       <c r="R69" t="n">
-        <v>6788324</v>
+        <v>6788287</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7636,7 +7636,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566839</v>
+        <v>122566865</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -7676,10 +7676,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461829</v>
+        <v>461628</v>
       </c>
       <c r="R70" t="n">
-        <v>6788287</v>
+        <v>6788142</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566865</v>
+        <v>122566824</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461628</v>
+        <v>461810</v>
       </c>
       <c r="R71" t="n">
-        <v>6788142</v>
+        <v>6788470</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7840,7 +7840,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566823</v>
+        <v>122566847</v>
       </c>
       <c r="B72" t="n">
         <v>78766</v>
@@ -7880,10 +7880,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461778</v>
+        <v>461789</v>
       </c>
       <c r="R72" t="n">
-        <v>6788485</v>
+        <v>6788194</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7942,7 +7942,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566847</v>
+        <v>122566823</v>
       </c>
       <c r="B73" t="n">
         <v>78766</v>
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461789</v>
+        <v>461778</v>
       </c>
       <c r="R73" t="n">
-        <v>6788194</v>
+        <v>6788485</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566869</v>
+        <v>122566811</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,34 +1721,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461678</v>
+        <v>461936</v>
       </c>
       <c r="R12" t="n">
-        <v>6788157</v>
+        <v>6788279</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566821</v>
+        <v>122566869</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1847,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461699</v>
+        <v>461678</v>
       </c>
       <c r="R13" t="n">
-        <v>6788443</v>
+        <v>6788157</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566811</v>
+        <v>122566821</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,39 +1930,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461936</v>
+        <v>461699</v>
       </c>
       <c r="R14" t="n">
-        <v>6788279</v>
+        <v>6788443</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -7330,7 +7330,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566853</v>
+        <v>122566824</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461732</v>
+        <v>461810</v>
       </c>
       <c r="R67" t="n">
-        <v>6788166</v>
+        <v>6788470</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7432,7 +7432,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566830</v>
+        <v>122566853</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461991</v>
+        <v>461732</v>
       </c>
       <c r="R68" t="n">
-        <v>6788324</v>
+        <v>6788166</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7534,7 +7534,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566839</v>
+        <v>122566830</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -7574,10 +7574,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461829</v>
+        <v>461991</v>
       </c>
       <c r="R69" t="n">
-        <v>6788287</v>
+        <v>6788324</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7636,7 +7636,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566865</v>
+        <v>122566839</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -7676,10 +7676,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461628</v>
+        <v>461829</v>
       </c>
       <c r="R70" t="n">
-        <v>6788142</v>
+        <v>6788287</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566824</v>
+        <v>122566865</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461810</v>
+        <v>461628</v>
       </c>
       <c r="R71" t="n">
-        <v>6788470</v>
+        <v>6788142</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -7330,7 +7330,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566824</v>
+        <v>122566853</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461810</v>
+        <v>461732</v>
       </c>
       <c r="R67" t="n">
-        <v>6788470</v>
+        <v>6788166</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7432,7 +7432,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566853</v>
+        <v>122566830</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461732</v>
+        <v>461991</v>
       </c>
       <c r="R68" t="n">
-        <v>6788166</v>
+        <v>6788324</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7534,7 +7534,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566830</v>
+        <v>122566839</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -7574,10 +7574,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461991</v>
+        <v>461829</v>
       </c>
       <c r="R69" t="n">
-        <v>6788324</v>
+        <v>6788287</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7636,7 +7636,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566839</v>
+        <v>122566865</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -7676,10 +7676,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461829</v>
+        <v>461628</v>
       </c>
       <c r="R70" t="n">
-        <v>6788287</v>
+        <v>6788142</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566865</v>
+        <v>122566824</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461628</v>
+        <v>461810</v>
       </c>
       <c r="R71" t="n">
-        <v>6788142</v>
+        <v>6788470</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7840,7 +7840,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566847</v>
+        <v>122566823</v>
       </c>
       <c r="B72" t="n">
         <v>78766</v>
@@ -7880,10 +7880,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461789</v>
+        <v>461778</v>
       </c>
       <c r="R72" t="n">
-        <v>6788194</v>
+        <v>6788485</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7942,7 +7942,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566823</v>
+        <v>122566847</v>
       </c>
       <c r="B73" t="n">
         <v>78766</v>
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461778</v>
+        <v>461789</v>
       </c>
       <c r="R73" t="n">
-        <v>6788485</v>
+        <v>6788194</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566820</v>
+        <v>122566854</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461732</v>
+        <v>461714</v>
       </c>
       <c r="R5" t="n">
-        <v>6788430</v>
+        <v>6788188</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566843</v>
+        <v>122566829</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461811</v>
+        <v>461952</v>
       </c>
       <c r="R6" t="n">
-        <v>6788237</v>
+        <v>6788327</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566859</v>
+        <v>122566838</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461506</v>
+        <v>461878</v>
       </c>
       <c r="R7" t="n">
-        <v>6788139</v>
+        <v>6788313</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566852</v>
+        <v>122566855</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461741</v>
+        <v>461704</v>
       </c>
       <c r="R8" t="n">
-        <v>6788170</v>
+        <v>6788171</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566838</v>
+        <v>122566865</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461878</v>
+        <v>461628</v>
       </c>
       <c r="R9" t="n">
-        <v>6788313</v>
+        <v>6788142</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566840</v>
+        <v>122566820</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461810</v>
+        <v>461732</v>
       </c>
       <c r="R10" t="n">
-        <v>6788278</v>
+        <v>6788430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566809</v>
+        <v>122566840</v>
       </c>
       <c r="B11" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461822</v>
+        <v>461810</v>
       </c>
       <c r="R11" t="n">
-        <v>6788353</v>
+        <v>6788278</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566811</v>
+        <v>122566814</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>78502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,39 +1721,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461936</v>
+        <v>461814</v>
       </c>
       <c r="R12" t="n">
-        <v>6788279</v>
+        <v>6788266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566869</v>
+        <v>122566830</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1852,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461678</v>
+        <v>461991</v>
       </c>
       <c r="R13" t="n">
-        <v>6788157</v>
+        <v>6788324</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566821</v>
+        <v>122566847</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461699</v>
+        <v>461789</v>
       </c>
       <c r="R14" t="n">
-        <v>6788443</v>
+        <v>6788194</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566888</v>
+        <v>122566872</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2023,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461791</v>
+        <v>461659</v>
       </c>
       <c r="R15" t="n">
-        <v>6788187</v>
+        <v>6788194</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566835</v>
+        <v>122566819</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2152,16 +2147,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461929</v>
+        <v>461667</v>
       </c>
       <c r="R16" t="n">
-        <v>6788278</v>
+        <v>6788182</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566834</v>
+        <v>122566886</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461929</v>
+        <v>461810</v>
       </c>
       <c r="R17" t="n">
-        <v>6788262</v>
+        <v>6788325</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566850</v>
+        <v>122566828</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461771</v>
+        <v>461923</v>
       </c>
       <c r="R18" t="n">
-        <v>6788185</v>
+        <v>6788324</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566831</v>
+        <v>122566821</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462004</v>
+        <v>461699</v>
       </c>
       <c r="R19" t="n">
-        <v>6788320</v>
+        <v>6788443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566848</v>
+        <v>122566888</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,25 +2538,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566875</v>
+        <v>122566844</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461669</v>
+        <v>461816</v>
       </c>
       <c r="R21" t="n">
-        <v>6788203</v>
+        <v>6788215</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566883</v>
+        <v>122566873</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461777</v>
+        <v>461655</v>
       </c>
       <c r="R22" t="n">
-        <v>6788298</v>
+        <v>6788205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566844</v>
+        <v>122566843</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461816</v>
+        <v>461811</v>
       </c>
       <c r="R23" t="n">
-        <v>6788215</v>
+        <v>6788237</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566829</v>
+        <v>122566877</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461952</v>
+        <v>461706</v>
       </c>
       <c r="R24" t="n">
-        <v>6788327</v>
+        <v>6788223</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566862</v>
+        <v>122566839</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461562</v>
+        <v>461829</v>
       </c>
       <c r="R25" t="n">
-        <v>6788141</v>
+        <v>6788287</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566861</v>
+        <v>122566848</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461537</v>
+        <v>461791</v>
       </c>
       <c r="R26" t="n">
-        <v>6788149</v>
+        <v>6788187</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566876</v>
+        <v>122566801</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3256,21 +3256,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461695</v>
+        <v>461945</v>
       </c>
       <c r="R27" t="n">
-        <v>6788224</v>
+        <v>6788255</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566805</v>
+        <v>122566804</v>
       </c>
       <c r="B28" t="n">
-        <v>74863</v>
+        <v>79384</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461848</v>
+        <v>461614</v>
       </c>
       <c r="R28" t="n">
-        <v>6788429</v>
+        <v>6788152</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566851</v>
+        <v>122566871</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461758</v>
+        <v>461676</v>
       </c>
       <c r="R29" t="n">
         <v>6788174</v>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566874</v>
+        <v>122566825</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461665</v>
+        <v>461843</v>
       </c>
       <c r="R30" t="n">
-        <v>6788207</v>
+        <v>6788468</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566884</v>
+        <v>122566802</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461793</v>
+        <v>461811</v>
       </c>
       <c r="R31" t="n">
-        <v>6788303</v>
+        <v>6788280</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,10 +3750,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566854</v>
+        <v>122566887</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3762,25 +3762,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461714</v>
+        <v>461810</v>
       </c>
       <c r="R32" t="n">
-        <v>6788188</v>
+        <v>6788470</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566814</v>
+        <v>122566837</v>
       </c>
       <c r="B33" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3868,21 +3868,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461814</v>
+        <v>461917</v>
       </c>
       <c r="R33" t="n">
-        <v>6788266</v>
+        <v>6788292</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3954,10 +3954,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566802</v>
+        <v>122566832</v>
       </c>
       <c r="B34" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3970,21 +3970,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461811</v>
+        <v>461991</v>
       </c>
       <c r="R34" t="n">
-        <v>6788280</v>
+        <v>6788292</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566863</v>
+        <v>122566864</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461589</v>
+        <v>461619</v>
       </c>
       <c r="R35" t="n">
-        <v>6788148</v>
+        <v>6788144</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566872</v>
+        <v>122566818</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461659</v>
+        <v>461816</v>
       </c>
       <c r="R36" t="n">
-        <v>6788194</v>
+        <v>6788330</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4260,7 +4260,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566832</v>
+        <v>122566826</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461991</v>
+        <v>461846</v>
       </c>
       <c r="R37" t="n">
-        <v>6788292</v>
+        <v>6788492</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4362,7 +4362,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566819</v>
+        <v>122566827</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4396,21 +4396,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461667</v>
+        <v>461879</v>
       </c>
       <c r="R38" t="n">
-        <v>6788182</v>
+        <v>6788396</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,10 +4464,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566808</v>
+        <v>122566869</v>
       </c>
       <c r="B39" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4485,21 +4480,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4509,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461872</v>
+        <v>461678</v>
       </c>
       <c r="R39" t="n">
-        <v>6788413</v>
+        <v>6788157</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,7 +4566,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566817</v>
+        <v>122566881</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461788</v>
+        <v>461742</v>
       </c>
       <c r="R40" t="n">
-        <v>6788303</v>
+        <v>6788295</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,7 +4668,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566882</v>
+        <v>122566876</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4713,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461757</v>
+        <v>461695</v>
       </c>
       <c r="R41" t="n">
-        <v>6788299</v>
+        <v>6788224</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4775,7 +4770,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566822</v>
+        <v>122566880</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4815,10 +4810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461763</v>
+        <v>461737</v>
       </c>
       <c r="R42" t="n">
-        <v>6788475</v>
+        <v>6788251</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4877,7 +4872,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566881</v>
+        <v>122566822</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -4917,10 +4912,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461742</v>
+        <v>461763</v>
       </c>
       <c r="R43" t="n">
-        <v>6788295</v>
+        <v>6788475</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4979,7 +4974,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566826</v>
+        <v>122566833</v>
       </c>
       <c r="B44" t="n">
         <v>78766</v>
@@ -5019,10 +5014,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461846</v>
+        <v>461972</v>
       </c>
       <c r="R44" t="n">
-        <v>6788492</v>
+        <v>6788277</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5081,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566807</v>
+        <v>122566852</v>
       </c>
       <c r="B45" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,21 +5092,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5121,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461739</v>
+        <v>461741</v>
       </c>
       <c r="R45" t="n">
-        <v>6788280</v>
+        <v>6788170</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,7 +5178,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566864</v>
+        <v>122566878</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5223,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461619</v>
+        <v>461712</v>
       </c>
       <c r="R46" t="n">
-        <v>6788144</v>
+        <v>6788236</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5285,7 +5280,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566849</v>
+        <v>122566835</v>
       </c>
       <c r="B47" t="n">
         <v>78766</v>
@@ -5325,10 +5320,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461787</v>
+        <v>461929</v>
       </c>
       <c r="R47" t="n">
-        <v>6788182</v>
+        <v>6788278</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,7 +5382,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566880</v>
+        <v>122566851</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5427,10 +5422,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461737</v>
+        <v>461758</v>
       </c>
       <c r="R48" t="n">
-        <v>6788251</v>
+        <v>6788174</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566804</v>
+        <v>122566850</v>
       </c>
       <c r="B49" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,21 +5500,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5529,10 +5524,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461614</v>
+        <v>461771</v>
       </c>
       <c r="R49" t="n">
-        <v>6788152</v>
+        <v>6788185</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5586,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566803</v>
+        <v>122566853</v>
       </c>
       <c r="B50" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,21 +5602,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5626,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461598</v>
+        <v>461732</v>
       </c>
       <c r="R50" t="n">
-        <v>6788148</v>
+        <v>6788166</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,10 +5688,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566801</v>
+        <v>122566863</v>
       </c>
       <c r="B51" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5709,21 +5704,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461945</v>
+        <v>461589</v>
       </c>
       <c r="R51" t="n">
-        <v>6788255</v>
+        <v>6788148</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,7 +5790,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566818</v>
+        <v>122566879</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -5835,10 +5830,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461816</v>
+        <v>461721</v>
       </c>
       <c r="R52" t="n">
-        <v>6788330</v>
+        <v>6788242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566825</v>
+        <v>122566807</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,21 +5908,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461843</v>
+        <v>461739</v>
       </c>
       <c r="R53" t="n">
-        <v>6788468</v>
+        <v>6788280</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,7 +5994,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566845</v>
+        <v>122566841</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6039,10 +6034,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461794</v>
+        <v>461809</v>
       </c>
       <c r="R54" t="n">
-        <v>6788217</v>
+        <v>6788250</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,7 +6096,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566878</v>
+        <v>122566884</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6141,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461712</v>
+        <v>461793</v>
       </c>
       <c r="R55" t="n">
-        <v>6788236</v>
+        <v>6788303</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6203,10 +6198,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566877</v>
+        <v>122566805</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6219,21 +6214,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6243,10 +6238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461706</v>
+        <v>461848</v>
       </c>
       <c r="R56" t="n">
-        <v>6788223</v>
+        <v>6788429</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6305,10 +6300,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566841</v>
+        <v>122566803</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6321,21 +6316,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6345,10 +6340,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461809</v>
+        <v>461598</v>
       </c>
       <c r="R57" t="n">
-        <v>6788250</v>
+        <v>6788148</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6407,10 +6402,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566879</v>
+        <v>122566816</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6423,34 +6418,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461721</v>
+        <v>461930</v>
       </c>
       <c r="R58" t="n">
-        <v>6788242</v>
+        <v>6788270</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6509,10 +6509,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566816</v>
+        <v>122566823</v>
       </c>
       <c r="B59" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6525,39 +6525,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461930</v>
+        <v>461778</v>
       </c>
       <c r="R59" t="n">
-        <v>6788270</v>
+        <v>6788485</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6616,7 +6611,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566837</v>
+        <v>122566882</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -6656,10 +6651,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461917</v>
+        <v>461757</v>
       </c>
       <c r="R60" t="n">
-        <v>6788292</v>
+        <v>6788299</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6718,10 +6713,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566887</v>
+        <v>122566885</v>
       </c>
       <c r="B61" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6730,25 +6725,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6753,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461810</v>
+        <v>461804</v>
       </c>
       <c r="R61" t="n">
-        <v>6788470</v>
+        <v>6788319</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6820,7 +6815,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566855</v>
+        <v>122566883</v>
       </c>
       <c r="B62" t="n">
         <v>78766</v>
@@ -6860,10 +6855,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461704</v>
+        <v>461777</v>
       </c>
       <c r="R62" t="n">
-        <v>6788171</v>
+        <v>6788298</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6922,7 +6917,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566873</v>
+        <v>122566849</v>
       </c>
       <c r="B63" t="n">
         <v>78766</v>
@@ -6962,10 +6957,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461655</v>
+        <v>461787</v>
       </c>
       <c r="R63" t="n">
-        <v>6788205</v>
+        <v>6788182</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7024,7 +7019,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566827</v>
+        <v>122566846</v>
       </c>
       <c r="B64" t="n">
         <v>78766</v>
@@ -7064,10 +7059,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461879</v>
+        <v>461791</v>
       </c>
       <c r="R64" t="n">
-        <v>6788396</v>
+        <v>6788209</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7126,7 +7121,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566886</v>
+        <v>122566875</v>
       </c>
       <c r="B65" t="n">
         <v>78766</v>
@@ -7166,10 +7161,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461810</v>
+        <v>461669</v>
       </c>
       <c r="R65" t="n">
-        <v>6788325</v>
+        <v>6788203</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7228,10 +7223,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566842</v>
+        <v>122566808</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7244,21 +7239,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7268,10 +7263,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461803</v>
+        <v>461872</v>
       </c>
       <c r="R66" t="n">
-        <v>6788243</v>
+        <v>6788413</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7330,7 +7325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566853</v>
+        <v>122566834</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -7370,10 +7365,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461732</v>
+        <v>461929</v>
       </c>
       <c r="R67" t="n">
-        <v>6788166</v>
+        <v>6788262</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7432,7 +7427,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566830</v>
+        <v>122566831</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -7472,10 +7467,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461991</v>
+        <v>462004</v>
       </c>
       <c r="R68" t="n">
-        <v>6788324</v>
+        <v>6788320</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7534,7 +7529,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566839</v>
+        <v>122566861</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -7574,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461829</v>
+        <v>461537</v>
       </c>
       <c r="R69" t="n">
-        <v>6788287</v>
+        <v>6788149</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7636,7 +7631,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566865</v>
+        <v>122566874</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -7676,10 +7671,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461628</v>
+        <v>461665</v>
       </c>
       <c r="R70" t="n">
-        <v>6788142</v>
+        <v>6788207</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7738,7 +7733,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566824</v>
+        <v>122566859</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -7778,10 +7773,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461810</v>
+        <v>461506</v>
       </c>
       <c r="R71" t="n">
-        <v>6788470</v>
+        <v>6788139</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7840,7 +7835,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566823</v>
+        <v>122566862</v>
       </c>
       <c r="B72" t="n">
         <v>78766</v>
@@ -7880,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461778</v>
+        <v>461562</v>
       </c>
       <c r="R72" t="n">
-        <v>6788485</v>
+        <v>6788141</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7942,10 +7937,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566847</v>
+        <v>122566811</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7958,34 +7953,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461789</v>
+        <v>461936</v>
       </c>
       <c r="R73" t="n">
-        <v>6788194</v>
+        <v>6788279</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8044,10 +8044,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566828</v>
+        <v>122566809</v>
       </c>
       <c r="B74" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8060,21 +8060,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461923</v>
+        <v>461822</v>
       </c>
       <c r="R74" t="n">
-        <v>6788324</v>
+        <v>6788353</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566833</v>
+        <v>122566817</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461972</v>
+        <v>461788</v>
       </c>
       <c r="R75" t="n">
-        <v>6788277</v>
+        <v>6788303</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8248,7 +8248,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566885</v>
+        <v>122566842</v>
       </c>
       <c r="B76" t="n">
         <v>78766</v>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461804</v>
+        <v>461803</v>
       </c>
       <c r="R76" t="n">
-        <v>6788319</v>
+        <v>6788243</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566846</v>
+        <v>122566845</v>
       </c>
       <c r="B77" t="n">
         <v>78766</v>
@@ -8390,10 +8390,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461791</v>
+        <v>461794</v>
       </c>
       <c r="R77" t="n">
-        <v>6788209</v>
+        <v>6788217</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8452,7 +8452,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566871</v>
+        <v>122566824</v>
       </c>
       <c r="B78" t="n">
         <v>78766</v>
@@ -8492,10 +8492,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461676</v>
+        <v>461810</v>
       </c>
       <c r="R78" t="n">
-        <v>6788174</v>
+        <v>6788470</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122566813</v>
+        <v>122489274</v>
       </c>
       <c r="B81" t="n">
         <v>57478</v>
@@ -8813,21 +8813,24 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461803</v>
+        <v>461895</v>
       </c>
       <c r="R81" t="n">
-        <v>6788243</v>
+        <v>6788288</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8854,17 +8857,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8879,19 +8882,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122489274</v>
+        <v>122566813</v>
       </c>
       <c r="B82" t="n">
         <v>57478</v>
@@ -8925,24 +8928,21 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461895</v>
+        <v>461803</v>
       </c>
       <c r="R82" t="n">
-        <v>6788288</v>
+        <v>6788243</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8994,12 +8994,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566888</v>
+        <v>122566844</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,25 +2538,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461791</v>
+        <v>461816</v>
       </c>
       <c r="R20" t="n">
-        <v>6788187</v>
+        <v>6788215</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566844</v>
+        <v>122566873</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461816</v>
+        <v>461655</v>
       </c>
       <c r="R21" t="n">
-        <v>6788215</v>
+        <v>6788205</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566873</v>
+        <v>122566843</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461655</v>
+        <v>461811</v>
       </c>
       <c r="R22" t="n">
-        <v>6788205</v>
+        <v>6788237</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566843</v>
+        <v>122566877</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461811</v>
+        <v>461706</v>
       </c>
       <c r="R23" t="n">
-        <v>6788237</v>
+        <v>6788223</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566877</v>
+        <v>122566839</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461706</v>
+        <v>461829</v>
       </c>
       <c r="R24" t="n">
-        <v>6788223</v>
+        <v>6788287</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566839</v>
+        <v>122566848</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461829</v>
+        <v>461791</v>
       </c>
       <c r="R25" t="n">
-        <v>6788287</v>
+        <v>6788187</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566848</v>
+        <v>122566801</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3154,21 +3154,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461791</v>
+        <v>461945</v>
       </c>
       <c r="R26" t="n">
-        <v>6788187</v>
+        <v>6788255</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566801</v>
+        <v>122566888</v>
       </c>
       <c r="B27" t="n">
-        <v>79384</v>
+        <v>5173</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3252,25 +3252,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461945</v>
+        <v>461791</v>
       </c>
       <c r="R27" t="n">
-        <v>6788255</v>
+        <v>6788187</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566802</v>
+        <v>122566837</v>
       </c>
       <c r="B31" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461811</v>
+        <v>461917</v>
       </c>
       <c r="R31" t="n">
-        <v>6788280</v>
+        <v>6788292</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,10 +3750,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566887</v>
+        <v>122566832</v>
       </c>
       <c r="B32" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3762,25 +3762,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461810</v>
+        <v>461991</v>
       </c>
       <c r="R32" t="n">
-        <v>6788470</v>
+        <v>6788292</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566837</v>
+        <v>122566887</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3864,25 +3864,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461917</v>
+        <v>461810</v>
       </c>
       <c r="R33" t="n">
-        <v>6788292</v>
+        <v>6788470</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3954,10 +3954,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566832</v>
+        <v>122566802</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3970,21 +3970,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461991</v>
+        <v>461811</v>
       </c>
       <c r="R34" t="n">
-        <v>6788292</v>
+        <v>6788280</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4362,7 +4362,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566827</v>
+        <v>122566869</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461879</v>
+        <v>461678</v>
       </c>
       <c r="R38" t="n">
-        <v>6788396</v>
+        <v>6788157</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,7 +4464,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566869</v>
+        <v>122566881</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461678</v>
+        <v>461742</v>
       </c>
       <c r="R39" t="n">
-        <v>6788157</v>
+        <v>6788295</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566881</v>
+        <v>122566876</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461742</v>
+        <v>461695</v>
       </c>
       <c r="R40" t="n">
-        <v>6788295</v>
+        <v>6788224</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566876</v>
+        <v>122566880</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461695</v>
+        <v>461737</v>
       </c>
       <c r="R41" t="n">
-        <v>6788224</v>
+        <v>6788251</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566880</v>
+        <v>122566827</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461737</v>
+        <v>461879</v>
       </c>
       <c r="R42" t="n">
-        <v>6788251</v>
+        <v>6788396</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5688,7 +5688,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566863</v>
+        <v>122566879</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461589</v>
+        <v>461721</v>
       </c>
       <c r="R51" t="n">
-        <v>6788148</v>
+        <v>6788242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566879</v>
+        <v>122566863</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461721</v>
+        <v>461589</v>
       </c>
       <c r="R52" t="n">
-        <v>6788242</v>
+        <v>6788148</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5994,10 +5994,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566841</v>
+        <v>122566805</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6010,21 +6010,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6034,10 +6034,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461809</v>
+        <v>461848</v>
       </c>
       <c r="R54" t="n">
-        <v>6788250</v>
+        <v>6788429</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566884</v>
+        <v>122566803</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6112,21 +6112,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461793</v>
+        <v>461598</v>
       </c>
       <c r="R55" t="n">
-        <v>6788303</v>
+        <v>6788148</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6198,10 +6198,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566805</v>
+        <v>122566841</v>
       </c>
       <c r="B56" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6214,21 +6214,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461848</v>
+        <v>461809</v>
       </c>
       <c r="R56" t="n">
-        <v>6788429</v>
+        <v>6788250</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6300,10 +6300,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566803</v>
+        <v>122566884</v>
       </c>
       <c r="B57" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461598</v>
+        <v>461793</v>
       </c>
       <c r="R57" t="n">
-        <v>6788148</v>
+        <v>6788303</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8044,10 +8044,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566809</v>
+        <v>122566817</v>
       </c>
       <c r="B74" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8060,21 +8060,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461822</v>
+        <v>461788</v>
       </c>
       <c r="R74" t="n">
-        <v>6788353</v>
+        <v>6788303</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566817</v>
+        <v>122566842</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461788</v>
+        <v>461803</v>
       </c>
       <c r="R75" t="n">
-        <v>6788303</v>
+        <v>6788243</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8248,10 +8248,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566842</v>
+        <v>122566809</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461803</v>
+        <v>461822</v>
       </c>
       <c r="R76" t="n">
-        <v>6788243</v>
+        <v>6788353</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -4362,7 +4362,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566869</v>
+        <v>122566827</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461678</v>
+        <v>461879</v>
       </c>
       <c r="R38" t="n">
-        <v>6788157</v>
+        <v>6788396</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,7 +4464,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566881</v>
+        <v>122566869</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461742</v>
+        <v>461678</v>
       </c>
       <c r="R39" t="n">
-        <v>6788295</v>
+        <v>6788157</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566876</v>
+        <v>122566881</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461695</v>
+        <v>461742</v>
       </c>
       <c r="R40" t="n">
-        <v>6788224</v>
+        <v>6788295</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566880</v>
+        <v>122566876</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461737</v>
+        <v>461695</v>
       </c>
       <c r="R41" t="n">
-        <v>6788251</v>
+        <v>6788224</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566827</v>
+        <v>122566880</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461879</v>
+        <v>461737</v>
       </c>
       <c r="R42" t="n">
-        <v>6788396</v>
+        <v>6788251</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5688,7 +5688,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566879</v>
+        <v>122566863</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461721</v>
+        <v>461589</v>
       </c>
       <c r="R51" t="n">
-        <v>6788242</v>
+        <v>6788148</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566863</v>
+        <v>122566879</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461589</v>
+        <v>461721</v>
       </c>
       <c r="R52" t="n">
-        <v>6788148</v>
+        <v>6788242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566874</v>
+        <v>122566811</v>
       </c>
       <c r="B70" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7647,34 +7647,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461665</v>
+        <v>461936</v>
       </c>
       <c r="R70" t="n">
-        <v>6788207</v>
+        <v>6788279</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7733,7 +7738,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566859</v>
+        <v>122566874</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -7773,10 +7778,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461506</v>
+        <v>461665</v>
       </c>
       <c r="R71" t="n">
-        <v>6788139</v>
+        <v>6788207</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7835,7 +7840,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566862</v>
+        <v>122566859</v>
       </c>
       <c r="B72" t="n">
         <v>78766</v>
@@ -7875,10 +7880,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461562</v>
+        <v>461506</v>
       </c>
       <c r="R72" t="n">
-        <v>6788141</v>
+        <v>6788139</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7937,10 +7942,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566811</v>
+        <v>122566862</v>
       </c>
       <c r="B73" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7953,39 +7958,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461936</v>
+        <v>461562</v>
       </c>
       <c r="R73" t="n">
-        <v>6788279</v>
+        <v>6788141</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8044,10 +8044,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566817</v>
+        <v>122566809</v>
       </c>
       <c r="B74" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8060,21 +8060,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461788</v>
+        <v>461822</v>
       </c>
       <c r="R74" t="n">
-        <v>6788303</v>
+        <v>6788353</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566842</v>
+        <v>122566817</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461803</v>
+        <v>461788</v>
       </c>
       <c r="R75" t="n">
-        <v>6788243</v>
+        <v>6788303</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8248,10 +8248,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566809</v>
+        <v>122566842</v>
       </c>
       <c r="B76" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461822</v>
+        <v>461803</v>
       </c>
       <c r="R76" t="n">
-        <v>6788353</v>
+        <v>6788243</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -8779,7 +8779,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122489274</v>
+        <v>122566813</v>
       </c>
       <c r="B81" t="n">
         <v>57478</v>
@@ -8813,24 +8813,21 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461895</v>
+        <v>461803</v>
       </c>
       <c r="R81" t="n">
-        <v>6788288</v>
+        <v>6788243</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8857,17 +8854,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8882,19 +8879,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122566813</v>
+        <v>122489274</v>
       </c>
       <c r="B82" t="n">
         <v>57478</v>
@@ -8928,21 +8925,24 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461803</v>
+        <v>461895</v>
       </c>
       <c r="R82" t="n">
-        <v>6788243</v>
+        <v>6788288</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8994,12 +8994,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -8779,7 +8779,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122566813</v>
+        <v>122489274</v>
       </c>
       <c r="B81" t="n">
         <v>57478</v>
@@ -8813,21 +8813,24 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461803</v>
+        <v>461895</v>
       </c>
       <c r="R81" t="n">
-        <v>6788243</v>
+        <v>6788288</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8854,17 +8857,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8879,19 +8882,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122489274</v>
+        <v>122566813</v>
       </c>
       <c r="B82" t="n">
         <v>57478</v>
@@ -8925,24 +8928,21 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461895</v>
+        <v>461803</v>
       </c>
       <c r="R82" t="n">
-        <v>6788288</v>
+        <v>6788243</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8994,12 +8994,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -8782,7 +8782,7 @@
         <v>122566813</v>
       </c>
       <c r="B81" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>122489274</v>
       </c>
       <c r="B82" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -8779,7 +8779,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122566813</v>
+        <v>122489274</v>
       </c>
       <c r="B81" t="n">
         <v>57481</v>
@@ -8813,21 +8813,24 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461803</v>
+        <v>461895</v>
       </c>
       <c r="R81" t="n">
-        <v>6788243</v>
+        <v>6788288</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8854,17 +8857,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8879,19 +8882,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122489274</v>
+        <v>122566813</v>
       </c>
       <c r="B82" t="n">
         <v>57481</v>
@@ -8925,24 +8928,21 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461895</v>
+        <v>461803</v>
       </c>
       <c r="R82" t="n">
-        <v>6788288</v>
+        <v>6788243</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8994,12 +8994,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9004,6 +9004,3370 @@
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>124072783</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>461781</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6788191</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>124076090</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>461711</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6788217</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>124070191</v>
+      </c>
+      <c r="B85" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>461842</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6788220</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>124077244</v>
+      </c>
+      <c r="B86" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>461645</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6788424</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>124078370</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>461702</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6788415</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>124070964</v>
+      </c>
+      <c r="B88" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>461765</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6788314</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>124077216</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78525</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>461645</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6788424</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>124071507</v>
+      </c>
+      <c r="B90" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>461771</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6788273</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>124079435</v>
+      </c>
+      <c r="B91" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>461848</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6788375</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter.</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>124069335</v>
+      </c>
+      <c r="B92" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>461867</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6788190</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>124072166</v>
+      </c>
+      <c r="B93" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>461825</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6788200</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>124071356</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>461771</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6788273</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>124074729</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>461635</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6788154</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>124073786</v>
+      </c>
+      <c r="B96" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>461765</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6788189</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>124076806</v>
+      </c>
+      <c r="B97" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>461730</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6788270</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>124075614</v>
+      </c>
+      <c r="B98" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>461717</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6788187</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ackspår i hög grov stubbe av gammal tall.</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>124071868</v>
+      </c>
+      <c r="B99" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>461779</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6788261</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Vid äldre tallar, mer än 200 år!</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>124075169</v>
+      </c>
+      <c r="B100" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>461717</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6788187</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>124070565</v>
+      </c>
+      <c r="B101" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>461821</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6788236</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>124078636</v>
+      </c>
+      <c r="B102" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>461747</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6788434</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>124074099</v>
+      </c>
+      <c r="B103" t="n">
+        <v>78525</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>461687</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6788172</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>124074329</v>
+      </c>
+      <c r="B104" t="n">
+        <v>78525</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>461635</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6788154</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>124070449</v>
+      </c>
+      <c r="B105" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>461827</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6788228</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>124072335</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>461826</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6788189</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>124070118</v>
+      </c>
+      <c r="B107" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>461846</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6788208</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>124073722</v>
+      </c>
+      <c r="B108" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>461781</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6788191</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>124077891</v>
+      </c>
+      <c r="B109" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>461645</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6788424</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Hög tallstubbe med många bohål.</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>124079560</v>
+      </c>
+      <c r="B110" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>461854</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6788321</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>124075859</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>461732</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6788226</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>124070750</v>
+      </c>
+      <c r="B112" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>461821</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6788236</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>124076637</v>
+      </c>
+      <c r="B113" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>461711</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6788217</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>124072920</v>
+      </c>
+      <c r="B114" t="n">
+        <v>78525</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>461781</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6788191</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY114"/>
+  <dimension ref="A1:AY124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9108,10 +9108,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124076090</v>
+        <v>124070191</v>
       </c>
       <c r="B84" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9124,39 +9124,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461711</v>
+        <v>461842</v>
       </c>
       <c r="R84" t="n">
-        <v>6788217</v>
+        <v>6788220</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9215,10 +9210,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124070191</v>
+        <v>124076090</v>
       </c>
       <c r="B85" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9231,34 +9226,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461842</v>
+        <v>461711</v>
       </c>
       <c r="R85" t="n">
-        <v>6788220</v>
+        <v>6788217</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9730,7 +9730,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124071507</v>
+        <v>124079435</v>
       </c>
       <c r="B90" t="n">
         <v>78788</v>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461771</v>
+        <v>461848</v>
       </c>
       <c r="R90" t="n">
-        <v>6788273</v>
+        <v>6788375</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9806,6 +9806,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9832,7 +9837,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124079435</v>
+        <v>124071507</v>
       </c>
       <c r="B91" t="n">
         <v>78788</v>
@@ -9872,10 +9877,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461848</v>
+        <v>461771</v>
       </c>
       <c r="R91" t="n">
-        <v>6788375</v>
+        <v>6788273</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9908,11 +9913,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10469,10 +10469,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124076806</v>
+        <v>124075614</v>
       </c>
       <c r="B97" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10485,34 +10485,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461730</v>
+        <v>461717</v>
       </c>
       <c r="R97" t="n">
-        <v>6788270</v>
+        <v>6788187</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10545,6 +10550,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ackspår i hög grov stubbe av gammal tall.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10571,10 +10581,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124075614</v>
+        <v>124076806</v>
       </c>
       <c r="B98" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10587,39 +10597,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461717</v>
+        <v>461730</v>
       </c>
       <c r="R98" t="n">
-        <v>6788187</v>
+        <v>6788270</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10652,11 +10657,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ackspår i hög grov stubbe av gammal tall.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10790,7 +10790,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124075169</v>
+        <v>124074066</v>
       </c>
       <c r="B100" t="n">
         <v>57491</v>
@@ -11101,10 +11101,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124074099</v>
+        <v>124070449</v>
       </c>
       <c r="B103" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11117,21 +11117,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11141,10 +11141,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461687</v>
+        <v>461827</v>
       </c>
       <c r="R103" t="n">
-        <v>6788172</v>
+        <v>6788228</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11177,11 +11177,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11208,7 +11203,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124074329</v>
+        <v>124074099</v>
       </c>
       <c r="B104" t="n">
         <v>78525</v>
@@ -11248,10 +11243,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461635</v>
+        <v>461687</v>
       </c>
       <c r="R104" t="n">
-        <v>6788154</v>
+        <v>6788172</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11288,7 +11283,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11315,10 +11310,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124070449</v>
+        <v>124074329</v>
       </c>
       <c r="B105" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11331,21 +11326,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11355,10 +11350,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461827</v>
+        <v>461635</v>
       </c>
       <c r="R105" t="n">
-        <v>6788228</v>
+        <v>6788154</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11391,6 +11386,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11845,7 +11845,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124079560</v>
+        <v>124075859</v>
       </c>
       <c r="B110" t="n">
         <v>57507</v>
@@ -11881,7 +11881,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -11890,10 +11890,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461854</v>
+        <v>461732</v>
       </c>
       <c r="R110" t="n">
-        <v>6788321</v>
+        <v>6788226</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11952,7 +11952,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124075859</v>
+        <v>124079560</v>
       </c>
       <c r="B111" t="n">
         <v>57507</v>
@@ -11988,7 +11988,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461732</v>
+        <v>461854</v>
       </c>
       <c r="R111" t="n">
-        <v>6788226</v>
+        <v>6788321</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12368,6 +12368,1036 @@
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>124100914</v>
+      </c>
+      <c r="B115" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>461788</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6788461</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>124102499</v>
+      </c>
+      <c r="B116" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>461897</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6788354</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>124103019</v>
+      </c>
+      <c r="B117" t="n">
+        <v>90990</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>461895</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6788288</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>124102323</v>
+      </c>
+      <c r="B118" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>461869</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6788429</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>124102093</v>
+      </c>
+      <c r="B119" t="n">
+        <v>91277</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>658</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>461869</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6788429</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>124101056</v>
+      </c>
+      <c r="B120" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>461781</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6788477</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>124100759</v>
+      </c>
+      <c r="B121" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>461815</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6788432</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>124103087</v>
+      </c>
+      <c r="B122" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>461895</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6788288</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>124100321</v>
+      </c>
+      <c r="B123" t="n">
+        <v>91277</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>658</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>461813</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6788469</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>124099222</v>
+      </c>
+      <c r="B124" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>461848</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6788394</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -9006,7 +9006,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124072783</v>
+        <v>124069949</v>
       </c>
       <c r="B83" t="n">
         <v>78788</v>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461781</v>
+        <v>461867</v>
       </c>
       <c r="R83" t="n">
-        <v>6788191</v>
+        <v>6788190</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9108,10 +9108,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124070191</v>
+        <v>124072920</v>
       </c>
       <c r="B84" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9124,21 +9124,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461842</v>
+        <v>461781</v>
       </c>
       <c r="R84" t="n">
-        <v>6788220</v>
+        <v>6788191</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9210,10 +9210,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124076090</v>
+        <v>124071868</v>
       </c>
       <c r="B85" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9226,39 +9226,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461711</v>
+        <v>461779</v>
       </c>
       <c r="R85" t="n">
-        <v>6788217</v>
+        <v>6788261</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9291,6 +9286,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9317,10 +9317,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124077244</v>
+        <v>124074329</v>
       </c>
       <c r="B86" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9333,21 +9333,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461645</v>
+        <v>461635</v>
       </c>
       <c r="R86" t="n">
-        <v>6788424</v>
+        <v>6788154</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9393,6 +9393,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9419,7 +9424,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124078370</v>
+        <v>124079560</v>
       </c>
       <c r="B87" t="n">
         <v>57507</v>
@@ -9464,10 +9469,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461702</v>
+        <v>461854</v>
       </c>
       <c r="R87" t="n">
-        <v>6788415</v>
+        <v>6788321</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9628,10 +9633,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124077216</v>
+        <v>124078370</v>
       </c>
       <c r="B89" t="n">
-        <v>78525</v>
+        <v>57507</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9644,34 +9649,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461645</v>
+        <v>461702</v>
       </c>
       <c r="R89" t="n">
-        <v>6788424</v>
+        <v>6788415</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9730,10 +9740,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124079435</v>
+        <v>124071356</v>
       </c>
       <c r="B90" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9746,34 +9756,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461848</v>
+        <v>461771</v>
       </c>
       <c r="R90" t="n">
-        <v>6788375</v>
+        <v>6788273</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9806,11 +9821,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9837,7 +9847,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124071507</v>
+        <v>124077345</v>
       </c>
       <c r="B91" t="n">
         <v>78788</v>
@@ -9877,10 +9887,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461771</v>
+        <v>461645</v>
       </c>
       <c r="R91" t="n">
-        <v>6788273</v>
+        <v>6788424</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9913,6 +9923,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9939,7 +9954,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124069335</v>
+        <v>124071507</v>
       </c>
       <c r="B92" t="n">
         <v>78788</v>
@@ -9979,10 +9994,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461867</v>
+        <v>461771</v>
       </c>
       <c r="R92" t="n">
-        <v>6788190</v>
+        <v>6788273</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10041,10 +10056,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124072166</v>
+        <v>124073722</v>
       </c>
       <c r="B93" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10057,34 +10072,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461825</v>
+        <v>461781</v>
       </c>
       <c r="R93" t="n">
-        <v>6788200</v>
+        <v>6788191</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10143,10 +10163,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124071356</v>
+        <v>124070191</v>
       </c>
       <c r="B94" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10159,39 +10179,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461771</v>
+        <v>461842</v>
       </c>
       <c r="R94" t="n">
-        <v>6788273</v>
+        <v>6788220</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10250,7 +10265,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124074729</v>
+        <v>124077891</v>
       </c>
       <c r="B95" t="n">
         <v>57507</v>
@@ -10286,7 +10301,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10295,10 +10310,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461635</v>
+        <v>461645</v>
       </c>
       <c r="R95" t="n">
-        <v>6788154</v>
+        <v>6788424</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10335,7 +10350,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
+          <t>Hög tallstubbe med många bohål.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10362,10 +10377,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124073786</v>
+        <v>124077216</v>
       </c>
       <c r="B96" t="n">
-        <v>56700</v>
+        <v>78525</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10374,43 +10389,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461765</v>
+        <v>461645</v>
       </c>
       <c r="R96" t="n">
-        <v>6788189</v>
+        <v>6788424</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10469,10 +10479,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124075614</v>
+        <v>124078636</v>
       </c>
       <c r="B97" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10485,39 +10495,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461717</v>
+        <v>461747</v>
       </c>
       <c r="R97" t="n">
-        <v>6788187</v>
+        <v>6788434</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10550,11 +10555,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ackspår i hög grov stubbe av gammal tall.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10581,10 +10581,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124076806</v>
+        <v>124074099</v>
       </c>
       <c r="B98" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10597,21 +10597,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10621,10 +10621,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461730</v>
+        <v>461687</v>
       </c>
       <c r="R98" t="n">
-        <v>6788270</v>
+        <v>6788172</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10657,6 +10657,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10683,7 +10688,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124071868</v>
+        <v>124079435</v>
       </c>
       <c r="B99" t="n">
         <v>78788</v>
@@ -10723,10 +10728,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461779</v>
+        <v>461848</v>
       </c>
       <c r="R99" t="n">
-        <v>6788261</v>
+        <v>6788375</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10763,7 +10768,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Vid äldre tallar, mer än 200 år!</t>
+          <t>Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10790,10 +10795,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124074066</v>
+        <v>124070118</v>
       </c>
       <c r="B100" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10806,39 +10811,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461717</v>
+        <v>461846</v>
       </c>
       <c r="R100" t="n">
-        <v>6788187</v>
+        <v>6788208</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10897,10 +10897,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124070565</v>
+        <v>124070449</v>
       </c>
       <c r="B101" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10913,21 +10913,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10937,10 +10937,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461821</v>
+        <v>461827</v>
       </c>
       <c r="R101" t="n">
-        <v>6788236</v>
+        <v>6788228</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124078636</v>
+        <v>124101056</v>
       </c>
       <c r="B102" t="n">
         <v>78788</v>
@@ -11039,10 +11039,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461747</v>
+        <v>461781</v>
       </c>
       <c r="R102" t="n">
-        <v>6788434</v>
+        <v>6788477</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11069,12 +11069,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11101,7 +11101,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124070449</v>
+        <v>124103087</v>
       </c>
       <c r="B103" t="n">
         <v>78788</v>
@@ -11141,10 +11141,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461827</v>
+        <v>461895</v>
       </c>
       <c r="R103" t="n">
-        <v>6788228</v>
+        <v>6788288</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11171,12 +11171,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11203,10 +11203,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124074099</v>
+        <v>124100914</v>
       </c>
       <c r="B104" t="n">
-        <v>78525</v>
+        <v>57507</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11219,34 +11219,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461687</v>
+        <v>461788</v>
       </c>
       <c r="R104" t="n">
-        <v>6788172</v>
+        <v>6788461</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11273,17 +11278,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11310,10 +11310,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124074329</v>
+        <v>124102429</v>
       </c>
       <c r="B105" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11326,21 +11326,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11350,10 +11350,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461635</v>
+        <v>461869</v>
       </c>
       <c r="R105" t="n">
-        <v>6788154</v>
+        <v>6788429</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11380,17 +11380,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11417,10 +11412,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124072335</v>
+        <v>124100816</v>
       </c>
       <c r="B106" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11433,39 +11428,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461826</v>
+        <v>461815</v>
       </c>
       <c r="R106" t="n">
-        <v>6788189</v>
+        <v>6788432</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11492,12 +11482,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11524,10 +11514,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124070118</v>
+        <v>124103019</v>
       </c>
       <c r="B107" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11540,21 +11530,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11564,10 +11554,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461846</v>
+        <v>461895</v>
       </c>
       <c r="R107" t="n">
-        <v>6788208</v>
+        <v>6788288</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11594,12 +11584,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11626,10 +11616,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124073722</v>
+        <v>124102093</v>
       </c>
       <c r="B108" t="n">
-        <v>57507</v>
+        <v>91277</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11642,39 +11632,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461781</v>
+        <v>461869</v>
       </c>
       <c r="R108" t="n">
-        <v>6788191</v>
+        <v>6788429</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11701,12 +11686,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11733,10 +11718,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124077891</v>
+        <v>124100321</v>
       </c>
       <c r="B109" t="n">
-        <v>57507</v>
+        <v>91277</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11749,39 +11734,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461645</v>
+        <v>461813</v>
       </c>
       <c r="R109" t="n">
-        <v>6788424</v>
+        <v>6788469</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11808,17 +11788,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Hög tallstubbe med många bohål.</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11845,10 +11820,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124075859</v>
+        <v>124102612</v>
       </c>
       <c r="B110" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11861,39 +11836,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461732</v>
+        <v>461897</v>
       </c>
       <c r="R110" t="n">
-        <v>6788226</v>
+        <v>6788354</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11920,12 +11890,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11952,10 +11922,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124079560</v>
+        <v>124099222</v>
       </c>
       <c r="B111" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11968,16 +11938,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -11997,10 +11967,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461854</v>
+        <v>461848</v>
       </c>
       <c r="R111" t="n">
-        <v>6788321</v>
+        <v>6788394</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12027,12 +11997,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12059,7 +12029,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124070750</v>
+        <v>124074066</v>
       </c>
       <c r="B112" t="n">
         <v>57491</v>
@@ -12104,10 +12074,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461821</v>
+        <v>461717</v>
       </c>
       <c r="R112" t="n">
-        <v>6788236</v>
+        <v>6788187</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12166,10 +12136,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124076637</v>
+        <v>124072335</v>
       </c>
       <c r="B113" t="n">
-        <v>8447</v>
+        <v>57491</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12178,38 +12148,46 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461711</v>
+        <v>461826</v>
       </c>
       <c r="R113" t="n">
-        <v>6788217</v>
+        <v>6788189</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12242,6 +12220,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12268,10 +12251,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124072920</v>
+        <v>124072166</v>
       </c>
       <c r="B114" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12284,21 +12267,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12308,10 +12291,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461781</v>
+        <v>461825</v>
       </c>
       <c r="R114" t="n">
-        <v>6788191</v>
+        <v>6788200</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12370,10 +12353,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124100914</v>
+        <v>124070750</v>
       </c>
       <c r="B115" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12386,16 +12369,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12406,7 +12389,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -12415,10 +12398,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461788</v>
+        <v>461821</v>
       </c>
       <c r="R115" t="n">
-        <v>6788461</v>
+        <v>6788236</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12445,12 +12428,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12477,10 +12460,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124102499</v>
+        <v>124074729</v>
       </c>
       <c r="B116" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12493,34 +12476,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461897</v>
+        <v>461635</v>
       </c>
       <c r="R116" t="n">
-        <v>6788354</v>
+        <v>6788154</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12547,12 +12535,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12579,10 +12572,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124103019</v>
+        <v>124075859</v>
       </c>
       <c r="B117" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12595,34 +12588,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461895</v>
+        <v>461732</v>
       </c>
       <c r="R117" t="n">
-        <v>6788288</v>
+        <v>6788226</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12649,12 +12650,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12681,7 +12687,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124102323</v>
+        <v>124072783</v>
       </c>
       <c r="B118" t="n">
         <v>78788</v>
@@ -12715,16 +12721,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461869</v>
+        <v>461781</v>
       </c>
       <c r="R118" t="n">
-        <v>6788429</v>
+        <v>6788191</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12751,12 +12760,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12765,6 +12779,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12783,10 +12798,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124102093</v>
+        <v>124075614</v>
       </c>
       <c r="B119" t="n">
-        <v>91277</v>
+        <v>57507</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12799,34 +12814,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461869</v>
+        <v>461717</v>
       </c>
       <c r="R119" t="n">
-        <v>6788429</v>
+        <v>6788187</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12853,12 +12876,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Ackspår i hög grov stubbe av gammal tall.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12885,10 +12913,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124101056</v>
+        <v>124073786</v>
       </c>
       <c r="B120" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12897,38 +12925,46 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461781</v>
+        <v>461765</v>
       </c>
       <c r="R120" t="n">
-        <v>6788477</v>
+        <v>6788189</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12955,12 +12991,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12987,7 +13028,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124100759</v>
+        <v>124076806</v>
       </c>
       <c r="B121" t="n">
         <v>78788</v>
@@ -13021,16 +13062,19 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461815</v>
+        <v>461730</v>
       </c>
       <c r="R121" t="n">
-        <v>6788432</v>
+        <v>6788270</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13057,12 +13101,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13071,6 +13120,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13089,10 +13139,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124103087</v>
+        <v>124070565</v>
       </c>
       <c r="B122" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13105,34 +13155,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461895</v>
+        <v>461821</v>
       </c>
       <c r="R122" t="n">
-        <v>6788288</v>
+        <v>6788236</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13159,12 +13217,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13191,10 +13249,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124100321</v>
+        <v>124076090</v>
       </c>
       <c r="B123" t="n">
-        <v>91277</v>
+        <v>57491</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13207,34 +13265,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461813</v>
+        <v>461711</v>
       </c>
       <c r="R123" t="n">
-        <v>6788469</v>
+        <v>6788217</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13261,12 +13324,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13293,10 +13356,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124099222</v>
+        <v>124076637</v>
       </c>
       <c r="B124" t="n">
-        <v>57491</v>
+        <v>8447</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13305,43 +13368,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461848</v>
+        <v>461711</v>
       </c>
       <c r="R124" t="n">
-        <v>6788394</v>
+        <v>6788217</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13368,12 +13426,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9210,10 +9210,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124071868</v>
+        <v>124074329</v>
       </c>
       <c r="B85" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9226,21 +9226,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461779</v>
+        <v>461635</v>
       </c>
       <c r="R85" t="n">
-        <v>6788261</v>
+        <v>6788154</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Vid äldre tallar, mer än 200 år!</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9317,10 +9317,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124074329</v>
+        <v>124071868</v>
       </c>
       <c r="B86" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9333,21 +9333,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461635</v>
+        <v>461779</v>
       </c>
       <c r="R86" t="n">
-        <v>6788154</v>
+        <v>6788261</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9424,10 +9424,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124079560</v>
+        <v>124070964</v>
       </c>
       <c r="B87" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9440,39 +9440,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461854</v>
+        <v>461765</v>
       </c>
       <c r="R87" t="n">
-        <v>6788321</v>
+        <v>6788314</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9531,10 +9526,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124070964</v>
+        <v>124071356</v>
       </c>
       <c r="B88" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9547,34 +9542,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461765</v>
+        <v>461771</v>
       </c>
       <c r="R88" t="n">
-        <v>6788314</v>
+        <v>6788273</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9633,10 +9633,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124078370</v>
+        <v>124071507</v>
       </c>
       <c r="B89" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9649,39 +9649,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461702</v>
+        <v>461771</v>
       </c>
       <c r="R89" t="n">
-        <v>6788415</v>
+        <v>6788273</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9740,7 +9735,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124071356</v>
+        <v>124073722</v>
       </c>
       <c r="B90" t="n">
         <v>57507</v>
@@ -9776,7 +9771,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -9785,10 +9780,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461771</v>
+        <v>461781</v>
       </c>
       <c r="R90" t="n">
-        <v>6788273</v>
+        <v>6788191</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9847,7 +9842,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124077345</v>
+        <v>124070191</v>
       </c>
       <c r="B91" t="n">
         <v>78788</v>
@@ -9887,10 +9882,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461645</v>
+        <v>461842</v>
       </c>
       <c r="R91" t="n">
-        <v>6788424</v>
+        <v>6788220</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9923,11 +9918,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9954,10 +9944,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124071507</v>
+        <v>124077216</v>
       </c>
       <c r="B92" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9970,21 +9960,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9994,10 +9984,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461771</v>
+        <v>461645</v>
       </c>
       <c r="R92" t="n">
-        <v>6788273</v>
+        <v>6788424</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10056,10 +10046,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124073722</v>
+        <v>124077244</v>
       </c>
       <c r="B93" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10072,39 +10062,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461781</v>
+        <v>461645</v>
       </c>
       <c r="R93" t="n">
-        <v>6788191</v>
+        <v>6788424</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10163,7 +10148,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124070191</v>
+        <v>124078636</v>
       </c>
       <c r="B94" t="n">
         <v>78788</v>
@@ -10203,10 +10188,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461842</v>
+        <v>461747</v>
       </c>
       <c r="R94" t="n">
-        <v>6788220</v>
+        <v>6788434</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10265,10 +10250,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124077891</v>
+        <v>124070118</v>
       </c>
       <c r="B95" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10281,39 +10266,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461645</v>
+        <v>461846</v>
       </c>
       <c r="R95" t="n">
-        <v>6788424</v>
+        <v>6788208</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10346,11 +10326,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Hög tallstubbe med många bohål.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10377,10 +10352,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124077216</v>
+        <v>124070449</v>
       </c>
       <c r="B96" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10393,21 +10368,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10417,10 +10392,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461645</v>
+        <v>461827</v>
       </c>
       <c r="R96" t="n">
-        <v>6788424</v>
+        <v>6788228</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10479,7 +10454,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124078636</v>
+        <v>124101056</v>
       </c>
       <c r="B97" t="n">
         <v>78788</v>
@@ -10519,10 +10494,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461747</v>
+        <v>461781</v>
       </c>
       <c r="R97" t="n">
-        <v>6788434</v>
+        <v>6788477</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10549,12 +10524,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10581,10 +10556,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124074099</v>
+        <v>124103087</v>
       </c>
       <c r="B98" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10597,21 +10572,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10621,10 +10596,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461687</v>
+        <v>461895</v>
       </c>
       <c r="R98" t="n">
-        <v>6788172</v>
+        <v>6788288</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10651,17 +10626,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10688,10 +10658,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124079435</v>
+        <v>124100914</v>
       </c>
       <c r="B99" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10704,34 +10674,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461848</v>
+        <v>461788</v>
       </c>
       <c r="R99" t="n">
-        <v>6788375</v>
+        <v>6788461</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10758,17 +10733,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter.</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10795,7 +10765,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124070118</v>
+        <v>124102429</v>
       </c>
       <c r="B100" t="n">
         <v>78788</v>
@@ -10835,10 +10805,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461846</v>
+        <v>461869</v>
       </c>
       <c r="R100" t="n">
-        <v>6788208</v>
+        <v>6788429</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10865,12 +10835,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10897,7 +10867,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124070449</v>
+        <v>124102612</v>
       </c>
       <c r="B101" t="n">
         <v>78788</v>
@@ -10937,10 +10907,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461827</v>
+        <v>461897</v>
       </c>
       <c r="R101" t="n">
-        <v>6788228</v>
+        <v>6788354</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10967,12 +10937,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10999,10 +10969,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124101056</v>
+        <v>124074066</v>
       </c>
       <c r="B102" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11015,34 +10985,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461781</v>
+        <v>461717</v>
       </c>
       <c r="R102" t="n">
-        <v>6788477</v>
+        <v>6788187</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11069,12 +11044,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11101,10 +11076,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124103087</v>
+        <v>124072335</v>
       </c>
       <c r="B103" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11117,34 +11092,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461895</v>
+        <v>461826</v>
       </c>
       <c r="R103" t="n">
-        <v>6788288</v>
+        <v>6788189</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11171,12 +11154,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11203,10 +11191,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124100914</v>
+        <v>124072166</v>
       </c>
       <c r="B104" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11219,39 +11207,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461788</v>
+        <v>461825</v>
       </c>
       <c r="R104" t="n">
-        <v>6788461</v>
+        <v>6788200</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11278,12 +11261,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11310,10 +11293,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124102429</v>
+        <v>124070750</v>
       </c>
       <c r="B105" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11326,34 +11309,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461869</v>
+        <v>461821</v>
       </c>
       <c r="R105" t="n">
-        <v>6788429</v>
+        <v>6788236</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11380,12 +11368,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11412,10 +11400,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124100816</v>
+        <v>124074729</v>
       </c>
       <c r="B106" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11428,34 +11416,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461815</v>
+        <v>461635</v>
       </c>
       <c r="R106" t="n">
-        <v>6788432</v>
+        <v>6788154</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11482,12 +11475,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11514,10 +11512,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124103019</v>
+        <v>124075859</v>
       </c>
       <c r="B107" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11530,34 +11528,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461895</v>
+        <v>461732</v>
       </c>
       <c r="R107" t="n">
-        <v>6788288</v>
+        <v>6788226</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11584,12 +11590,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11616,10 +11627,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124102093</v>
+        <v>124072783</v>
       </c>
       <c r="B108" t="n">
-        <v>91277</v>
+        <v>78788</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11632,34 +11643,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461869</v>
+        <v>461781</v>
       </c>
       <c r="R108" t="n">
-        <v>6788429</v>
+        <v>6788191</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11686,12 +11700,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11700,6 +11719,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11718,10 +11738,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124100321</v>
+        <v>124075614</v>
       </c>
       <c r="B109" t="n">
-        <v>91277</v>
+        <v>57507</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11734,34 +11754,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461813</v>
+        <v>461717</v>
       </c>
       <c r="R109" t="n">
-        <v>6788469</v>
+        <v>6788187</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11788,12 +11816,17 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Ackspår i hög grov stubbe av gammal tall.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11820,10 +11853,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124102612</v>
+        <v>124073786</v>
       </c>
       <c r="B110" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11832,38 +11865,46 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461897</v>
+        <v>461765</v>
       </c>
       <c r="R110" t="n">
-        <v>6788354</v>
+        <v>6788189</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11890,12 +11931,17 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11922,10 +11968,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124099222</v>
+        <v>124076806</v>
       </c>
       <c r="B111" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11938,39 +11984,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461848</v>
+        <v>461730</v>
       </c>
       <c r="R111" t="n">
-        <v>6788394</v>
+        <v>6788270</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11997,12 +12041,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12011,6 +12060,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12029,10 +12079,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124074066</v>
+        <v>124070565</v>
       </c>
       <c r="B112" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12045,16 +12095,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -12063,21 +12113,24 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461717</v>
+        <v>461821</v>
       </c>
       <c r="R112" t="n">
-        <v>6788187</v>
+        <v>6788236</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12136,7 +12189,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124072335</v>
+        <v>124076090</v>
       </c>
       <c r="B113" t="n">
         <v>57491</v>
@@ -12170,24 +12223,21 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461826</v>
+        <v>461711</v>
       </c>
       <c r="R113" t="n">
-        <v>6788189</v>
+        <v>6788217</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12220,11 +12270,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12251,10 +12296,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124072166</v>
+        <v>124076637</v>
       </c>
       <c r="B114" t="n">
-        <v>78788</v>
+        <v>8447</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12263,25 +12308,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12291,10 +12336,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461825</v>
+        <v>461711</v>
       </c>
       <c r="R114" t="n">
-        <v>6788200</v>
+        <v>6788217</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12353,10 +12398,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124070750</v>
+        <v>124078370</v>
       </c>
       <c r="B115" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12369,16 +12414,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12387,21 +12432,24 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461821</v>
+        <v>461702</v>
       </c>
       <c r="R115" t="n">
-        <v>6788236</v>
+        <v>6788415</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12434,6 +12482,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12460,10 +12513,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124074729</v>
+        <v>124100816</v>
       </c>
       <c r="B116" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12476,39 +12529,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461635</v>
+        <v>461815</v>
       </c>
       <c r="R116" t="n">
-        <v>6788154</v>
+        <v>6788432</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12535,17 +12586,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
+          <t>Miljöbilder. Garnlav och revlummer.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12554,6 +12605,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12572,10 +12624,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124075859</v>
+        <v>124102093</v>
       </c>
       <c r="B117" t="n">
-        <v>57507</v>
+        <v>91277</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12588,31 +12640,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12620,10 +12667,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461732</v>
+        <v>461869</v>
       </c>
       <c r="R117" t="n">
-        <v>6788226</v>
+        <v>6788429</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12650,17 +12697,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Miljöbild med äldre högstubbe!</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12669,6 +12716,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12687,10 +12735,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124072783</v>
+        <v>124074099</v>
       </c>
       <c r="B118" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12703,21 +12751,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12730,10 +12778,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461781</v>
+        <v>461687</v>
       </c>
       <c r="R118" t="n">
-        <v>6788191</v>
+        <v>6788172</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12770,7 +12818,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12798,10 +12846,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124075614</v>
+        <v>124103019</v>
       </c>
       <c r="B119" t="n">
-        <v>57507</v>
+        <v>91008</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12814,31 +12862,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12846,10 +12889,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461717</v>
+        <v>461895</v>
       </c>
       <c r="R119" t="n">
-        <v>6788187</v>
+        <v>6788288</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12876,17 +12919,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Miljöbilder. Ackspår i hög grov stubbe av gammal tall.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12895,6 +12938,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12913,10 +12957,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124073786</v>
+        <v>124077891</v>
       </c>
       <c r="B120" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12925,25 +12969,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12951,7 +12995,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -12961,10 +13005,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461765</v>
+        <v>461645</v>
       </c>
       <c r="R120" t="n">
-        <v>6788189</v>
+        <v>6788424</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13001,7 +13045,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Miljöbild. Så kallad tjädertall.</t>
+          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13028,10 +13072,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124076806</v>
+        <v>124150783</v>
       </c>
       <c r="B121" t="n">
-        <v>78788</v>
+        <v>8447</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13040,30 +13084,32 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13071,10 +13117,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461730</v>
+        <v>461702</v>
       </c>
       <c r="R121" t="n">
-        <v>6788270</v>
+        <v>6788415</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13111,7 +13157,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13139,10 +13185,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124070565</v>
+        <v>124079435</v>
       </c>
       <c r="B122" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13155,31 +13201,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13187,10 +13228,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461821</v>
+        <v>461848</v>
       </c>
       <c r="R122" t="n">
-        <v>6788236</v>
+        <v>6788375</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13225,12 +13266,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13249,7 +13296,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124076090</v>
+        <v>124099222</v>
       </c>
       <c r="B123" t="n">
         <v>57491</v>
@@ -13283,21 +13330,24 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461711</v>
+        <v>461848</v>
       </c>
       <c r="R123" t="n">
-        <v>6788217</v>
+        <v>6788394</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13324,12 +13374,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13356,10 +13411,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124076637</v>
+        <v>124079560</v>
       </c>
       <c r="B124" t="n">
-        <v>8447</v>
+        <v>57507</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13368,38 +13423,46 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461711</v>
+        <v>461854</v>
       </c>
       <c r="R124" t="n">
-        <v>6788217</v>
+        <v>6788321</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13434,6 +13497,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -13455,6 +13523,117 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124100321</v>
+      </c>
+      <c r="B125" t="n">
+        <v>91277</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>658</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>461813</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6788469</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -9006,10 +9006,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124069949</v>
+        <v>124074329</v>
       </c>
       <c r="B83" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461867</v>
+        <v>461635</v>
       </c>
       <c r="R83" t="n">
-        <v>6788190</v>
+        <v>6788154</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9082,6 +9082,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9108,10 +9113,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124072920</v>
+        <v>124070964</v>
       </c>
       <c r="B84" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9124,21 +9129,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9148,10 +9153,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461781</v>
+        <v>461765</v>
       </c>
       <c r="R84" t="n">
-        <v>6788191</v>
+        <v>6788314</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9210,10 +9215,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124074329</v>
+        <v>124069938</v>
       </c>
       <c r="B85" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9226,21 +9231,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9250,10 +9255,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461635</v>
+        <v>461867</v>
       </c>
       <c r="R85" t="n">
-        <v>6788154</v>
+        <v>6788190</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9286,11 +9291,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9317,7 +9317,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124071868</v>
+        <v>124071683</v>
       </c>
       <c r="B86" t="n">
         <v>78788</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461779</v>
+        <v>461771</v>
       </c>
       <c r="R86" t="n">
-        <v>6788261</v>
+        <v>6788273</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9393,11 +9393,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9424,7 +9419,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124070964</v>
+        <v>124077244</v>
       </c>
       <c r="B87" t="n">
         <v>78788</v>
@@ -9464,10 +9459,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461765</v>
+        <v>461645</v>
       </c>
       <c r="R87" t="n">
-        <v>6788314</v>
+        <v>6788424</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9526,7 +9521,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124071356</v>
+        <v>124073722</v>
       </c>
       <c r="B88" t="n">
         <v>57507</v>
@@ -9562,7 +9557,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9571,10 +9566,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461771</v>
+        <v>461781</v>
       </c>
       <c r="R88" t="n">
-        <v>6788273</v>
+        <v>6788191</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9633,7 +9628,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124071507</v>
+        <v>124070191</v>
       </c>
       <c r="B89" t="n">
         <v>78788</v>
@@ -9673,10 +9668,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461771</v>
+        <v>461842</v>
       </c>
       <c r="R89" t="n">
-        <v>6788273</v>
+        <v>6788220</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9735,10 +9730,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124073722</v>
+        <v>124070118</v>
       </c>
       <c r="B90" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9751,39 +9746,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461781</v>
+        <v>461846</v>
       </c>
       <c r="R90" t="n">
-        <v>6788191</v>
+        <v>6788208</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9842,7 +9832,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124070191</v>
+        <v>124070449</v>
       </c>
       <c r="B91" t="n">
         <v>78788</v>
@@ -9882,10 +9872,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461842</v>
+        <v>461827</v>
       </c>
       <c r="R91" t="n">
-        <v>6788220</v>
+        <v>6788228</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9944,10 +9934,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124077216</v>
+        <v>124071356</v>
       </c>
       <c r="B92" t="n">
-        <v>78525</v>
+        <v>57507</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9960,34 +9950,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461645</v>
+        <v>461771</v>
       </c>
       <c r="R92" t="n">
-        <v>6788424</v>
+        <v>6788273</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10046,10 +10041,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124077244</v>
+        <v>124077216</v>
       </c>
       <c r="B93" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10062,21 +10057,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10250,7 +10245,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124070118</v>
+        <v>124071868</v>
       </c>
       <c r="B95" t="n">
         <v>78788</v>
@@ -10290,10 +10285,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461846</v>
+        <v>461779</v>
       </c>
       <c r="R95" t="n">
-        <v>6788208</v>
+        <v>6788261</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10326,6 +10321,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10352,10 +10352,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124070449</v>
+        <v>124072920</v>
       </c>
       <c r="B96" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10368,21 +10368,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461827</v>
+        <v>461781</v>
       </c>
       <c r="R96" t="n">
-        <v>6788228</v>
+        <v>6788191</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124101056</v>
+        <v>124103283</v>
       </c>
       <c r="B97" t="n">
         <v>78788</v>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461781</v>
+        <v>461895</v>
       </c>
       <c r="R97" t="n">
-        <v>6788477</v>
+        <v>6788288</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10556,7 +10556,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124103087</v>
+        <v>124102323</v>
       </c>
       <c r="B98" t="n">
         <v>78788</v>
@@ -10596,10 +10596,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461895</v>
+        <v>461869</v>
       </c>
       <c r="R98" t="n">
-        <v>6788288</v>
+        <v>6788429</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10658,10 +10658,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124100914</v>
+        <v>124102664</v>
       </c>
       <c r="B99" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10674,39 +10674,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461788</v>
+        <v>461897</v>
       </c>
       <c r="R99" t="n">
-        <v>6788461</v>
+        <v>6788354</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10739,6 +10734,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav runt mig.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10765,7 +10765,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124102429</v>
+        <v>124101056</v>
       </c>
       <c r="B100" t="n">
         <v>78788</v>
@@ -10805,10 +10805,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461869</v>
+        <v>461781</v>
       </c>
       <c r="R100" t="n">
-        <v>6788429</v>
+        <v>6788477</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10867,10 +10867,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124102612</v>
+        <v>124100914</v>
       </c>
       <c r="B101" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10883,34 +10883,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461897</v>
+        <v>461788</v>
       </c>
       <c r="R101" t="n">
-        <v>6788354</v>
+        <v>6788461</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10969,10 +10974,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124074066</v>
+        <v>124072783</v>
       </c>
       <c r="B102" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10985,39 +10990,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461717</v>
+        <v>461781</v>
       </c>
       <c r="R102" t="n">
-        <v>6788187</v>
+        <v>6788191</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11052,12 +11055,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11076,10 +11085,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124072335</v>
+        <v>124074255</v>
       </c>
       <c r="B103" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11092,16 +11101,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11124,10 +11133,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461826</v>
+        <v>461635</v>
       </c>
       <c r="R103" t="n">
-        <v>6788189</v>
+        <v>6788154</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11191,10 +11200,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124072166</v>
+        <v>124070565</v>
       </c>
       <c r="B104" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11207,34 +11216,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461825</v>
+        <v>461821</v>
       </c>
       <c r="R104" t="n">
-        <v>6788200</v>
+        <v>6788236</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11293,7 +11310,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124070750</v>
+        <v>124074066</v>
       </c>
       <c r="B105" t="n">
         <v>57491</v>
@@ -11338,10 +11355,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461821</v>
+        <v>461717</v>
       </c>
       <c r="R105" t="n">
-        <v>6788236</v>
+        <v>6788187</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11400,10 +11417,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124074729</v>
+        <v>124076090</v>
       </c>
       <c r="B106" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11416,16 +11433,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11445,10 +11462,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461635</v>
+        <v>461711</v>
       </c>
       <c r="R106" t="n">
-        <v>6788154</v>
+        <v>6788217</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11481,11 +11498,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11512,10 +11524,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124075859</v>
+        <v>124072335</v>
       </c>
       <c r="B107" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11528,16 +11540,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11550,7 +11562,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -11560,10 +11572,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461732</v>
+        <v>461826</v>
       </c>
       <c r="R107" t="n">
-        <v>6788226</v>
+        <v>6788189</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11600,7 +11612,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Miljöbild med äldre högstubbe!</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11627,10 +11639,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124072783</v>
+        <v>124075614</v>
       </c>
       <c r="B108" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11643,26 +11655,31 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -11670,10 +11687,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461781</v>
+        <v>461717</v>
       </c>
       <c r="R108" t="n">
-        <v>6788191</v>
+        <v>6788187</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11710,7 +11727,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder. Ackspår i hög grov stubbe av gammal tall.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11719,7 +11736,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11738,10 +11754,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124075614</v>
+        <v>124076637</v>
       </c>
       <c r="B109" t="n">
-        <v>57507</v>
+        <v>8447</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11750,46 +11766,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461717</v>
+        <v>461711</v>
       </c>
       <c r="R109" t="n">
-        <v>6788187</v>
+        <v>6788217</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11822,11 +11830,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Ackspår i hög grov stubbe av gammal tall.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11853,10 +11856,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124073786</v>
+        <v>124070750</v>
       </c>
       <c r="B110" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11865,46 +11868,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461765</v>
+        <v>461821</v>
       </c>
       <c r="R110" t="n">
-        <v>6788189</v>
+        <v>6788236</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11937,11 +11937,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11968,7 +11963,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124076806</v>
+        <v>124072166</v>
       </c>
       <c r="B111" t="n">
         <v>78788</v>
@@ -12002,19 +11997,16 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461730</v>
+        <v>461825</v>
       </c>
       <c r="R111" t="n">
-        <v>6788270</v>
+        <v>6788200</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12049,18 +12041,12 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12079,7 +12065,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124070565</v>
+        <v>124075859</v>
       </c>
       <c r="B112" t="n">
         <v>57507</v>
@@ -12127,10 +12113,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461821</v>
+        <v>461732</v>
       </c>
       <c r="R112" t="n">
-        <v>6788236</v>
+        <v>6788226</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12163,6 +12149,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12189,10 +12180,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124076090</v>
+        <v>124076806</v>
       </c>
       <c r="B113" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12205,39 +12196,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461711</v>
+        <v>461730</v>
       </c>
       <c r="R113" t="n">
-        <v>6788217</v>
+        <v>6788270</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12272,12 +12261,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12296,10 +12291,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124076637</v>
+        <v>124073786</v>
       </c>
       <c r="B114" t="n">
-        <v>8447</v>
+        <v>56700</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12312,34 +12307,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461711</v>
+        <v>461765</v>
       </c>
       <c r="R114" t="n">
-        <v>6788217</v>
+        <v>6788189</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12372,6 +12375,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12398,10 +12406,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124078370</v>
+        <v>124150783</v>
       </c>
       <c r="B115" t="n">
-        <v>57507</v>
+        <v>8447</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12410,35 +12418,32 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12486,7 +12491,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12495,6 +12500,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12513,10 +12519,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124100816</v>
+        <v>124074099</v>
       </c>
       <c r="B116" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12529,21 +12535,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12556,10 +12562,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461815</v>
+        <v>461687</v>
       </c>
       <c r="R116" t="n">
-        <v>6788432</v>
+        <v>6788172</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12586,17 +12592,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav och revlummer.</t>
+          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12624,10 +12630,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124102093</v>
+        <v>124100759</v>
       </c>
       <c r="B117" t="n">
-        <v>91277</v>
+        <v>78788</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12640,21 +12646,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12667,10 +12673,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461869</v>
+        <v>461815</v>
       </c>
       <c r="R117" t="n">
-        <v>6788429</v>
+        <v>6788432</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12707,7 +12713,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12735,10 +12741,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124074099</v>
+        <v>124102093</v>
       </c>
       <c r="B118" t="n">
-        <v>78525</v>
+        <v>91277</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12751,21 +12757,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12778,10 +12784,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461687</v>
+        <v>461869</v>
       </c>
       <c r="R118" t="n">
-        <v>6788172</v>
+        <v>6788429</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12808,17 +12814,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12846,10 +12852,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124103019</v>
+        <v>124100321</v>
       </c>
       <c r="B119" t="n">
-        <v>91008</v>
+        <v>91277</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12862,21 +12868,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12889,10 +12895,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461895</v>
+        <v>461813</v>
       </c>
       <c r="R119" t="n">
-        <v>6788288</v>
+        <v>6788469</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12929,7 +12935,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12957,10 +12963,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124077891</v>
+        <v>124079435</v>
       </c>
       <c r="B120" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12973,31 +12979,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13005,10 +13006,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461645</v>
+        <v>461848</v>
       </c>
       <c r="R120" t="n">
-        <v>6788424</v>
+        <v>6788375</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13045,7 +13046,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13054,6 +13055,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13072,10 +13074,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124150783</v>
+        <v>124077891</v>
       </c>
       <c r="B121" t="n">
-        <v>8447</v>
+        <v>57507</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13084,32 +13086,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13117,10 +13122,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461702</v>
+        <v>461645</v>
       </c>
       <c r="R121" t="n">
-        <v>6788415</v>
+        <v>6788424</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13157,7 +13162,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13166,7 +13171,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13185,10 +13189,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124079435</v>
+        <v>124079560</v>
       </c>
       <c r="B122" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13201,26 +13205,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13228,10 +13237,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461848</v>
+        <v>461854</v>
       </c>
       <c r="R122" t="n">
-        <v>6788375</v>
+        <v>6788321</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13268,7 +13277,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13277,7 +13286,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13411,10 +13419,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124079560</v>
+        <v>124103019</v>
       </c>
       <c r="B124" t="n">
-        <v>57507</v>
+        <v>91008</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13427,31 +13435,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13459,10 +13462,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461854</v>
+        <v>461895</v>
       </c>
       <c r="R124" t="n">
-        <v>6788321</v>
+        <v>6788288</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13489,17 +13492,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13508,6 +13511,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13526,10 +13530,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124100321</v>
+        <v>124078370</v>
       </c>
       <c r="B125" t="n">
-        <v>91277</v>
+        <v>57507</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13542,26 +13546,31 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -13569,10 +13578,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>461813</v>
+        <v>461702</v>
       </c>
       <c r="R125" t="n">
-        <v>6788469</v>
+        <v>6788415</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13599,17 +13608,17 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13618,7 +13627,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -9006,7 +9006,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124078636</v>
+        <v>124069949</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461747</v>
+        <v>461867</v>
       </c>
       <c r="R83" t="n">
-        <v>6788434</v>
+        <v>6788190</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9108,10 +9108,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124069314</v>
+        <v>124072920</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9124,21 +9124,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461867</v>
+        <v>461781</v>
       </c>
       <c r="R84" t="n">
-        <v>6788190</v>
+        <v>6788191</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9210,7 +9210,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124070964</v>
+        <v>124070118</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461765</v>
+        <v>461846</v>
       </c>
       <c r="R85" t="n">
-        <v>6788314</v>
+        <v>6788208</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9312,7 +9312,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124071683</v>
+        <v>124077244</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461771</v>
+        <v>461645</v>
       </c>
       <c r="R86" t="n">
-        <v>6788273</v>
+        <v>6788424</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9414,10 +9414,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124073722</v>
+        <v>124074329</v>
       </c>
       <c r="B87" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9430,39 +9430,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461781</v>
+        <v>461635</v>
       </c>
       <c r="R87" t="n">
-        <v>6788191</v>
+        <v>6788154</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9495,6 +9490,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9521,7 +9521,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124071868</v>
+        <v>124078636</v>
       </c>
       <c r="B88" t="n">
         <v>78810</v>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461779</v>
+        <v>461747</v>
       </c>
       <c r="R88" t="n">
-        <v>6788261</v>
+        <v>6788434</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9597,11 +9597,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9628,10 +9623,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124072920</v>
+        <v>124071683</v>
       </c>
       <c r="B89" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9644,21 +9639,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9668,10 +9663,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461781</v>
+        <v>461771</v>
       </c>
       <c r="R89" t="n">
-        <v>6788191</v>
+        <v>6788273</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9730,7 +9725,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124070191</v>
+        <v>124070964</v>
       </c>
       <c r="B90" t="n">
         <v>78810</v>
@@ -9770,10 +9765,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461842</v>
+        <v>461765</v>
       </c>
       <c r="R90" t="n">
-        <v>6788220</v>
+        <v>6788314</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9832,10 +9827,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124071356</v>
+        <v>124070449</v>
       </c>
       <c r="B91" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9848,39 +9843,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461771</v>
+        <v>461827</v>
       </c>
       <c r="R91" t="n">
-        <v>6788273</v>
+        <v>6788228</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9939,10 +9929,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124070118</v>
+        <v>124073722</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9955,34 +9945,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461846</v>
+        <v>461781</v>
       </c>
       <c r="R92" t="n">
-        <v>6788208</v>
+        <v>6788191</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10041,10 +10036,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124070449</v>
+        <v>124077216</v>
       </c>
       <c r="B93" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10057,21 +10052,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10081,10 +10076,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461827</v>
+        <v>461645</v>
       </c>
       <c r="R93" t="n">
-        <v>6788228</v>
+        <v>6788424</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10143,10 +10138,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124074329</v>
+        <v>124071356</v>
       </c>
       <c r="B94" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10159,34 +10154,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461635</v>
+        <v>461771</v>
       </c>
       <c r="R94" t="n">
-        <v>6788154</v>
+        <v>6788273</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10219,11 +10219,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10250,7 +10245,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124077244</v>
+        <v>124071868</v>
       </c>
       <c r="B95" t="n">
         <v>78810</v>
@@ -10290,10 +10285,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461645</v>
+        <v>461779</v>
       </c>
       <c r="R95" t="n">
-        <v>6788424</v>
+        <v>6788261</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10326,6 +10321,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10352,10 +10352,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124077216</v>
+        <v>124070191</v>
       </c>
       <c r="B96" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10368,21 +10368,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461645</v>
+        <v>461842</v>
       </c>
       <c r="R96" t="n">
-        <v>6788424</v>
+        <v>6788220</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124102499</v>
+        <v>124101056</v>
       </c>
       <c r="B97" t="n">
         <v>78810</v>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461897</v>
+        <v>461781</v>
       </c>
       <c r="R97" t="n">
-        <v>6788354</v>
+        <v>6788477</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10556,10 +10556,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124102429</v>
+        <v>124100914</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10572,34 +10572,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461869</v>
+        <v>461788</v>
       </c>
       <c r="R98" t="n">
-        <v>6788429</v>
+        <v>6788461</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10658,7 +10663,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124103283</v>
+        <v>124102612</v>
       </c>
       <c r="B99" t="n">
         <v>78810</v>
@@ -10698,10 +10703,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461895</v>
+        <v>461897</v>
       </c>
       <c r="R99" t="n">
-        <v>6788288</v>
+        <v>6788354</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10760,10 +10765,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124100914</v>
+        <v>124103087</v>
       </c>
       <c r="B100" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10776,39 +10781,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461788</v>
+        <v>461895</v>
       </c>
       <c r="R100" t="n">
-        <v>6788461</v>
+        <v>6788288</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10867,7 +10867,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124101056</v>
+        <v>124102323</v>
       </c>
       <c r="B101" t="n">
         <v>78810</v>
@@ -10907,10 +10907,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461781</v>
+        <v>461869</v>
       </c>
       <c r="R101" t="n">
-        <v>6788477</v>
+        <v>6788429</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10969,10 +10969,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124075859</v>
+        <v>124072166</v>
       </c>
       <c r="B102" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10985,42 +10985,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461732</v>
+        <v>461825</v>
       </c>
       <c r="R102" t="n">
-        <v>6788226</v>
+        <v>6788200</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11053,11 +11045,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11084,10 +11071,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124075614</v>
+        <v>124075169</v>
       </c>
       <c r="B103" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11100,16 +11087,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11122,7 +11109,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -11172,7 +11159,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Miljöbilder. Ackspår i hög grov stubbe av gammal tall.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11199,10 +11186,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124076637</v>
+        <v>124076806</v>
       </c>
       <c r="B104" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11211,38 +11198,41 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461711</v>
+        <v>461730</v>
       </c>
       <c r="R104" t="n">
-        <v>6788217</v>
+        <v>6788270</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11277,12 +11267,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11301,10 +11297,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124076806</v>
+        <v>124070750</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11317,37 +11313,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461730</v>
+        <v>461821</v>
       </c>
       <c r="R105" t="n">
-        <v>6788270</v>
+        <v>6788236</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11382,18 +11380,12 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11412,10 +11404,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124070750</v>
+        <v>124075859</v>
       </c>
       <c r="B106" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11428,16 +11420,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11446,21 +11438,24 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461821</v>
+        <v>461732</v>
       </c>
       <c r="R106" t="n">
-        <v>6788236</v>
+        <v>6788226</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11493,6 +11488,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11519,10 +11519,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124076090</v>
+        <v>124074255</v>
       </c>
       <c r="B107" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11535,16 +11535,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11553,21 +11553,24 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461711</v>
+        <v>461635</v>
       </c>
       <c r="R107" t="n">
-        <v>6788217</v>
+        <v>6788154</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11600,6 +11603,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11626,7 +11634,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124074255</v>
+        <v>124070565</v>
       </c>
       <c r="B108" t="n">
         <v>57529</v>
@@ -11664,7 +11672,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -11674,10 +11682,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461635</v>
+        <v>461821</v>
       </c>
       <c r="R108" t="n">
-        <v>6788154</v>
+        <v>6788236</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11710,11 +11718,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11741,10 +11744,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124072335</v>
+        <v>124076637</v>
       </c>
       <c r="B109" t="n">
-        <v>57513</v>
+        <v>8447</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11753,46 +11756,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461826</v>
+        <v>461711</v>
       </c>
       <c r="R109" t="n">
-        <v>6788189</v>
+        <v>6788217</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11825,11 +11820,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11856,10 +11846,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124075169</v>
+        <v>124072783</v>
       </c>
       <c r="B110" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11872,31 +11862,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11904,10 +11889,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461717</v>
+        <v>461781</v>
       </c>
       <c r="R110" t="n">
-        <v>6788187</v>
+        <v>6788191</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11944,7 +11929,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11953,6 +11938,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11971,7 +11957,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124070565</v>
+        <v>124075614</v>
       </c>
       <c r="B111" t="n">
         <v>57529</v>
@@ -12019,10 +12005,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461821</v>
+        <v>461717</v>
       </c>
       <c r="R111" t="n">
-        <v>6788236</v>
+        <v>6788187</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12055,6 +12041,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Ackspår i hög grov stubbe av gammal tall.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12081,10 +12072,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124072166</v>
+        <v>124073786</v>
       </c>
       <c r="B112" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12093,38 +12084,46 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461825</v>
+        <v>461765</v>
       </c>
       <c r="R112" t="n">
-        <v>6788200</v>
+        <v>6788189</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12157,6 +12156,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12183,10 +12187,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124073786</v>
+        <v>124076090</v>
       </c>
       <c r="B113" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12195,46 +12199,43 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461765</v>
+        <v>461711</v>
       </c>
       <c r="R113" t="n">
-        <v>6788189</v>
+        <v>6788217</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12267,11 +12268,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12298,10 +12294,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124072783</v>
+        <v>124072335</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12314,26 +12310,31 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12341,10 +12342,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461781</v>
+        <v>461826</v>
       </c>
       <c r="R114" t="n">
-        <v>6788191</v>
+        <v>6788189</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12381,7 +12382,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12390,7 +12391,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12409,10 +12409,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124078370</v>
+        <v>124102093</v>
       </c>
       <c r="B115" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12425,31 +12425,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12457,10 +12452,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461702</v>
+        <v>461869</v>
       </c>
       <c r="R115" t="n">
-        <v>6788415</v>
+        <v>6788429</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12487,17 +12482,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12506,6 +12501,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12524,10 +12520,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124150783</v>
+        <v>124103019</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>91030</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12536,32 +12532,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12569,10 +12563,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461702</v>
+        <v>461895</v>
       </c>
       <c r="R116" t="n">
-        <v>6788415</v>
+        <v>6788288</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12599,17 +12593,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12637,10 +12631,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124102093</v>
+        <v>124079560</v>
       </c>
       <c r="B117" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12653,26 +12647,31 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12680,10 +12679,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461869</v>
+        <v>461854</v>
       </c>
       <c r="R117" t="n">
-        <v>6788429</v>
+        <v>6788321</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12710,17 +12709,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12729,7 +12728,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12748,10 +12746,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124100816</v>
+        <v>124078370</v>
       </c>
       <c r="B118" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12764,26 +12762,31 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -12791,10 +12794,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461815</v>
+        <v>461702</v>
       </c>
       <c r="R118" t="n">
-        <v>6788432</v>
+        <v>6788415</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12821,17 +12824,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav och revlummer.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12840,7 +12843,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12859,10 +12861,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124079435</v>
+        <v>124077891</v>
       </c>
       <c r="B119" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12875,26 +12877,31 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12902,10 +12909,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461848</v>
+        <v>461645</v>
       </c>
       <c r="R119" t="n">
-        <v>6788375</v>
+        <v>6788424</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12942,7 +12949,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12951,7 +12958,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12970,10 +12976,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124100321</v>
+        <v>124099222</v>
       </c>
       <c r="B120" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12986,26 +12992,31 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13013,10 +13024,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461813</v>
+        <v>461848</v>
       </c>
       <c r="R120" t="n">
-        <v>6788469</v>
+        <v>6788394</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13053,7 +13064,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13062,7 +13073,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13081,10 +13091,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124103019</v>
+        <v>124100759</v>
       </c>
       <c r="B121" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13097,21 +13107,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13124,10 +13134,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461895</v>
+        <v>461815</v>
       </c>
       <c r="R121" t="n">
-        <v>6788288</v>
+        <v>6788432</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13164,7 +13174,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13192,10 +13202,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124079560</v>
+        <v>124100321</v>
       </c>
       <c r="B122" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13208,31 +13218,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13240,10 +13245,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461854</v>
+        <v>461813</v>
       </c>
       <c r="R122" t="n">
-        <v>6788321</v>
+        <v>6788469</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13270,17 +13275,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13289,6 +13294,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13418,10 +13424,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124099222</v>
+        <v>124079435</v>
       </c>
       <c r="B124" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13434,31 +13440,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13469,7 +13470,7 @@
         <v>461848</v>
       </c>
       <c r="R124" t="n">
-        <v>6788394</v>
+        <v>6788375</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13496,17 +13497,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13515,6 +13516,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13533,10 +13535,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124077891</v>
+        <v>124150783</v>
       </c>
       <c r="B125" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13545,35 +13547,32 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -13581,10 +13580,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>461645</v>
+        <v>461702</v>
       </c>
       <c r="R125" t="n">
-        <v>6788424</v>
+        <v>6788415</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13621,7 +13620,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13630,6 +13629,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -9006,7 +9006,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124069949</v>
+        <v>124078636</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461867</v>
+        <v>461747</v>
       </c>
       <c r="R83" t="n">
-        <v>6788190</v>
+        <v>6788434</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9108,10 +9108,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124072920</v>
+        <v>124071356</v>
       </c>
       <c r="B84" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9124,34 +9124,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461781</v>
+        <v>461771</v>
       </c>
       <c r="R84" t="n">
-        <v>6788191</v>
+        <v>6788273</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9312,7 +9317,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124077244</v>
+        <v>124069938</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -9352,10 +9357,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461645</v>
+        <v>461867</v>
       </c>
       <c r="R86" t="n">
-        <v>6788424</v>
+        <v>6788190</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9414,10 +9419,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124074329</v>
+        <v>124071868</v>
       </c>
       <c r="B87" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9430,21 +9435,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9454,10 +9459,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461635</v>
+        <v>461779</v>
       </c>
       <c r="R87" t="n">
-        <v>6788154</v>
+        <v>6788261</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9494,7 +9499,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9521,7 +9526,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124078636</v>
+        <v>124077244</v>
       </c>
       <c r="B88" t="n">
         <v>78810</v>
@@ -9561,10 +9566,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461747</v>
+        <v>461645</v>
       </c>
       <c r="R88" t="n">
-        <v>6788434</v>
+        <v>6788424</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9623,7 +9628,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124071683</v>
+        <v>124070191</v>
       </c>
       <c r="B89" t="n">
         <v>78810</v>
@@ -9663,10 +9668,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461771</v>
+        <v>461842</v>
       </c>
       <c r="R89" t="n">
-        <v>6788273</v>
+        <v>6788220</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9725,7 +9730,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124070964</v>
+        <v>124071507</v>
       </c>
       <c r="B90" t="n">
         <v>78810</v>
@@ -9765,10 +9770,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461765</v>
+        <v>461771</v>
       </c>
       <c r="R90" t="n">
-        <v>6788314</v>
+        <v>6788273</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9827,10 +9832,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124070449</v>
+        <v>124072920</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9843,21 +9848,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9867,10 +9872,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461827</v>
+        <v>461781</v>
       </c>
       <c r="R91" t="n">
-        <v>6788228</v>
+        <v>6788191</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10036,7 +10041,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124077216</v>
+        <v>124074329</v>
       </c>
       <c r="B93" t="n">
         <v>78547</v>
@@ -10076,10 +10081,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461645</v>
+        <v>461635</v>
       </c>
       <c r="R93" t="n">
-        <v>6788424</v>
+        <v>6788154</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10112,6 +10117,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10138,10 +10148,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124071356</v>
+        <v>124070449</v>
       </c>
       <c r="B94" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10154,39 +10164,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461771</v>
+        <v>461827</v>
       </c>
       <c r="R94" t="n">
-        <v>6788273</v>
+        <v>6788228</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10245,10 +10250,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124071868</v>
+        <v>124077216</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10261,21 +10266,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10285,10 +10290,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461779</v>
+        <v>461645</v>
       </c>
       <c r="R95" t="n">
-        <v>6788261</v>
+        <v>6788424</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10321,11 +10326,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10352,7 +10352,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124070191</v>
+        <v>124070964</v>
       </c>
       <c r="B96" t="n">
         <v>78810</v>
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461842</v>
+        <v>461765</v>
       </c>
       <c r="R96" t="n">
-        <v>6788220</v>
+        <v>6788314</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124101056</v>
+        <v>124103087</v>
       </c>
       <c r="B97" t="n">
         <v>78810</v>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461781</v>
+        <v>461895</v>
       </c>
       <c r="R97" t="n">
-        <v>6788477</v>
+        <v>6788288</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10556,10 +10556,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124100914</v>
+        <v>124102499</v>
       </c>
       <c r="B98" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10572,39 +10572,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461788</v>
+        <v>461897</v>
       </c>
       <c r="R98" t="n">
-        <v>6788461</v>
+        <v>6788354</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10663,7 +10658,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124102612</v>
+        <v>124101056</v>
       </c>
       <c r="B99" t="n">
         <v>78810</v>
@@ -10703,10 +10698,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461897</v>
+        <v>461781</v>
       </c>
       <c r="R99" t="n">
-        <v>6788354</v>
+        <v>6788477</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10765,7 +10760,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124103087</v>
+        <v>124102429</v>
       </c>
       <c r="B100" t="n">
         <v>78810</v>
@@ -10805,10 +10800,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461895</v>
+        <v>461869</v>
       </c>
       <c r="R100" t="n">
-        <v>6788288</v>
+        <v>6788429</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10867,10 +10862,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124102323</v>
+        <v>124100914</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10883,34 +10878,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461869</v>
+        <v>461788</v>
       </c>
       <c r="R101" t="n">
-        <v>6788429</v>
+        <v>6788461</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10969,10 +10969,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124072166</v>
+        <v>124070565</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10985,34 +10985,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461825</v>
+        <v>461821</v>
       </c>
       <c r="R102" t="n">
-        <v>6788200</v>
+        <v>6788236</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11186,10 +11194,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124076806</v>
+        <v>124070750</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11202,37 +11210,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461730</v>
+        <v>461821</v>
       </c>
       <c r="R104" t="n">
-        <v>6788270</v>
+        <v>6788236</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11267,18 +11277,12 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11297,10 +11301,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124070750</v>
+        <v>124072166</v>
       </c>
       <c r="B105" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11313,39 +11317,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461821</v>
+        <v>461825</v>
       </c>
       <c r="R105" t="n">
-        <v>6788236</v>
+        <v>6788200</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11404,10 +11403,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124075859</v>
+        <v>124076090</v>
       </c>
       <c r="B106" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11420,16 +11419,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11438,24 +11437,21 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461732</v>
+        <v>461711</v>
       </c>
       <c r="R106" t="n">
-        <v>6788226</v>
+        <v>6788217</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11488,11 +11484,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11519,10 +11510,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124074255</v>
+        <v>124072335</v>
       </c>
       <c r="B107" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11535,16 +11526,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11567,10 +11558,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461635</v>
+        <v>461826</v>
       </c>
       <c r="R107" t="n">
-        <v>6788154</v>
+        <v>6788189</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11634,7 +11625,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124070565</v>
+        <v>124074036</v>
       </c>
       <c r="B108" t="n">
         <v>57529</v>
@@ -11668,24 +11659,21 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461821</v>
+        <v>461717</v>
       </c>
       <c r="R108" t="n">
-        <v>6788236</v>
+        <v>6788187</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11718,6 +11706,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Flera bohål i hög, grov, torraka av tall.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11744,10 +11737,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124076637</v>
+        <v>124072783</v>
       </c>
       <c r="B109" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11756,38 +11749,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461711</v>
+        <v>461781</v>
       </c>
       <c r="R109" t="n">
-        <v>6788217</v>
+        <v>6788191</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11822,12 +11818,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11846,10 +11848,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124072783</v>
+        <v>124074255</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11862,26 +11864,31 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11889,10 +11896,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461781</v>
+        <v>461635</v>
       </c>
       <c r="R110" t="n">
-        <v>6788191</v>
+        <v>6788154</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11929,7 +11936,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11938,7 +11945,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11957,10 +11963,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124075614</v>
+        <v>124073786</v>
       </c>
       <c r="B111" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11969,25 +11975,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11995,7 +12001,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -12005,10 +12011,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461717</v>
+        <v>461765</v>
       </c>
       <c r="R111" t="n">
-        <v>6788187</v>
+        <v>6788189</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12045,7 +12051,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Miljöbilder. Ackspår i hög grov stubbe av gammal tall.</t>
+          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12072,10 +12078,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124073786</v>
+        <v>124075859</v>
       </c>
       <c r="B112" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12084,25 +12090,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12110,7 +12116,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -12120,10 +12126,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461765</v>
+        <v>461732</v>
       </c>
       <c r="R112" t="n">
-        <v>6788189</v>
+        <v>6788226</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12160,7 +12166,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Miljöbild. Så kallad tjädertall.</t>
+          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12187,10 +12193,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124076090</v>
+        <v>124076637</v>
       </c>
       <c r="B113" t="n">
-        <v>57513</v>
+        <v>8447</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12199,33 +12205,28 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -12294,10 +12295,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124072335</v>
+        <v>124076806</v>
       </c>
       <c r="B114" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12310,31 +12311,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12342,10 +12338,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461826</v>
+        <v>461730</v>
       </c>
       <c r="R114" t="n">
-        <v>6788189</v>
+        <v>6788270</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12382,7 +12378,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12391,6 +12387,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12409,10 +12406,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124102093</v>
+        <v>124079560</v>
       </c>
       <c r="B115" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12425,26 +12422,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12452,10 +12454,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461869</v>
+        <v>461854</v>
       </c>
       <c r="R115" t="n">
-        <v>6788429</v>
+        <v>6788321</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12482,17 +12484,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12501,7 +12503,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12520,10 +12521,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124103019</v>
+        <v>124077891</v>
       </c>
       <c r="B116" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12536,26 +12537,31 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12563,10 +12569,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461895</v>
+        <v>461645</v>
       </c>
       <c r="R116" t="n">
-        <v>6788288</v>
+        <v>6788424</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12593,17 +12599,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12612,7 +12618,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12631,10 +12636,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124079560</v>
+        <v>124150783</v>
       </c>
       <c r="B117" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12643,35 +12648,32 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12679,10 +12681,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461854</v>
+        <v>461702</v>
       </c>
       <c r="R117" t="n">
-        <v>6788321</v>
+        <v>6788415</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12719,7 +12721,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12728,6 +12730,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12746,10 +12749,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124078370</v>
+        <v>124102093</v>
       </c>
       <c r="B118" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12762,31 +12765,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -12794,10 +12792,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461702</v>
+        <v>461869</v>
       </c>
       <c r="R118" t="n">
-        <v>6788415</v>
+        <v>6788429</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12824,17 +12822,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12843,6 +12841,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12861,10 +12860,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124077891</v>
+        <v>124100816</v>
       </c>
       <c r="B119" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12877,31 +12876,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12909,10 +12903,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461645</v>
+        <v>461815</v>
       </c>
       <c r="R119" t="n">
-        <v>6788424</v>
+        <v>6788432</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12939,17 +12933,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
+          <t>Miljöbilder. Garnlav och revlummer.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12958,6 +12952,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12976,10 +12971,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124099222</v>
+        <v>124074099</v>
       </c>
       <c r="B120" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12992,31 +12987,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13024,10 +13014,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461848</v>
+        <v>461687</v>
       </c>
       <c r="R120" t="n">
-        <v>6788394</v>
+        <v>6788172</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13054,17 +13044,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13073,6 +13063,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13091,10 +13082,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124100759</v>
+        <v>124078370</v>
       </c>
       <c r="B121" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13107,26 +13098,31 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13134,10 +13130,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461815</v>
+        <v>461702</v>
       </c>
       <c r="R121" t="n">
-        <v>6788432</v>
+        <v>6788415</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13164,17 +13160,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13183,7 +13179,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13313,10 +13308,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124074099</v>
+        <v>124079435</v>
       </c>
       <c r="B123" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13329,21 +13324,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13356,10 +13351,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461687</v>
+        <v>461848</v>
       </c>
       <c r="R123" t="n">
-        <v>6788172</v>
+        <v>6788375</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13396,7 +13391,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13424,10 +13419,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124079435</v>
+        <v>124103019</v>
       </c>
       <c r="B124" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13440,21 +13435,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13467,10 +13462,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461848</v>
+        <v>461895</v>
       </c>
       <c r="R124" t="n">
-        <v>6788375</v>
+        <v>6788288</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13497,17 +13492,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13535,10 +13530,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124150783</v>
+        <v>124099222</v>
       </c>
       <c r="B125" t="n">
-        <v>8447</v>
+        <v>57513</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13547,32 +13542,35 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -13580,10 +13578,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>461702</v>
+        <v>461848</v>
       </c>
       <c r="R125" t="n">
-        <v>6788415</v>
+        <v>6788394</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13610,17 +13608,17 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13629,7 +13627,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -9006,10 +9006,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124078636</v>
+        <v>124072920</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461747</v>
+        <v>461781</v>
       </c>
       <c r="R83" t="n">
-        <v>6788434</v>
+        <v>6788191</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9108,10 +9108,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124071356</v>
+        <v>124071507</v>
       </c>
       <c r="B84" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9124,29 +9124,24 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -9215,7 +9210,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124070118</v>
+        <v>124070191</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -9255,10 +9250,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461846</v>
+        <v>461842</v>
       </c>
       <c r="R85" t="n">
-        <v>6788208</v>
+        <v>6788220</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9419,7 +9414,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124071868</v>
+        <v>124070964</v>
       </c>
       <c r="B87" t="n">
         <v>78810</v>
@@ -9459,10 +9454,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461779</v>
+        <v>461765</v>
       </c>
       <c r="R87" t="n">
-        <v>6788261</v>
+        <v>6788314</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9495,11 +9490,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9526,10 +9516,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124077244</v>
+        <v>124074329</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9542,21 +9532,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9566,10 +9556,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461645</v>
+        <v>461635</v>
       </c>
       <c r="R88" t="n">
-        <v>6788424</v>
+        <v>6788154</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9602,6 +9592,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9628,10 +9623,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124070191</v>
+        <v>124073722</v>
       </c>
       <c r="B89" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9644,34 +9639,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461842</v>
+        <v>461781</v>
       </c>
       <c r="R89" t="n">
-        <v>6788220</v>
+        <v>6788191</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9730,7 +9730,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124071507</v>
+        <v>124071868</v>
       </c>
       <c r="B90" t="n">
         <v>78810</v>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461771</v>
+        <v>461779</v>
       </c>
       <c r="R90" t="n">
-        <v>6788273</v>
+        <v>6788261</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9806,6 +9806,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9832,10 +9837,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124072920</v>
+        <v>124078636</v>
       </c>
       <c r="B91" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9848,21 +9853,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9872,10 +9877,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461781</v>
+        <v>461747</v>
       </c>
       <c r="R91" t="n">
-        <v>6788191</v>
+        <v>6788434</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9934,10 +9939,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124073722</v>
+        <v>124070449</v>
       </c>
       <c r="B92" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9950,39 +9955,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461781</v>
+        <v>461827</v>
       </c>
       <c r="R92" t="n">
-        <v>6788191</v>
+        <v>6788228</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10041,10 +10041,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124074329</v>
+        <v>124070118</v>
       </c>
       <c r="B93" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10057,21 +10057,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10081,10 +10081,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461635</v>
+        <v>461846</v>
       </c>
       <c r="R93" t="n">
-        <v>6788154</v>
+        <v>6788208</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10117,11 +10117,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10148,7 +10143,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124070449</v>
+        <v>124077244</v>
       </c>
       <c r="B94" t="n">
         <v>78810</v>
@@ -10188,10 +10183,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461827</v>
+        <v>461645</v>
       </c>
       <c r="R94" t="n">
-        <v>6788228</v>
+        <v>6788424</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10250,10 +10245,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124077216</v>
+        <v>124071356</v>
       </c>
       <c r="B95" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10266,34 +10261,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461645</v>
+        <v>461771</v>
       </c>
       <c r="R95" t="n">
-        <v>6788424</v>
+        <v>6788273</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10352,10 +10352,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124070964</v>
+        <v>124077216</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10368,21 +10368,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461765</v>
+        <v>461645</v>
       </c>
       <c r="R96" t="n">
-        <v>6788314</v>
+        <v>6788424</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124103087</v>
+        <v>124102429</v>
       </c>
       <c r="B97" t="n">
         <v>78810</v>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461895</v>
+        <v>461869</v>
       </c>
       <c r="R97" t="n">
-        <v>6788288</v>
+        <v>6788429</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10556,7 +10556,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124102499</v>
+        <v>124102612</v>
       </c>
       <c r="B98" t="n">
         <v>78810</v>
@@ -10658,7 +10658,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124101056</v>
+        <v>124103283</v>
       </c>
       <c r="B99" t="n">
         <v>78810</v>
@@ -10698,10 +10698,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461781</v>
+        <v>461895</v>
       </c>
       <c r="R99" t="n">
-        <v>6788477</v>
+        <v>6788288</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10760,10 +10760,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124102429</v>
+        <v>124100914</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10776,34 +10776,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461869</v>
+        <v>461788</v>
       </c>
       <c r="R100" t="n">
-        <v>6788429</v>
+        <v>6788461</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10862,10 +10867,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124100914</v>
+        <v>124101056</v>
       </c>
       <c r="B101" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10878,39 +10883,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461788</v>
+        <v>461781</v>
       </c>
       <c r="R101" t="n">
-        <v>6788461</v>
+        <v>6788477</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10969,10 +10969,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124070565</v>
+        <v>124075169</v>
       </c>
       <c r="B102" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10985,16 +10985,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11007,7 +11007,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -11017,10 +11017,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461821</v>
+        <v>461717</v>
       </c>
       <c r="R102" t="n">
-        <v>6788236</v>
+        <v>6788187</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11053,6 +11053,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11079,7 +11084,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124075169</v>
+        <v>124072335</v>
       </c>
       <c r="B103" t="n">
         <v>57513</v>
@@ -11127,10 +11132,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461717</v>
+        <v>461826</v>
       </c>
       <c r="R103" t="n">
-        <v>6788187</v>
+        <v>6788189</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11167,7 +11172,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11194,10 +11199,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124070750</v>
+        <v>124074036</v>
       </c>
       <c r="B104" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11210,16 +11215,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11230,7 +11235,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11239,10 +11244,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461821</v>
+        <v>461717</v>
       </c>
       <c r="R104" t="n">
-        <v>6788236</v>
+        <v>6788187</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11275,6 +11280,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Flera bohål i hög, grov, torraka av tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11301,10 +11311,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124072166</v>
+        <v>124070565</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11317,34 +11327,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461825</v>
+        <v>461821</v>
       </c>
       <c r="R105" t="n">
-        <v>6788200</v>
+        <v>6788236</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11403,10 +11421,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124076090</v>
+        <v>124074729</v>
       </c>
       <c r="B106" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11419,16 +11437,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11448,10 +11466,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461711</v>
+        <v>461635</v>
       </c>
       <c r="R106" t="n">
-        <v>6788217</v>
+        <v>6788154</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11484,6 +11502,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11510,7 +11533,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124072335</v>
+        <v>124070750</v>
       </c>
       <c r="B107" t="n">
         <v>57513</v>
@@ -11544,24 +11567,21 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461826</v>
+        <v>461821</v>
       </c>
       <c r="R107" t="n">
-        <v>6788189</v>
+        <v>6788236</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11594,11 +11614,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11625,10 +11640,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124074036</v>
+        <v>124076090</v>
       </c>
       <c r="B108" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11641,16 +11656,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -11661,7 +11676,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -11670,10 +11685,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461717</v>
+        <v>461711</v>
       </c>
       <c r="R108" t="n">
-        <v>6788187</v>
+        <v>6788217</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11706,11 +11721,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Flera bohål i hög, grov, torraka av tall.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11848,10 +11858,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124074255</v>
+        <v>124076637</v>
       </c>
       <c r="B110" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11860,46 +11870,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461635</v>
+        <v>461711</v>
       </c>
       <c r="R110" t="n">
-        <v>6788154</v>
+        <v>6788217</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11932,11 +11934,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11963,10 +11960,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124073786</v>
+        <v>124072166</v>
       </c>
       <c r="B111" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11975,46 +11972,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461765</v>
+        <v>461825</v>
       </c>
       <c r="R111" t="n">
-        <v>6788189</v>
+        <v>6788200</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12047,11 +12036,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12193,10 +12177,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124076637</v>
+        <v>124076806</v>
       </c>
       <c r="B113" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12205,38 +12189,41 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461711</v>
+        <v>461730</v>
       </c>
       <c r="R113" t="n">
-        <v>6788217</v>
+        <v>6788270</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12271,12 +12258,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12295,10 +12288,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124076806</v>
+        <v>124073786</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12307,30 +12300,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12338,10 +12336,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461730</v>
+        <v>461765</v>
       </c>
       <c r="R114" t="n">
-        <v>6788270</v>
+        <v>6788189</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12378,7 +12376,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
+          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12387,7 +12385,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12406,7 +12403,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124079560</v>
+        <v>124078370</v>
       </c>
       <c r="B115" t="n">
         <v>57529</v>
@@ -12454,10 +12451,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461854</v>
+        <v>461702</v>
       </c>
       <c r="R115" t="n">
-        <v>6788321</v>
+        <v>6788415</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12521,10 +12518,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124077891</v>
+        <v>124074099</v>
       </c>
       <c r="B116" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12537,31 +12534,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12569,10 +12561,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461645</v>
+        <v>461687</v>
       </c>
       <c r="R116" t="n">
-        <v>6788424</v>
+        <v>6788172</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12609,7 +12601,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
+          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12618,6 +12610,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12636,10 +12629,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124150783</v>
+        <v>124079560</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12648,32 +12641,35 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12681,10 +12677,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461702</v>
+        <v>461854</v>
       </c>
       <c r="R117" t="n">
-        <v>6788415</v>
+        <v>6788321</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12721,7 +12717,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12730,7 +12726,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12749,10 +12744,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124102093</v>
+        <v>124077891</v>
       </c>
       <c r="B118" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12765,26 +12760,31 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -12792,10 +12792,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461869</v>
+        <v>461645</v>
       </c>
       <c r="R118" t="n">
-        <v>6788429</v>
+        <v>6788424</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12822,17 +12822,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12841,7 +12841,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12860,7 +12859,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124100816</v>
+        <v>124079435</v>
       </c>
       <c r="B119" t="n">
         <v>78810</v>
@@ -12903,10 +12902,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461815</v>
+        <v>461848</v>
       </c>
       <c r="R119" t="n">
-        <v>6788432</v>
+        <v>6788375</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12933,17 +12932,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav och revlummer.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12971,10 +12970,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124074099</v>
+        <v>124099222</v>
       </c>
       <c r="B120" t="n">
-        <v>78547</v>
+        <v>57513</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12987,26 +12986,31 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13014,10 +13018,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461687</v>
+        <v>461848</v>
       </c>
       <c r="R120" t="n">
-        <v>6788172</v>
+        <v>6788394</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13044,17 +13048,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13063,7 +13067,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13082,10 +13085,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124078370</v>
+        <v>124103019</v>
       </c>
       <c r="B121" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13098,31 +13101,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13130,10 +13128,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461702</v>
+        <v>461895</v>
       </c>
       <c r="R121" t="n">
-        <v>6788415</v>
+        <v>6788288</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13160,17 +13158,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13179,6 +13177,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13308,10 +13307,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124079435</v>
+        <v>124102093</v>
       </c>
       <c r="B123" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13324,21 +13323,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13351,10 +13350,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461848</v>
+        <v>461869</v>
       </c>
       <c r="R123" t="n">
-        <v>6788375</v>
+        <v>6788429</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13381,17 +13380,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13419,10 +13418,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124103019</v>
+        <v>124150783</v>
       </c>
       <c r="B124" t="n">
-        <v>91030</v>
+        <v>8447</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13431,30 +13430,32 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13462,10 +13463,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461895</v>
+        <v>461702</v>
       </c>
       <c r="R124" t="n">
-        <v>6788288</v>
+        <v>6788415</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13492,17 +13493,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13530,10 +13531,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124099222</v>
+        <v>124100816</v>
       </c>
       <c r="B125" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13546,31 +13547,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -13578,10 +13574,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>461848</v>
+        <v>461815</v>
       </c>
       <c r="R125" t="n">
-        <v>6788394</v>
+        <v>6788432</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13618,7 +13614,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbilder. Garnlav och revlummer.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13627,6 +13623,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -9006,10 +9006,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124072920</v>
+        <v>124070118</v>
       </c>
       <c r="B83" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461781</v>
+        <v>461846</v>
       </c>
       <c r="R83" t="n">
-        <v>6788191</v>
+        <v>6788208</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9108,7 +9108,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124071507</v>
+        <v>124070191</v>
       </c>
       <c r="B84" t="n">
         <v>78810</v>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461771</v>
+        <v>461842</v>
       </c>
       <c r="R84" t="n">
-        <v>6788273</v>
+        <v>6788220</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9210,7 +9210,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124070191</v>
+        <v>124069938</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461842</v>
+        <v>461867</v>
       </c>
       <c r="R85" t="n">
-        <v>6788220</v>
+        <v>6788190</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9312,7 +9312,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124069938</v>
+        <v>124077244</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461867</v>
+        <v>461645</v>
       </c>
       <c r="R86" t="n">
-        <v>6788190</v>
+        <v>6788424</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9414,10 +9414,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124070964</v>
+        <v>124077216</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9430,21 +9430,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461765</v>
+        <v>461645</v>
       </c>
       <c r="R87" t="n">
-        <v>6788314</v>
+        <v>6788424</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9516,10 +9516,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124074329</v>
+        <v>124071683</v>
       </c>
       <c r="B88" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9532,21 +9532,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9556,10 +9556,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461635</v>
+        <v>461771</v>
       </c>
       <c r="R88" t="n">
-        <v>6788154</v>
+        <v>6788273</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9592,11 +9592,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9623,10 +9618,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124073722</v>
+        <v>124074329</v>
       </c>
       <c r="B89" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9639,39 +9634,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461781</v>
+        <v>461635</v>
       </c>
       <c r="R89" t="n">
-        <v>6788191</v>
+        <v>6788154</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9704,6 +9694,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9730,10 +9725,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124071868</v>
+        <v>124071356</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9746,34 +9741,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461779</v>
+        <v>461771</v>
       </c>
       <c r="R90" t="n">
-        <v>6788261</v>
+        <v>6788273</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9806,11 +9806,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9837,7 +9832,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124078636</v>
+        <v>124070449</v>
       </c>
       <c r="B91" t="n">
         <v>78810</v>
@@ -9877,10 +9872,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461747</v>
+        <v>461827</v>
       </c>
       <c r="R91" t="n">
-        <v>6788434</v>
+        <v>6788228</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9939,10 +9934,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124070449</v>
+        <v>124072920</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9955,21 +9950,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9979,10 +9974,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461827</v>
+        <v>461781</v>
       </c>
       <c r="R92" t="n">
-        <v>6788228</v>
+        <v>6788191</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10041,7 +10036,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124070118</v>
+        <v>124078636</v>
       </c>
       <c r="B93" t="n">
         <v>78810</v>
@@ -10081,10 +10076,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461846</v>
+        <v>461747</v>
       </c>
       <c r="R93" t="n">
-        <v>6788208</v>
+        <v>6788434</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10143,7 +10138,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124077244</v>
+        <v>124071868</v>
       </c>
       <c r="B94" t="n">
         <v>78810</v>
@@ -10183,10 +10178,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461645</v>
+        <v>461779</v>
       </c>
       <c r="R94" t="n">
-        <v>6788424</v>
+        <v>6788261</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10219,6 +10214,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10245,7 +10245,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124071356</v>
+        <v>124073722</v>
       </c>
       <c r="B95" t="n">
         <v>57529</v>
@@ -10281,7 +10281,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10290,10 +10290,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461771</v>
+        <v>461781</v>
       </c>
       <c r="R95" t="n">
-        <v>6788273</v>
+        <v>6788191</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10352,10 +10352,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124077216</v>
+        <v>124070964</v>
       </c>
       <c r="B96" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10368,21 +10368,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461645</v>
+        <v>461765</v>
       </c>
       <c r="R96" t="n">
-        <v>6788424</v>
+        <v>6788314</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124102429</v>
+        <v>124102664</v>
       </c>
       <c r="B97" t="n">
         <v>78810</v>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461869</v>
+        <v>461897</v>
       </c>
       <c r="R97" t="n">
-        <v>6788429</v>
+        <v>6788354</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10530,6 +10530,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav runt mig.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10556,7 +10561,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124102612</v>
+        <v>124101056</v>
       </c>
       <c r="B98" t="n">
         <v>78810</v>
@@ -10596,10 +10601,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461897</v>
+        <v>461781</v>
       </c>
       <c r="R98" t="n">
-        <v>6788354</v>
+        <v>6788477</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10760,10 +10765,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124100914</v>
+        <v>124102429</v>
       </c>
       <c r="B100" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10776,39 +10781,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461788</v>
+        <v>461869</v>
       </c>
       <c r="R100" t="n">
-        <v>6788461</v>
+        <v>6788429</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10867,10 +10867,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124101056</v>
+        <v>124100914</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10883,34 +10883,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461781</v>
+        <v>461788</v>
       </c>
       <c r="R101" t="n">
-        <v>6788477</v>
+        <v>6788461</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10969,10 +10974,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124075169</v>
+        <v>124075614</v>
       </c>
       <c r="B102" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10985,16 +10990,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11007,7 +11012,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -11057,7 +11062,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Ackspår i hög grov stubbe av gammal tall.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11084,10 +11089,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124072335</v>
+        <v>124074255</v>
       </c>
       <c r="B103" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11100,16 +11105,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11132,10 +11137,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461826</v>
+        <v>461635</v>
       </c>
       <c r="R103" t="n">
-        <v>6788189</v>
+        <v>6788154</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11199,7 +11204,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124074036</v>
+        <v>124075859</v>
       </c>
       <c r="B104" t="n">
         <v>57529</v>
@@ -11233,21 +11238,24 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461717</v>
+        <v>461732</v>
       </c>
       <c r="R104" t="n">
-        <v>6788187</v>
+        <v>6788226</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11284,7 +11292,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Flera bohål i hög, grov, torraka av tall.</t>
+          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11311,10 +11319,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124070565</v>
+        <v>124074066</v>
       </c>
       <c r="B105" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11327,16 +11335,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11345,24 +11353,21 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461821</v>
+        <v>461717</v>
       </c>
       <c r="R105" t="n">
-        <v>6788236</v>
+        <v>6788187</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11421,10 +11426,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124074729</v>
+        <v>124072335</v>
       </c>
       <c r="B106" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11437,16 +11442,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11455,21 +11460,24 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461635</v>
+        <v>461826</v>
       </c>
       <c r="R106" t="n">
-        <v>6788154</v>
+        <v>6788189</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11506,7 +11514,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11533,10 +11541,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124070750</v>
+        <v>124072166</v>
       </c>
       <c r="B107" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11549,39 +11557,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461821</v>
+        <v>461825</v>
       </c>
       <c r="R107" t="n">
-        <v>6788236</v>
+        <v>6788200</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11640,7 +11643,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124076090</v>
+        <v>124070750</v>
       </c>
       <c r="B108" t="n">
         <v>57513</v>
@@ -11685,10 +11688,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461711</v>
+        <v>461821</v>
       </c>
       <c r="R108" t="n">
-        <v>6788217</v>
+        <v>6788236</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11747,10 +11750,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124072783</v>
+        <v>124073786</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11759,30 +11762,35 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11790,10 +11798,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461781</v>
+        <v>461765</v>
       </c>
       <c r="R109" t="n">
-        <v>6788191</v>
+        <v>6788189</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11830,7 +11838,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11839,7 +11847,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11858,10 +11865,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124076637</v>
+        <v>124076090</v>
       </c>
       <c r="B110" t="n">
-        <v>8447</v>
+        <v>57513</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11870,28 +11877,33 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -11960,7 +11972,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124072166</v>
+        <v>124072783</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -11994,16 +12006,19 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461825</v>
+        <v>461781</v>
       </c>
       <c r="R111" t="n">
-        <v>6788200</v>
+        <v>6788191</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12038,12 +12053,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12062,7 +12083,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124075859</v>
+        <v>124070565</v>
       </c>
       <c r="B112" t="n">
         <v>57529</v>
@@ -12110,10 +12131,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461732</v>
+        <v>461821</v>
       </c>
       <c r="R112" t="n">
-        <v>6788226</v>
+        <v>6788236</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12146,11 +12167,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12288,10 +12304,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124073786</v>
+        <v>124076637</v>
       </c>
       <c r="B114" t="n">
-        <v>56722</v>
+        <v>8447</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12304,42 +12320,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461765</v>
+        <v>461711</v>
       </c>
       <c r="R114" t="n">
-        <v>6788189</v>
+        <v>6788217</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12372,11 +12380,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12403,10 +12406,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124078370</v>
+        <v>124099222</v>
       </c>
       <c r="B115" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12419,16 +12422,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12451,10 +12454,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461702</v>
+        <v>461848</v>
       </c>
       <c r="R115" t="n">
-        <v>6788415</v>
+        <v>6788394</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12481,17 +12484,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12518,10 +12521,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124074099</v>
+        <v>124077891</v>
       </c>
       <c r="B116" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12534,26 +12537,31 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12561,10 +12569,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461687</v>
+        <v>461645</v>
       </c>
       <c r="R116" t="n">
-        <v>6788172</v>
+        <v>6788424</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12601,7 +12609,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
+          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12610,7 +12618,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12629,10 +12636,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124079560</v>
+        <v>124103019</v>
       </c>
       <c r="B117" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12645,31 +12652,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12677,10 +12679,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461854</v>
+        <v>461895</v>
       </c>
       <c r="R117" t="n">
-        <v>6788321</v>
+        <v>6788288</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12707,17 +12709,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12726,6 +12728,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12744,10 +12747,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124077891</v>
+        <v>124079435</v>
       </c>
       <c r="B118" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12760,31 +12763,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -12792,10 +12790,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461645</v>
+        <v>461848</v>
       </c>
       <c r="R118" t="n">
-        <v>6788424</v>
+        <v>6788375</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12832,7 +12830,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12841,6 +12839,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12859,10 +12858,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124079435</v>
+        <v>124074099</v>
       </c>
       <c r="B119" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12875,21 +12874,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12902,10 +12901,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461848</v>
+        <v>461687</v>
       </c>
       <c r="R119" t="n">
-        <v>6788375</v>
+        <v>6788172</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12942,7 +12941,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12970,10 +12969,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124099222</v>
+        <v>124079560</v>
       </c>
       <c r="B120" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12986,16 +12985,16 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -13018,10 +13017,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461848</v>
+        <v>461854</v>
       </c>
       <c r="R120" t="n">
-        <v>6788394</v>
+        <v>6788321</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13048,17 +13047,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13085,10 +13084,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124103019</v>
+        <v>124150783</v>
       </c>
       <c r="B121" t="n">
-        <v>91030</v>
+        <v>8447</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13097,30 +13096,32 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13128,10 +13129,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461895</v>
+        <v>461702</v>
       </c>
       <c r="R121" t="n">
-        <v>6788288</v>
+        <v>6788415</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13158,17 +13159,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13418,10 +13419,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124150783</v>
+        <v>124078370</v>
       </c>
       <c r="B124" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13430,32 +13431,35 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13503,7 +13507,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13512,7 +13516,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13531,7 +13534,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124100816</v>
+        <v>124100759</v>
       </c>
       <c r="B125" t="n">
         <v>78810</v>
@@ -13614,7 +13617,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav och revlummer.</t>
+          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
         </is>
       </c>
       <c r="AD125" t="b">

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -10245,10 +10245,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124073722</v>
+        <v>124070964</v>
       </c>
       <c r="B95" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10261,39 +10261,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461781</v>
+        <v>461765</v>
       </c>
       <c r="R95" t="n">
-        <v>6788191</v>
+        <v>6788314</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10352,10 +10347,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124070964</v>
+        <v>124073722</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10368,34 +10363,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461765</v>
+        <v>461781</v>
       </c>
       <c r="R96" t="n">
-        <v>6788314</v>
+        <v>6788191</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12083,10 +12083,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124070565</v>
+        <v>124076806</v>
       </c>
       <c r="B112" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12099,31 +12099,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -12131,10 +12126,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461821</v>
+        <v>461730</v>
       </c>
       <c r="R112" t="n">
-        <v>6788236</v>
+        <v>6788270</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12169,12 +12164,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12193,10 +12194,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124076806</v>
+        <v>124070565</v>
       </c>
       <c r="B113" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12209,26 +12210,31 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12236,10 +12242,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461730</v>
+        <v>461821</v>
       </c>
       <c r="R113" t="n">
-        <v>6788270</v>
+        <v>6788236</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12274,18 +12280,12 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -9006,7 +9006,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124070118</v>
+        <v>124070964</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461846</v>
+        <v>461765</v>
       </c>
       <c r="R83" t="n">
-        <v>6788208</v>
+        <v>6788314</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9108,7 +9108,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124070191</v>
+        <v>124071868</v>
       </c>
       <c r="B84" t="n">
         <v>78810</v>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461842</v>
+        <v>461779</v>
       </c>
       <c r="R84" t="n">
-        <v>6788220</v>
+        <v>6788261</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9184,6 +9184,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9210,7 +9215,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124069938</v>
+        <v>124078636</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -9250,10 +9255,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461867</v>
+        <v>461747</v>
       </c>
       <c r="R85" t="n">
-        <v>6788190</v>
+        <v>6788434</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9312,7 +9317,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124077244</v>
+        <v>124069447</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -9352,10 +9357,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461645</v>
+        <v>461867</v>
       </c>
       <c r="R86" t="n">
-        <v>6788424</v>
+        <v>6788190</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9414,10 +9419,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124077216</v>
+        <v>124077244</v>
       </c>
       <c r="B87" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9430,21 +9435,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9516,10 +9521,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124071683</v>
+        <v>124074329</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9532,21 +9537,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9556,10 +9561,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461771</v>
+        <v>461635</v>
       </c>
       <c r="R88" t="n">
-        <v>6788273</v>
+        <v>6788154</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9592,6 +9597,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9618,10 +9628,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124074329</v>
+        <v>124071683</v>
       </c>
       <c r="B89" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9634,21 +9644,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9658,10 +9668,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461635</v>
+        <v>461771</v>
       </c>
       <c r="R89" t="n">
-        <v>6788154</v>
+        <v>6788273</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9694,11 +9704,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9832,7 +9837,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124070449</v>
+        <v>124070118</v>
       </c>
       <c r="B91" t="n">
         <v>78810</v>
@@ -9872,10 +9877,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461827</v>
+        <v>461846</v>
       </c>
       <c r="R91" t="n">
-        <v>6788228</v>
+        <v>6788208</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9934,7 +9939,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124072920</v>
+        <v>124077216</v>
       </c>
       <c r="B92" t="n">
         <v>78547</v>
@@ -9974,10 +9979,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461781</v>
+        <v>461645</v>
       </c>
       <c r="R92" t="n">
-        <v>6788191</v>
+        <v>6788424</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10036,7 +10041,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124078636</v>
+        <v>124070191</v>
       </c>
       <c r="B93" t="n">
         <v>78810</v>
@@ -10076,10 +10081,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461747</v>
+        <v>461842</v>
       </c>
       <c r="R93" t="n">
-        <v>6788434</v>
+        <v>6788220</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10138,7 +10143,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124071868</v>
+        <v>124070449</v>
       </c>
       <c r="B94" t="n">
         <v>78810</v>
@@ -10178,10 +10183,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461779</v>
+        <v>461827</v>
       </c>
       <c r="R94" t="n">
-        <v>6788261</v>
+        <v>6788228</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10214,11 +10219,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10245,10 +10245,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124070964</v>
+        <v>124072920</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10261,21 +10261,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10285,10 +10285,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461765</v>
+        <v>461781</v>
       </c>
       <c r="R95" t="n">
-        <v>6788314</v>
+        <v>6788191</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124102664</v>
+        <v>124103283</v>
       </c>
       <c r="B97" t="n">
         <v>78810</v>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461897</v>
+        <v>461895</v>
       </c>
       <c r="R97" t="n">
-        <v>6788354</v>
+        <v>6788288</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10530,11 +10530,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav runt mig.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10561,10 +10556,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124101056</v>
+        <v>124100914</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10577,34 +10572,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461781</v>
+        <v>461788</v>
       </c>
       <c r="R98" t="n">
-        <v>6788477</v>
+        <v>6788461</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10663,7 +10663,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124103283</v>
+        <v>124101056</v>
       </c>
       <c r="B99" t="n">
         <v>78810</v>
@@ -10703,10 +10703,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461895</v>
+        <v>461781</v>
       </c>
       <c r="R99" t="n">
-        <v>6788288</v>
+        <v>6788477</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10765,7 +10765,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124102429</v>
+        <v>124102323</v>
       </c>
       <c r="B100" t="n">
         <v>78810</v>
@@ -10867,10 +10867,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124100914</v>
+        <v>124102612</v>
       </c>
       <c r="B101" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10883,39 +10883,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461788</v>
+        <v>461897</v>
       </c>
       <c r="R101" t="n">
-        <v>6788461</v>
+        <v>6788354</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11204,10 +11199,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124075859</v>
+        <v>124072783</v>
       </c>
       <c r="B104" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11220,31 +11215,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -11252,10 +11242,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461732</v>
+        <v>461781</v>
       </c>
       <c r="R104" t="n">
-        <v>6788226</v>
+        <v>6788191</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11292,7 +11282,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Miljöbild med äldre högstubbe!</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11301,6 +11291,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11319,7 +11310,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124074066</v>
+        <v>124075169</v>
       </c>
       <c r="B105" t="n">
         <v>57513</v>
@@ -11353,11 +11344,14 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -11400,6 +11394,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11426,10 +11425,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124072335</v>
+        <v>124073786</v>
       </c>
       <c r="B106" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11438,25 +11437,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11464,7 +11463,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -11474,7 +11473,7 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461826</v>
+        <v>461765</v>
       </c>
       <c r="R106" t="n">
         <v>6788189</v>
@@ -11514,7 +11513,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11541,10 +11540,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124072166</v>
+        <v>124070750</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11557,34 +11556,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461825</v>
+        <v>461821</v>
       </c>
       <c r="R107" t="n">
-        <v>6788200</v>
+        <v>6788236</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11643,10 +11647,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124070750</v>
+        <v>124076637</v>
       </c>
       <c r="B108" t="n">
-        <v>57513</v>
+        <v>8447</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11655,43 +11659,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461821</v>
+        <v>461711</v>
       </c>
       <c r="R108" t="n">
-        <v>6788236</v>
+        <v>6788217</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11750,10 +11749,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124073786</v>
+        <v>124072166</v>
       </c>
       <c r="B109" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11762,46 +11761,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461765</v>
+        <v>461825</v>
       </c>
       <c r="R109" t="n">
-        <v>6788189</v>
+        <v>6788200</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11834,11 +11825,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11865,10 +11851,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124076090</v>
+        <v>124070565</v>
       </c>
       <c r="B110" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11881,16 +11867,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -11899,21 +11885,24 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461711</v>
+        <v>461821</v>
       </c>
       <c r="R110" t="n">
-        <v>6788217</v>
+        <v>6788236</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11972,10 +11961,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124072783</v>
+        <v>124075859</v>
       </c>
       <c r="B111" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11988,26 +11977,31 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12015,10 +12009,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461781</v>
+        <v>461732</v>
       </c>
       <c r="R111" t="n">
-        <v>6788191</v>
+        <v>6788226</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12055,7 +12049,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12064,7 +12058,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12083,10 +12076,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124076806</v>
+        <v>124076090</v>
       </c>
       <c r="B112" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12099,37 +12092,39 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461730</v>
+        <v>461711</v>
       </c>
       <c r="R112" t="n">
-        <v>6788270</v>
+        <v>6788217</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12164,18 +12159,12 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12194,10 +12183,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124070565</v>
+        <v>124072335</v>
       </c>
       <c r="B113" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12210,16 +12199,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12232,7 +12221,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12242,10 +12231,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461821</v>
+        <v>461826</v>
       </c>
       <c r="R113" t="n">
-        <v>6788236</v>
+        <v>6788189</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12278,6 +12267,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12304,10 +12298,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124076637</v>
+        <v>124076806</v>
       </c>
       <c r="B114" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12316,38 +12310,41 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461711</v>
+        <v>461730</v>
       </c>
       <c r="R114" t="n">
-        <v>6788217</v>
+        <v>6788270</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12382,12 +12379,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12406,10 +12409,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124099222</v>
+        <v>124078370</v>
       </c>
       <c r="B115" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12422,16 +12425,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12454,10 +12457,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461848</v>
+        <v>461702</v>
       </c>
       <c r="R115" t="n">
-        <v>6788394</v>
+        <v>6788415</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12484,17 +12487,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12521,10 +12524,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124077891</v>
+        <v>124150783</v>
       </c>
       <c r="B116" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12533,35 +12536,32 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12569,10 +12569,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461645</v>
+        <v>461702</v>
       </c>
       <c r="R116" t="n">
-        <v>6788424</v>
+        <v>6788415</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12618,6 +12618,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12747,10 +12748,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124079435</v>
+        <v>124077891</v>
       </c>
       <c r="B118" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12763,26 +12764,31 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -12790,10 +12796,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461848</v>
+        <v>461645</v>
       </c>
       <c r="R118" t="n">
-        <v>6788375</v>
+        <v>6788424</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12830,7 +12836,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12839,7 +12845,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12858,10 +12863,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124074099</v>
+        <v>124100321</v>
       </c>
       <c r="B119" t="n">
-        <v>78547</v>
+        <v>91299</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12874,21 +12879,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12901,10 +12906,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461687</v>
+        <v>461813</v>
       </c>
       <c r="R119" t="n">
-        <v>6788172</v>
+        <v>6788469</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12931,17 +12936,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12969,10 +12974,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124079560</v>
+        <v>124079435</v>
       </c>
       <c r="B120" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12985,31 +12990,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13017,10 +13017,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461854</v>
+        <v>461848</v>
       </c>
       <c r="R120" t="n">
-        <v>6788321</v>
+        <v>6788375</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13057,7 +13057,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13066,6 +13066,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13084,10 +13085,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124150783</v>
+        <v>124074099</v>
       </c>
       <c r="B121" t="n">
-        <v>8447</v>
+        <v>78547</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13096,32 +13097,30 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13129,10 +13128,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461702</v>
+        <v>461687</v>
       </c>
       <c r="R121" t="n">
-        <v>6788415</v>
+        <v>6788172</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13169,7 +13168,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13197,10 +13196,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124100321</v>
+        <v>124079560</v>
       </c>
       <c r="B122" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13213,26 +13212,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13240,10 +13244,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461813</v>
+        <v>461854</v>
       </c>
       <c r="R122" t="n">
-        <v>6788469</v>
+        <v>6788321</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13270,17 +13274,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13289,7 +13293,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13419,10 +13422,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124078370</v>
+        <v>124099222</v>
       </c>
       <c r="B124" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13435,16 +13438,16 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -13467,10 +13470,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461702</v>
+        <v>461848</v>
       </c>
       <c r="R124" t="n">
-        <v>6788415</v>
+        <v>6788394</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13497,17 +13500,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -9006,10 +9006,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124070964</v>
+        <v>124077216</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461765</v>
+        <v>461645</v>
       </c>
       <c r="R83" t="n">
-        <v>6788314</v>
+        <v>6788424</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9108,7 +9108,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124071868</v>
+        <v>124069314</v>
       </c>
       <c r="B84" t="n">
         <v>78810</v>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461779</v>
+        <v>461867</v>
       </c>
       <c r="R84" t="n">
-        <v>6788261</v>
+        <v>6788190</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9184,11 +9184,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9215,10 +9210,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124078636</v>
+        <v>124073722</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9231,34 +9226,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461747</v>
+        <v>461781</v>
       </c>
       <c r="R85" t="n">
-        <v>6788434</v>
+        <v>6788191</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9317,10 +9317,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124069447</v>
+        <v>124074329</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9333,21 +9333,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461867</v>
+        <v>461635</v>
       </c>
       <c r="R86" t="n">
-        <v>6788190</v>
+        <v>6788154</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9393,6 +9393,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9419,7 +9424,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124077244</v>
+        <v>124070449</v>
       </c>
       <c r="B87" t="n">
         <v>78810</v>
@@ -9459,10 +9464,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461645</v>
+        <v>461827</v>
       </c>
       <c r="R87" t="n">
-        <v>6788424</v>
+        <v>6788228</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9521,10 +9526,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124074329</v>
+        <v>124070191</v>
       </c>
       <c r="B88" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9537,21 +9542,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9561,10 +9566,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461635</v>
+        <v>461842</v>
       </c>
       <c r="R88" t="n">
-        <v>6788154</v>
+        <v>6788220</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9597,11 +9602,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9628,7 +9628,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124071683</v>
+        <v>124077244</v>
       </c>
       <c r="B89" t="n">
         <v>78810</v>
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461771</v>
+        <v>461645</v>
       </c>
       <c r="R89" t="n">
-        <v>6788273</v>
+        <v>6788424</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9730,10 +9730,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124071356</v>
+        <v>124071507</v>
       </c>
       <c r="B90" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9746,29 +9746,24 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -9837,7 +9832,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124070118</v>
+        <v>124071868</v>
       </c>
       <c r="B91" t="n">
         <v>78810</v>
@@ -9877,10 +9872,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461846</v>
+        <v>461779</v>
       </c>
       <c r="R91" t="n">
-        <v>6788208</v>
+        <v>6788261</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9913,6 +9908,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9939,10 +9939,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124077216</v>
+        <v>124071356</v>
       </c>
       <c r="B92" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9955,34 +9955,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461645</v>
+        <v>461771</v>
       </c>
       <c r="R92" t="n">
-        <v>6788424</v>
+        <v>6788273</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10041,7 +10046,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124070191</v>
+        <v>124078636</v>
       </c>
       <c r="B93" t="n">
         <v>78810</v>
@@ -10081,10 +10086,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461842</v>
+        <v>461747</v>
       </c>
       <c r="R93" t="n">
-        <v>6788220</v>
+        <v>6788434</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10143,7 +10148,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124070449</v>
+        <v>124070118</v>
       </c>
       <c r="B94" t="n">
         <v>78810</v>
@@ -10183,10 +10188,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461827</v>
+        <v>461846</v>
       </c>
       <c r="R94" t="n">
-        <v>6788228</v>
+        <v>6788208</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10245,10 +10250,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124072920</v>
+        <v>124070964</v>
       </c>
       <c r="B95" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10261,21 +10266,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10285,10 +10290,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461781</v>
+        <v>461765</v>
       </c>
       <c r="R95" t="n">
-        <v>6788191</v>
+        <v>6788314</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10347,10 +10352,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124073722</v>
+        <v>124072920</v>
       </c>
       <c r="B96" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10363,29 +10368,24 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124103283</v>
+        <v>124102664</v>
       </c>
       <c r="B97" t="n">
         <v>78810</v>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461895</v>
+        <v>461897</v>
       </c>
       <c r="R97" t="n">
-        <v>6788288</v>
+        <v>6788354</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10530,6 +10530,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav runt mig.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10867,7 +10872,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124102612</v>
+        <v>124103087</v>
       </c>
       <c r="B101" t="n">
         <v>78810</v>
@@ -10907,10 +10912,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461897</v>
+        <v>461895</v>
       </c>
       <c r="R101" t="n">
-        <v>6788354</v>
+        <v>6788288</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10969,7 +10974,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124075614</v>
+        <v>124074729</v>
       </c>
       <c r="B102" t="n">
         <v>57529</v>
@@ -11003,24 +11008,21 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461717</v>
+        <v>461635</v>
       </c>
       <c r="R102" t="n">
-        <v>6788187</v>
+        <v>6788154</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11057,7 +11059,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Miljöbilder. Ackspår i hög grov stubbe av gammal tall.</t>
+          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11084,7 +11086,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124074255</v>
+        <v>124074036</v>
       </c>
       <c r="B103" t="n">
         <v>57529</v>
@@ -11118,24 +11120,21 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461635</v>
+        <v>461717</v>
       </c>
       <c r="R103" t="n">
-        <v>6788154</v>
+        <v>6788187</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11172,7 +11171,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Flera bohål i hög, grov, torraka av tall.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11199,10 +11198,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124072783</v>
+        <v>124076090</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11215,37 +11214,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461781</v>
+        <v>461711</v>
       </c>
       <c r="R104" t="n">
-        <v>6788191</v>
+        <v>6788217</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11280,18 +11281,12 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11425,10 +11420,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124073786</v>
+        <v>124070750</v>
       </c>
       <c r="B106" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11437,46 +11432,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461765</v>
+        <v>461821</v>
       </c>
       <c r="R106" t="n">
-        <v>6788189</v>
+        <v>6788236</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11509,11 +11501,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11540,10 +11527,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124070750</v>
+        <v>124076637</v>
       </c>
       <c r="B107" t="n">
-        <v>57513</v>
+        <v>8447</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11552,43 +11539,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461821</v>
+        <v>461711</v>
       </c>
       <c r="R107" t="n">
-        <v>6788236</v>
+        <v>6788217</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11647,10 +11629,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124076637</v>
+        <v>124072335</v>
       </c>
       <c r="B108" t="n">
-        <v>8447</v>
+        <v>57513</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11659,38 +11641,46 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461711</v>
+        <v>461826</v>
       </c>
       <c r="R108" t="n">
-        <v>6788217</v>
+        <v>6788189</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11723,6 +11713,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11851,10 +11846,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124070565</v>
+        <v>124076806</v>
       </c>
       <c r="B110" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11867,31 +11862,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11899,10 +11889,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461821</v>
+        <v>461730</v>
       </c>
       <c r="R110" t="n">
-        <v>6788236</v>
+        <v>6788270</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11937,12 +11927,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11961,10 +11957,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124075859</v>
+        <v>124072783</v>
       </c>
       <c r="B111" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11977,31 +11973,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12009,10 +12000,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461732</v>
+        <v>461781</v>
       </c>
       <c r="R111" t="n">
-        <v>6788226</v>
+        <v>6788191</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12049,7 +12040,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Miljöbild med äldre högstubbe!</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12058,6 +12049,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12076,10 +12068,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124076090</v>
+        <v>124073786</v>
       </c>
       <c r="B112" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12088,43 +12080,46 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461711</v>
+        <v>461765</v>
       </c>
       <c r="R112" t="n">
-        <v>6788217</v>
+        <v>6788189</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12157,6 +12152,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12183,10 +12183,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124072335</v>
+        <v>124075859</v>
       </c>
       <c r="B113" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12199,16 +12199,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12221,7 +12221,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12231,10 +12231,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461826</v>
+        <v>461732</v>
       </c>
       <c r="R113" t="n">
-        <v>6788189</v>
+        <v>6788226</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12271,7 +12271,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12298,10 +12298,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124076806</v>
+        <v>124070565</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12314,26 +12314,31 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12341,10 +12346,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461730</v>
+        <v>461821</v>
       </c>
       <c r="R114" t="n">
-        <v>6788270</v>
+        <v>6788236</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12379,18 +12384,12 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12524,10 +12523,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124150783</v>
+        <v>124079560</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12536,32 +12535,35 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12569,10 +12571,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461702</v>
+        <v>461854</v>
       </c>
       <c r="R116" t="n">
-        <v>6788415</v>
+        <v>6788321</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12609,7 +12611,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12618,7 +12620,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12637,10 +12638,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124103019</v>
+        <v>124150783</v>
       </c>
       <c r="B117" t="n">
-        <v>91030</v>
+        <v>8447</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12649,30 +12650,32 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12680,10 +12683,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461895</v>
+        <v>461702</v>
       </c>
       <c r="R117" t="n">
-        <v>6788288</v>
+        <v>6788415</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12710,17 +12713,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12748,10 +12751,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124077891</v>
+        <v>124099222</v>
       </c>
       <c r="B118" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12764,16 +12767,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12786,7 +12789,7 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -12796,10 +12799,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461645</v>
+        <v>461848</v>
       </c>
       <c r="R118" t="n">
-        <v>6788424</v>
+        <v>6788394</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12826,17 +12829,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12863,10 +12866,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124100321</v>
+        <v>124103019</v>
       </c>
       <c r="B119" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12879,21 +12882,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12906,10 +12909,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461813</v>
+        <v>461895</v>
       </c>
       <c r="R119" t="n">
-        <v>6788469</v>
+        <v>6788288</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12946,7 +12949,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12974,10 +12977,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124079435</v>
+        <v>124074099</v>
       </c>
       <c r="B120" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12990,21 +12993,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13017,10 +13020,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461848</v>
+        <v>461687</v>
       </c>
       <c r="R120" t="n">
-        <v>6788375</v>
+        <v>6788172</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13057,7 +13060,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13085,10 +13088,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124074099</v>
+        <v>124102093</v>
       </c>
       <c r="B121" t="n">
-        <v>78547</v>
+        <v>91299</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13101,21 +13104,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13128,10 +13131,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461687</v>
+        <v>461869</v>
       </c>
       <c r="R121" t="n">
-        <v>6788172</v>
+        <v>6788429</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13158,17 +13161,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13196,10 +13199,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124079560</v>
+        <v>124079435</v>
       </c>
       <c r="B122" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13212,31 +13215,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13244,10 +13242,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461854</v>
+        <v>461848</v>
       </c>
       <c r="R122" t="n">
-        <v>6788321</v>
+        <v>6788375</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13284,7 +13282,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13293,6 +13291,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13311,7 +13310,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124102093</v>
+        <v>124100321</v>
       </c>
       <c r="B123" t="n">
         <v>91299</v>
@@ -13354,10 +13353,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461869</v>
+        <v>461813</v>
       </c>
       <c r="R123" t="n">
-        <v>6788429</v>
+        <v>6788469</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13394,7 +13393,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13422,10 +13421,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124099222</v>
+        <v>124077891</v>
       </c>
       <c r="B124" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13438,16 +13437,16 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -13460,7 +13459,7 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -13470,10 +13469,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461848</v>
+        <v>461645</v>
       </c>
       <c r="R124" t="n">
-        <v>6788394</v>
+        <v>6788424</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13500,17 +13499,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -9108,7 +9108,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124069314</v>
+        <v>124071683</v>
       </c>
       <c r="B84" t="n">
         <v>78810</v>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461867</v>
+        <v>461771</v>
       </c>
       <c r="R84" t="n">
-        <v>6788190</v>
+        <v>6788273</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9210,10 +9210,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124073722</v>
+        <v>124069314</v>
       </c>
       <c r="B85" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9226,39 +9226,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461781</v>
+        <v>461867</v>
       </c>
       <c r="R85" t="n">
-        <v>6788191</v>
+        <v>6788190</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9317,10 +9312,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124074329</v>
+        <v>124077244</v>
       </c>
       <c r="B86" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9333,21 +9328,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9357,10 +9352,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461635</v>
+        <v>461645</v>
       </c>
       <c r="R86" t="n">
-        <v>6788154</v>
+        <v>6788424</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9393,11 +9388,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9424,7 +9414,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124070449</v>
+        <v>124070964</v>
       </c>
       <c r="B87" t="n">
         <v>78810</v>
@@ -9464,10 +9454,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461827</v>
+        <v>461765</v>
       </c>
       <c r="R87" t="n">
-        <v>6788228</v>
+        <v>6788314</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9526,10 +9516,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124070191</v>
+        <v>124073722</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9542,34 +9532,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461842</v>
+        <v>461781</v>
       </c>
       <c r="R88" t="n">
-        <v>6788220</v>
+        <v>6788191</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9628,10 +9623,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124077244</v>
+        <v>124071356</v>
       </c>
       <c r="B89" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9644,34 +9639,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461645</v>
+        <v>461771</v>
       </c>
       <c r="R89" t="n">
-        <v>6788424</v>
+        <v>6788273</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9730,7 +9730,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124071507</v>
+        <v>124071868</v>
       </c>
       <c r="B90" t="n">
         <v>78810</v>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461771</v>
+        <v>461779</v>
       </c>
       <c r="R90" t="n">
-        <v>6788273</v>
+        <v>6788261</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9806,6 +9806,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9832,10 +9837,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124071868</v>
+        <v>124074329</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9848,21 +9853,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9872,10 +9877,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461779</v>
+        <v>461635</v>
       </c>
       <c r="R91" t="n">
-        <v>6788261</v>
+        <v>6788154</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9912,7 +9917,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Vid äldre tallar, mer än 200 år!</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9939,10 +9944,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124071356</v>
+        <v>124070191</v>
       </c>
       <c r="B92" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9955,39 +9960,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461771</v>
+        <v>461842</v>
       </c>
       <c r="R92" t="n">
-        <v>6788273</v>
+        <v>6788220</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10046,7 +10046,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124078636</v>
+        <v>124070449</v>
       </c>
       <c r="B93" t="n">
         <v>78810</v>
@@ -10086,10 +10086,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461747</v>
+        <v>461827</v>
       </c>
       <c r="R93" t="n">
-        <v>6788434</v>
+        <v>6788228</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10250,10 +10250,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124070964</v>
+        <v>124072920</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10266,21 +10266,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10290,10 +10290,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461765</v>
+        <v>461781</v>
       </c>
       <c r="R95" t="n">
-        <v>6788314</v>
+        <v>6788191</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10352,10 +10352,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124072920</v>
+        <v>124078636</v>
       </c>
       <c r="B96" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10368,21 +10368,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461781</v>
+        <v>461747</v>
       </c>
       <c r="R96" t="n">
-        <v>6788191</v>
+        <v>6788434</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10454,10 +10454,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124102664</v>
+        <v>124100914</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10470,34 +10470,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461897</v>
+        <v>461788</v>
       </c>
       <c r="R97" t="n">
-        <v>6788354</v>
+        <v>6788461</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10530,11 +10535,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav runt mig.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10561,10 +10561,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124100914</v>
+        <v>124103087</v>
       </c>
       <c r="B98" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10577,39 +10577,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461788</v>
+        <v>461895</v>
       </c>
       <c r="R98" t="n">
-        <v>6788461</v>
+        <v>6788288</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10668,7 +10663,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124101056</v>
+        <v>124102429</v>
       </c>
       <c r="B99" t="n">
         <v>78810</v>
@@ -10708,10 +10703,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461781</v>
+        <v>461869</v>
       </c>
       <c r="R99" t="n">
-        <v>6788477</v>
+        <v>6788429</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10770,7 +10765,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124102323</v>
+        <v>124102664</v>
       </c>
       <c r="B100" t="n">
         <v>78810</v>
@@ -10810,10 +10805,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461869</v>
+        <v>461897</v>
       </c>
       <c r="R100" t="n">
-        <v>6788429</v>
+        <v>6788354</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10846,6 +10841,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav runt mig.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10872,7 +10872,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124103087</v>
+        <v>124101056</v>
       </c>
       <c r="B101" t="n">
         <v>78810</v>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461895</v>
+        <v>461781</v>
       </c>
       <c r="R101" t="n">
-        <v>6788288</v>
+        <v>6788477</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10974,10 +10974,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124074729</v>
+        <v>124075169</v>
       </c>
       <c r="B102" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10990,16 +10990,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11008,21 +11008,24 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461635</v>
+        <v>461717</v>
       </c>
       <c r="R102" t="n">
-        <v>6788154</v>
+        <v>6788187</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11059,7 +11062,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11198,10 +11201,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124076090</v>
+        <v>124076637</v>
       </c>
       <c r="B104" t="n">
-        <v>57513</v>
+        <v>8447</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11210,33 +11213,28 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -11305,10 +11303,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124075169</v>
+        <v>124074729</v>
       </c>
       <c r="B105" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11321,16 +11319,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11339,24 +11337,21 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461717</v>
+        <v>461635</v>
       </c>
       <c r="R105" t="n">
-        <v>6788187</v>
+        <v>6788154</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11393,7 +11388,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11420,7 +11415,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124070750</v>
+        <v>124076090</v>
       </c>
       <c r="B106" t="n">
         <v>57513</v>
@@ -11465,10 +11460,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461821</v>
+        <v>461711</v>
       </c>
       <c r="R106" t="n">
-        <v>6788236</v>
+        <v>6788217</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11527,10 +11522,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124076637</v>
+        <v>124076806</v>
       </c>
       <c r="B107" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11539,38 +11534,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461711</v>
+        <v>461730</v>
       </c>
       <c r="R107" t="n">
-        <v>6788217</v>
+        <v>6788270</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11605,12 +11603,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11744,7 +11748,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124072166</v>
+        <v>124072783</v>
       </c>
       <c r="B109" t="n">
         <v>78810</v>
@@ -11778,16 +11782,19 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461825</v>
+        <v>461781</v>
       </c>
       <c r="R109" t="n">
-        <v>6788200</v>
+        <v>6788191</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11822,12 +11829,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11846,10 +11859,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124076806</v>
+        <v>124073786</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11858,30 +11871,35 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11889,10 +11907,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461730</v>
+        <v>461765</v>
       </c>
       <c r="R110" t="n">
-        <v>6788270</v>
+        <v>6788189</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11929,7 +11947,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
+          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11938,7 +11956,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11957,10 +11974,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124072783</v>
+        <v>124070750</v>
       </c>
       <c r="B111" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11973,37 +11990,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461781</v>
+        <v>461821</v>
       </c>
       <c r="R111" t="n">
-        <v>6788191</v>
+        <v>6788236</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12038,18 +12057,12 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12068,10 +12081,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124073786</v>
+        <v>124075859</v>
       </c>
       <c r="B112" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12080,25 +12093,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12106,7 +12119,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -12116,10 +12129,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461765</v>
+        <v>461732</v>
       </c>
       <c r="R112" t="n">
-        <v>6788189</v>
+        <v>6788226</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12156,7 +12169,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Miljöbild. Så kallad tjädertall.</t>
+          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12183,10 +12196,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124075859</v>
+        <v>124072166</v>
       </c>
       <c r="B113" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12199,42 +12212,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461732</v>
+        <v>461825</v>
       </c>
       <c r="R113" t="n">
-        <v>6788226</v>
+        <v>6788200</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12267,11 +12272,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12408,10 +12408,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124078370</v>
+        <v>124100321</v>
       </c>
       <c r="B115" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12424,31 +12424,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12456,10 +12451,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461702</v>
+        <v>461813</v>
       </c>
       <c r="R115" t="n">
-        <v>6788415</v>
+        <v>6788469</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12486,17 +12481,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12505,6 +12500,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12523,10 +12519,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124079560</v>
+        <v>124150783</v>
       </c>
       <c r="B116" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12535,35 +12531,32 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12571,10 +12564,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461854</v>
+        <v>461702</v>
       </c>
       <c r="R116" t="n">
-        <v>6788321</v>
+        <v>6788415</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12611,7 +12604,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12620,6 +12613,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12638,10 +12632,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124150783</v>
+        <v>124078370</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12650,32 +12644,35 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12723,7 +12720,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12732,7 +12729,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12751,10 +12747,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124099222</v>
+        <v>124103019</v>
       </c>
       <c r="B118" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12767,31 +12763,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -12799,10 +12790,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461848</v>
+        <v>461895</v>
       </c>
       <c r="R118" t="n">
-        <v>6788394</v>
+        <v>6788288</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12839,7 +12830,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12848,6 +12839,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12866,10 +12858,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124103019</v>
+        <v>124099222</v>
       </c>
       <c r="B119" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12882,26 +12874,31 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12909,10 +12906,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461895</v>
+        <v>461848</v>
       </c>
       <c r="R119" t="n">
-        <v>6788288</v>
+        <v>6788394</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12949,7 +12946,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12958,7 +12955,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13088,10 +13084,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124102093</v>
+        <v>124079560</v>
       </c>
       <c r="B121" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13104,26 +13100,31 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13131,10 +13132,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461869</v>
+        <v>461854</v>
       </c>
       <c r="R121" t="n">
-        <v>6788429</v>
+        <v>6788321</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13161,17 +13162,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13180,7 +13181,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13199,10 +13199,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124079435</v>
+        <v>124077891</v>
       </c>
       <c r="B122" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13215,26 +13215,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13242,10 +13247,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461848</v>
+        <v>461645</v>
       </c>
       <c r="R122" t="n">
-        <v>6788375</v>
+        <v>6788424</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13282,7 +13287,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13291,7 +13296,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13310,7 +13314,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124100321</v>
+        <v>124102093</v>
       </c>
       <c r="B123" t="n">
         <v>91299</v>
@@ -13353,10 +13357,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461813</v>
+        <v>461869</v>
       </c>
       <c r="R123" t="n">
-        <v>6788469</v>
+        <v>6788429</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13393,7 +13397,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13421,10 +13425,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124077891</v>
+        <v>124079435</v>
       </c>
       <c r="B124" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13437,31 +13441,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13469,10 +13468,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461645</v>
+        <v>461848</v>
       </c>
       <c r="R124" t="n">
-        <v>6788424</v>
+        <v>6788375</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13509,7 +13508,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13518,6 +13517,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -11201,10 +11201,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124076637</v>
+        <v>124074729</v>
       </c>
       <c r="B104" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11213,38 +11213,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461711</v>
+        <v>461635</v>
       </c>
       <c r="R104" t="n">
-        <v>6788217</v>
+        <v>6788154</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11277,6 +11282,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11303,10 +11313,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124074729</v>
+        <v>124076637</v>
       </c>
       <c r="B105" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11315,43 +11325,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461635</v>
+        <v>461711</v>
       </c>
       <c r="R105" t="n">
-        <v>6788154</v>
+        <v>6788217</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11384,11 +11389,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -10974,10 +10974,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124075169</v>
+        <v>124076637</v>
       </c>
       <c r="B102" t="n">
-        <v>57513</v>
+        <v>8447</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10986,46 +10986,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461717</v>
+        <v>461711</v>
       </c>
       <c r="R102" t="n">
-        <v>6788187</v>
+        <v>6788217</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11058,11 +11050,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11201,10 +11188,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124074729</v>
+        <v>124072335</v>
       </c>
       <c r="B104" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11217,16 +11204,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11235,21 +11222,24 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461635</v>
+        <v>461826</v>
       </c>
       <c r="R104" t="n">
-        <v>6788154</v>
+        <v>6788189</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11286,7 +11276,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11313,10 +11303,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124076637</v>
+        <v>124070565</v>
       </c>
       <c r="B105" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11325,38 +11315,46 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461711</v>
+        <v>461821</v>
       </c>
       <c r="R105" t="n">
-        <v>6788217</v>
+        <v>6788236</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11415,7 +11413,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124076090</v>
+        <v>124070750</v>
       </c>
       <c r="B106" t="n">
         <v>57513</v>
@@ -11460,10 +11458,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461711</v>
+        <v>461821</v>
       </c>
       <c r="R106" t="n">
-        <v>6788217</v>
+        <v>6788236</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11633,10 +11631,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124072335</v>
+        <v>124074729</v>
       </c>
       <c r="B108" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11649,16 +11647,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -11667,24 +11665,21 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461826</v>
+        <v>461635</v>
       </c>
       <c r="R108" t="n">
-        <v>6788189</v>
+        <v>6788154</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11721,7 +11716,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11748,10 +11743,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124072783</v>
+        <v>124074066</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11764,37 +11759,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461781</v>
+        <v>461717</v>
       </c>
       <c r="R109" t="n">
-        <v>6788191</v>
+        <v>6788187</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11829,18 +11826,12 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11859,10 +11850,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124073786</v>
+        <v>124075859</v>
       </c>
       <c r="B110" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11871,25 +11862,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11897,7 +11888,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -11907,10 +11898,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461765</v>
+        <v>461732</v>
       </c>
       <c r="R110" t="n">
-        <v>6788189</v>
+        <v>6788226</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11947,7 +11938,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Miljöbild. Så kallad tjädertall.</t>
+          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11974,10 +11965,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124070750</v>
+        <v>124072166</v>
       </c>
       <c r="B111" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11990,39 +11981,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461821</v>
+        <v>461825</v>
       </c>
       <c r="R111" t="n">
-        <v>6788236</v>
+        <v>6788200</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12081,10 +12067,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124075859</v>
+        <v>124076090</v>
       </c>
       <c r="B112" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12097,16 +12083,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -12115,24 +12101,21 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461732</v>
+        <v>461711</v>
       </c>
       <c r="R112" t="n">
-        <v>6788226</v>
+        <v>6788217</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12165,11 +12148,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12196,10 +12174,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124072166</v>
+        <v>124073786</v>
       </c>
       <c r="B113" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12208,38 +12186,46 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461825</v>
+        <v>461765</v>
       </c>
       <c r="R113" t="n">
-        <v>6788200</v>
+        <v>6788189</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12272,6 +12258,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Miljöbild. Så kallad tjädertall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12298,10 +12289,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124070565</v>
+        <v>124072783</v>
       </c>
       <c r="B114" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12314,31 +12305,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12346,10 +12332,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461821</v>
+        <v>461781</v>
       </c>
       <c r="R114" t="n">
-        <v>6788236</v>
+        <v>6788191</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12384,12 +12370,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12408,10 +12400,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124100321</v>
+        <v>124077891</v>
       </c>
       <c r="B115" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12424,26 +12416,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12451,10 +12448,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461813</v>
+        <v>461645</v>
       </c>
       <c r="R115" t="n">
-        <v>6788469</v>
+        <v>6788424</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12481,17 +12478,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12500,7 +12497,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12519,10 +12515,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124150783</v>
+        <v>124078370</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12531,32 +12527,35 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12604,7 +12603,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12613,7 +12612,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12632,10 +12630,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124078370</v>
+        <v>124100321</v>
       </c>
       <c r="B117" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12648,31 +12646,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12680,10 +12673,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461702</v>
+        <v>461813</v>
       </c>
       <c r="R117" t="n">
-        <v>6788415</v>
+        <v>6788469</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12710,17 +12703,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12729,6 +12722,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12747,10 +12741,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124103019</v>
+        <v>124150783</v>
       </c>
       <c r="B118" t="n">
-        <v>91030</v>
+        <v>8447</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12759,30 +12753,32 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -12790,10 +12786,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461895</v>
+        <v>461702</v>
       </c>
       <c r="R118" t="n">
-        <v>6788288</v>
+        <v>6788415</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12820,17 +12816,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12858,10 +12854,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124099222</v>
+        <v>124074099</v>
       </c>
       <c r="B119" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12874,31 +12870,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12906,10 +12897,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461848</v>
+        <v>461687</v>
       </c>
       <c r="R119" t="n">
-        <v>6788394</v>
+        <v>6788172</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12936,17 +12927,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12955,6 +12946,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12973,10 +12965,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124074099</v>
+        <v>124079435</v>
       </c>
       <c r="B120" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12989,21 +12981,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13016,10 +13008,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461687</v>
+        <v>461848</v>
       </c>
       <c r="R120" t="n">
-        <v>6788172</v>
+        <v>6788375</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13056,7 +13048,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13084,10 +13076,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124079560</v>
+        <v>124102093</v>
       </c>
       <c r="B121" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13100,31 +13092,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13132,10 +13119,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461854</v>
+        <v>461869</v>
       </c>
       <c r="R121" t="n">
-        <v>6788321</v>
+        <v>6788429</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13162,17 +13149,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13181,6 +13168,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13199,10 +13187,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124077891</v>
+        <v>124103019</v>
       </c>
       <c r="B122" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13215,31 +13203,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13247,10 +13230,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461645</v>
+        <v>461895</v>
       </c>
       <c r="R122" t="n">
-        <v>6788424</v>
+        <v>6788288</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13277,17 +13260,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Miljöbilder. Hög tallstubbe med många bohål.</t>
+          <t>Miljöbilder. Fuktigt område med bäck.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13296,6 +13279,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13314,10 +13298,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124102093</v>
+        <v>124079560</v>
       </c>
       <c r="B123" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13330,26 +13314,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13357,10 +13346,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461869</v>
+        <v>461854</v>
       </c>
       <c r="R123" t="n">
-        <v>6788429</v>
+        <v>6788321</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13387,17 +13376,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13406,7 +13395,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13425,10 +13413,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124079435</v>
+        <v>124099222</v>
       </c>
       <c r="B124" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13441,26 +13429,31 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13471,7 +13464,7 @@
         <v>461848</v>
       </c>
       <c r="R124" t="n">
-        <v>6788375</v>
+        <v>6788394</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13498,17 +13491,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13517,7 +13510,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -13528,7 +13528,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124100759</v>
+        <v>124100816</v>
       </c>
       <c r="B125" t="n">
         <v>78810</v>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
+          <t>Miljöbilder. Garnlav och revlummer.</t>
         </is>
       </c>
       <c r="AD125" t="b">

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -13528,7 +13528,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124100816</v>
+        <v>124100759</v>
       </c>
       <c r="B125" t="n">
         <v>78810</v>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Miljöbilder. Garnlav och revlummer.</t>
+          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
         </is>
       </c>
       <c r="AD125" t="b">

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -13531,7 +13531,7 @@
         <v>124100759</v>
       </c>
       <c r="B125" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY125"/>
+  <dimension ref="A1:AY137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122489220</v>
+        <v>124100321</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461881</v>
+        <v>461813</v>
       </c>
       <c r="R2" t="n">
-        <v>6788296</v>
+        <v>6788469</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,17 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska hackspår nedre delen av äldre gran.</t>
+          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122489147</v>
+        <v>124102093</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461988</v>
+        <v>461869</v>
       </c>
       <c r="R3" t="n">
-        <v>6788288</v>
+        <v>6788429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +849,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122488593</v>
+        <v>122566808</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461988</v>
+        <v>461872</v>
       </c>
       <c r="R4" t="n">
-        <v>6788288</v>
+        <v>6788413</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,62 +972,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566854</v>
+        <v>124101674</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461714</v>
+        <v>461803</v>
       </c>
       <c r="R5" t="n">
-        <v>6788188</v>
+        <v>6788496</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1052,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,33 +1071,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122566829</v>
+        <v>122489147</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1101,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461952</v>
+        <v>461988</v>
       </c>
       <c r="R6" t="n">
-        <v>6788327</v>
+        <v>6788288</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,12 +1155,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,27 +1175,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122566838</v>
+        <v>122566809</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1198,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461878</v>
+        <v>461822</v>
       </c>
       <c r="R7" t="n">
-        <v>6788313</v>
+        <v>6788353</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,19 +1284,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122566855</v>
+        <v>122488593</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1337,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461704</v>
+        <v>461988</v>
       </c>
       <c r="R8" t="n">
-        <v>6788171</v>
+        <v>6788288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,12 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,31 +1369,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122566865</v>
+        <v>122566817</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1439,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461628</v>
+        <v>461788</v>
       </c>
       <c r="R9" t="n">
-        <v>6788142</v>
+        <v>6788303</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,19 +1478,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122566820</v>
+        <v>122566818</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1541,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461732</v>
+        <v>461816</v>
       </c>
       <c r="R10" t="n">
-        <v>6788430</v>
+        <v>6788330</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,19 +1575,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122566840</v>
+        <v>122566819</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1637,16 +1604,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461810</v>
+        <v>461667</v>
       </c>
       <c r="R11" t="n">
-        <v>6788278</v>
+        <v>6788182</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,37 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122566814</v>
+        <v>122566820</v>
       </c>
       <c r="B12" t="n">
-        <v>78502</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461814</v>
+        <v>461732</v>
       </c>
       <c r="R12" t="n">
-        <v>6788266</v>
+        <v>6788430</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,19 +1774,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122566830</v>
+        <v>122566821</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1847,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461991</v>
+        <v>461699</v>
       </c>
       <c r="R13" t="n">
-        <v>6788324</v>
+        <v>6788443</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,19 +1871,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122566847</v>
+        <v>122566822</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1949,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461789</v>
+        <v>461763</v>
       </c>
       <c r="R14" t="n">
-        <v>6788194</v>
+        <v>6788475</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,19 +1968,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122566872</v>
+        <v>122566823</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2051,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461659</v>
+        <v>461778</v>
       </c>
       <c r="R15" t="n">
-        <v>6788194</v>
+        <v>6788485</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,19 +2065,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122566819</v>
+        <v>122566824</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2147,21 +2094,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461667</v>
+        <v>461810</v>
       </c>
       <c r="R16" t="n">
-        <v>6788182</v>
+        <v>6788470</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,19 +2162,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122566886</v>
+        <v>122566825</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2260,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461810</v>
+        <v>461843</v>
       </c>
       <c r="R17" t="n">
-        <v>6788325</v>
+        <v>6788468</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,19 +2259,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122566828</v>
+        <v>122566826</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2362,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461923</v>
+        <v>461846</v>
       </c>
       <c r="R18" t="n">
-        <v>6788324</v>
+        <v>6788492</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,19 +2356,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122566821</v>
+        <v>122566827</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2464,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461699</v>
+        <v>461879</v>
       </c>
       <c r="R19" t="n">
-        <v>6788443</v>
+        <v>6788396</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,19 +2453,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122566844</v>
+        <v>122566828</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2566,10 +2488,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461816</v>
+        <v>461923</v>
       </c>
       <c r="R20" t="n">
-        <v>6788215</v>
+        <v>6788324</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,19 +2550,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122566873</v>
+        <v>122566829</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2668,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461655</v>
+        <v>461952</v>
       </c>
       <c r="R21" t="n">
-        <v>6788205</v>
+        <v>6788327</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,19 +2647,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122566843</v>
+        <v>122566830</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2770,10 +2682,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461811</v>
+        <v>461991</v>
       </c>
       <c r="R22" t="n">
-        <v>6788237</v>
+        <v>6788324</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,19 +2744,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122566877</v>
+        <v>122566831</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2872,10 +2779,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461706</v>
+        <v>462004</v>
       </c>
       <c r="R23" t="n">
-        <v>6788223</v>
+        <v>6788320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,19 +2841,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122566839</v>
+        <v>122566832</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2974,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461829</v>
+        <v>461991</v>
       </c>
       <c r="R24" t="n">
-        <v>6788287</v>
+        <v>6788292</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,19 +2938,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122566848</v>
+        <v>122566833</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3076,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461791</v>
+        <v>461972</v>
       </c>
       <c r="R25" t="n">
-        <v>6788187</v>
+        <v>6788277</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,37 +3035,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122566801</v>
+        <v>122566834</v>
       </c>
       <c r="B26" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3178,10 +3070,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461945</v>
+        <v>461929</v>
       </c>
       <c r="R26" t="n">
-        <v>6788255</v>
+        <v>6788262</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,37 +3132,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122566888</v>
+        <v>122566835</v>
       </c>
       <c r="B27" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3280,10 +3167,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461791</v>
+        <v>461929</v>
       </c>
       <c r="R27" t="n">
-        <v>6788187</v>
+        <v>6788278</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,37 +3229,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122566804</v>
+        <v>122566837</v>
       </c>
       <c r="B28" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3382,10 +3264,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461614</v>
+        <v>461917</v>
       </c>
       <c r="R28" t="n">
-        <v>6788152</v>
+        <v>6788292</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,19 +3326,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122566871</v>
+        <v>122566838</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3484,10 +3361,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461676</v>
+        <v>461878</v>
       </c>
       <c r="R29" t="n">
-        <v>6788174</v>
+        <v>6788313</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3546,19 +3423,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122566825</v>
+        <v>122566839</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3586,10 +3458,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461843</v>
+        <v>461829</v>
       </c>
       <c r="R30" t="n">
-        <v>6788468</v>
+        <v>6788287</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,19 +3520,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122566837</v>
+        <v>122566840</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3688,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461917</v>
+        <v>461810</v>
       </c>
       <c r="R31" t="n">
-        <v>6788292</v>
+        <v>6788278</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,19 +3617,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122566832</v>
+        <v>122566841</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3790,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461991</v>
+        <v>461809</v>
       </c>
       <c r="R32" t="n">
-        <v>6788292</v>
+        <v>6788250</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,37 +3714,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122566887</v>
+        <v>122566842</v>
       </c>
       <c r="B33" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3892,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461810</v>
+        <v>461803</v>
       </c>
       <c r="R33" t="n">
-        <v>6788470</v>
+        <v>6788243</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3954,37 +3811,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122566802</v>
+        <v>122566843</v>
       </c>
       <c r="B34" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3997,7 +3849,7 @@
         <v>461811</v>
       </c>
       <c r="R34" t="n">
-        <v>6788280</v>
+        <v>6788237</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,19 +3908,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122566864</v>
+        <v>122566844</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4096,10 +3943,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461619</v>
+        <v>461816</v>
       </c>
       <c r="R35" t="n">
-        <v>6788144</v>
+        <v>6788215</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4158,19 +4005,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122566818</v>
+        <v>122566845</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4198,10 +4040,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461816</v>
+        <v>461794</v>
       </c>
       <c r="R36" t="n">
-        <v>6788330</v>
+        <v>6788217</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4260,19 +4102,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122566826</v>
+        <v>122566846</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4300,10 +4137,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461846</v>
+        <v>461791</v>
       </c>
       <c r="R37" t="n">
-        <v>6788492</v>
+        <v>6788209</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4362,19 +4199,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122566827</v>
+        <v>122566847</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4402,10 +4234,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461879</v>
+        <v>461789</v>
       </c>
       <c r="R38" t="n">
-        <v>6788396</v>
+        <v>6788194</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,19 +4296,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122566869</v>
+        <v>122566848</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4504,10 +4331,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461678</v>
+        <v>461791</v>
       </c>
       <c r="R39" t="n">
-        <v>6788157</v>
+        <v>6788187</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,19 +4393,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122566881</v>
+        <v>122566849</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4606,10 +4428,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461742</v>
+        <v>461787</v>
       </c>
       <c r="R40" t="n">
-        <v>6788295</v>
+        <v>6788182</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,19 +4490,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122566876</v>
+        <v>122566850</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4708,10 +4525,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461695</v>
+        <v>461771</v>
       </c>
       <c r="R41" t="n">
-        <v>6788224</v>
+        <v>6788185</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,19 +4587,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122566880</v>
+        <v>122566851</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4810,10 +4622,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461737</v>
+        <v>461758</v>
       </c>
       <c r="R42" t="n">
-        <v>6788251</v>
+        <v>6788174</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4872,19 +4684,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122566822</v>
+        <v>122566852</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4912,10 +4719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461763</v>
+        <v>461741</v>
       </c>
       <c r="R43" t="n">
-        <v>6788475</v>
+        <v>6788170</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,19 +4781,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122566833</v>
+        <v>122566853</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5014,10 +4816,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461972</v>
+        <v>461732</v>
       </c>
       <c r="R44" t="n">
-        <v>6788277</v>
+        <v>6788166</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5076,19 +4878,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122566852</v>
+        <v>122566854</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5116,10 +4913,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461741</v>
+        <v>461714</v>
       </c>
       <c r="R45" t="n">
-        <v>6788170</v>
+        <v>6788188</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5178,19 +4975,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122566878</v>
+        <v>122566855</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5218,10 +5010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461712</v>
+        <v>461704</v>
       </c>
       <c r="R46" t="n">
-        <v>6788236</v>
+        <v>6788171</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5280,19 +5072,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122566835</v>
+        <v>122566856</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5320,10 +5107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461929</v>
+        <v>461665</v>
       </c>
       <c r="R47" t="n">
-        <v>6788278</v>
+        <v>6788146</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5382,19 +5169,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122566851</v>
+        <v>122566858</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5422,10 +5204,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461758</v>
+        <v>461615</v>
       </c>
       <c r="R48" t="n">
-        <v>6788174</v>
+        <v>6788118</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5484,19 +5266,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122566850</v>
+        <v>122566859</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5524,10 +5301,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461771</v>
+        <v>461506</v>
       </c>
       <c r="R49" t="n">
-        <v>6788185</v>
+        <v>6788139</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5586,19 +5363,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122566853</v>
+        <v>122566861</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5626,10 +5398,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461732</v>
+        <v>461537</v>
       </c>
       <c r="R50" t="n">
-        <v>6788166</v>
+        <v>6788149</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5688,19 +5460,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122566863</v>
+        <v>122566862</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5728,10 +5495,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461589</v>
+        <v>461562</v>
       </c>
       <c r="R51" t="n">
-        <v>6788148</v>
+        <v>6788141</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5790,19 +5557,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122566879</v>
+        <v>122566863</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5830,10 +5592,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461721</v>
+        <v>461589</v>
       </c>
       <c r="R52" t="n">
-        <v>6788242</v>
+        <v>6788148</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5892,37 +5654,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122566807</v>
+        <v>122566864</v>
       </c>
       <c r="B53" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5932,10 +5689,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461739</v>
+        <v>461619</v>
       </c>
       <c r="R53" t="n">
-        <v>6788280</v>
+        <v>6788144</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5994,37 +5751,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122566805</v>
+        <v>122566865</v>
       </c>
       <c r="B54" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6034,10 +5786,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461848</v>
+        <v>461628</v>
       </c>
       <c r="R54" t="n">
-        <v>6788429</v>
+        <v>6788142</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6096,37 +5848,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122566803</v>
+        <v>122566867</v>
       </c>
       <c r="B55" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,10 +5883,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461598</v>
+        <v>461650</v>
       </c>
       <c r="R55" t="n">
-        <v>6788148</v>
+        <v>6788137</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6198,19 +5945,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122566841</v>
+        <v>122566868</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6238,10 +5980,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461809</v>
+        <v>461672</v>
       </c>
       <c r="R56" t="n">
-        <v>6788250</v>
+        <v>6788136</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6300,19 +6042,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122566884</v>
+        <v>122566869</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6340,10 +6077,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461793</v>
+        <v>461678</v>
       </c>
       <c r="R57" t="n">
-        <v>6788303</v>
+        <v>6788157</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6402,55 +6139,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122566816</v>
+        <v>122566871</v>
       </c>
       <c r="B58" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461930</v>
+        <v>461676</v>
       </c>
       <c r="R58" t="n">
-        <v>6788270</v>
+        <v>6788174</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6509,19 +6236,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122566823</v>
+        <v>122566872</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6549,10 +6271,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461778</v>
+        <v>461659</v>
       </c>
       <c r="R59" t="n">
-        <v>6788485</v>
+        <v>6788194</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,19 +6333,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122566882</v>
+        <v>122566873</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -6651,10 +6368,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461757</v>
+        <v>461655</v>
       </c>
       <c r="R60" t="n">
-        <v>6788299</v>
+        <v>6788205</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6713,19 +6430,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122566885</v>
+        <v>122566874</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -6753,10 +6465,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461804</v>
+        <v>461665</v>
       </c>
       <c r="R61" t="n">
-        <v>6788319</v>
+        <v>6788207</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6815,19 +6527,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122566883</v>
+        <v>122566875</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6855,10 +6562,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461777</v>
+        <v>461669</v>
       </c>
       <c r="R62" t="n">
-        <v>6788298</v>
+        <v>6788203</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6917,19 +6624,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122566849</v>
+        <v>122566876</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -6957,10 +6659,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461787</v>
+        <v>461695</v>
       </c>
       <c r="R63" t="n">
-        <v>6788182</v>
+        <v>6788224</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7019,19 +6721,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122566846</v>
+        <v>122566877</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -7059,10 +6756,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461791</v>
+        <v>461706</v>
       </c>
       <c r="R64" t="n">
-        <v>6788209</v>
+        <v>6788223</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7121,19 +6818,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122566875</v>
+        <v>122566878</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -7161,10 +6853,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461669</v>
+        <v>461712</v>
       </c>
       <c r="R65" t="n">
-        <v>6788203</v>
+        <v>6788236</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7223,37 +6915,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122566808</v>
+        <v>122566879</v>
       </c>
       <c r="B66" t="n">
-        <v>90944</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7263,10 +6950,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461872</v>
+        <v>461721</v>
       </c>
       <c r="R66" t="n">
-        <v>6788413</v>
+        <v>6788242</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7325,19 +7012,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122566834</v>
+        <v>122566880</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -7365,10 +7047,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461929</v>
+        <v>461737</v>
       </c>
       <c r="R67" t="n">
-        <v>6788262</v>
+        <v>6788251</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7427,19 +7109,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122566831</v>
+        <v>122566881</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -7467,10 +7144,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>462004</v>
+        <v>461742</v>
       </c>
       <c r="R68" t="n">
-        <v>6788320</v>
+        <v>6788295</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7529,19 +7206,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122566861</v>
+        <v>122566882</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -7569,10 +7241,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461537</v>
+        <v>461757</v>
       </c>
       <c r="R69" t="n">
-        <v>6788149</v>
+        <v>6788299</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7631,55 +7303,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122566811</v>
+        <v>122566883</v>
       </c>
       <c r="B70" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461936</v>
+        <v>461777</v>
       </c>
       <c r="R70" t="n">
-        <v>6788279</v>
+        <v>6788298</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7738,19 +7400,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122566874</v>
+        <v>122566884</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -7778,10 +7435,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461665</v>
+        <v>461793</v>
       </c>
       <c r="R71" t="n">
-        <v>6788207</v>
+        <v>6788303</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7840,19 +7497,14 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122566859</v>
+        <v>122566885</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -7880,10 +7532,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461506</v>
+        <v>461804</v>
       </c>
       <c r="R72" t="n">
-        <v>6788139</v>
+        <v>6788319</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7942,19 +7594,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122566862</v>
+        <v>122566886</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -7982,10 +7629,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461562</v>
+        <v>461810</v>
       </c>
       <c r="R73" t="n">
-        <v>6788141</v>
+        <v>6788325</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8044,37 +7691,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122566809</v>
+        <v>124069314</v>
       </c>
       <c r="B74" t="n">
-        <v>90964</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8084,10 +7726,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461822</v>
+        <v>461867</v>
       </c>
       <c r="R74" t="n">
-        <v>6788353</v>
+        <v>6788190</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8114,12 +7756,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8134,31 +7776,26 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122566817</v>
+        <v>124070118</v>
       </c>
       <c r="B75" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -8186,10 +7823,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461788</v>
+        <v>461846</v>
       </c>
       <c r="R75" t="n">
-        <v>6788303</v>
+        <v>6788208</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8216,12 +7853,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8236,31 +7873,26 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122566842</v>
+        <v>124070191</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -8288,10 +7920,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461803</v>
+        <v>461842</v>
       </c>
       <c r="R76" t="n">
-        <v>6788243</v>
+        <v>6788220</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8318,12 +7950,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8338,31 +7970,26 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122566845</v>
+        <v>124070449</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -8390,10 +8017,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461794</v>
+        <v>461827</v>
       </c>
       <c r="R77" t="n">
-        <v>6788217</v>
+        <v>6788228</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8420,12 +8047,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8440,31 +8067,26 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122566824</v>
+        <v>124070964</v>
       </c>
       <c r="B78" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -8492,10 +8114,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461810</v>
+        <v>461765</v>
       </c>
       <c r="R78" t="n">
-        <v>6788470</v>
+        <v>6788314</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8522,12 +8144,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8542,70 +8164,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122566812</v>
+        <v>124071507</v>
       </c>
       <c r="B79" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461803</v>
+        <v>461771</v>
       </c>
       <c r="R79" t="n">
-        <v>6788243</v>
+        <v>6788273</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8632,12 +8241,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8652,70 +8261,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122488168</v>
+        <v>124071868</v>
       </c>
       <c r="B80" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461923</v>
+        <v>461779</v>
       </c>
       <c r="R80" t="n">
-        <v>6788245</v>
+        <v>6788261</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8742,17 +8338,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre gran med hackhål. Hörde spillkråkan i området.</t>
+          <t>Vid äldre tallar, mer än 200 år!</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8779,58 +8375,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122489274</v>
+        <v>124072166</v>
       </c>
       <c r="B81" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461895</v>
+        <v>461825</v>
       </c>
       <c r="R81" t="n">
-        <v>6788288</v>
+        <v>6788200</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8857,17 +8440,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8894,55 +8472,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122566813</v>
+        <v>124072783</v>
       </c>
       <c r="B82" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461803</v>
+        <v>461781</v>
       </c>
       <c r="R82" t="n">
-        <v>6788243</v>
+        <v>6788191</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8969,17 +8540,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8988,68 +8559,67 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124077216</v>
+        <v>124076806</v>
       </c>
       <c r="B83" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461645</v>
+        <v>461730</v>
       </c>
       <c r="R83" t="n">
-        <v>6788424</v>
+        <v>6788270</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9084,12 +8654,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9108,19 +8684,14 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124071683</v>
+        <v>124077244</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -9148,10 +8719,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461771</v>
+        <v>461645</v>
       </c>
       <c r="R84" t="n">
-        <v>6788273</v>
+        <v>6788424</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9210,19 +8781,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124069314</v>
+        <v>124078636</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -9250,10 +8816,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461867</v>
+        <v>461747</v>
       </c>
       <c r="R85" t="n">
-        <v>6788190</v>
+        <v>6788434</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9312,19 +8878,14 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124077244</v>
+        <v>124079435</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -9346,16 +8907,19 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461645</v>
+        <v>461848</v>
       </c>
       <c r="R86" t="n">
-        <v>6788424</v>
+        <v>6788375</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9390,12 +8954,18 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9414,19 +8984,14 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124070964</v>
+        <v>124100759</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -9448,16 +9013,19 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461765</v>
+        <v>461815</v>
       </c>
       <c r="R87" t="n">
-        <v>6788314</v>
+        <v>6788432</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9484,12 +9052,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9498,6 +9071,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9516,45 +9090,35 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124073722</v>
+        <v>124101056</v>
       </c>
       <c r="B88" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -9564,7 +9128,7 @@
         <v>461781</v>
       </c>
       <c r="R88" t="n">
-        <v>6788191</v>
+        <v>6788477</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9591,12 +9155,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9623,55 +9187,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124071356</v>
+        <v>124101160</v>
       </c>
       <c r="B89" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461771</v>
+        <v>461780</v>
       </c>
       <c r="R89" t="n">
-        <v>6788273</v>
+        <v>6788503</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9698,12 +9252,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9730,19 +9284,14 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124071868</v>
+        <v>124101245</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -9770,10 +9319,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461779</v>
+        <v>461803</v>
       </c>
       <c r="R90" t="n">
-        <v>6788261</v>
+        <v>6788496</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9800,17 +9349,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Vid äldre tallar, mer än 200 år!</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9837,37 +9381,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124074329</v>
+        <v>124102323</v>
       </c>
       <c r="B91" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9877,10 +9416,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461635</v>
+        <v>461869</v>
       </c>
       <c r="R91" t="n">
-        <v>6788154</v>
+        <v>6788429</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9907,17 +9446,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9944,19 +9478,14 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124070191</v>
+        <v>124102499</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -9984,10 +9513,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461842</v>
+        <v>461897</v>
       </c>
       <c r="R92" t="n">
-        <v>6788220</v>
+        <v>6788354</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10014,12 +9543,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10046,19 +9575,14 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124070449</v>
+        <v>124103087</v>
       </c>
       <c r="B93" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -10086,10 +9610,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461827</v>
+        <v>461895</v>
       </c>
       <c r="R93" t="n">
-        <v>6788228</v>
+        <v>6788288</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10116,12 +9640,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10148,19 +9672,14 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124070118</v>
+        <v>132755844</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -10188,13 +9707,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461846</v>
+        <v>461491</v>
       </c>
       <c r="R94" t="n">
-        <v>6788208</v>
+        <v>6788102</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10218,12 +9737,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10238,49 +9757,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124072920</v>
+        <v>132844924</v>
       </c>
       <c r="B95" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10290,13 +9804,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461781</v>
+        <v>461639</v>
       </c>
       <c r="R95" t="n">
-        <v>6788191</v>
+        <v>6788124</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10320,12 +9834,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10340,27 +9854,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124078636</v>
+        <v>122566805</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10368,21 +9877,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10392,10 +9901,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461747</v>
+        <v>461848</v>
       </c>
       <c r="R96" t="n">
-        <v>6788434</v>
+        <v>6788429</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10422,12 +9931,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10442,27 +9951,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124100914</v>
+        <v>122566806</v>
       </c>
       <c r="B97" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10470,39 +9974,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461788</v>
+        <v>461615</v>
       </c>
       <c r="R97" t="n">
-        <v>6788461</v>
+        <v>6788118</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10529,12 +10028,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10549,27 +10048,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124103087</v>
+        <v>122566807</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10577,21 +10071,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10601,10 +10095,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461895</v>
+        <v>461739</v>
       </c>
       <c r="R98" t="n">
-        <v>6788288</v>
+        <v>6788280</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10631,12 +10125,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10651,27 +10145,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124102429</v>
+        <v>122566814</v>
       </c>
       <c r="B99" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10679,21 +10168,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10703,10 +10192,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461869</v>
+        <v>461814</v>
       </c>
       <c r="R99" t="n">
-        <v>6788429</v>
+        <v>6788266</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10733,12 +10222,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10753,27 +10242,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124102664</v>
+        <v>122566801</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10781,21 +10265,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10805,10 +10289,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461897</v>
+        <v>461945</v>
       </c>
       <c r="R100" t="n">
-        <v>6788354</v>
+        <v>6788255</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10835,17 +10319,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav runt mig.</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10860,27 +10339,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124101056</v>
+        <v>122566802</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10888,21 +10362,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10912,10 +10386,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461781</v>
+        <v>461811</v>
       </c>
       <c r="R101" t="n">
-        <v>6788477</v>
+        <v>6788280</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10942,12 +10416,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10962,49 +10436,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124076637</v>
+        <v>122566803</v>
       </c>
       <c r="B102" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11014,10 +10483,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461711</v>
+        <v>461598</v>
       </c>
       <c r="R102" t="n">
-        <v>6788217</v>
+        <v>6788148</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11044,12 +10513,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11064,27 +10533,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124074036</v>
+        <v>122566804</v>
       </c>
       <c r="B103" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11092,39 +10556,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461717</v>
+        <v>461614</v>
       </c>
       <c r="R103" t="n">
-        <v>6788187</v>
+        <v>6788152</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11151,17 +10610,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Flera bohål i hög, grov, torraka av tall.</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11176,44 +10630,39 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124072335</v>
+        <v>122488168</v>
       </c>
       <c r="B104" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11226,7 +10675,7 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -11236,10 +10685,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461826</v>
+        <v>461923</v>
       </c>
       <c r="R104" t="n">
-        <v>6788189</v>
+        <v>6788245</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11266,17 +10715,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Äldre gran med hackhål. Hörde spillkråkan i området.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11303,19 +10752,14 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124070565</v>
+        <v>122489220</v>
       </c>
       <c r="B105" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -11337,24 +10781,21 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461821</v>
+        <v>461881</v>
       </c>
       <c r="R105" t="n">
-        <v>6788236</v>
+        <v>6788296</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11381,12 +10822,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Färska hackspår nedre delen av äldre gran.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11413,32 +10859,27 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124070750</v>
+        <v>122566811</v>
       </c>
       <c r="B106" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11458,10 +10899,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461821</v>
+        <v>461936</v>
       </c>
       <c r="R106" t="n">
-        <v>6788236</v>
+        <v>6788279</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11488,12 +10929,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11508,54 +10949,54 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124076806</v>
+        <v>122566812</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11563,10 +11004,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461730</v>
+        <v>461803</v>
       </c>
       <c r="R107" t="n">
-        <v>6788270</v>
+        <v>6788243</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11593,17 +11034,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Rikligt med lågor och torrakor i området.</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11612,38 +11048,32 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124074729</v>
+        <v>122566816</v>
       </c>
       <c r="B108" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -11676,10 +11106,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461635</v>
+        <v>461930</v>
       </c>
       <c r="R108" t="n">
-        <v>6788154</v>
+        <v>6788270</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11706,17 +11136,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Räknar till 8 högstubbar i en radie av ca 15 meter med hackspår, äldre samt färska.</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11731,44 +11156,39 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124074066</v>
+        <v>124070565</v>
       </c>
       <c r="B109" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -11777,21 +11197,24 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461717</v>
+        <v>461821</v>
       </c>
       <c r="R109" t="n">
-        <v>6788187</v>
+        <v>6788236</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11850,19 +11273,14 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124075859</v>
+        <v>124071356</v>
       </c>
       <c r="B110" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -11884,24 +11302,21 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461732</v>
+        <v>461771</v>
       </c>
       <c r="R110" t="n">
-        <v>6788226</v>
+        <v>6788273</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11934,11 +11349,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11965,50 +11375,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124072166</v>
+        <v>124073722</v>
       </c>
       <c r="B111" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461825</v>
+        <v>461781</v>
       </c>
       <c r="R111" t="n">
-        <v>6788200</v>
+        <v>6788191</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12067,32 +11477,27 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124076090</v>
+        <v>124074036</v>
       </c>
       <c r="B112" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -12103,7 +11508,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -12112,10 +11517,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461711</v>
+        <v>461717</v>
       </c>
       <c r="R112" t="n">
-        <v>6788217</v>
+        <v>6788187</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12148,6 +11553,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Flera bohål i hög, grov, torraka av tall.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12174,15 +11584,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124073786</v>
+        <v>124074255</v>
       </c>
       <c r="B113" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12190,21 +11595,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12212,7 +11617,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12222,10 +11627,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461765</v>
+        <v>461635</v>
       </c>
       <c r="R113" t="n">
-        <v>6788189</v>
+        <v>6788154</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12262,7 +11667,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Miljöbild. Så kallad tjädertall.</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12289,42 +11694,42 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124072783</v>
+        <v>124075859</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12332,10 +11737,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461781</v>
+        <v>461732</v>
       </c>
       <c r="R114" t="n">
-        <v>6788191</v>
+        <v>6788226</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12372,7 +11777,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild med äldre högstubbe!</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12381,7 +11786,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12403,16 +11807,11 @@
         <v>124077891</v>
       </c>
       <c r="B115" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -12518,16 +11917,11 @@
         <v>124078370</v>
       </c>
       <c r="B116" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -12630,42 +12024,42 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124100321</v>
+        <v>124079560</v>
       </c>
       <c r="B117" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12673,10 +12067,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461813</v>
+        <v>461854</v>
       </c>
       <c r="R117" t="n">
-        <v>6788469</v>
+        <v>6788321</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12703,17 +12097,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fågelbo högt upp i tall, sista två bilderna. Tre sänkor fanns i detta område, två vattenfyllda.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12722,7 +12116,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12741,15 +12134,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124150783</v>
+        <v>124100914</v>
       </c>
       <c r="B118" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12757,39 +12145,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461702</v>
+        <v>461788</v>
       </c>
       <c r="R118" t="n">
-        <v>6788415</v>
+        <v>6788461</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12816,17 +12204,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12835,7 +12218,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12854,42 +12236,42 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124074099</v>
+        <v>124101129</v>
       </c>
       <c r="B119" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12897,10 +12279,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461687</v>
+        <v>461780</v>
       </c>
       <c r="R119" t="n">
-        <v>6788172</v>
+        <v>6788503</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12927,17 +12309,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12946,7 +12328,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12965,42 +12346,42 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124079435</v>
+        <v>124101365</v>
       </c>
       <c r="B120" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13008,10 +12389,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461848</v>
+        <v>461803</v>
       </c>
       <c r="R120" t="n">
-        <v>6788375</v>
+        <v>6788496</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13038,17 +12419,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Miljöbild. Synligt i en radie av ca 50 meter.</t>
+          <t>Miljöbilder. Blodlav fanns i området.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13057,7 +12438,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13076,15 +12456,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124102093</v>
+        <v>122489274</v>
       </c>
       <c r="B121" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13092,26 +12467,31 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13119,10 +12499,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461869</v>
+        <v>461895</v>
       </c>
       <c r="R121" t="n">
-        <v>6788429</v>
+        <v>6788288</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13149,17 +12529,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Miljöbilder. En källåder mynnade nära Våmån. Återkommande lågor i området.</t>
+          <t>Bohål i torraka. Garnlav, återkommande i området.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13168,7 +12548,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13187,15 +12566,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124103019</v>
+        <v>122566813</v>
       </c>
       <c r="B122" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13203,37 +12577,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461895</v>
+        <v>461803</v>
       </c>
       <c r="R122" t="n">
-        <v>6788288</v>
+        <v>6788243</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13260,17 +12636,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Miljöbilder. Fuktigt område med bäck.</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13279,34 +12655,28 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124079560</v>
+        <v>124070750</v>
       </c>
       <c r="B123" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13314,16 +12684,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13332,24 +12702,21 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461854</v>
+        <v>461821</v>
       </c>
       <c r="R123" t="n">
-        <v>6788321</v>
+        <v>6788236</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13382,11 +12749,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13413,15 +12775,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124099222</v>
+        <v>124072335</v>
       </c>
       <c r="B124" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13461,10 +12818,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461848</v>
+        <v>461826</v>
       </c>
       <c r="R124" t="n">
-        <v>6788394</v>
+        <v>6788189</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13491,17 +12848,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13528,15 +12885,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124100759</v>
+        <v>124074066</v>
       </c>
       <c r="B125" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13544,37 +12896,39 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>461815</v>
+        <v>461717</v>
       </c>
       <c r="R125" t="n">
-        <v>6788432</v>
+        <v>6788187</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13601,17 +12955,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Garnlav samt återkommande hackspår i området.</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13620,7 +12969,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13636,6 +12984,1234 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124076090</v>
+      </c>
+      <c r="B126" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>461711</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6788217</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>124099222</v>
+      </c>
+      <c r="B127" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>461848</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6788394</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Färska spår på tre stammar nära varandra.</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>132755747</v>
+      </c>
+      <c r="B128" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>461495</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6788097</v>
+      </c>
+      <c r="S128" t="n">
+        <v>25</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>124073786</v>
+      </c>
+      <c r="B129" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>461765</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6788189</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Miljöbild. Så kallad tjädertall.</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>122566887</v>
+      </c>
+      <c r="B130" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>461810</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6788470</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>122566888</v>
+      </c>
+      <c r="B131" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>461791</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6788187</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>124076637</v>
+      </c>
+      <c r="B132" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>461711</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6788217</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>124150783</v>
+      </c>
+      <c r="B133" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>461702</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6788415</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>124072920</v>
+      </c>
+      <c r="B134" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>461781</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6788191</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>124074099</v>
+      </c>
+      <c r="B135" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>461687</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6788172</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Miljöbild. 10 till 15 kolade stubbar sågs i sydvästra delen av området.</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>124074329</v>
+      </c>
+      <c r="B136" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>461635</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6788154</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>124077216</v>
+      </c>
+      <c r="B137" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Våmån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>461645</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6788424</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56438-2024 artfynd.xlsx
+++ b/artfynd/A 56438-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY137"/>
+  <dimension ref="A1:AZ137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124100321</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124101674</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566809</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566818</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1277,6 +1307,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566819</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1374,6 +1409,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566820</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1471,6 +1511,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566821</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1568,6 +1613,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566822</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566823</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1762,6 +1817,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566824</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1859,6 +1919,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566825</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1956,6 +2021,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566826</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2053,6 +2123,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566839</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2150,6 +2225,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566840</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2247,6 +2327,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566841</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2344,6 +2429,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566842</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2441,6 +2531,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566843</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2538,6 +2633,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566844</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2635,6 +2735,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566845</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2732,6 +2837,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566846</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2829,6 +2939,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566847</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2926,6 +3041,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566848</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3023,6 +3143,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566849</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3120,6 +3245,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566850</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3217,6 +3347,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566851</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3314,6 +3449,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566852</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3411,6 +3551,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566853</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3508,6 +3653,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566854</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3605,6 +3755,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566855</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3702,6 +3857,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566856</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3799,6 +3959,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566858</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3896,6 +4061,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566859</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3993,6 +4163,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566861</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4090,6 +4265,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566862</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4187,6 +4367,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566863</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4284,6 +4469,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566864</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4381,6 +4571,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566865</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4478,6 +4673,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566867</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4575,6 +4775,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566868</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4672,6 +4877,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566869</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4769,6 +4979,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566871</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4866,6 +5081,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566872</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4963,6 +5183,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566873</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5060,6 +5285,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566874</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5157,6 +5387,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566875</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5254,6 +5489,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566876</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5351,6 +5591,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566877</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5448,6 +5693,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566878</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5545,6 +5795,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566879</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5642,6 +5897,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566880</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5739,6 +5999,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566881</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5836,6 +6101,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566882</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5933,6 +6203,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566883</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6030,6 +6305,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566884</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6127,6 +6407,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566885</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6224,6 +6509,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566886</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6321,6 +6611,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124070118</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6418,6 +6713,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124070191</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6515,6 +6815,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124070449</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6612,6 +6917,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124070964</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6709,6 +7019,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071507</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6811,6 +7126,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071868</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6908,6 +7228,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124072166</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7014,6 +7339,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124072783</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7120,6 +7450,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124076806</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7217,6 +7552,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124077244</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7314,6 +7654,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078636</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7420,6 +7765,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124079435</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7526,6 +7876,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124100759</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7623,6 +7978,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124101056</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7720,6 +8080,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124101160</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7817,6 +8182,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124101245</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7914,6 +8284,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132755844</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8011,6 +8386,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132844924</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8108,6 +8488,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566805</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8205,6 +8590,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566806</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8302,6 +8692,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566807</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8399,6 +8794,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566814</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8496,6 +8896,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566802</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8593,6 +8998,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566803</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8690,6 +9100,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566804</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8795,6 +9210,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566812</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8900,6 +9320,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124070565</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9002,6 +9427,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071356</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9104,6 +9534,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124073722</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9211,6 +9646,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074036</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9321,6 +9761,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074255</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9431,6 +9876,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124075859</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9541,6 +9991,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124077891</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9651,6 +10106,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078370</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9761,6 +10221,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124079560</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9863,6 +10328,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124100914</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9973,6 +10443,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124101129</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10083,6 +10558,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124101365</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10190,6 +10670,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566813</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10292,6 +10777,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124070750</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10402,6 +10892,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124072335</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10504,6 +10999,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074066</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10606,6 +11106,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124076090</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10716,6 +11221,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124099222</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10821,6 +11331,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132755747</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10931,6 +11446,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124073786</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11028,6 +11548,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566887</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11125,6 +11650,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566888</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11222,6 +11752,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124076637</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11330,6 +11865,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124150783</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11427,6 +11967,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124072920</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11533,6 +12078,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074099</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11635,6 +12185,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074329</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11732,6 +12287,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124077216</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11838,6 +12398,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124102093</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11935,6 +12500,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566808</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12032,6 +12602,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122489147</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12129,6 +12704,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122488593</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12226,6 +12806,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566827</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12323,6 +12908,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566828</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12420,6 +13010,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566829</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12517,6 +13112,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566830</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12614,6 +13214,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566831</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12711,6 +13316,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566832</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12808,6 +13418,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566833</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12905,6 +13520,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566834</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13002,6 +13622,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566835</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13099,6 +13724,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566837</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13196,6 +13826,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566838</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13293,6 +13928,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124069314</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13390,6 +14030,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124102323</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13487,6 +14132,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124102499</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13584,6 +14234,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124103087</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13681,6 +14336,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566801</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13791,6 +14451,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122488168</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13898,6 +14563,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122489220</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14000,6 +14670,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566811</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14102,6 +14777,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566816</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14212,8 +14892,151 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122489274</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>